--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="125">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,141 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>US MLS</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>01:30:00</t>
+  </si>
+  <si>
+    <t>02:30:00</t>
+  </si>
+  <si>
+    <t>Manta FC</t>
+  </si>
+  <si>
+    <t>Charlotte FC</t>
+  </si>
+  <si>
+    <t>Sao Paulo</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Nautico PE</t>
+  </si>
+  <si>
+    <t>Kansas City</t>
+  </si>
+  <si>
+    <t>Houston Dynamo</t>
+  </si>
+  <si>
+    <t>Nashville SC</t>
+  </si>
+  <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
+    <t>Colorado Switchbacks FC</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>San Jose Earthquakes</t>
+  </si>
+  <si>
+    <t>Los Angeles FC</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>LDU</t>
+  </si>
+  <si>
+    <t>Atlanta Utd</t>
+  </si>
+  <si>
+    <t>Athletico-PR</t>
+  </si>
+  <si>
+    <t>Cruzeiro MG</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
+    <t>Minnesota Utd</t>
+  </si>
+  <si>
+    <t>DC Utd</t>
+  </si>
+  <si>
+    <t>CF Montreal</t>
+  </si>
+  <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
+    <t>Miami FC</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
+    <t>Orlando City</t>
+  </si>
+  <si>
+    <t>Real Salt Lake</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
+  </si>
+  <si>
+    <t>St Louis City SC</t>
+  </si>
+  <si>
+    <t>2026-07-21 00:46:03</t>
   </si>
 </sst>
 </file>
@@ -585,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +965,3878 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2">
+        <v>5.3</v>
+      </c>
+      <c r="G2">
+        <v>6.6</v>
+      </c>
+      <c r="H2">
+        <v>1.75</v>
+      </c>
+      <c r="I2">
+        <v>1.9</v>
+      </c>
+      <c r="J2">
+        <v>3.25</v>
+      </c>
+      <c r="K2">
+        <v>3.85</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.61</v>
+      </c>
+      <c r="O2">
+        <v>1.42</v>
+      </c>
+      <c r="P2">
+        <v>1.6</v>
+      </c>
+      <c r="Q2">
+        <v>2.32</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>3.9</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.67</v>
+      </c>
+      <c r="V2">
+        <v>2.1</v>
+      </c>
+      <c r="W2">
+        <v>1.18</v>
+      </c>
+      <c r="X2">
+        <v>14.5</v>
+      </c>
+      <c r="Y2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>14.5</v>
+      </c>
+      <c r="AA2">
+        <v>30</v>
+      </c>
+      <c r="AB2">
+        <v>22</v>
+      </c>
+      <c r="AC2">
+        <v>11.5</v>
+      </c>
+      <c r="AD2">
+        <v>15.5</v>
+      </c>
+      <c r="AE2">
+        <v>34</v>
+      </c>
+      <c r="AF2">
+        <v>65</v>
+      </c>
+      <c r="AG2">
+        <v>34</v>
+      </c>
+      <c r="AH2">
+        <v>38</v>
+      </c>
+      <c r="AI2">
+        <v>75</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.08</v>
+      </c>
+      <c r="AQ2">
+        <v>1.93</v>
+      </c>
+      <c r="AR2">
+        <v>2.08</v>
+      </c>
+      <c r="AS2">
+        <v>13.5</v>
+      </c>
+      <c r="AT2">
+        <v>2.18</v>
+      </c>
+      <c r="AU2">
+        <v>2</v>
+      </c>
+      <c r="AV2">
+        <v>2.1</v>
+      </c>
+      <c r="AW2">
+        <v>2.26</v>
+      </c>
+      <c r="AX2">
+        <v>2.34</v>
+      </c>
+      <c r="AY2">
+        <v>2.26</v>
+      </c>
+      <c r="AZ2">
+        <v>2.28</v>
+      </c>
+      <c r="BA2">
+        <v>2.36</v>
+      </c>
+      <c r="BB2">
+        <v>2.44</v>
+      </c>
+      <c r="BC2">
+        <v>2.44</v>
+      </c>
+      <c r="BD2">
+        <v>2.44</v>
+      </c>
+      <c r="BE2">
+        <v>2.44</v>
+      </c>
+      <c r="BF2">
+        <v>2.44</v>
+      </c>
+      <c r="BG2">
+        <v>2.44</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>2.34</v>
+      </c>
+      <c r="BJ2">
+        <v>17</v>
+      </c>
+      <c r="BK2">
+        <v>7.2</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>21</v>
+      </c>
+      <c r="BN2">
+        <v>13</v>
+      </c>
+      <c r="BO2">
+        <v>5.6</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>21</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>21</v>
+      </c>
+      <c r="BT2">
+        <v>5.8</v>
+      </c>
+      <c r="BU2">
+        <v>2.84</v>
+      </c>
+      <c r="BV2">
+        <v>20</v>
+      </c>
+      <c r="BW2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX2">
+        <v>50</v>
+      </c>
+      <c r="BY2">
+        <v>21</v>
+      </c>
+      <c r="BZ2">
+        <v>50</v>
+      </c>
+      <c r="CA2">
+        <v>19</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3">
+        <v>1.92</v>
+      </c>
+      <c r="G3">
+        <v>1.96</v>
+      </c>
+      <c r="H3">
+        <v>4.2</v>
+      </c>
+      <c r="I3">
+        <v>4.5</v>
+      </c>
+      <c r="J3">
+        <v>3.85</v>
+      </c>
+      <c r="K3">
+        <v>4.1</v>
+      </c>
+      <c r="L3">
+        <v>1.33</v>
+      </c>
+      <c r="M3">
+        <v>1.05</v>
+      </c>
+      <c r="N3">
+        <v>4.8</v>
+      </c>
+      <c r="O3">
+        <v>1.25</v>
+      </c>
+      <c r="P3">
+        <v>2.28</v>
+      </c>
+      <c r="Q3">
+        <v>1.74</v>
+      </c>
+      <c r="R3">
+        <v>1.5</v>
+      </c>
+      <c r="S3">
+        <v>2.88</v>
+      </c>
+      <c r="T3">
+        <v>1.61</v>
+      </c>
+      <c r="U3">
+        <v>2.1</v>
+      </c>
+      <c r="V3">
+        <v>1.29</v>
+      </c>
+      <c r="W3">
+        <v>2.04</v>
+      </c>
+      <c r="X3">
+        <v>24</v>
+      </c>
+      <c r="Y3">
+        <v>24</v>
+      </c>
+      <c r="Z3">
+        <v>44</v>
+      </c>
+      <c r="AA3">
+        <v>100</v>
+      </c>
+      <c r="AB3">
+        <v>13</v>
+      </c>
+      <c r="AC3">
+        <v>11</v>
+      </c>
+      <c r="AD3">
+        <v>22</v>
+      </c>
+      <c r="AE3">
+        <v>65</v>
+      </c>
+      <c r="AF3">
+        <v>15.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>21</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>25</v>
+      </c>
+      <c r="AK3">
+        <v>23</v>
+      </c>
+      <c r="AL3">
+        <v>44</v>
+      </c>
+      <c r="AM3">
+        <v>95</v>
+      </c>
+      <c r="AN3">
+        <v>12.5</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.4</v>
+      </c>
+      <c r="AQ3">
+        <v>15</v>
+      </c>
+      <c r="AR3">
+        <v>3.65</v>
+      </c>
+      <c r="AS3">
+        <v>3.8</v>
+      </c>
+      <c r="AT3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU3">
+        <v>7.6</v>
+      </c>
+      <c r="AV3">
+        <v>13</v>
+      </c>
+      <c r="AW3">
+        <v>3.75</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>8.6</v>
+      </c>
+      <c r="AZ3">
+        <v>13</v>
+      </c>
+      <c r="BA3">
+        <v>3.75</v>
+      </c>
+      <c r="BB3">
+        <v>3.4</v>
+      </c>
+      <c r="BC3">
+        <v>14.5</v>
+      </c>
+      <c r="BD3">
+        <v>21</v>
+      </c>
+      <c r="BE3">
+        <v>3.8</v>
+      </c>
+      <c r="BF3">
+        <v>7.8</v>
+      </c>
+      <c r="BG3">
+        <v>3.95</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>2.88</v>
+      </c>
+      <c r="BJ3">
+        <v>12.5</v>
+      </c>
+      <c r="BK3">
+        <v>6.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>22</v>
+      </c>
+      <c r="BN3">
+        <v>6</v>
+      </c>
+      <c r="BO3">
+        <v>3.45</v>
+      </c>
+      <c r="BP3">
+        <v>16.5</v>
+      </c>
+      <c r="BQ3">
+        <v>8.4</v>
+      </c>
+      <c r="BR3">
+        <v>30</v>
+      </c>
+      <c r="BS3">
+        <v>15.5</v>
+      </c>
+      <c r="BT3">
+        <v>10</v>
+      </c>
+      <c r="BU3">
+        <v>5.5</v>
+      </c>
+      <c r="BV3">
+        <v>44</v>
+      </c>
+      <c r="BW3">
+        <v>22</v>
+      </c>
+      <c r="BX3">
+        <v>50</v>
+      </c>
+      <c r="BY3">
+        <v>22</v>
+      </c>
+      <c r="BZ3">
+        <v>24</v>
+      </c>
+      <c r="CA3">
+        <v>12</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4">
+        <v>2.02</v>
+      </c>
+      <c r="G4">
+        <v>2.12</v>
+      </c>
+      <c r="H4">
+        <v>4.1</v>
+      </c>
+      <c r="I4">
+        <v>4.4</v>
+      </c>
+      <c r="J4">
+        <v>3.4</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>1.4</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>3.05</v>
+      </c>
+      <c r="O4">
+        <v>1.43</v>
+      </c>
+      <c r="P4">
+        <v>1.7</v>
+      </c>
+      <c r="Q4">
+        <v>2.28</v>
+      </c>
+      <c r="R4">
+        <v>1.26</v>
+      </c>
+      <c r="S4">
+        <v>4.3</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>1.89</v>
+      </c>
+      <c r="V4">
+        <v>1.29</v>
+      </c>
+      <c r="W4">
+        <v>1.9</v>
+      </c>
+      <c r="X4">
+        <v>11.5</v>
+      </c>
+      <c r="Y4">
+        <v>12.5</v>
+      </c>
+      <c r="Z4">
+        <v>30</v>
+      </c>
+      <c r="AA4">
+        <v>120</v>
+      </c>
+      <c r="AB4">
+        <v>7.8</v>
+      </c>
+      <c r="AC4">
+        <v>8</v>
+      </c>
+      <c r="AD4">
+        <v>17.5</v>
+      </c>
+      <c r="AE4">
+        <v>65</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>11</v>
+      </c>
+      <c r="AH4">
+        <v>22</v>
+      </c>
+      <c r="AI4">
+        <v>75</v>
+      </c>
+      <c r="AJ4">
+        <v>27</v>
+      </c>
+      <c r="AK4">
+        <v>26</v>
+      </c>
+      <c r="AL4">
+        <v>48</v>
+      </c>
+      <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>21</v>
+      </c>
+      <c r="AO4">
+        <v>85</v>
+      </c>
+      <c r="AP4">
+        <v>10</v>
+      </c>
+      <c r="AQ4">
+        <v>11</v>
+      </c>
+      <c r="AR4">
+        <v>9.4</v>
+      </c>
+      <c r="AS4">
+        <v>12.5</v>
+      </c>
+      <c r="AT4">
+        <v>6.8</v>
+      </c>
+      <c r="AU4">
+        <v>7</v>
+      </c>
+      <c r="AV4">
+        <v>15</v>
+      </c>
+      <c r="AW4">
+        <v>11.5</v>
+      </c>
+      <c r="AX4">
+        <v>10.5</v>
+      </c>
+      <c r="AY4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4">
+        <v>19</v>
+      </c>
+      <c r="BA4">
+        <v>11.5</v>
+      </c>
+      <c r="BB4">
+        <v>19</v>
+      </c>
+      <c r="BC4">
+        <v>18.5</v>
+      </c>
+      <c r="BD4">
+        <v>40</v>
+      </c>
+      <c r="BE4">
+        <v>13</v>
+      </c>
+      <c r="BF4">
+        <v>15</v>
+      </c>
+      <c r="BG4">
+        <v>12</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.76</v>
+      </c>
+      <c r="BJ4">
+        <v>15.5</v>
+      </c>
+      <c r="BK4">
+        <v>1.58</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.76</v>
+      </c>
+      <c r="BN4">
+        <v>6.4</v>
+      </c>
+      <c r="BO4">
+        <v>3.15</v>
+      </c>
+      <c r="BP4">
+        <v>23</v>
+      </c>
+      <c r="BQ4">
+        <v>1.63</v>
+      </c>
+      <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
+        <v>1.7</v>
+      </c>
+      <c r="BT4">
+        <v>10.5</v>
+      </c>
+      <c r="BU4">
+        <v>4.8</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.7</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.72</v>
+      </c>
+      <c r="BZ4">
+        <v>50</v>
+      </c>
+      <c r="CA4">
+        <v>1.7</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5">
+        <v>2.24</v>
+      </c>
+      <c r="G5">
+        <v>2.4</v>
+      </c>
+      <c r="H5">
+        <v>3.4</v>
+      </c>
+      <c r="I5">
+        <v>3.75</v>
+      </c>
+      <c r="J5">
+        <v>3.35</v>
+      </c>
+      <c r="K5">
+        <v>3.6</v>
+      </c>
+      <c r="L5">
+        <v>1.34</v>
+      </c>
+      <c r="M5">
+        <v>1.08</v>
+      </c>
+      <c r="N5">
+        <v>3.35</v>
+      </c>
+      <c r="O5">
+        <v>1.36</v>
+      </c>
+      <c r="P5">
+        <v>1.81</v>
+      </c>
+      <c r="Q5">
+        <v>2.1</v>
+      </c>
+      <c r="R5">
+        <v>1.3</v>
+      </c>
+      <c r="S5">
+        <v>3.85</v>
+      </c>
+      <c r="T5">
+        <v>1.82</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>1.36</v>
+      </c>
+      <c r="W5">
+        <v>1.71</v>
+      </c>
+      <c r="X5">
+        <v>14.5</v>
+      </c>
+      <c r="Y5">
+        <v>14</v>
+      </c>
+      <c r="Z5">
+        <v>28</v>
+      </c>
+      <c r="AA5">
+        <v>75</v>
+      </c>
+      <c r="AB5">
+        <v>11</v>
+      </c>
+      <c r="AC5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>15.5</v>
+      </c>
+      <c r="AE5">
+        <v>50</v>
+      </c>
+      <c r="AF5">
+        <v>16.5</v>
+      </c>
+      <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
+        <v>22</v>
+      </c>
+      <c r="AI5">
+        <v>65</v>
+      </c>
+      <c r="AJ5">
+        <v>32</v>
+      </c>
+      <c r="AK5">
+        <v>32</v>
+      </c>
+      <c r="AL5">
+        <v>50</v>
+      </c>
+      <c r="AM5">
+        <v>130</v>
+      </c>
+      <c r="AN5">
+        <v>26</v>
+      </c>
+      <c r="AO5">
+        <v>55</v>
+      </c>
+      <c r="AP5">
+        <v>10.5</v>
+      </c>
+      <c r="AQ5">
+        <v>10</v>
+      </c>
+      <c r="AR5">
+        <v>20</v>
+      </c>
+      <c r="AS5">
+        <v>5.4</v>
+      </c>
+      <c r="AT5">
+        <v>7.8</v>
+      </c>
+      <c r="AU5">
+        <v>6.6</v>
+      </c>
+      <c r="AV5">
+        <v>12.5</v>
+      </c>
+      <c r="AW5">
+        <v>5.2</v>
+      </c>
+      <c r="AX5">
+        <v>12</v>
+      </c>
+      <c r="AY5">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5">
+        <v>15.5</v>
+      </c>
+      <c r="BA5">
+        <v>5.3</v>
+      </c>
+      <c r="BB5">
+        <v>4.9</v>
+      </c>
+      <c r="BC5">
+        <v>19</v>
+      </c>
+      <c r="BD5">
+        <v>5.2</v>
+      </c>
+      <c r="BE5">
+        <v>5.6</v>
+      </c>
+      <c r="BF5">
+        <v>17</v>
+      </c>
+      <c r="BG5">
+        <v>5.2</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.87</v>
+      </c>
+      <c r="BJ5">
+        <v>13.5</v>
+      </c>
+      <c r="BK5">
+        <v>1.65</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.87</v>
+      </c>
+      <c r="BN5">
+        <v>6.6</v>
+      </c>
+      <c r="BO5">
+        <v>3.55</v>
+      </c>
+      <c r="BP5">
+        <v>24</v>
+      </c>
+      <c r="BQ5">
+        <v>1.74</v>
+      </c>
+      <c r="BR5">
+        <v>46</v>
+      </c>
+      <c r="BS5">
+        <v>1.8</v>
+      </c>
+      <c r="BT5">
+        <v>9</v>
+      </c>
+      <c r="BU5">
+        <v>4.5</v>
+      </c>
+      <c r="BV5">
+        <v>40</v>
+      </c>
+      <c r="BW5">
+        <v>1.79</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.81</v>
+      </c>
+      <c r="BZ5">
+        <v>44</v>
+      </c>
+      <c r="CA5">
+        <v>1.8</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H6">
+        <v>1.49</v>
+      </c>
+      <c r="I6">
+        <v>1.51</v>
+      </c>
+      <c r="J6">
+        <v>4.4</v>
+      </c>
+      <c r="K6">
+        <v>4.7</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>3.95</v>
+      </c>
+      <c r="O6">
+        <v>1.31</v>
+      </c>
+      <c r="P6">
+        <v>2.04</v>
+      </c>
+      <c r="Q6">
+        <v>1.9</v>
+      </c>
+      <c r="R6">
+        <v>1.39</v>
+      </c>
+      <c r="S6">
+        <v>3.2</v>
+      </c>
+      <c r="T6">
+        <v>2.08</v>
+      </c>
+      <c r="U6">
+        <v>1.83</v>
+      </c>
+      <c r="V6">
+        <v>2.96</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>18</v>
+      </c>
+      <c r="Y6">
+        <v>7.6</v>
+      </c>
+      <c r="Z6">
+        <v>9.4</v>
+      </c>
+      <c r="AA6">
+        <v>14</v>
+      </c>
+      <c r="AB6">
+        <v>30</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>18.5</v>
+      </c>
+      <c r="AF6">
+        <v>80</v>
+      </c>
+      <c r="AG6">
+        <v>36</v>
+      </c>
+      <c r="AH6">
+        <v>30</v>
+      </c>
+      <c r="AI6">
+        <v>46</v>
+      </c>
+      <c r="AJ6">
+        <v>350</v>
+      </c>
+      <c r="AK6">
+        <v>160</v>
+      </c>
+      <c r="AL6">
+        <v>130</v>
+      </c>
+      <c r="AM6">
+        <v>180</v>
+      </c>
+      <c r="AN6">
+        <v>210</v>
+      </c>
+      <c r="AO6">
+        <v>8</v>
+      </c>
+      <c r="AP6">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6">
+        <v>7</v>
+      </c>
+      <c r="AR6">
+        <v>7.6</v>
+      </c>
+      <c r="AS6">
+        <v>11.5</v>
+      </c>
+      <c r="AT6">
+        <v>23</v>
+      </c>
+      <c r="AU6">
+        <v>9.6</v>
+      </c>
+      <c r="AV6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW6">
+        <v>14.5</v>
+      </c>
+      <c r="AX6">
+        <v>7</v>
+      </c>
+      <c r="AY6">
+        <v>28</v>
+      </c>
+      <c r="AZ6">
+        <v>24</v>
+      </c>
+      <c r="BA6">
+        <v>34</v>
+      </c>
+      <c r="BB6">
+        <v>7.4</v>
+      </c>
+      <c r="BC6">
+        <v>7.2</v>
+      </c>
+      <c r="BD6">
+        <v>7.2</v>
+      </c>
+      <c r="BE6">
+        <v>7.2</v>
+      </c>
+      <c r="BF6">
+        <v>7.4</v>
+      </c>
+      <c r="BG6">
+        <v>7.2</v>
+      </c>
+      <c r="BH6">
+        <v>3.6</v>
+      </c>
+      <c r="BI6">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6">
+        <v>11.5</v>
+      </c>
+      <c r="BK6">
+        <v>6.8</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>16</v>
+      </c>
+      <c r="BN6">
+        <v>11.5</v>
+      </c>
+      <c r="BO6">
+        <v>6.8</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>14</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>14</v>
+      </c>
+      <c r="BT6">
+        <v>3.9</v>
+      </c>
+      <c r="BU6">
+        <v>3.5</v>
+      </c>
+      <c r="BV6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BW6">
+        <v>6</v>
+      </c>
+      <c r="BX6">
+        <v>27</v>
+      </c>
+      <c r="BY6">
+        <v>10.5</v>
+      </c>
+      <c r="BZ6">
+        <v>17.5</v>
+      </c>
+      <c r="CA6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7">
+        <v>1.94</v>
+      </c>
+      <c r="G7">
+        <v>2.08</v>
+      </c>
+      <c r="H7">
+        <v>4.1</v>
+      </c>
+      <c r="I7">
+        <v>4.9</v>
+      </c>
+      <c r="J7">
+        <v>3.3</v>
+      </c>
+      <c r="K7">
+        <v>3.75</v>
+      </c>
+      <c r="L7">
+        <v>1.33</v>
+      </c>
+      <c r="M7">
+        <v>1.08</v>
+      </c>
+      <c r="N7">
+        <v>2.88</v>
+      </c>
+      <c r="O7">
+        <v>1.3</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>2.02</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
+        <v>3.6</v>
+      </c>
+      <c r="T7">
+        <v>1.83</v>
+      </c>
+      <c r="U7">
+        <v>1.96</v>
+      </c>
+      <c r="V7">
+        <v>1.25</v>
+      </c>
+      <c r="W7">
+        <v>1.92</v>
+      </c>
+      <c r="X7">
+        <v>13</v>
+      </c>
+      <c r="Y7">
+        <v>15.5</v>
+      </c>
+      <c r="Z7">
+        <v>36</v>
+      </c>
+      <c r="AA7">
+        <v>130</v>
+      </c>
+      <c r="AB7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7">
+        <v>18.5</v>
+      </c>
+      <c r="AE7">
+        <v>85</v>
+      </c>
+      <c r="AF7">
+        <v>13</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>23</v>
+      </c>
+      <c r="AI7">
+        <v>95</v>
+      </c>
+      <c r="AJ7">
+        <v>25</v>
+      </c>
+      <c r="AK7">
+        <v>24</v>
+      </c>
+      <c r="AL7">
+        <v>44</v>
+      </c>
+      <c r="AM7">
+        <v>140</v>
+      </c>
+      <c r="AN7">
+        <v>17</v>
+      </c>
+      <c r="AO7">
+        <v>95</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>12</v>
+      </c>
+      <c r="AR7">
+        <v>26</v>
+      </c>
+      <c r="AS7">
+        <v>7.8</v>
+      </c>
+      <c r="AT7">
+        <v>7.4</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>15</v>
+      </c>
+      <c r="AW7">
+        <v>7.2</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
+        <v>7.4</v>
+      </c>
+      <c r="BB7">
+        <v>19.5</v>
+      </c>
+      <c r="BC7">
+        <v>19</v>
+      </c>
+      <c r="BD7">
+        <v>34</v>
+      </c>
+      <c r="BE7">
+        <v>7.8</v>
+      </c>
+      <c r="BF7">
+        <v>11.5</v>
+      </c>
+      <c r="BG7">
+        <v>7.6</v>
+      </c>
+      <c r="BH7">
+        <v>3.9</v>
+      </c>
+      <c r="BI7">
+        <v>2.58</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8">
+        <v>3.5</v>
+      </c>
+      <c r="G8">
+        <v>3.6</v>
+      </c>
+      <c r="H8">
+        <v>2.06</v>
+      </c>
+      <c r="I8">
+        <v>2.1</v>
+      </c>
+      <c r="J8">
+        <v>4.2</v>
+      </c>
+      <c r="K8">
+        <v>4.4</v>
+      </c>
+      <c r="L8">
+        <v>1.28</v>
+      </c>
+      <c r="M8">
+        <v>1.04</v>
+      </c>
+      <c r="N8">
+        <v>6</v>
+      </c>
+      <c r="O8">
+        <v>1.18</v>
+      </c>
+      <c r="P8">
+        <v>2.66</v>
+      </c>
+      <c r="Q8">
+        <v>1.56</v>
+      </c>
+      <c r="R8">
+        <v>1.66</v>
+      </c>
+      <c r="S8">
+        <v>2.42</v>
+      </c>
+      <c r="T8">
+        <v>1.51</v>
+      </c>
+      <c r="U8">
+        <v>2.66</v>
+      </c>
+      <c r="V8">
+        <v>1.9</v>
+      </c>
+      <c r="W8">
+        <v>1.38</v>
+      </c>
+      <c r="X8">
+        <v>26</v>
+      </c>
+      <c r="Y8">
+        <v>15.5</v>
+      </c>
+      <c r="Z8">
+        <v>16.5</v>
+      </c>
+      <c r="AA8">
+        <v>28</v>
+      </c>
+      <c r="AB8">
+        <v>23</v>
+      </c>
+      <c r="AC8">
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <v>11.5</v>
+      </c>
+      <c r="AE8">
+        <v>19</v>
+      </c>
+      <c r="AF8">
+        <v>32</v>
+      </c>
+      <c r="AG8">
+        <v>15.5</v>
+      </c>
+      <c r="AH8">
+        <v>15.5</v>
+      </c>
+      <c r="AI8">
+        <v>27</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>36</v>
+      </c>
+      <c r="AL8">
+        <v>38</v>
+      </c>
+      <c r="AM8">
+        <v>60</v>
+      </c>
+      <c r="AN8">
+        <v>25</v>
+      </c>
+      <c r="AO8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AP8">
+        <v>22</v>
+      </c>
+      <c r="AQ8">
+        <v>13</v>
+      </c>
+      <c r="AR8">
+        <v>14</v>
+      </c>
+      <c r="AS8">
+        <v>22</v>
+      </c>
+      <c r="AT8">
+        <v>18</v>
+      </c>
+      <c r="AU8">
+        <v>9</v>
+      </c>
+      <c r="AV8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW8">
+        <v>16</v>
+      </c>
+      <c r="AX8">
+        <v>24</v>
+      </c>
+      <c r="AY8">
+        <v>13</v>
+      </c>
+      <c r="AZ8">
+        <v>13.5</v>
+      </c>
+      <c r="BA8">
+        <v>21</v>
+      </c>
+      <c r="BB8">
+        <v>32</v>
+      </c>
+      <c r="BC8">
+        <v>27</v>
+      </c>
+      <c r="BD8">
+        <v>28</v>
+      </c>
+      <c r="BE8">
+        <v>44</v>
+      </c>
+      <c r="BF8">
+        <v>18.5</v>
+      </c>
+      <c r="BG8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>12.5</v>
+      </c>
+      <c r="BK8">
+        <v>5.4</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>21</v>
+      </c>
+      <c r="BN8">
+        <v>10.5</v>
+      </c>
+      <c r="BO8">
+        <v>4.8</v>
+      </c>
+      <c r="BP8">
+        <v>38</v>
+      </c>
+      <c r="BQ8">
+        <v>15.5</v>
+      </c>
+      <c r="BR8">
+        <v>44</v>
+      </c>
+      <c r="BS8">
+        <v>17.5</v>
+      </c>
+      <c r="BT8">
+        <v>7.4</v>
+      </c>
+      <c r="BU8">
+        <v>3.45</v>
+      </c>
+      <c r="BV8">
+        <v>18.5</v>
+      </c>
+      <c r="BW8">
+        <v>8</v>
+      </c>
+      <c r="BX8">
+        <v>30</v>
+      </c>
+      <c r="BY8">
+        <v>12.5</v>
+      </c>
+      <c r="BZ8">
+        <v>21</v>
+      </c>
+      <c r="CA8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9">
+        <v>1.84</v>
+      </c>
+      <c r="G9">
+        <v>1.88</v>
+      </c>
+      <c r="H9">
+        <v>4.5</v>
+      </c>
+      <c r="I9">
+        <v>4.9</v>
+      </c>
+      <c r="J9">
+        <v>3.85</v>
+      </c>
+      <c r="K9">
+        <v>4.2</v>
+      </c>
+      <c r="L9">
+        <v>1.36</v>
+      </c>
+      <c r="M9">
+        <v>1.06</v>
+      </c>
+      <c r="N9">
+        <v>4.3</v>
+      </c>
+      <c r="O9">
+        <v>1.27</v>
+      </c>
+      <c r="P9">
+        <v>2.12</v>
+      </c>
+      <c r="Q9">
+        <v>1.83</v>
+      </c>
+      <c r="R9">
+        <v>1.44</v>
+      </c>
+      <c r="S9">
+        <v>3.1</v>
+      </c>
+      <c r="T9">
+        <v>1.75</v>
+      </c>
+      <c r="U9">
+        <v>2.18</v>
+      </c>
+      <c r="V9">
+        <v>1.26</v>
+      </c>
+      <c r="W9">
+        <v>2.12</v>
+      </c>
+      <c r="X9">
+        <v>20</v>
+      </c>
+      <c r="Y9">
+        <v>19.5</v>
+      </c>
+      <c r="Z9">
+        <v>44</v>
+      </c>
+      <c r="AA9">
+        <v>120</v>
+      </c>
+      <c r="AB9">
+        <v>10.5</v>
+      </c>
+      <c r="AC9">
+        <v>9.4</v>
+      </c>
+      <c r="AD9">
+        <v>19.5</v>
+      </c>
+      <c r="AE9">
+        <v>60</v>
+      </c>
+      <c r="AF9">
+        <v>13</v>
+      </c>
+      <c r="AG9">
+        <v>11</v>
+      </c>
+      <c r="AH9">
+        <v>19</v>
+      </c>
+      <c r="AI9">
+        <v>70</v>
+      </c>
+      <c r="AJ9">
+        <v>22</v>
+      </c>
+      <c r="AK9">
+        <v>19.5</v>
+      </c>
+      <c r="AL9">
+        <v>34</v>
+      </c>
+      <c r="AM9">
+        <v>110</v>
+      </c>
+      <c r="AN9">
+        <v>11.5</v>
+      </c>
+      <c r="AO9">
+        <v>70</v>
+      </c>
+      <c r="AP9">
+        <v>5.8</v>
+      </c>
+      <c r="AQ9">
+        <v>15.5</v>
+      </c>
+      <c r="AR9">
+        <v>30</v>
+      </c>
+      <c r="AS9">
+        <v>7.8</v>
+      </c>
+      <c r="AT9">
+        <v>8.6</v>
+      </c>
+      <c r="AU9">
+        <v>7.8</v>
+      </c>
+      <c r="AV9">
+        <v>15.5</v>
+      </c>
+      <c r="AW9">
+        <v>7.4</v>
+      </c>
+      <c r="AX9">
+        <v>10</v>
+      </c>
+      <c r="AY9">
+        <v>9</v>
+      </c>
+      <c r="AZ9">
+        <v>15</v>
+      </c>
+      <c r="BA9">
+        <v>7.4</v>
+      </c>
+      <c r="BB9">
+        <v>17</v>
+      </c>
+      <c r="BC9">
+        <v>15.5</v>
+      </c>
+      <c r="BD9">
+        <v>6.8</v>
+      </c>
+      <c r="BE9">
+        <v>7.8</v>
+      </c>
+      <c r="BF9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG9">
+        <v>42</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>13</v>
+      </c>
+      <c r="BK9">
+        <v>6.2</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>21</v>
+      </c>
+      <c r="BN9">
+        <v>6</v>
+      </c>
+      <c r="BO9">
+        <v>3.2</v>
+      </c>
+      <c r="BP9">
+        <v>17.5</v>
+      </c>
+      <c r="BQ9">
+        <v>8</v>
+      </c>
+      <c r="BR9">
+        <v>34</v>
+      </c>
+      <c r="BS9">
+        <v>16</v>
+      </c>
+      <c r="BT9">
+        <v>11</v>
+      </c>
+      <c r="BU9">
+        <v>5.3</v>
+      </c>
+      <c r="BV9">
+        <v>50</v>
+      </c>
+      <c r="BW9">
+        <v>21</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>21</v>
+      </c>
+      <c r="BZ9">
+        <v>29</v>
+      </c>
+      <c r="CA9">
+        <v>12.5</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F10">
+        <v>1.52</v>
+      </c>
+      <c r="G10">
+        <v>1.53</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>7.6</v>
+      </c>
+      <c r="J10">
+        <v>4.7</v>
+      </c>
+      <c r="K10">
+        <v>5.1</v>
+      </c>
+      <c r="L10">
+        <v>1.31</v>
+      </c>
+      <c r="M10">
+        <v>1.04</v>
+      </c>
+      <c r="N10">
+        <v>5.1</v>
+      </c>
+      <c r="O10">
+        <v>1.23</v>
+      </c>
+      <c r="P10">
+        <v>2.4</v>
+      </c>
+      <c r="Q10">
+        <v>1.68</v>
+      </c>
+      <c r="R10">
+        <v>1.54</v>
+      </c>
+      <c r="S10">
+        <v>2.72</v>
+      </c>
+      <c r="T10">
+        <v>1.83</v>
+      </c>
+      <c r="U10">
+        <v>2.1</v>
+      </c>
+      <c r="V10">
+        <v>1.16</v>
+      </c>
+      <c r="W10">
+        <v>2.84</v>
+      </c>
+      <c r="X10">
+        <v>28</v>
+      </c>
+      <c r="Y10">
+        <v>36</v>
+      </c>
+      <c r="Z10">
+        <v>65</v>
+      </c>
+      <c r="AA10">
+        <v>230</v>
+      </c>
+      <c r="AB10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10">
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <v>34</v>
+      </c>
+      <c r="AE10">
+        <v>120</v>
+      </c>
+      <c r="AF10">
+        <v>10.5</v>
+      </c>
+      <c r="AG10">
+        <v>10</v>
+      </c>
+      <c r="AH10">
+        <v>26</v>
+      </c>
+      <c r="AI10">
+        <v>100</v>
+      </c>
+      <c r="AJ10">
+        <v>16.5</v>
+      </c>
+      <c r="AK10">
+        <v>18.5</v>
+      </c>
+      <c r="AL10">
+        <v>36</v>
+      </c>
+      <c r="AM10">
+        <v>120</v>
+      </c>
+      <c r="AN10">
+        <v>6.6</v>
+      </c>
+      <c r="AO10">
+        <v>120</v>
+      </c>
+      <c r="AP10">
+        <v>19.5</v>
+      </c>
+      <c r="AQ10">
+        <v>5.6</v>
+      </c>
+      <c r="AR10">
+        <v>6</v>
+      </c>
+      <c r="AS10">
+        <v>6.4</v>
+      </c>
+      <c r="AT10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10">
+        <v>9.6</v>
+      </c>
+      <c r="AV10">
+        <v>5.6</v>
+      </c>
+      <c r="AW10">
+        <v>6.2</v>
+      </c>
+      <c r="AX10">
+        <v>9</v>
+      </c>
+      <c r="AY10">
+        <v>9</v>
+      </c>
+      <c r="AZ10">
+        <v>18.5</v>
+      </c>
+      <c r="BA10">
+        <v>6.2</v>
+      </c>
+      <c r="BB10">
+        <v>11.5</v>
+      </c>
+      <c r="BC10">
+        <v>13</v>
+      </c>
+      <c r="BD10">
+        <v>5.6</v>
+      </c>
+      <c r="BE10">
+        <v>6.2</v>
+      </c>
+      <c r="BF10">
+        <v>5.9</v>
+      </c>
+      <c r="BG10">
+        <v>6.2</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>2.94</v>
+      </c>
+      <c r="BJ10">
+        <v>14.5</v>
+      </c>
+      <c r="BK10">
+        <v>6.6</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>22</v>
+      </c>
+      <c r="BN10">
+        <v>5.7</v>
+      </c>
+      <c r="BO10">
+        <v>3</v>
+      </c>
+      <c r="BP10">
+        <v>13</v>
+      </c>
+      <c r="BQ10">
+        <v>6.2</v>
+      </c>
+      <c r="BR10">
+        <v>30</v>
+      </c>
+      <c r="BS10">
+        <v>13.5</v>
+      </c>
+      <c r="BT10">
+        <v>14.5</v>
+      </c>
+      <c r="BU10">
+        <v>6.8</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>22</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>22</v>
+      </c>
+      <c r="BZ10">
+        <v>19</v>
+      </c>
+      <c r="CA10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>3.45</v>
+      </c>
+      <c r="G11">
+        <v>3.65</v>
+      </c>
+      <c r="H11">
+        <v>2.12</v>
+      </c>
+      <c r="I11">
+        <v>2.2</v>
+      </c>
+      <c r="J11">
+        <v>3.85</v>
+      </c>
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11">
+        <v>1.32</v>
+      </c>
+      <c r="M11">
+        <v>1.04</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>1.23</v>
+      </c>
+      <c r="P11">
+        <v>2.32</v>
+      </c>
+      <c r="Q11">
+        <v>1.7</v>
+      </c>
+      <c r="R11">
+        <v>1.52</v>
+      </c>
+      <c r="S11">
+        <v>2.78</v>
+      </c>
+      <c r="T11">
+        <v>1.54</v>
+      </c>
+      <c r="U11">
+        <v>2.2</v>
+      </c>
+      <c r="V11">
+        <v>1.84</v>
+      </c>
+      <c r="W11">
+        <v>1.37</v>
+      </c>
+      <c r="X11">
+        <v>24</v>
+      </c>
+      <c r="Y11">
+        <v>14.5</v>
+      </c>
+      <c r="Z11">
+        <v>18</v>
+      </c>
+      <c r="AA11">
+        <v>38</v>
+      </c>
+      <c r="AB11">
+        <v>21</v>
+      </c>
+      <c r="AC11">
+        <v>10.5</v>
+      </c>
+      <c r="AD11">
+        <v>12.5</v>
+      </c>
+      <c r="AE11">
+        <v>24</v>
+      </c>
+      <c r="AF11">
+        <v>32</v>
+      </c>
+      <c r="AG11">
+        <v>19</v>
+      </c>
+      <c r="AH11">
+        <v>19</v>
+      </c>
+      <c r="AI11">
+        <v>36</v>
+      </c>
+      <c r="AJ11">
+        <v>75</v>
+      </c>
+      <c r="AK11">
+        <v>44</v>
+      </c>
+      <c r="AL11">
+        <v>50</v>
+      </c>
+      <c r="AM11">
+        <v>75</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>13</v>
+      </c>
+      <c r="AQ11">
+        <v>9.6</v>
+      </c>
+      <c r="AR11">
+        <v>11.5</v>
+      </c>
+      <c r="AS11">
+        <v>2.96</v>
+      </c>
+      <c r="AT11">
+        <v>2.8</v>
+      </c>
+      <c r="AU11">
+        <v>7.8</v>
+      </c>
+      <c r="AV11">
+        <v>9</v>
+      </c>
+      <c r="AW11">
+        <v>2.84</v>
+      </c>
+      <c r="AX11">
+        <v>19.5</v>
+      </c>
+      <c r="AY11">
+        <v>12</v>
+      </c>
+      <c r="AZ11">
+        <v>2.76</v>
+      </c>
+      <c r="BA11">
+        <v>2.96</v>
+      </c>
+      <c r="BB11">
+        <v>3.05</v>
+      </c>
+      <c r="BC11">
+        <v>3</v>
+      </c>
+      <c r="BD11">
+        <v>3</v>
+      </c>
+      <c r="BE11">
+        <v>3.05</v>
+      </c>
+      <c r="BF11">
+        <v>3.2</v>
+      </c>
+      <c r="BG11">
+        <v>3.2</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.01</v>
+      </c>
+      <c r="BJ11">
+        <v>13</v>
+      </c>
+      <c r="BK11">
+        <v>5.6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>21</v>
+      </c>
+      <c r="BN11">
+        <v>10</v>
+      </c>
+      <c r="BO11">
+        <v>4.7</v>
+      </c>
+      <c r="BP11">
+        <v>38</v>
+      </c>
+      <c r="BQ11">
+        <v>15.5</v>
+      </c>
+      <c r="BR11">
+        <v>48</v>
+      </c>
+      <c r="BS11">
+        <v>19</v>
+      </c>
+      <c r="BT11">
+        <v>7.4</v>
+      </c>
+      <c r="BU11">
+        <v>3.45</v>
+      </c>
+      <c r="BV11">
+        <v>21</v>
+      </c>
+      <c r="BW11">
+        <v>8.4</v>
+      </c>
+      <c r="BX11">
+        <v>34</v>
+      </c>
+      <c r="BY11">
+        <v>14</v>
+      </c>
+      <c r="BZ11">
+        <v>26</v>
+      </c>
+      <c r="CA11">
+        <v>11</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12">
+        <v>1.48</v>
+      </c>
+      <c r="G12">
+        <v>1.61</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
+      </c>
+      <c r="I12">
+        <v>8</v>
+      </c>
+      <c r="J12">
+        <v>4.2</v>
+      </c>
+      <c r="K12">
+        <v>5.5</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>2.48</v>
+      </c>
+      <c r="O12">
+        <v>1.01</v>
+      </c>
+      <c r="P12">
+        <v>2.48</v>
+      </c>
+      <c r="Q12">
+        <v>1.54</v>
+      </c>
+      <c r="R12">
+        <v>1.57</v>
+      </c>
+      <c r="S12">
+        <v>2.3</v>
+      </c>
+      <c r="T12">
+        <v>1.01</v>
+      </c>
+      <c r="U12">
+        <v>1.01</v>
+      </c>
+      <c r="V12">
+        <v>1.15</v>
+      </c>
+      <c r="W12">
+        <v>2.62</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12">
+        <v>1.03</v>
+      </c>
+      <c r="AR12">
+        <v>1.03</v>
+      </c>
+      <c r="AS12">
+        <v>1.03</v>
+      </c>
+      <c r="AT12">
+        <v>1.03</v>
+      </c>
+      <c r="AU12">
+        <v>1.03</v>
+      </c>
+      <c r="AV12">
+        <v>1.03</v>
+      </c>
+      <c r="AW12">
+        <v>1.03</v>
+      </c>
+      <c r="AX12">
+        <v>1.03</v>
+      </c>
+      <c r="AY12">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12">
+        <v>1.03</v>
+      </c>
+      <c r="BA12">
+        <v>1.03</v>
+      </c>
+      <c r="BB12">
+        <v>1.03</v>
+      </c>
+      <c r="BC12">
+        <v>1.03</v>
+      </c>
+      <c r="BD12">
+        <v>1.03</v>
+      </c>
+      <c r="BE12">
+        <v>1.03</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.01</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.01</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.01</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.01</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.01</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.01</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.01</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13">
+        <v>2.14</v>
+      </c>
+      <c r="G13">
+        <v>2.22</v>
+      </c>
+      <c r="H13">
+        <v>3.2</v>
+      </c>
+      <c r="I13">
+        <v>3.4</v>
+      </c>
+      <c r="J13">
+        <v>4.1</v>
+      </c>
+      <c r="K13">
+        <v>4.4</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>7</v>
+      </c>
+      <c r="O13">
+        <v>1.15</v>
+      </c>
+      <c r="P13">
+        <v>3.05</v>
+      </c>
+      <c r="Q13">
+        <v>1.44</v>
+      </c>
+      <c r="R13">
+        <v>1.83</v>
+      </c>
+      <c r="S13">
+        <v>2.1</v>
+      </c>
+      <c r="T13">
+        <v>1.46</v>
+      </c>
+      <c r="U13">
+        <v>2.98</v>
+      </c>
+      <c r="V13">
+        <v>1.41</v>
+      </c>
+      <c r="W13">
+        <v>1.81</v>
+      </c>
+      <c r="X13">
+        <v>40</v>
+      </c>
+      <c r="Y13">
+        <v>25</v>
+      </c>
+      <c r="Z13">
+        <v>32</v>
+      </c>
+      <c r="AA13">
+        <v>55</v>
+      </c>
+      <c r="AB13">
+        <v>19.5</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>16.5</v>
+      </c>
+      <c r="AE13">
+        <v>32</v>
+      </c>
+      <c r="AF13">
+        <v>21</v>
+      </c>
+      <c r="AG13">
+        <v>13</v>
+      </c>
+      <c r="AH13">
+        <v>14.5</v>
+      </c>
+      <c r="AI13">
+        <v>32</v>
+      </c>
+      <c r="AJ13">
+        <v>30</v>
+      </c>
+      <c r="AK13">
+        <v>21</v>
+      </c>
+      <c r="AL13">
+        <v>25</v>
+      </c>
+      <c r="AM13">
+        <v>44</v>
+      </c>
+      <c r="AN13">
+        <v>8.4</v>
+      </c>
+      <c r="AO13">
+        <v>17</v>
+      </c>
+      <c r="AP13">
+        <v>7.8</v>
+      </c>
+      <c r="AQ13">
+        <v>20</v>
+      </c>
+      <c r="AR13">
+        <v>7.6</v>
+      </c>
+      <c r="AS13">
+        <v>8.4</v>
+      </c>
+      <c r="AT13">
+        <v>15.5</v>
+      </c>
+      <c r="AU13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV13">
+        <v>13</v>
+      </c>
+      <c r="AW13">
+        <v>7.6</v>
+      </c>
+      <c r="AX13">
+        <v>16.5</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>7.6</v>
+      </c>
+      <c r="BB13">
+        <v>7.4</v>
+      </c>
+      <c r="BC13">
+        <v>16</v>
+      </c>
+      <c r="BD13">
+        <v>20</v>
+      </c>
+      <c r="BE13">
+        <v>34</v>
+      </c>
+      <c r="BF13">
+        <v>7.4</v>
+      </c>
+      <c r="BG13">
+        <v>13.5</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.01</v>
+      </c>
+      <c r="BJ13">
+        <v>11</v>
+      </c>
+      <c r="BK13">
+        <v>5.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>21</v>
+      </c>
+      <c r="BN13">
+        <v>7.8</v>
+      </c>
+      <c r="BO13">
+        <v>3.95</v>
+      </c>
+      <c r="BP13">
+        <v>18.5</v>
+      </c>
+      <c r="BQ13">
+        <v>8.4</v>
+      </c>
+      <c r="BR13">
+        <v>28</v>
+      </c>
+      <c r="BS13">
+        <v>12</v>
+      </c>
+      <c r="BT13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU13">
+        <v>4.9</v>
+      </c>
+      <c r="BV13">
+        <v>29</v>
+      </c>
+      <c r="BW13">
+        <v>13</v>
+      </c>
+      <c r="BX13">
+        <v>34</v>
+      </c>
+      <c r="BY13">
+        <v>15</v>
+      </c>
+      <c r="BZ13">
+        <v>17</v>
+      </c>
+      <c r="CA13">
+        <v>7.8</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>1.56</v>
+      </c>
+      <c r="G14">
+        <v>1.6</v>
+      </c>
+      <c r="H14">
+        <v>5.4</v>
+      </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>5.4</v>
+      </c>
+      <c r="L14">
+        <v>1.18</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>7.6</v>
+      </c>
+      <c r="O14">
+        <v>1.12</v>
+      </c>
+      <c r="P14">
+        <v>3.3</v>
+      </c>
+      <c r="Q14">
+        <v>1.37</v>
+      </c>
+      <c r="R14">
+        <v>1.94</v>
+      </c>
+      <c r="S14">
+        <v>1.92</v>
+      </c>
+      <c r="T14">
+        <v>1.51</v>
+      </c>
+      <c r="U14">
+        <v>2.68</v>
+      </c>
+      <c r="V14">
+        <v>1.2</v>
+      </c>
+      <c r="W14">
+        <v>2.64</v>
+      </c>
+      <c r="X14">
+        <v>55</v>
+      </c>
+      <c r="Y14">
+        <v>44</v>
+      </c>
+      <c r="Z14">
+        <v>70</v>
+      </c>
+      <c r="AA14">
+        <v>140</v>
+      </c>
+      <c r="AB14">
+        <v>20</v>
+      </c>
+      <c r="AC14">
+        <v>17</v>
+      </c>
+      <c r="AD14">
+        <v>29</v>
+      </c>
+      <c r="AE14">
+        <v>70</v>
+      </c>
+      <c r="AF14">
+        <v>17.5</v>
+      </c>
+      <c r="AG14">
+        <v>13.5</v>
+      </c>
+      <c r="AH14">
+        <v>21</v>
+      </c>
+      <c r="AI14">
+        <v>55</v>
+      </c>
+      <c r="AJ14">
+        <v>21</v>
+      </c>
+      <c r="AK14">
+        <v>17.5</v>
+      </c>
+      <c r="AL14">
+        <v>27</v>
+      </c>
+      <c r="AM14">
+        <v>65</v>
+      </c>
+      <c r="AN14">
+        <v>4.8</v>
+      </c>
+      <c r="AO14">
+        <v>40</v>
+      </c>
+      <c r="AP14">
+        <v>4.8</v>
+      </c>
+      <c r="AQ14">
+        <v>4.7</v>
+      </c>
+      <c r="AR14">
+        <v>4.9</v>
+      </c>
+      <c r="AS14">
+        <v>5</v>
+      </c>
+      <c r="AT14">
+        <v>14.5</v>
+      </c>
+      <c r="AU14">
+        <v>11.5</v>
+      </c>
+      <c r="AV14">
+        <v>20</v>
+      </c>
+      <c r="AW14">
+        <v>4.9</v>
+      </c>
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>9.4</v>
+      </c>
+      <c r="AZ14">
+        <v>14.5</v>
+      </c>
+      <c r="BA14">
+        <v>4.8</v>
+      </c>
+      <c r="BB14">
+        <v>15</v>
+      </c>
+      <c r="BC14">
+        <v>12</v>
+      </c>
+      <c r="BD14">
+        <v>18.5</v>
+      </c>
+      <c r="BE14">
+        <v>4.8</v>
+      </c>
+      <c r="BF14">
+        <v>4.2</v>
+      </c>
+      <c r="BG14">
+        <v>4.6</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>13</v>
+      </c>
+      <c r="BK14">
+        <v>5.6</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>21</v>
+      </c>
+      <c r="BN14">
+        <v>7</v>
+      </c>
+      <c r="BO14">
+        <v>3.35</v>
+      </c>
+      <c r="BP14">
+        <v>13.5</v>
+      </c>
+      <c r="BQ14">
+        <v>5.9</v>
+      </c>
+      <c r="BR14">
+        <v>25</v>
+      </c>
+      <c r="BS14">
+        <v>10</v>
+      </c>
+      <c r="BT14">
+        <v>14.5</v>
+      </c>
+      <c r="BU14">
+        <v>6.2</v>
+      </c>
+      <c r="BV14">
+        <v>50</v>
+      </c>
+      <c r="BW14">
+        <v>21</v>
+      </c>
+      <c r="BX14">
+        <v>48</v>
+      </c>
+      <c r="BY14">
+        <v>19</v>
+      </c>
+      <c r="BZ14">
+        <v>13.5</v>
+      </c>
+      <c r="CA14">
+        <v>5.8</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15">
+        <v>1.7</v>
+      </c>
+      <c r="G15">
+        <v>1.78</v>
+      </c>
+      <c r="H15">
+        <v>4.7</v>
+      </c>
+      <c r="I15">
+        <v>5.8</v>
+      </c>
+      <c r="J15">
+        <v>4.2</v>
+      </c>
+      <c r="K15">
+        <v>4.6</v>
+      </c>
+      <c r="L15">
+        <v>1.27</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>4.8</v>
+      </c>
+      <c r="O15">
+        <v>1.16</v>
+      </c>
+      <c r="P15">
+        <v>2.56</v>
+      </c>
+      <c r="Q15">
+        <v>1.58</v>
+      </c>
+      <c r="R15">
+        <v>1.57</v>
+      </c>
+      <c r="S15">
+        <v>2.32</v>
+      </c>
+      <c r="T15">
+        <v>1.52</v>
+      </c>
+      <c r="U15">
+        <v>2.4</v>
+      </c>
+      <c r="V15">
+        <v>1.23</v>
+      </c>
+      <c r="W15">
+        <v>2.28</v>
+      </c>
+      <c r="X15">
+        <v>30</v>
+      </c>
+      <c r="Y15">
+        <v>30</v>
+      </c>
+      <c r="Z15">
+        <v>50</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>15.5</v>
+      </c>
+      <c r="AC15">
+        <v>13.5</v>
+      </c>
+      <c r="AD15">
+        <v>25</v>
+      </c>
+      <c r="AE15">
+        <v>65</v>
+      </c>
+      <c r="AF15">
+        <v>17</v>
+      </c>
+      <c r="AG15">
+        <v>13.5</v>
+      </c>
+      <c r="AH15">
+        <v>19.5</v>
+      </c>
+      <c r="AI15">
+        <v>60</v>
+      </c>
+      <c r="AJ15">
+        <v>25</v>
+      </c>
+      <c r="AK15">
+        <v>23</v>
+      </c>
+      <c r="AL15">
+        <v>32</v>
+      </c>
+      <c r="AM15">
+        <v>85</v>
+      </c>
+      <c r="AN15">
+        <v>9</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>3.15</v>
+      </c>
+      <c r="AQ15">
+        <v>3.15</v>
+      </c>
+      <c r="AR15">
+        <v>3.3</v>
+      </c>
+      <c r="AS15">
+        <v>3.55</v>
+      </c>
+      <c r="AT15">
+        <v>9.6</v>
+      </c>
+      <c r="AU15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV15">
+        <v>3.1</v>
+      </c>
+      <c r="AW15">
+        <v>3.35</v>
+      </c>
+      <c r="AX15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>3</v>
+      </c>
+      <c r="BA15">
+        <v>3.35</v>
+      </c>
+      <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
+        <v>3.2</v>
+      </c>
+      <c r="BE15">
+        <v>3.4</v>
+      </c>
+      <c r="BF15">
+        <v>6.2</v>
+      </c>
+      <c r="BG15">
+        <v>3.55</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>12.5</v>
+      </c>
+      <c r="BK15">
+        <v>5.9</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>21</v>
+      </c>
+      <c r="BN15">
+        <v>6.4</v>
+      </c>
+      <c r="BO15">
+        <v>3.4</v>
+      </c>
+      <c r="BP15">
+        <v>15.5</v>
+      </c>
+      <c r="BQ15">
+        <v>7.2</v>
+      </c>
+      <c r="BR15">
+        <v>29</v>
+      </c>
+      <c r="BS15">
+        <v>13</v>
+      </c>
+      <c r="BT15">
+        <v>11.5</v>
+      </c>
+      <c r="BU15">
+        <v>5.4</v>
+      </c>
+      <c r="BV15">
+        <v>46</v>
+      </c>
+      <c r="BW15">
+        <v>20</v>
+      </c>
+      <c r="BX15">
+        <v>50</v>
+      </c>
+      <c r="BY15">
+        <v>21</v>
+      </c>
+      <c r="BZ15">
+        <v>20</v>
+      </c>
+      <c r="CA15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16">
+        <v>2.44</v>
+      </c>
+      <c r="G16">
+        <v>2.56</v>
+      </c>
+      <c r="H16">
+        <v>2.74</v>
+      </c>
+      <c r="I16">
+        <v>2.92</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>4.2</v>
+      </c>
+      <c r="L16">
+        <v>1.24</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>6.2</v>
+      </c>
+      <c r="O16">
+        <v>1.16</v>
+      </c>
+      <c r="P16">
+        <v>2.74</v>
+      </c>
+      <c r="Q16">
+        <v>1.52</v>
+      </c>
+      <c r="R16">
+        <v>1.71</v>
+      </c>
+      <c r="S16">
+        <v>2.26</v>
+      </c>
+      <c r="T16">
+        <v>1.49</v>
+      </c>
+      <c r="U16">
+        <v>2.76</v>
+      </c>
+      <c r="V16">
+        <v>1.52</v>
+      </c>
+      <c r="W16">
+        <v>1.64</v>
+      </c>
+      <c r="X16">
+        <v>36</v>
+      </c>
+      <c r="Y16">
+        <v>21</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>36</v>
+      </c>
+      <c r="AJ16">
+        <v>42</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>34</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.14</v>
+      </c>
+      <c r="AQ16">
+        <v>1.12</v>
+      </c>
+      <c r="AR16">
+        <v>1.18</v>
+      </c>
+      <c r="AS16">
+        <v>1.18</v>
+      </c>
+      <c r="AT16">
+        <v>1.18</v>
+      </c>
+      <c r="AU16">
+        <v>1.18</v>
+      </c>
+      <c r="AV16">
+        <v>1.18</v>
+      </c>
+      <c r="AW16">
+        <v>1.18</v>
+      </c>
+      <c r="AX16">
+        <v>1.18</v>
+      </c>
+      <c r="AY16">
+        <v>1.18</v>
+      </c>
+      <c r="AZ16">
+        <v>1.18</v>
+      </c>
+      <c r="BA16">
+        <v>1.14</v>
+      </c>
+      <c r="BB16">
+        <v>1.15</v>
+      </c>
+      <c r="BC16">
+        <v>1.18</v>
+      </c>
+      <c r="BD16">
+        <v>19</v>
+      </c>
+      <c r="BE16">
+        <v>1.18</v>
+      </c>
+      <c r="BF16">
+        <v>1.18</v>
+      </c>
+      <c r="BG16">
+        <v>1.18</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>11.5</v>
+      </c>
+      <c r="BK16">
+        <v>5.4</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>21</v>
+      </c>
+      <c r="BN16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO16">
+        <v>4.1</v>
+      </c>
+      <c r="BP16">
+        <v>21</v>
+      </c>
+      <c r="BQ16">
+        <v>10</v>
+      </c>
+      <c r="BR16">
+        <v>30</v>
+      </c>
+      <c r="BS16">
+        <v>14</v>
+      </c>
+      <c r="BT16">
+        <v>9</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>26</v>
+      </c>
+      <c r="BW16">
+        <v>12</v>
+      </c>
+      <c r="BX16">
+        <v>34</v>
+      </c>
+      <c r="BY16">
+        <v>15</v>
+      </c>
+      <c r="BZ16">
+        <v>19</v>
+      </c>
+      <c r="CA16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17">
+        <v>1.99</v>
+      </c>
+      <c r="G17">
+        <v>2.12</v>
+      </c>
+      <c r="H17">
+        <v>3.55</v>
+      </c>
+      <c r="I17">
+        <v>3.85</v>
+      </c>
+      <c r="J17">
+        <v>3.9</v>
+      </c>
+      <c r="K17">
+        <v>4.3</v>
+      </c>
+      <c r="L17">
+        <v>1.26</v>
+      </c>
+      <c r="M17">
+        <v>1.04</v>
+      </c>
+      <c r="N17">
+        <v>5.1</v>
+      </c>
+      <c r="O17">
+        <v>1.2</v>
+      </c>
+      <c r="P17">
+        <v>2.44</v>
+      </c>
+      <c r="Q17">
+        <v>1.59</v>
+      </c>
+      <c r="R17">
+        <v>1.26</v>
+      </c>
+      <c r="S17">
+        <v>1.6</v>
+      </c>
+      <c r="T17">
+        <v>1.56</v>
+      </c>
+      <c r="U17">
+        <v>2.5</v>
+      </c>
+      <c r="V17">
+        <v>1.35</v>
+      </c>
+      <c r="W17">
+        <v>1.89</v>
+      </c>
+      <c r="X17">
+        <v>1000</v>
+      </c>
+      <c r="Y17">
+        <v>1000</v>
+      </c>
+      <c r="Z17">
+        <v>1000</v>
+      </c>
+      <c r="AA17">
+        <v>1000</v>
+      </c>
+      <c r="AB17">
+        <v>1000</v>
+      </c>
+      <c r="AC17">
+        <v>11</v>
+      </c>
+      <c r="AD17">
+        <v>1000</v>
+      </c>
+      <c r="AE17">
+        <v>1000</v>
+      </c>
+      <c r="AF17">
+        <v>1000</v>
+      </c>
+      <c r="AG17">
+        <v>1000</v>
+      </c>
+      <c r="AH17">
+        <v>1000</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>1000</v>
+      </c>
+      <c r="AK17">
+        <v>1000</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>1000</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>1.1</v>
+      </c>
+      <c r="AQ17">
+        <v>1.1</v>
+      </c>
+      <c r="AR17">
+        <v>1.1</v>
+      </c>
+      <c r="AS17">
+        <v>1.1</v>
+      </c>
+      <c r="AT17">
+        <v>1.1</v>
+      </c>
+      <c r="AU17">
+        <v>1.03</v>
+      </c>
+      <c r="AV17">
+        <v>1.1</v>
+      </c>
+      <c r="AW17">
+        <v>1.1</v>
+      </c>
+      <c r="AX17">
+        <v>1.1</v>
+      </c>
+      <c r="AY17">
+        <v>1.1</v>
+      </c>
+      <c r="AZ17">
+        <v>1.1</v>
+      </c>
+      <c r="BA17">
+        <v>1.1</v>
+      </c>
+      <c r="BB17">
+        <v>1.1</v>
+      </c>
+      <c r="BC17">
+        <v>1.1</v>
+      </c>
+      <c r="BD17">
+        <v>1.1</v>
+      </c>
+      <c r="BE17">
+        <v>1.1</v>
+      </c>
+      <c r="BF17">
+        <v>1.1</v>
+      </c>
+      <c r="BG17">
+        <v>1.1</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>12</v>
+      </c>
+      <c r="BK17">
+        <v>5.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>21</v>
+      </c>
+      <c r="BN17">
+        <v>7</v>
+      </c>
+      <c r="BO17">
+        <v>3.6</v>
+      </c>
+      <c r="BP17">
+        <v>18.5</v>
+      </c>
+      <c r="BQ17">
+        <v>8.4</v>
+      </c>
+      <c r="BR17">
+        <v>30</v>
+      </c>
+      <c r="BS17">
+        <v>14</v>
+      </c>
+      <c r="BT17">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU17">
+        <v>4.9</v>
+      </c>
+      <c r="BV17">
+        <v>34</v>
+      </c>
+      <c r="BW17">
+        <v>15.5</v>
+      </c>
+      <c r="BX17">
+        <v>44</v>
+      </c>
+      <c r="BY17">
+        <v>18.5</v>
+      </c>
+      <c r="BZ17">
+        <v>21</v>
+      </c>
+      <c r="CA17">
+        <v>10</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -319,15 +319,15 @@
     <t>Nashville SC</t>
   </si>
   <si>
+    <t>Colorado Switchbacks FC</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
     <t>Austin FC</t>
   </si>
   <si>
-    <t>Colorado Switchbacks FC</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes</t>
   </si>
   <si>
@@ -367,15 +367,15 @@
     <t>CF Montreal</t>
   </si>
   <si>
+    <t>Miami FC</t>
+  </si>
+  <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>Miami FC</t>
-  </si>
-  <si>
-    <t>San Diego FC</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 00:46:03</t>
+    <t>2026-07-21 02:53:07</t>
   </si>
 </sst>
 </file>
@@ -1003,145 +1003,145 @@
         <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
+        <v>2.76</v>
+      </c>
+      <c r="O2">
+        <v>1.45</v>
+      </c>
+      <c r="P2">
         <v>1.61</v>
       </c>
-      <c r="O2">
-        <v>1.42</v>
-      </c>
-      <c r="P2">
-        <v>1.6</v>
-      </c>
       <c r="Q2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W2">
         <v>1.18</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y2">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="Z2">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA2">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AF2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AG2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AH2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>2.08</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
-        <v>1.93</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>2.08</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AT2">
-        <v>2.18</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="AW2">
-        <v>2.26</v>
+        <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>2.34</v>
+        <v>5.2</v>
       </c>
       <c r="AY2">
-        <v>2.26</v>
+        <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>2.28</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>2.36</v>
+        <v>42</v>
       </c>
       <c r="BB2">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="BC2">
-        <v>2.44</v>
+        <v>5.6</v>
       </c>
       <c r="BD2">
-        <v>2.44</v>
+        <v>5.6</v>
       </c>
       <c r="BE2">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="BF2">
-        <v>2.44</v>
+        <v>5.7</v>
       </c>
       <c r="BG2">
-        <v>2.44</v>
+        <v>12.5</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1150,58 +1150,58 @@
         <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="BV2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1224,16 +1224,16 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
         <v>4.2</v>
-      </c>
-      <c r="I3">
-        <v>4.5</v>
       </c>
       <c r="J3">
         <v>3.85</v>
@@ -1242,82 +1242,82 @@
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
         <v>2.88</v>
       </c>
       <c r="T3">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="X3">
+        <v>19.5</v>
+      </c>
+      <c r="Y3">
+        <v>18</v>
+      </c>
+      <c r="Z3">
+        <v>32</v>
+      </c>
+      <c r="AA3">
+        <v>75</v>
+      </c>
+      <c r="AB3">
+        <v>12</v>
+      </c>
+      <c r="AC3">
+        <v>9.4</v>
+      </c>
+      <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>46</v>
+      </c>
+      <c r="AF3">
+        <v>14</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>17</v>
+      </c>
+      <c r="AI3">
+        <v>48</v>
+      </c>
+      <c r="AJ3">
         <v>24</v>
       </c>
-      <c r="Y3">
-        <v>24</v>
-      </c>
-      <c r="Z3">
-        <v>44</v>
-      </c>
-      <c r="AA3">
-        <v>100</v>
-      </c>
-      <c r="AB3">
-        <v>13</v>
-      </c>
-      <c r="AC3">
-        <v>11</v>
-      </c>
-      <c r="AD3">
-        <v>22</v>
-      </c>
-      <c r="AE3">
-        <v>65</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
-      <c r="AG3">
-        <v>12.5</v>
-      </c>
-      <c r="AH3">
-        <v>21</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>25</v>
-      </c>
       <c r="AK3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL3">
         <v>44</v>
@@ -1326,124 +1326,124 @@
         <v>95</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP3">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3">
-        <v>3.65</v>
+        <v>24</v>
       </c>
       <c r="AS3">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AT3">
+        <v>9.6</v>
+      </c>
+      <c r="AU3">
+        <v>7.8</v>
+      </c>
+      <c r="AV3">
+        <v>14.5</v>
+      </c>
+      <c r="AW3">
+        <v>32</v>
+      </c>
+      <c r="AX3">
+        <v>11</v>
+      </c>
+      <c r="AY3">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU3">
-        <v>7.6</v>
-      </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>3.75</v>
-      </c>
-      <c r="AX3">
-        <v>10</v>
-      </c>
-      <c r="AY3">
-        <v>8.6</v>
-      </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA3">
-        <v>3.75</v>
+        <v>36</v>
       </c>
       <c r="BB3">
-        <v>3.4</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD3">
         <v>21</v>
       </c>
       <c r="BE3">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
+        <v>10</v>
+      </c>
+      <c r="BG3">
+        <v>27</v>
+      </c>
+      <c r="BH3">
+        <v>4.1</v>
+      </c>
+      <c r="BI3">
+        <v>3.2</v>
+      </c>
+      <c r="BJ3">
+        <v>9.4</v>
+      </c>
+      <c r="BK3">
+        <v>7</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>21</v>
+      </c>
+      <c r="BN3">
+        <v>5.2</v>
+      </c>
+      <c r="BO3">
+        <v>4.3</v>
+      </c>
+      <c r="BP3">
+        <v>14</v>
+      </c>
+      <c r="BQ3">
+        <v>10.5</v>
+      </c>
+      <c r="BR3">
+        <v>25</v>
+      </c>
+      <c r="BS3">
+        <v>18</v>
+      </c>
+      <c r="BT3">
         <v>7.8</v>
       </c>
-      <c r="BG3">
-        <v>3.95</v>
-      </c>
-      <c r="BH3">
-        <v>1000</v>
-      </c>
-      <c r="BI3">
-        <v>2.88</v>
-      </c>
-      <c r="BJ3">
-        <v>12.5</v>
-      </c>
-      <c r="BK3">
-        <v>6.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>22</v>
-      </c>
-      <c r="BN3">
-        <v>6</v>
-      </c>
-      <c r="BO3">
-        <v>3.45</v>
-      </c>
-      <c r="BP3">
-        <v>16.5</v>
-      </c>
-      <c r="BQ3">
-        <v>8.4</v>
-      </c>
-      <c r="BR3">
+      <c r="BU3">
+        <v>5.8</v>
+      </c>
+      <c r="BV3">
         <v>30</v>
       </c>
-      <c r="BS3">
-        <v>15.5</v>
-      </c>
-      <c r="BT3">
-        <v>10</v>
-      </c>
-      <c r="BU3">
-        <v>5.5</v>
-      </c>
-      <c r="BV3">
-        <v>44</v>
-      </c>
       <c r="BW3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BY3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BZ3">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1466,19 +1466,19 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I4">
         <v>4.4</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.6</v>
@@ -1487,37 +1487,37 @@
         <v>1.4</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
         <v>4.3</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
         <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1532,7 +1532,7 @@
         <v>120</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1556,7 +1556,7 @@
         <v>75</v>
       </c>
       <c r="AJ4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1568,22 +1568,22 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO4">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1595,7 +1595,7 @@
         <v>15</v>
       </c>
       <c r="AW4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1619,7 +1619,7 @@
         <v>40</v>
       </c>
       <c r="BE4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF4">
         <v>15</v>
@@ -1711,7 +1711,7 @@
         <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
         <v>3.4</v>
@@ -1735,13 +1735,13 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1753,13 +1753,13 @@
         <v>1.82</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X5">
         <v>14.5</v>
@@ -1777,10 +1777,10 @@
         <v>11</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5">
         <v>50</v>
@@ -1789,10 +1789,10 @@
         <v>16.5</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -1825,10 +1825,10 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
@@ -1837,7 +1837,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1849,25 +1849,25 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC5">
         <v>19</v>
       </c>
       <c r="BD5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF5">
         <v>17</v>
       </c>
       <c r="BG5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1950,7 +1950,7 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>9.199999999999999</v>
@@ -1959,22 +1959,22 @@
         <v>1.49</v>
       </c>
       <c r="I6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
         <v>4.4</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1989,16 +1989,16 @@
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="W6">
         <v>1.12</v>
@@ -2010,7 +2010,7 @@
         <v>7.6</v>
       </c>
       <c r="Z6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA6">
         <v>14</v>
@@ -2052,10 +2052,10 @@
         <v>180</v>
       </c>
       <c r="AN6">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AO6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP6">
         <v>14.5</v>
@@ -2082,37 +2082,37 @@
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
         <v>3.25</v>
@@ -2121,31 +2121,31 @@
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT6">
         <v>3.9</v>
@@ -2157,19 +2157,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX6">
         <v>27</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>17.5</v>
       </c>
       <c r="CA6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
         <v>124</v>
@@ -2195,7 +2195,7 @@
         <v>1.94</v>
       </c>
       <c r="G7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H7">
         <v>4.1</v>
@@ -2216,40 +2216,40 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
         <v>1.25</v>
       </c>
       <c r="W7">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7">
         <v>36</v>
@@ -2270,7 +2270,7 @@
         <v>85</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2282,7 +2282,7 @@
         <v>95</v>
       </c>
       <c r="AJ7">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK7">
         <v>24</v>
@@ -2294,7 +2294,7 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO7">
         <v>95</v>
@@ -2309,7 +2309,7 @@
         <v>26</v>
       </c>
       <c r="AS7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2321,7 +2321,7 @@
         <v>15</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
         <v>10</v>
@@ -2333,7 +2333,7 @@
         <v>16.5</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB7">
         <v>19.5</v>
@@ -2345,13 +2345,13 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
         <v>11.5</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH7">
         <v>3.9</v>
@@ -2437,7 +2437,7 @@
         <v>3.5</v>
       </c>
       <c r="G8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
         <v>2.06</v>
@@ -2449,7 +2449,7 @@
         <v>4.2</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8">
         <v>1.28</v>
@@ -2461,7 +2461,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
         <v>2.66</v>
@@ -2470,13 +2470,13 @@
         <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S8">
         <v>2.42</v>
       </c>
       <c r="T8">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="U8">
         <v>2.66</v>
@@ -2491,16 +2491,16 @@
         <v>26</v>
       </c>
       <c r="Y8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z8">
         <v>16.5</v>
       </c>
       <c r="AA8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -2509,37 +2509,37 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
         <v>1000</v>
       </c>
       <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
         <v>36</v>
       </c>
-      <c r="AL8">
-        <v>38</v>
-      </c>
       <c r="AM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AP8">
         <v>22</v>
@@ -2548,10 +2548,10 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8">
         <v>18</v>
@@ -2560,100 +2560,100 @@
         <v>9</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB8">
         <v>32</v>
       </c>
       <c r="BC8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BD8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE8">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF8">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BK8">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM8">
         <v>21</v>
       </c>
       <c r="BN8">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
+        <v>17.5</v>
+      </c>
+      <c r="BR8">
+        <v>30</v>
+      </c>
+      <c r="BS8">
+        <v>20</v>
+      </c>
+      <c r="BT8">
+        <v>5.6</v>
+      </c>
+      <c r="BU8">
+        <v>4.6</v>
+      </c>
+      <c r="BV8">
+        <v>14</v>
+      </c>
+      <c r="BW8">
+        <v>11</v>
+      </c>
+      <c r="BX8">
+        <v>22</v>
+      </c>
+      <c r="BY8">
+        <v>17.5</v>
+      </c>
+      <c r="BZ8">
         <v>15.5</v>
       </c>
-      <c r="BR8">
-        <v>44</v>
-      </c>
-      <c r="BS8">
-        <v>17.5</v>
-      </c>
-      <c r="BT8">
-        <v>7.4</v>
-      </c>
-      <c r="BU8">
-        <v>3.45</v>
-      </c>
-      <c r="BV8">
-        <v>18.5</v>
-      </c>
-      <c r="BW8">
-        <v>8</v>
-      </c>
-      <c r="BX8">
-        <v>30</v>
-      </c>
-      <c r="BY8">
-        <v>12.5</v>
-      </c>
-      <c r="BZ8">
-        <v>21</v>
-      </c>
       <c r="CA8">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="CB8" t="s">
         <v>124</v>
@@ -2679,7 +2679,7 @@
         <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
         <v>4.5</v>
@@ -2715,7 +2715,7 @@
         <v>1.44</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
         <v>1.75</v>
@@ -2733,10 +2733,10 @@
         <v>20</v>
       </c>
       <c r="Y9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>120</v>
@@ -2763,10 +2763,10 @@
         <v>19</v>
       </c>
       <c r="AI9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK9">
         <v>19.5</v>
@@ -2784,13 +2784,13 @@
         <v>70</v>
       </c>
       <c r="AP9">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9">
         <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="AS9">
         <v>7.8</v>
@@ -2805,7 +2805,7 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2826,7 +2826,7 @@
         <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE9">
         <v>7.8</v>
@@ -2835,7 +2835,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2921,34 +2921,34 @@
         <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
         <v>7</v>
       </c>
       <c r="I10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>1.68</v>
@@ -2957,25 +2957,25 @@
         <v>1.54</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
         <v>2.84</v>
       </c>
       <c r="X10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z10">
         <v>65</v>
@@ -2987,7 +2987,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD10">
         <v>34</v>
@@ -3029,25 +3029,25 @@
         <v>19.5</v>
       </c>
       <c r="AQ10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AR10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX10">
         <v>9</v>
@@ -3059,7 +3059,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB10">
         <v>11.5</v>
@@ -3068,16 +3068,16 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3086,58 +3086,58 @@
         <v>2.94</v>
       </c>
       <c r="BJ10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>124</v>
@@ -3145,13 +3145,13 @@
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
         <v>101</v>
@@ -3160,106 +3160,106 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>3.45</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>3.65</v>
+        <v>1.6</v>
       </c>
       <c r="H11">
-        <v>2.12</v>
+        <v>5.5</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>870</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>2.72</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>500</v>
       </c>
       <c r="L11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="Q11">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="R11">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="T11">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.37</v>
+        <v>2.66</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
         <v>1000</v>
@@ -3268,58 +3268,58 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>2.84</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3328,58 +3328,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3387,13 +3387,13 @@
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
         <v>102</v>
@@ -3402,166 +3402,166 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>1.48</v>
+        <v>2.14</v>
       </c>
       <c r="G12">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I12">
+        <v>3.35</v>
+      </c>
+      <c r="J12">
+        <v>4.1</v>
+      </c>
+      <c r="K12">
+        <v>4.4</v>
+      </c>
+      <c r="L12">
+        <v>1.23</v>
+      </c>
+      <c r="M12">
+        <v>1.02</v>
+      </c>
+      <c r="N12">
+        <v>7.2</v>
+      </c>
+      <c r="O12">
+        <v>1.15</v>
+      </c>
+      <c r="P12">
+        <v>3.1</v>
+      </c>
+      <c r="Q12">
+        <v>1.45</v>
+      </c>
+      <c r="R12">
+        <v>1.86</v>
+      </c>
+      <c r="S12">
+        <v>2.08</v>
+      </c>
+      <c r="T12">
+        <v>1.46</v>
+      </c>
+      <c r="U12">
+        <v>2.98</v>
+      </c>
+      <c r="V12">
+        <v>1.42</v>
+      </c>
+      <c r="W12">
+        <v>1.82</v>
+      </c>
+      <c r="X12">
+        <v>36</v>
+      </c>
+      <c r="Y12">
+        <v>25</v>
+      </c>
+      <c r="Z12">
+        <v>32</v>
+      </c>
+      <c r="AA12">
+        <v>55</v>
+      </c>
+      <c r="AB12">
+        <v>19.5</v>
+      </c>
+      <c r="AC12">
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <v>16.5</v>
+      </c>
+      <c r="AE12">
+        <v>32</v>
+      </c>
+      <c r="AF12">
+        <v>21</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>14.5</v>
+      </c>
+      <c r="AI12">
+        <v>32</v>
+      </c>
+      <c r="AJ12">
+        <v>30</v>
+      </c>
+      <c r="AK12">
+        <v>21</v>
+      </c>
+      <c r="AL12">
+        <v>25</v>
+      </c>
+      <c r="AM12">
+        <v>44</v>
+      </c>
+      <c r="AN12">
+        <v>8.4</v>
+      </c>
+      <c r="AO12">
+        <v>16.5</v>
+      </c>
+      <c r="AP12">
         <v>8</v>
       </c>
-      <c r="J12">
-        <v>4.2</v>
-      </c>
-      <c r="K12">
-        <v>5.5</v>
-      </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>2.48</v>
-      </c>
-      <c r="O12">
-        <v>1.01</v>
-      </c>
-      <c r="P12">
-        <v>2.48</v>
-      </c>
-      <c r="Q12">
-        <v>1.54</v>
-      </c>
-      <c r="R12">
-        <v>1.57</v>
-      </c>
-      <c r="S12">
-        <v>2.3</v>
-      </c>
-      <c r="T12">
-        <v>1.01</v>
-      </c>
-      <c r="U12">
-        <v>1.01</v>
-      </c>
-      <c r="V12">
-        <v>1.15</v>
-      </c>
-      <c r="W12">
-        <v>2.62</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
-      <c r="Y12">
-        <v>1000</v>
-      </c>
-      <c r="Z12">
-        <v>1000</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>1000</v>
-      </c>
-      <c r="AC12">
-        <v>1000</v>
-      </c>
-      <c r="AD12">
-        <v>1000</v>
-      </c>
-      <c r="AE12">
-        <v>1000</v>
-      </c>
-      <c r="AF12">
-        <v>1000</v>
-      </c>
-      <c r="AG12">
-        <v>1000</v>
-      </c>
-      <c r="AH12">
-        <v>1000</v>
-      </c>
-      <c r="AI12">
-        <v>1000</v>
-      </c>
-      <c r="AJ12">
-        <v>1000</v>
-      </c>
-      <c r="AK12">
-        <v>1000</v>
-      </c>
-      <c r="AL12">
-        <v>1000</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
-        <v>1000</v>
-      </c>
-      <c r="AO12">
-        <v>1000</v>
-      </c>
-      <c r="AP12">
-        <v>1.03</v>
-      </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3570,58 +3570,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BT12">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3644,166 +3644,166 @@
         <v>119</v>
       </c>
       <c r="F13">
-        <v>2.14</v>
+        <v>3.45</v>
       </c>
       <c r="G13">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="I13">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N13">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="R13">
+        <v>1.52</v>
+      </c>
+      <c r="S13">
+        <v>2.78</v>
+      </c>
+      <c r="T13">
+        <v>1.57</v>
+      </c>
+      <c r="U13">
+        <v>2.34</v>
+      </c>
+      <c r="V13">
         <v>1.83</v>
       </c>
-      <c r="S13">
-        <v>2.1</v>
-      </c>
-      <c r="T13">
-        <v>1.46</v>
-      </c>
-      <c r="U13">
-        <v>2.98</v>
-      </c>
-      <c r="V13">
-        <v>1.41</v>
-      </c>
       <c r="W13">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="X13">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Y13">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="AA13">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AB13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AC13">
+        <v>9.4</v>
+      </c>
+      <c r="AD13">
         <v>11</v>
       </c>
-      <c r="AD13">
-        <v>16.5</v>
-      </c>
       <c r="AE13">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AF13">
+        <v>28</v>
+      </c>
+      <c r="AG13">
+        <v>15.5</v>
+      </c>
+      <c r="AH13">
+        <v>16</v>
+      </c>
+      <c r="AI13">
+        <v>30</v>
+      </c>
+      <c r="AJ13">
+        <v>65</v>
+      </c>
+      <c r="AK13">
+        <v>38</v>
+      </c>
+      <c r="AL13">
+        <v>42</v>
+      </c>
+      <c r="AM13">
+        <v>70</v>
+      </c>
+      <c r="AN13">
+        <v>29</v>
+      </c>
+      <c r="AO13">
+        <v>12.5</v>
+      </c>
+      <c r="AP13">
+        <v>17</v>
+      </c>
+      <c r="AQ13">
+        <v>10.5</v>
+      </c>
+      <c r="AR13">
+        <v>13</v>
+      </c>
+      <c r="AS13">
+        <v>22</v>
+      </c>
+      <c r="AT13">
+        <v>14.5</v>
+      </c>
+      <c r="AU13">
+        <v>7.8</v>
+      </c>
+      <c r="AV13">
+        <v>9.6</v>
+      </c>
+      <c r="AW13">
+        <v>18</v>
+      </c>
+      <c r="AX13">
+        <v>23</v>
+      </c>
+      <c r="AY13">
+        <v>13</v>
+      </c>
+      <c r="AZ13">
+        <v>13.5</v>
+      </c>
+      <c r="BA13">
+        <v>8</v>
+      </c>
+      <c r="BB13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC13">
+        <v>8.4</v>
+      </c>
+      <c r="BD13">
+        <v>8.6</v>
+      </c>
+      <c r="BE13">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF13">
         <v>21</v>
       </c>
-      <c r="AG13">
-        <v>13</v>
-      </c>
-      <c r="AH13">
-        <v>14.5</v>
-      </c>
-      <c r="AI13">
-        <v>32</v>
-      </c>
-      <c r="AJ13">
-        <v>30</v>
-      </c>
-      <c r="AK13">
-        <v>21</v>
-      </c>
-      <c r="AL13">
-        <v>25</v>
-      </c>
-      <c r="AM13">
-        <v>44</v>
-      </c>
-      <c r="AN13">
-        <v>8.4</v>
-      </c>
-      <c r="AO13">
-        <v>17</v>
-      </c>
-      <c r="AP13">
-        <v>7.8</v>
-      </c>
-      <c r="AQ13">
-        <v>20</v>
-      </c>
-      <c r="AR13">
-        <v>7.6</v>
-      </c>
-      <c r="AS13">
-        <v>8.4</v>
-      </c>
-      <c r="AT13">
-        <v>15.5</v>
-      </c>
-      <c r="AU13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV13">
-        <v>13</v>
-      </c>
-      <c r="AW13">
-        <v>7.6</v>
-      </c>
-      <c r="AX13">
-        <v>16.5</v>
-      </c>
-      <c r="AY13">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13">
-        <v>12</v>
-      </c>
-      <c r="BA13">
-        <v>7.6</v>
-      </c>
-      <c r="BB13">
-        <v>7.4</v>
-      </c>
-      <c r="BC13">
-        <v>16</v>
-      </c>
-      <c r="BD13">
-        <v>20</v>
-      </c>
-      <c r="BE13">
-        <v>34</v>
-      </c>
-      <c r="BF13">
-        <v>7.4</v>
-      </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3812,10 +3812,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BK13">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3824,46 +3824,46 @@
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BO13">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP13">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BQ13">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BR13">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BT13">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BU13">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="BV13">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BW13">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BY13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BZ13">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="CA13">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3886,16 +3886,16 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I14">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -3904,28 +3904,28 @@
         <v>5.4</v>
       </c>
       <c r="L14">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R14">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="S14">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="T14">
         <v>1.51</v>
@@ -3934,10 +3934,10 @@
         <v>2.68</v>
       </c>
       <c r="V14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X14">
         <v>55</v>
@@ -3970,7 +3970,7 @@
         <v>13.5</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI14">
         <v>55</v>
@@ -3994,16 +3994,16 @@
         <v>40</v>
       </c>
       <c r="AP14">
+        <v>4.9</v>
+      </c>
+      <c r="AQ14">
         <v>4.8</v>
       </c>
-      <c r="AQ14">
-        <v>4.7</v>
-      </c>
       <c r="AR14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS14">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT14">
         <v>14.5</v>
@@ -4015,7 +4015,7 @@
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX14">
         <v>12</v>
@@ -4027,7 +4027,7 @@
         <v>14.5</v>
       </c>
       <c r="BA14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB14">
         <v>15</v>
@@ -4039,13 +4039,13 @@
         <v>18.5</v>
       </c>
       <c r="BE14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF14">
         <v>4.2</v>
       </c>
       <c r="BG14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
         <v>121</v>
       </c>
       <c r="F15">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="G15">
         <v>1.78</v>
@@ -4137,37 +4137,37 @@
         <v>4.7</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K15">
         <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R15">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="S15">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T15">
         <v>1.52</v>
@@ -4176,124 +4176,124 @@
         <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
         <v>2.28</v>
       </c>
       <c r="X15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Z15">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB15">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC15">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AD15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE15">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF15">
+        <v>14</v>
+      </c>
+      <c r="AG15">
+        <v>11</v>
+      </c>
+      <c r="AH15">
         <v>17</v>
-      </c>
-      <c r="AG15">
-        <v>13.5</v>
-      </c>
-      <c r="AH15">
-        <v>19.5</v>
       </c>
       <c r="AI15">
         <v>60</v>
       </c>
       <c r="AJ15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK15">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AL15">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM15">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN15">
+        <v>7.8</v>
+      </c>
+      <c r="AO15">
+        <v>50</v>
+      </c>
+      <c r="AP15">
+        <v>21</v>
+      </c>
+      <c r="AQ15">
+        <v>21</v>
+      </c>
+      <c r="AR15">
+        <v>7.2</v>
+      </c>
+      <c r="AS15">
+        <v>8</v>
+      </c>
+      <c r="AT15">
+        <v>10.5</v>
+      </c>
+      <c r="AU15">
         <v>9</v>
       </c>
-      <c r="AO15">
-        <v>1000</v>
-      </c>
-      <c r="AP15">
-        <v>3.15</v>
-      </c>
-      <c r="AQ15">
-        <v>3.15</v>
-      </c>
-      <c r="AR15">
-        <v>3.3</v>
-      </c>
-      <c r="AS15">
-        <v>3.55</v>
-      </c>
-      <c r="AT15">
-        <v>9.6</v>
-      </c>
-      <c r="AU15">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AV15">
-        <v>3.1</v>
+        <v>17</v>
       </c>
       <c r="AW15">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="AX15">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ15">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="BA15">
-        <v>3.35</v>
+        <v>7.4</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC15">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
-        <v>3.2</v>
+        <v>21</v>
       </c>
       <c r="BE15">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG15">
-        <v>3.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH15">
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
         <v>12.5</v>
@@ -4370,13 +4370,13 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="I16">
         <v>2.92</v>
@@ -4388,10 +4388,10 @@
         <v>4.2</v>
       </c>
       <c r="L16">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>6.2</v>
@@ -4400,19 +4400,19 @@
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S16">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="U16">
         <v>2.76</v>
@@ -4421,124 +4421,124 @@
         <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X16">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y16">
         <v>21</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI16">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ16">
         <v>42</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL16">
         <v>34</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP16">
-        <v>1.14</v>
+        <v>5.9</v>
       </c>
       <c r="AQ16">
-        <v>1.12</v>
+        <v>17</v>
       </c>
       <c r="AR16">
-        <v>1.18</v>
+        <v>20</v>
       </c>
       <c r="AS16">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AT16">
-        <v>1.18</v>
+        <v>15.5</v>
       </c>
       <c r="AU16">
-        <v>1.18</v>
+        <v>9</v>
       </c>
       <c r="AV16">
-        <v>1.18</v>
+        <v>12</v>
       </c>
       <c r="AW16">
-        <v>1.18</v>
+        <v>5.9</v>
       </c>
       <c r="AX16">
-        <v>1.18</v>
+        <v>17</v>
       </c>
       <c r="AY16">
-        <v>1.18</v>
+        <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>1.18</v>
+        <v>12.5</v>
       </c>
       <c r="BA16">
-        <v>1.14</v>
+        <v>21</v>
       </c>
       <c r="BB16">
-        <v>1.15</v>
+        <v>6</v>
       </c>
       <c r="BC16">
-        <v>1.18</v>
+        <v>18.5</v>
       </c>
       <c r="BD16">
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>1.18</v>
+        <v>6.4</v>
       </c>
       <c r="BF16">
-        <v>1.18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG16">
-        <v>1.18</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK16">
         <v>5.4</v>
@@ -4550,46 +4550,46 @@
         <v>21</v>
       </c>
       <c r="BN16">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BP16">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BQ16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BS16">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BT16">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
         <v>12</v>
       </c>
       <c r="BX16">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BY16">
         <v>15</v>
       </c>
       <c r="BZ16">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CA16">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB16" t="s">
         <v>124</v>
@@ -4612,7 +4612,7 @@
         <v>123</v>
       </c>
       <c r="F17">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G17">
         <v>2.12</v>
@@ -4621,157 +4621,157 @@
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
         <v>4.3</v>
       </c>
       <c r="L17">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q17">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R17">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="S17">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U17">
         <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.89</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>17</v>
+      </c>
+      <c r="AE17">
+        <v>38</v>
+      </c>
+      <c r="AF17">
+        <v>16.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>16</v>
+      </c>
+      <c r="AI17">
+        <v>40</v>
+      </c>
+      <c r="AJ17">
+        <v>29</v>
+      </c>
+      <c r="AK17">
+        <v>20</v>
+      </c>
+      <c r="AL17">
+        <v>32</v>
+      </c>
+      <c r="AM17">
+        <v>70</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
+        <v>29</v>
+      </c>
+      <c r="AP17">
+        <v>20</v>
+      </c>
+      <c r="AQ17">
+        <v>5.1</v>
+      </c>
+      <c r="AR17">
+        <v>5.6</v>
+      </c>
+      <c r="AS17">
+        <v>6</v>
+      </c>
+      <c r="AT17">
         <v>11</v>
       </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.1</v>
-      </c>
-      <c r="AQ17">
-        <v>1.1</v>
-      </c>
-      <c r="AR17">
-        <v>1.1</v>
-      </c>
-      <c r="AS17">
-        <v>1.1</v>
-      </c>
-      <c r="AT17">
-        <v>1.1</v>
-      </c>
       <c r="AU17">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AV17">
-        <v>1.1</v>
+        <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX17">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="AY17">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="BA17">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB17">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="BC17">
-        <v>1.1</v>
+        <v>16</v>
       </c>
       <c r="BD17">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE17">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF17">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="BG17">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -4813,7 +4813,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV17">
         <v>34</v>
@@ -4822,7 +4822,7 @@
         <v>15.5</v>
       </c>
       <c r="BX17">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BY17">
         <v>18.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 02:53:07</t>
+    <t>2026-07-21 05:00:08</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1000,7 @@
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -1012,16 +1012,16 @@
         <v>1.45</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R2">
         <v>1.21</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
         <v>2.1</v>
@@ -1036,7 +1036,7 @@
         <v>1.18</v>
       </c>
       <c r="X2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2">
         <v>7</v>
@@ -1048,10 +1048,10 @@
         <v>21</v>
       </c>
       <c r="AB2">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>13</v>
@@ -1072,7 +1072,7 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK2">
         <v>130</v>
@@ -1087,7 +1087,7 @@
         <v>200</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2">
         <v>8.6</v>
@@ -1114,7 +1114,7 @@
         <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY2">
         <v>19.5</v>
@@ -1123,85 +1123,85 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>42</v>
+        <v>6.2</v>
       </c>
       <c r="BB2">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD2">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF2">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>2.86</v>
+        <v>3.65</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1224,7 +1224,7 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G3">
         <v>2.02</v>
@@ -1236,7 +1236,7 @@
         <v>4.2</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K3">
         <v>4.1</v>
@@ -1248,7 +1248,7 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
         <v>1.25</v>
@@ -1260,7 +1260,7 @@
         <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
         <v>2.88</v>
@@ -1269,16 +1269,16 @@
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
         <v>1.98</v>
       </c>
       <c r="X3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y3">
         <v>18</v>
@@ -1287,28 +1287,28 @@
         <v>32</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>12</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
         <v>46</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
         <v>48</v>
@@ -1317,73 +1317,73 @@
         <v>24</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AM3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>11.5</v>
       </c>
       <c r="AO3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AR3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AS3">
+        <v>55</v>
+      </c>
+      <c r="AT3">
+        <v>10.5</v>
+      </c>
+      <c r="AU3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV3">
+        <v>15</v>
+      </c>
+      <c r="AW3">
+        <v>38</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
         <v>9.6</v>
       </c>
-      <c r="AT3">
-        <v>9.6</v>
-      </c>
-      <c r="AU3">
-        <v>7.8</v>
-      </c>
-      <c r="AV3">
+      <c r="AZ3">
         <v>14.5</v>
       </c>
-      <c r="AW3">
-        <v>32</v>
-      </c>
-      <c r="AX3">
-        <v>11</v>
-      </c>
-      <c r="AY3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3">
-        <v>14</v>
-      </c>
       <c r="BA3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE3">
-        <v>9.6</v>
+        <v>48</v>
       </c>
       <c r="BF3">
         <v>10</v>
       </c>
       <c r="BG3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>4.1</v>
@@ -1407,7 +1407,7 @@
         <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP3">
         <v>14</v>
@@ -1469,7 +1469,7 @@
         <v>2.04</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -1505,7 +1505,7 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
         <v>2.02</v>
@@ -1568,7 +1568,7 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO4">
         <v>110</v>
@@ -1580,10 +1580,10 @@
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1595,7 +1595,7 @@
         <v>15</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1711,28 +1711,28 @@
         <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I5">
         <v>3.75</v>
       </c>
       <c r="J5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.37</v>
@@ -1744,7 +1744,7 @@
         <v>2.08</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
         <v>3.85</v>
@@ -1759,7 +1759,7 @@
         <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X5">
         <v>14.5</v>
@@ -1825,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1837,7 +1837,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1858,76 +1858,76 @@
         <v>19</v>
       </c>
       <c r="BD5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF5">
         <v>17</v>
       </c>
       <c r="BG5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>1.87</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.65</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.87</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
-        <v>1.74</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
+        <v>34</v>
+      </c>
+      <c r="BS5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT5">
+        <v>7</v>
+      </c>
+      <c r="BU5">
+        <v>5.7</v>
+      </c>
+      <c r="BV5">
+        <v>32</v>
+      </c>
+      <c r="BW5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX5">
         <v>46</v>
       </c>
-      <c r="BS5">
-        <v>1.8</v>
-      </c>
-      <c r="BT5">
-        <v>9</v>
-      </c>
-      <c r="BU5">
-        <v>4.5</v>
-      </c>
-      <c r="BV5">
-        <v>40</v>
-      </c>
-      <c r="BW5">
-        <v>1.79</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
       <c r="BY5">
-        <v>1.81</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="CA5">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>124</v>
@@ -1950,10 +1950,10 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H6">
         <v>1.49</v>
@@ -1962,7 +1962,7 @@
         <v>1.52</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
         <v>4.8</v>
@@ -1974,7 +1974,7 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1998,7 +1998,7 @@
         <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="W6">
         <v>1.12</v>
@@ -2082,7 +2082,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="AY6">
         <v>27</v>
@@ -2157,7 +2157,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BW6">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX6">
         <v>27</v>
@@ -2192,40 +2192,40 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="G7">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="H7">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <v>1.33</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
         <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
         <v>1.31</v>
@@ -2234,124 +2234,124 @@
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>1.87</v>
+        <v>2.18</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AB7">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>23</v>
       </c>
       <c r="AI7">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AN7">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR7">
-        <v>26</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AT7">
+        <v>7</v>
+      </c>
+      <c r="AU7">
+        <v>7.2</v>
+      </c>
+      <c r="AV7">
+        <v>17.5</v>
+      </c>
+      <c r="AW7">
+        <v>7.2</v>
+      </c>
+      <c r="AX7">
+        <v>9</v>
+      </c>
+      <c r="AY7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>17.5</v>
+      </c>
+      <c r="BA7">
         <v>7.4</v>
       </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>15</v>
-      </c>
-      <c r="AW7">
-        <v>7.8</v>
-      </c>
-      <c r="AX7">
-        <v>10</v>
-      </c>
-      <c r="AY7">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7">
-        <v>16.5</v>
-      </c>
-      <c r="BA7">
-        <v>7.8</v>
-      </c>
       <c r="BB7">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BC7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>3.9</v>
@@ -2482,7 +2482,7 @@
         <v>2.66</v>
       </c>
       <c r="V8">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W8">
         <v>1.38</v>
@@ -2524,10 +2524,10 @@
         <v>26</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL8">
         <v>36</v>
@@ -2542,7 +2542,7 @@
         <v>9.6</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2563,10 +2563,10 @@
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY8">
         <v>14</v>
@@ -2587,7 +2587,7 @@
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF8">
         <v>20</v>
@@ -2635,25 +2635,25 @@
         <v>5.6</v>
       </c>
       <c r="BU8">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BZ8">
         <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>124</v>
@@ -2679,7 +2679,7 @@
         <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H9">
         <v>4.5</v>
@@ -2715,7 +2715,7 @@
         <v>1.44</v>
       </c>
       <c r="S9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
         <v>1.75</v>
@@ -2790,7 +2790,7 @@
         <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AS9">
         <v>7.8</v>
@@ -2835,7 +2835,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG9">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2918,10 +2918,10 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -2939,7 +2939,7 @@
         <v>1.32</v>
       </c>
       <c r="M10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -2963,13 +2963,13 @@
         <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X10">
         <v>27</v>
@@ -3038,7 +3038,7 @@
         <v>6.6</v>
       </c>
       <c r="AT10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
@@ -3163,19 +3163,19 @@
         <v>1.46</v>
       </c>
       <c r="G11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H11">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I11">
-        <v>870</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="K11">
-        <v>500</v>
+        <v>5.6</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3190,16 +3190,16 @@
         <v>1.15</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q11">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R11">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S11">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3208,67 +3208,67 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
         <v>1.03</v>
@@ -3280,46 +3280,46 @@
         <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AW11">
         <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA11">
         <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE11">
         <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3423,7 +3423,7 @@
         <v>1.23</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
         <v>7.2</v>
@@ -3615,7 +3615,7 @@
         <v>34</v>
       </c>
       <c r="BY12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ12">
         <v>17</v>
@@ -3653,7 +3653,7 @@
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J13">
         <v>3.85</v>
@@ -3686,13 +3686,13 @@
         <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U13">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3812,7 +3812,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK13">
         <v>5.6</v>
@@ -3839,7 +3839,7 @@
         <v>48</v>
       </c>
       <c r="BS13">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BT13">
         <v>7.4</v>
@@ -3848,16 +3848,16 @@
         <v>3.55</v>
       </c>
       <c r="BV13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW13">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ13">
         <v>26</v>
@@ -3886,22 +3886,22 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H14">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L14">
         <v>1.21</v>
@@ -3910,103 +3910,103 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="T14">
         <v>1.51</v>
       </c>
       <c r="U14">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="V14">
         <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="X14">
         <v>55</v>
       </c>
       <c r="Y14">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="Z14">
-        <v>70</v>
+        <v>590</v>
       </c>
       <c r="AA14">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC14">
+        <v>14</v>
+      </c>
+      <c r="AD14">
+        <v>28</v>
+      </c>
+      <c r="AE14">
+        <v>360</v>
+      </c>
+      <c r="AF14">
         <v>17</v>
       </c>
-      <c r="AD14">
-        <v>29</v>
-      </c>
-      <c r="AE14">
-        <v>70</v>
-      </c>
-      <c r="AF14">
-        <v>17.5</v>
-      </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI14">
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK14">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM14">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AN14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO14">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AP14">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="AQ14">
-        <v>4.8</v>
+        <v>22</v>
       </c>
       <c r="AR14">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AS14">
-        <v>5.2</v>
+        <v>42</v>
       </c>
       <c r="AT14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU14">
         <v>11.5</v>
@@ -4015,19 +4015,19 @@
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="AX14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>14.5</v>
       </c>
       <c r="BA14">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="BB14">
         <v>15</v>
@@ -4039,13 +4039,13 @@
         <v>18.5</v>
       </c>
       <c r="BE14">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="BF14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG14">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
         <v>121</v>
       </c>
       <c r="F15">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G15">
         <v>1.78</v>
@@ -4143,7 +4143,7 @@
         <v>4.3</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.29</v>
@@ -4155,7 +4155,7 @@
         <v>5.7</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
         <v>2.58</v>
@@ -4170,10 +4170,10 @@
         <v>2.48</v>
       </c>
       <c r="T15">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
         <v>1.25</v>
@@ -4370,10 +4370,10 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H16">
         <v>2.86</v>
@@ -4382,7 +4382,7 @@
         <v>2.92</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16">
         <v>4.2</v>
@@ -4397,7 +4397,7 @@
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
         <v>2.8</v>
@@ -4412,7 +4412,7 @@
         <v>2.28</v>
       </c>
       <c r="T16">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="U16">
         <v>2.76</v>
@@ -4553,7 +4553,7 @@
         <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP16">
         <v>16.5</v>
@@ -4615,7 +4615,7 @@
         <v>2.04</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H17">
         <v>3.55</v>
@@ -4624,7 +4624,7 @@
         <v>3.8</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -4657,13 +4657,13 @@
         <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X17">
         <v>28</v>
@@ -4723,10 +4723,10 @@
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS17">
         <v>6</v>
@@ -4753,7 +4753,7 @@
         <v>13</v>
       </c>
       <c r="BA17">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB17">
         <v>20</v>
@@ -4762,10 +4762,10 @@
         <v>16</v>
       </c>
       <c r="BD17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF17">
         <v>7.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 05:00:08</t>
+    <t>2026-07-21 07:07:08</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
         <v>1.75</v>
       </c>
       <c r="I2">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J2">
         <v>3.25</v>
@@ -1000,7 +1000,7 @@
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
         <v>1.1</v>
@@ -1018,7 +1018,7 @@
         <v>2.32</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
         <v>4.6</v>
@@ -1057,7 +1057,7 @@
         <v>13</v>
       </c>
       <c r="AE2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AF2">
         <v>46</v>
@@ -1123,10 +1123,10 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC2">
         <v>6.8</v>
@@ -1138,7 +1138,7 @@
         <v>7</v>
       </c>
       <c r="BF2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
@@ -1260,7 +1260,7 @@
         <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
         <v>2.88</v>
@@ -1269,7 +1269,7 @@
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
         <v>1.31</v>
@@ -1413,13 +1413,13 @@
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
@@ -1428,22 +1428,22 @@
         <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BX3">
         <v>38</v>
       </c>
       <c r="BY3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1469,7 +1469,7 @@
         <v>2.04</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -1478,13 +1478,13 @@
         <v>4.4</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1496,16 +1496,16 @@
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
         <v>2.02</v>
@@ -1571,16 +1571,16 @@
         <v>22</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS4">
         <v>12.5</v>
@@ -1619,7 +1619,7 @@
         <v>40</v>
       </c>
       <c r="BE4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF4">
         <v>15</v>
@@ -1628,64 +1628,64 @@
         <v>12</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>1.76</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.58</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.76</v>
+        <v>17</v>
       </c>
       <c r="BN4">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>1.63</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>1.7</v>
+        <v>12</v>
       </c>
       <c r="BT4">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.7</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>1.72</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>1.7</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>124</v>
@@ -1735,10 +1735,10 @@
         <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
         <v>2.08</v>
@@ -1774,7 +1774,7 @@
         <v>75</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT5">
         <v>8.199999999999999</v>
@@ -1837,7 +1837,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AX5">
         <v>12</v>
@@ -1849,31 +1849,31 @@
         <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC5">
         <v>19</v>
       </c>
       <c r="BD5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
         <v>17</v>
       </c>
       <c r="BG5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
@@ -1950,7 +1950,7 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>9</v>
@@ -1974,7 +1974,7 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1989,10 +1989,10 @@
         <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U6">
         <v>1.84</v>
@@ -2004,7 +2004,7 @@
         <v>1.12</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y6">
         <v>7.6</v>
@@ -2034,7 +2034,7 @@
         <v>36</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI6">
         <v>46</v>
@@ -2055,10 +2055,10 @@
         <v>200</v>
       </c>
       <c r="AO6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
         <v>7</v>
@@ -2073,7 +2073,7 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2094,19 +2094,19 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC6">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BE6">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF6">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
@@ -2121,34 +2121,34 @@
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BT6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BU6">
         <v>3.5</v>
@@ -2163,13 +2163,13 @@
         <v>27</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
         <v>17.5</v>
       </c>
       <c r="CA6">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>124</v>
@@ -2192,28 +2192,28 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="G7">
         <v>1.84</v>
       </c>
       <c r="H7">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
         <v>3.4</v>
@@ -2225,7 +2225,7 @@
         <v>1.81</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
         <v>1.31</v>
@@ -2240,91 +2240,91 @@
         <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
         <v>2.18</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y7">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA7">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE7">
+        <v>95</v>
+      </c>
+      <c r="AF7">
+        <v>13.5</v>
+      </c>
+      <c r="AG7">
+        <v>11.5</v>
+      </c>
+      <c r="AH7">
+        <v>21</v>
+      </c>
+      <c r="AI7">
         <v>100</v>
       </c>
-      <c r="AF7">
-        <v>11</v>
-      </c>
-      <c r="AG7">
-        <v>10.5</v>
-      </c>
-      <c r="AH7">
-        <v>23</v>
-      </c>
-      <c r="AI7">
-        <v>110</v>
-      </c>
       <c r="AJ7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN7">
         <v>14</v>
       </c>
       <c r="AO7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AR7">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="AS7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU7">
         <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
         <v>8.800000000000001</v>
@@ -2333,7 +2333,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2345,25 +2345,25 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH7">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2372,46 +2372,46 @@
         <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="CB7" t="s">
         <v>124</v>
@@ -2434,7 +2434,7 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
         <v>3.65</v>
@@ -2443,7 +2443,7 @@
         <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J8">
         <v>4.2</v>
@@ -2455,19 +2455,19 @@
         <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
         <v>1.67</v>
@@ -2503,7 +2503,7 @@
         <v>21</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2512,37 +2512,37 @@
         <v>18.5</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ8">
         <v>70</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM8">
         <v>55</v>
       </c>
       <c r="AN8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2557,7 +2557,7 @@
         <v>18</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2688,13 +2688,13 @@
         <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9">
         <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
         <v>1.06</v>
@@ -2712,7 +2712,7 @@
         <v>1.83</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>3.1</v>
@@ -2838,16 +2838,16 @@
         <v>42</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2856,46 +2856,46 @@
         <v>21</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BQ9">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BR9">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BT9">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
+        <v>32</v>
+      </c>
+      <c r="BZ9">
         <v>21</v>
       </c>
-      <c r="BZ9">
-        <v>29</v>
-      </c>
       <c r="CA9">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="CB9" t="s">
         <v>124</v>
@@ -2921,13 +2921,13 @@
         <v>1.51</v>
       </c>
       <c r="G10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
         <v>7</v>
       </c>
       <c r="I10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -2942,7 +2942,7 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
         <v>1.23</v>
@@ -2960,7 +2960,7 @@
         <v>2.74</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U10">
         <v>2.08</v>
@@ -2969,7 +2969,7 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X10">
         <v>27</v>
@@ -3011,7 +3011,7 @@
         <v>16.5</v>
       </c>
       <c r="AK10">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL10">
         <v>36</v>
@@ -3029,13 +3029,13 @@
         <v>19.5</v>
       </c>
       <c r="AQ10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AR10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS10">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT10">
         <v>8.800000000000001</v>
@@ -3044,10 +3044,10 @@
         <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX10">
         <v>9</v>
@@ -3059,7 +3059,7 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10">
         <v>11.5</v>
@@ -3068,76 +3068,76 @@
         <v>13</v>
       </c>
       <c r="BD10">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF10">
         <v>6</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>124</v>
@@ -3163,7 +3163,7 @@
         <v>1.46</v>
       </c>
       <c r="G11">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H11">
         <v>6.2</v>
@@ -3178,16 +3178,16 @@
         <v>5.6</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P11">
         <v>2.48</v>
@@ -3202,16 +3202,16 @@
         <v>2.32</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X11">
         <v>32</v>
@@ -3322,16 +3322,16 @@
         <v>55</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI11">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3340,46 +3340,46 @@
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO11">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3405,16 +3405,16 @@
         <v>2.14</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.4</v>
@@ -3423,13 +3423,13 @@
         <v>1.23</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>7.2</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
         <v>3.1</v>
@@ -3441,19 +3441,19 @@
         <v>1.86</v>
       </c>
       <c r="S12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U12">
         <v>2.98</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3510,7 +3510,7 @@
         <v>16.5</v>
       </c>
       <c r="AP12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3558,7 +3558,7 @@
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG12">
         <v>13.5</v>
@@ -3591,7 +3591,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR12">
         <v>28</v>
@@ -3603,7 +3603,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
         <v>29</v>
@@ -3621,7 +3621,7 @@
         <v>17</v>
       </c>
       <c r="CA12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3644,7 +3644,7 @@
         <v>119</v>
       </c>
       <c r="F13">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G13">
         <v>3.7</v>
@@ -3656,7 +3656,7 @@
         <v>2.18</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -3707,7 +3707,7 @@
         <v>15.5</v>
       </c>
       <c r="AA13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB13">
         <v>21</v>
@@ -3749,7 +3749,7 @@
         <v>29</v>
       </c>
       <c r="AO13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP13">
         <v>17</v>
@@ -3785,19 +3785,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC13">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BE13">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13">
         <v>21</v>
@@ -3806,16 +3806,16 @@
         <v>10</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
@@ -3824,46 +3824,46 @@
         <v>21</v>
       </c>
       <c r="BN13">
+        <v>7.2</v>
+      </c>
+      <c r="BO13">
+        <v>5.3</v>
+      </c>
+      <c r="BP13">
+        <v>26</v>
+      </c>
+      <c r="BQ13">
+        <v>22</v>
+      </c>
+      <c r="BR13">
+        <v>32</v>
+      </c>
+      <c r="BS13">
+        <v>22</v>
+      </c>
+      <c r="BT13">
+        <v>5.3</v>
+      </c>
+      <c r="BU13">
+        <v>4.1</v>
+      </c>
+      <c r="BV13">
+        <v>14.5</v>
+      </c>
+      <c r="BW13">
         <v>10</v>
       </c>
-      <c r="BO13">
-        <v>4.5</v>
-      </c>
-      <c r="BP13">
-        <v>36</v>
-      </c>
-      <c r="BQ13">
-        <v>15</v>
-      </c>
-      <c r="BR13">
-        <v>48</v>
-      </c>
-      <c r="BS13">
-        <v>18.5</v>
-      </c>
-      <c r="BT13">
-        <v>7.4</v>
-      </c>
-      <c r="BU13">
-        <v>3.55</v>
-      </c>
-      <c r="BV13">
-        <v>20</v>
-      </c>
-      <c r="BW13">
-        <v>8.4</v>
-      </c>
       <c r="BX13">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BY13">
         <v>14</v>
       </c>
       <c r="BZ13">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="CA13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3919,7 +3919,7 @@
         <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R14">
         <v>2</v>
@@ -3928,16 +3928,16 @@
         <v>1.94</v>
       </c>
       <c r="T14">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U14">
         <v>2.76</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W14">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X14">
         <v>55</v>
@@ -3946,22 +3946,22 @@
         <v>75</v>
       </c>
       <c r="Z14">
-        <v>590</v>
+        <v>500</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD14">
         <v>28</v>
       </c>
       <c r="AE14">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AF14">
         <v>17</v>
@@ -3979,10 +3979,10 @@
         <v>20</v>
       </c>
       <c r="AK14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AM14">
         <v>230</v>
@@ -3994,7 +3994,7 @@
         <v>80</v>
       </c>
       <c r="AP14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ14">
         <v>22</v>
@@ -4015,7 +4015,7 @@
         <v>20</v>
       </c>
       <c r="AW14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX14">
         <v>13</v>
@@ -4036,7 +4036,7 @@
         <v>12</v>
       </c>
       <c r="BD14">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BE14">
         <v>27</v>
@@ -4048,64 +4048,64 @@
         <v>23</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BJ14">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="BN14">
+        <v>5.2</v>
+      </c>
+      <c r="BO14">
+        <v>4.3</v>
+      </c>
+      <c r="BP14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BQ14">
         <v>7</v>
       </c>
-      <c r="BO14">
-        <v>3.35</v>
-      </c>
-      <c r="BP14">
-        <v>13.5</v>
-      </c>
-      <c r="BQ14">
-        <v>5.9</v>
-      </c>
       <c r="BR14">
+        <v>17.5</v>
+      </c>
+      <c r="BS14">
+        <v>12</v>
+      </c>
+      <c r="BT14">
+        <v>10.5</v>
+      </c>
+      <c r="BU14">
+        <v>7.2</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
         <v>25</v>
       </c>
-      <c r="BS14">
-        <v>10</v>
-      </c>
-      <c r="BT14">
-        <v>14.5</v>
-      </c>
-      <c r="BU14">
-        <v>6.2</v>
-      </c>
-      <c r="BV14">
-        <v>50</v>
-      </c>
-      <c r="BW14">
-        <v>21</v>
-      </c>
       <c r="BX14">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BY14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BZ14">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA14">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>
@@ -4131,16 +4131,16 @@
         <v>1.75</v>
       </c>
       <c r="G15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15">
         <v>4.5</v>
@@ -4158,28 +4158,28 @@
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
         <v>1.59</v>
       </c>
       <c r="R15">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S15">
         <v>2.48</v>
       </c>
       <c r="T15">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V15">
         <v>1.25</v>
       </c>
       <c r="W15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X15">
         <v>29</v>
@@ -4233,7 +4233,7 @@
         <v>7.8</v>
       </c>
       <c r="AO15">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP15">
         <v>21</v>
@@ -4290,16 +4290,16 @@
         <v>7.2</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BJ15">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4308,46 +4308,46 @@
         <v>21</v>
       </c>
       <c r="BN15">
+        <v>5.1</v>
+      </c>
+      <c r="BO15">
+        <v>4.2</v>
+      </c>
+      <c r="BP15">
+        <v>12</v>
+      </c>
+      <c r="BQ15">
+        <v>8.6</v>
+      </c>
+      <c r="BR15">
+        <v>22</v>
+      </c>
+      <c r="BS15">
+        <v>15.5</v>
+      </c>
+      <c r="BT15">
+        <v>8.6</v>
+      </c>
+      <c r="BU15">
         <v>6.4</v>
       </c>
-      <c r="BO15">
-        <v>3.4</v>
-      </c>
-      <c r="BP15">
-        <v>15.5</v>
-      </c>
-      <c r="BQ15">
-        <v>7.2</v>
-      </c>
-      <c r="BR15">
-        <v>29</v>
-      </c>
-      <c r="BS15">
-        <v>13</v>
-      </c>
-      <c r="BT15">
-        <v>11.5</v>
-      </c>
-      <c r="BU15">
-        <v>5.4</v>
-      </c>
       <c r="BV15">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BW15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BX15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BZ15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CA15">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4370,19 +4370,19 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G16">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
         <v>2.92</v>
       </c>
       <c r="J16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
         <v>4.2</v>
@@ -4400,7 +4400,7 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
@@ -4409,7 +4409,7 @@
         <v>1.73</v>
       </c>
       <c r="S16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T16">
         <v>1.49</v>
@@ -4421,7 +4421,7 @@
         <v>1.52</v>
       </c>
       <c r="W16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4430,7 +4430,7 @@
         <v>21</v>
       </c>
       <c r="Z16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA16">
         <v>50</v>
@@ -4463,7 +4463,7 @@
         <v>42</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL16">
         <v>34</v>
@@ -4478,7 +4478,7 @@
         <v>16.5</v>
       </c>
       <c r="AP16">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,7 +4487,7 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT16">
         <v>15.5</v>
@@ -4499,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX16">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="BB16">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
@@ -4523,7 +4523,7 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF16">
         <v>9.800000000000001</v>
@@ -4574,7 +4574,7 @@
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW16">
         <v>12</v>
@@ -4589,7 +4589,7 @@
         <v>15</v>
       </c>
       <c r="CA16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB16" t="s">
         <v>124</v>
@@ -4624,7 +4624,7 @@
         <v>3.8</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
         <v>4.3</v>
@@ -4642,7 +4642,7 @@
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q17">
         <v>1.6</v>
@@ -4651,7 +4651,7 @@
         <v>1.61</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
         <v>1.57</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 07:07:08</t>
+    <t>2026-07-21 09:14:34</t>
   </si>
 </sst>
 </file>
@@ -985,49 +985,49 @@
         <v>5.3</v>
       </c>
       <c r="G2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I2">
         <v>1.88</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="O2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q2">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
         <v>1.22</v>
       </c>
       <c r="S2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
         <v>2.12</v>
@@ -1036,10 +1036,10 @@
         <v>1.18</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z2">
         <v>10.5</v>
@@ -1054,7 +1054,7 @@
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE2">
         <v>25</v>
@@ -1063,7 +1063,7 @@
         <v>46</v>
       </c>
       <c r="AG2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AH2">
         <v>32</v>
@@ -1090,7 +1090,7 @@
         <v>20</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ2">
         <v>5.8</v>
@@ -1099,10 +1099,10 @@
         <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>17</v>
+        <v>5.5</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
@@ -1111,49 +1111,49 @@
         <v>9</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY2">
-        <v>19.5</v>
+        <v>5.7</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="BA2">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BB2">
+        <v>7.2</v>
+      </c>
+      <c r="BC2">
         <v>7</v>
       </c>
-      <c r="BC2">
-        <v>6.8</v>
-      </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1162,16 +1162,16 @@
         <v>21</v>
       </c>
       <c r="BN2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO2">
         <v>6.6</v>
       </c>
       <c r="BP2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1180,7 +1180,7 @@
         <v>50</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU2">
         <v>3.65</v>
@@ -1192,16 +1192,16 @@
         <v>10</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY2">
         <v>25</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1224,10 +1224,10 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1257,25 +1257,25 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T3">
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
         <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1317,7 +1317,7 @@
         <v>24</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL3">
         <v>30</v>
@@ -1326,7 +1326,7 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO3">
         <v>38</v>
@@ -1371,7 +1371,7 @@
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
         <v>27</v>
@@ -1407,7 +1407,7 @@
         <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
         <v>14</v>
@@ -1425,7 +1425,7 @@
         <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV3">
         <v>32</v>
@@ -1440,10 +1440,10 @@
         <v>27</v>
       </c>
       <c r="BZ3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1466,13 +1466,13 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
         <v>4.4</v>
@@ -1481,7 +1481,7 @@
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.49</v>
@@ -1490,58 +1490,58 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
         <v>2.02</v>
       </c>
       <c r="U4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y4">
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA4">
         <v>120</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF4">
         <v>12</v>
@@ -1568,7 +1568,7 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4">
         <v>100</v>
@@ -1580,16 +1580,16 @@
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>15</v>
@@ -1607,7 +1607,7 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB4">
         <v>19</v>
@@ -1619,31 +1619,31 @@
         <v>40</v>
       </c>
       <c r="BE4">
+        <v>13.5</v>
+      </c>
+      <c r="BF4">
+        <v>18</v>
+      </c>
+      <c r="BG4">
         <v>13</v>
-      </c>
-      <c r="BF4">
-        <v>15</v>
-      </c>
-      <c r="BG4">
-        <v>12</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1655,13 +1655,13 @@
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
@@ -1673,19 +1673,19 @@
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
         <v>34</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>124</v>
@@ -1708,16 +1708,16 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H5">
         <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J5">
         <v>3.45</v>
@@ -1732,40 +1732,40 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z5">
         <v>28</v>
@@ -1774,7 +1774,7 @@
         <v>75</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1786,13 +1786,13 @@
         <v>50</v>
       </c>
       <c r="AF5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -1801,73 +1801,73 @@
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR5">
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW5">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BB5">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BC5">
         <v>19</v>
       </c>
       <c r="BD5">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1953,19 +1953,19 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
         <v>1.52</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.38</v>
@@ -1974,7 +1974,7 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1992,16 +1992,16 @@
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
         <v>2.92</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>16</v>
@@ -2013,22 +2013,22 @@
         <v>8.6</v>
       </c>
       <c r="AA6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AB6">
         <v>30</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AG6">
         <v>36</v>
@@ -2040,10 +2040,10 @@
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AK6">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL6">
         <v>130</v>
@@ -2052,7 +2052,7 @@
         <v>180</v>
       </c>
       <c r="AN6">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AO6">
         <v>8</v>
@@ -2061,7 +2061,7 @@
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
         <v>7.6</v>
@@ -2073,7 +2073,7 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2094,22 +2094,22 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC6">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD6">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BF6">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
         <v>3.55</v>
@@ -2198,16 +2198,16 @@
         <v>1.84</v>
       </c>
       <c r="H7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>5.3</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L7">
         <v>1.41</v>
@@ -2222,7 +2222,7 @@
         <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
@@ -2234,10 +2234,10 @@
         <v>3.6</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
         <v>1.23</v>
@@ -2255,7 +2255,7 @@
         <v>40</v>
       </c>
       <c r="AA7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7">
         <v>8.800000000000001</v>
@@ -2270,7 +2270,7 @@
         <v>95</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG7">
         <v>11.5</v>
@@ -2279,7 +2279,7 @@
         <v>21</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
         <v>22</v>
@@ -2297,7 +2297,7 @@
         <v>14</v>
       </c>
       <c r="AO7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP7">
         <v>10.5</v>
@@ -2309,7 +2309,7 @@
         <v>25</v>
       </c>
       <c r="AS7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
@@ -2321,7 +2321,7 @@
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX7">
         <v>9.4</v>
@@ -2333,7 +2333,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2345,13 +2345,13 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF7">
         <v>12</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
@@ -2363,7 +2363,7 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2375,13 +2375,13 @@
         <v>4.5</v>
       </c>
       <c r="BO7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BR7">
         <v>32</v>
@@ -2390,13 +2390,13 @@
         <v>21</v>
       </c>
       <c r="BT7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW7">
         <v>32</v>
@@ -2405,7 +2405,7 @@
         <v>60</v>
       </c>
       <c r="BY7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BZ7">
         <v>27</v>
@@ -2434,13 +2434,13 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
         <v>2.08</v>
@@ -2455,7 +2455,7 @@
         <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.9</v>
@@ -2464,28 +2464,28 @@
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="S8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T8">
         <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X8">
         <v>26</v>
@@ -2497,10 +2497,10 @@
         <v>16.5</v>
       </c>
       <c r="AA8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC8">
         <v>9.800000000000001</v>
@@ -2515,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="AG8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
@@ -2527,10 +2527,10 @@
         <v>70</v>
       </c>
       <c r="AK8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2539,7 +2539,7 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP8">
         <v>22</v>
@@ -2551,7 +2551,7 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT8">
         <v>18</v>
@@ -2587,19 +2587,19 @@
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF8">
         <v>20</v>
       </c>
       <c r="BG8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ8">
         <v>9</v>
@@ -2617,7 +2617,7 @@
         <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BP8">
         <v>25</v>
@@ -2641,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX8">
         <v>22</v>
@@ -2650,7 +2650,7 @@
         <v>15</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA8">
         <v>10.5</v>
@@ -2676,10 +2676,10 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H9">
         <v>4.5</v>
@@ -2712,25 +2712,25 @@
         <v>1.83</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
         <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
         <v>2.18</v>
       </c>
       <c r="V9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>2.12</v>
       </c>
       <c r="X9">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y9">
         <v>19</v>
@@ -2745,7 +2745,7 @@
         <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD9">
         <v>19.5</v>
@@ -2754,10 +2754,10 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9">
         <v>19</v>
@@ -2778,13 +2778,13 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO9">
         <v>70</v>
       </c>
       <c r="AP9">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
         <v>15.5</v>
@@ -2793,10 +2793,10 @@
         <v>30</v>
       </c>
       <c r="AS9">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -2805,7 +2805,7 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2814,25 +2814,25 @@
         <v>9</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB9">
         <v>17</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD9">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE9">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG9">
         <v>42</v>
@@ -2918,10 +2918,10 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -2930,7 +2930,7 @@
         <v>7.6</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -2945,139 +2945,139 @@
         <v>5.1</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T10">
         <v>1.83</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V10">
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="X10">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z10">
         <v>65</v>
       </c>
       <c r="AA10">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AE10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
       </c>
       <c r="AH10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL10">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
         <v>19.5</v>
       </c>
       <c r="AQ10">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AR10">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="AT10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AW10">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AX10">
         <v>9</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>6.8</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BE10">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="BF10">
         <v>6</v>
       </c>
       <c r="BG10">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="BH10">
         <v>4.3</v>
@@ -3101,10 +3101,10 @@
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10">
         <v>6.8</v>
@@ -3178,7 +3178,7 @@
         <v>5.6</v>
       </c>
       <c r="L11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M11">
         <v>1.01</v>
@@ -3187,22 +3187,22 @@
         <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P11">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R11">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S11">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U11">
         <v>2.14</v>
@@ -3214,7 +3214,7 @@
         <v>2.72</v>
       </c>
       <c r="X11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y11">
         <v>34</v>
@@ -3226,10 +3226,10 @@
         <v>200</v>
       </c>
       <c r="AB11">
+        <v>13</v>
+      </c>
+      <c r="AC11">
         <v>13.5</v>
-      </c>
-      <c r="AC11">
-        <v>14</v>
       </c>
       <c r="AD11">
         <v>30</v>
@@ -3238,7 +3238,7 @@
         <v>95</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3262,13 +3262,13 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
         <v>90</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
         <v>1.03</v>
@@ -3283,7 +3283,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV11">
         <v>19.5</v>
@@ -3322,7 +3322,7 @@
         <v>55</v>
       </c>
       <c r="BH11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI11">
         <v>3.6</v>
@@ -3352,10 +3352,10 @@
         <v>7</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BT11">
         <v>11</v>
@@ -3373,13 +3373,13 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BZ11">
         <v>13</v>
       </c>
       <c r="CA11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3402,16 +3402,16 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H12">
         <v>3.25</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J12">
         <v>4.2</v>
@@ -3432,28 +3432,28 @@
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q12">
         <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U12">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V12">
         <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3462,40 +3462,40 @@
         <v>25</v>
       </c>
       <c r="Z12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA12">
         <v>55</v>
       </c>
       <c r="AB12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC12">
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>21</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
         <v>30</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL12">
         <v>25</v>
@@ -3510,19 +3510,19 @@
         <v>16.5</v>
       </c>
       <c r="AP12">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ12">
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="AS12">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="AT12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU12">
         <v>9.800000000000001</v>
@@ -3531,7 +3531,7 @@
         <v>13</v>
       </c>
       <c r="AW12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12">
         <v>16.5</v>
@@ -3543,13 +3543,13 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12">
         <v>23</v>
       </c>
       <c r="BC12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
         <v>20</v>
@@ -3561,7 +3561,7 @@
         <v>7.4</v>
       </c>
       <c r="BG12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3644,19 +3644,19 @@
         <v>119</v>
       </c>
       <c r="F13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H13">
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -3668,7 +3668,7 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
         <v>1.24</v>
@@ -3686,13 +3686,13 @@
         <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U13">
         <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3704,16 +3704,16 @@
         <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AA13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB13">
         <v>21</v>
       </c>
       <c r="AC13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD13">
         <v>11</v>
@@ -3728,7 +3728,7 @@
         <v>15.5</v>
       </c>
       <c r="AH13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI13">
         <v>30</v>
@@ -3746,37 +3746,37 @@
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AO13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP13">
         <v>17</v>
       </c>
       <c r="AQ13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR13">
         <v>13</v>
       </c>
       <c r="AS13">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="AT13">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13">
         <v>18</v>
       </c>
       <c r="AX13">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY13">
         <v>13</v>
@@ -3785,19 +3785,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BB13">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC13">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BD13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BE13">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF13">
         <v>21</v>
@@ -3809,10 +3809,10 @@
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK13">
         <v>6.6</v>
@@ -3824,46 +3824,46 @@
         <v>21</v>
       </c>
       <c r="BN13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BV13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BW13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY13">
         <v>14</v>
       </c>
       <c r="BZ13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="CA13">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3898,7 +3898,7 @@
         <v>5.9</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K14">
         <v>5.5</v>
@@ -3916,28 +3916,28 @@
         <v>1.12</v>
       </c>
       <c r="P14">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q14">
         <v>1.38</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T14">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U14">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="V14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X14">
         <v>55</v>
@@ -3946,19 +3946,19 @@
         <v>75</v>
       </c>
       <c r="Z14">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AA14">
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC14">
         <v>13.5</v>
       </c>
       <c r="AD14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE14">
         <v>350</v>
@@ -3970,22 +3970,22 @@
         <v>11.5</v>
       </c>
       <c r="AH14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI14">
         <v>55</v>
       </c>
       <c r="AJ14">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AK14">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL14">
         <v>23</v>
       </c>
       <c r="AM14">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN14">
         <v>4.7</v>
@@ -4033,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="BC14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD14">
         <v>16</v>
@@ -4051,7 +4051,7 @@
         <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14">
         <v>9.199999999999999</v>
@@ -4069,7 +4069,7 @@
         <v>5.2</v>
       </c>
       <c r="BO14">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
         <v>9.800000000000001</v>
@@ -4105,7 +4105,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CA14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>
@@ -4131,16 +4131,16 @@
         <v>1.75</v>
       </c>
       <c r="G15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
         <v>5</v>
       </c>
       <c r="J15">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K15">
         <v>4.5</v>
@@ -4149,28 +4149,28 @@
         <v>1.29</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
         <v>5.7</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15">
         <v>2.6</v>
       </c>
       <c r="Q15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
         <v>1.64</v>
       </c>
       <c r="S15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T15">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U15">
         <v>2.52</v>
@@ -4182,10 +4182,10 @@
         <v>2.26</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z15">
         <v>46</v>
@@ -4200,16 +4200,16 @@
         <v>11</v>
       </c>
       <c r="AD15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE15">
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH15">
         <v>17</v>
@@ -4227,10 +4227,10 @@
         <v>27</v>
       </c>
       <c r="AM15">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN15">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO15">
         <v>42</v>
@@ -4242,13 +4242,13 @@
         <v>21</v>
       </c>
       <c r="AR15">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AS15">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU15">
         <v>9</v>
@@ -4257,37 +4257,37 @@
         <v>17</v>
       </c>
       <c r="AW15">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX15">
         <v>11</v>
       </c>
       <c r="AY15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15">
+        <v>14</v>
+      </c>
+      <c r="BA15">
         <v>9</v>
       </c>
-      <c r="AZ15">
-        <v>13.5</v>
-      </c>
-      <c r="BA15">
-        <v>7.4</v>
-      </c>
       <c r="BB15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD15">
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
         <v>6.8</v>
       </c>
       <c r="BG15">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH15">
         <v>4.6</v>
@@ -4311,7 +4311,7 @@
         <v>5.1</v>
       </c>
       <c r="BO15">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BP15">
         <v>12</v>
@@ -4326,7 +4326,7 @@
         <v>15.5</v>
       </c>
       <c r="BT15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU15">
         <v>6.4</v>
@@ -4338,7 +4338,7 @@
         <v>24</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15">
         <v>26</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="CA15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4370,13 +4370,13 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
         <v>2.52</v>
       </c>
       <c r="H16">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I16">
         <v>2.92</v>
@@ -4397,7 +4397,7 @@
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P16">
         <v>2.78</v>
@@ -4406,7 +4406,7 @@
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S16">
         <v>2.3</v>
@@ -4415,7 +4415,7 @@
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V16">
         <v>1.52</v>
@@ -4424,10 +4424,10 @@
         <v>1.66</v>
       </c>
       <c r="X16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z16">
         <v>26</v>
@@ -4442,19 +4442,19 @@
         <v>10.5</v>
       </c>
       <c r="AD16">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG16">
         <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI16">
         <v>32</v>
@@ -4466,7 +4466,7 @@
         <v>24</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -4475,10 +4475,10 @@
         <v>11.5</v>
       </c>
       <c r="AO16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP16">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,7 +4487,7 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT16">
         <v>15.5</v>
@@ -4499,10 +4499,10 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4514,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="BB16">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
@@ -4523,16 +4523,16 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BF16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG16">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI16">
         <v>3.75</v>
@@ -4562,7 +4562,7 @@
         <v>12</v>
       </c>
       <c r="BR16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS16">
         <v>17</v>
@@ -4574,10 +4574,10 @@
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BX16">
         <v>26</v>
@@ -4645,28 +4645,28 @@
         <v>2.54</v>
       </c>
       <c r="Q17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S17">
         <v>2.52</v>
       </c>
       <c r="T17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
         <v>1.92</v>
       </c>
       <c r="X17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y17">
         <v>21</v>
@@ -4678,22 +4678,22 @@
         <v>75</v>
       </c>
       <c r="AB17">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE17">
         <v>38</v>
       </c>
       <c r="AF17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH17">
         <v>16</v>
@@ -4702,19 +4702,19 @@
         <v>40</v>
       </c>
       <c r="AJ17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK17">
         <v>20</v>
       </c>
       <c r="AL17">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM17">
         <v>70</v>
       </c>
       <c r="AN17">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO17">
         <v>29</v>
@@ -4723,16 +4723,16 @@
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AR17">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS17">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU17">
         <v>8.6</v>
@@ -4741,34 +4741,34 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="AX17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BB17">
         <v>20</v>
       </c>
       <c r="BC17">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD17">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE17">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF17">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG17">
         <v>20</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 09:14:34</t>
+    <t>2026-07-21 11:21:35</t>
   </si>
 </sst>
 </file>
@@ -982,7 +982,7 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G2">
         <v>6.4</v>
@@ -991,55 +991,55 @@
         <v>1.76</v>
       </c>
       <c r="I2">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2">
+        <v>2.16</v>
+      </c>
+      <c r="U2">
+        <v>1.7</v>
+      </c>
+      <c r="V2">
         <v>2.08</v>
       </c>
-      <c r="U2">
-        <v>1.74</v>
-      </c>
-      <c r="V2">
-        <v>2.12</v>
-      </c>
       <c r="W2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z2">
         <v>10.5</v>
@@ -1048,22 +1048,22 @@
         <v>21</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF2">
         <v>46</v>
       </c>
       <c r="AG2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AH2">
         <v>32</v>
@@ -1075,7 +1075,7 @@
         <v>210</v>
       </c>
       <c r="AK2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL2">
         <v>130</v>
@@ -1084,103 +1084,103 @@
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AO2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AR2">
         <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT2">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AV2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AY2">
-        <v>5.7</v>
+        <v>19</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BB2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE2">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO2">
         <v>6.6</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ2">
-        <v>40</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>50</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
         <v>3.65</v>
@@ -1189,19 +1189,19 @@
         <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
+        <v>38</v>
+      </c>
+      <c r="BY2">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2">
         <v>36</v>
       </c>
-      <c r="BY2">
-        <v>25</v>
-      </c>
-      <c r="BZ2">
-        <v>34</v>
-      </c>
       <c r="CA2">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1224,7 +1224,7 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1239,7 +1239,7 @@
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1.34</v>
@@ -1263,13 +1263,13 @@
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T3">
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
         <v>1.31</v>
@@ -1287,7 +1287,7 @@
         <v>32</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB3">
         <v>12</v>
@@ -1296,7 +1296,7 @@
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE3">
         <v>46</v>
@@ -1314,7 +1314,7 @@
         <v>48</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK3">
         <v>19</v>
@@ -1371,7 +1371,7 @@
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD3">
         <v>27</v>
@@ -1395,55 +1395,55 @@
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="BN3">
         <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>15.5</v>
+        <v>7.2</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>38</v>
       </c>
       <c r="BY3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1484,28 +1484,28 @@
         <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
         <v>1.27</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
         <v>2.02</v>
@@ -1532,10 +1532,10 @@
         <v>120</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>17</v>
@@ -1571,7 +1571,7 @@
         <v>21</v>
       </c>
       <c r="AO4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
@@ -1580,10 +1580,10 @@
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1595,19 +1595,19 @@
         <v>15</v>
       </c>
       <c r="AW4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BB4">
         <v>19</v>
@@ -1619,19 +1619,19 @@
         <v>40</v>
       </c>
       <c r="BE4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
         <v>18</v>
       </c>
       <c r="BG4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -1708,7 +1708,7 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
         <v>2.36</v>
@@ -1717,7 +1717,7 @@
         <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J5">
         <v>3.45</v>
@@ -1726,22 +1726,22 @@
         <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R5">
         <v>1.33</v>
@@ -1750,31 +1750,31 @@
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
         <v>1.73</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>12.5</v>
       </c>
       <c r="Z5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA5">
         <v>75</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
         <v>8</v>
@@ -1783,16 +1783,16 @@
         <v>15</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG5">
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI5">
         <v>65</v>
@@ -1804,7 +1804,7 @@
         <v>28</v>
       </c>
       <c r="AL5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM5">
         <v>130</v>
@@ -1825,13 +1825,13 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5">
         <v>13</v>
@@ -1849,10 +1849,10 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC5">
         <v>19</v>
@@ -1861,73 +1861,73 @@
         <v>8.6</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BN5">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
         <v>18</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV5">
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>46</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
         <v>124</v>
@@ -1959,16 +1959,16 @@
         <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -1995,10 +1995,10 @@
         <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W6">
         <v>1.13</v>
@@ -2013,10 +2013,10 @@
         <v>8.6</v>
       </c>
       <c r="AA6">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AB6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2031,13 +2031,13 @@
         <v>70</v>
       </c>
       <c r="AG6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH6">
         <v>32</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6">
         <v>330</v>
@@ -2094,16 +2094,16 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF6">
         <v>12</v>
@@ -2151,7 +2151,7 @@
         <v>3.85</v>
       </c>
       <c r="BU6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
         <v>9.199999999999999</v>
@@ -2192,25 +2192,25 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M7">
         <v>1.08</v>
@@ -2237,13 +2237,13 @@
         <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>1.23</v>
       </c>
       <c r="W7">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X7">
         <v>13.5</v>
@@ -2252,7 +2252,7 @@
         <v>16</v>
       </c>
       <c r="Z7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA7">
         <v>150</v>
@@ -2264,10 +2264,10 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AF7">
         <v>13</v>
@@ -2282,7 +2282,7 @@
         <v>75</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
         <v>22</v>
@@ -2294,7 +2294,7 @@
         <v>150</v>
       </c>
       <c r="AN7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
         <v>110</v>
@@ -2309,7 +2309,7 @@
         <v>25</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7">
         <v>7.2</v>
@@ -2321,7 +2321,7 @@
         <v>16</v>
       </c>
       <c r="AW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7">
         <v>9.4</v>
@@ -2333,7 +2333,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB7">
         <v>17</v>
@@ -2345,13 +2345,13 @@
         <v>32</v>
       </c>
       <c r="BE7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7">
         <v>12</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
@@ -2363,55 +2363,55 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>4.5</v>
       </c>
       <c r="BO7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP7">
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU7">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BW7">
-        <v>32</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>60</v>
       </c>
       <c r="BY7">
-        <v>38</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>27</v>
       </c>
       <c r="CA7">
-        <v>18.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>124</v>
@@ -2434,10 +2434,10 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H8">
         <v>2.04</v>
@@ -2446,7 +2446,7 @@
         <v>2.08</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>4.3</v>
@@ -2458,19 +2458,19 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q8">
         <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S8">
         <v>2.4</v>
@@ -2506,7 +2506,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE8">
         <v>18.5</v>
@@ -2515,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
@@ -2530,7 +2530,7 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2551,13 +2551,13 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2593,13 +2593,13 @@
         <v>20</v>
       </c>
       <c r="BG8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
         <v>9</v>
@@ -2617,7 +2617,7 @@
         <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
         <v>25</v>
@@ -2641,16 +2641,16 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BZ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
         <v>10.5</v>
@@ -2676,19 +2676,19 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
         <v>4.9</v>
       </c>
       <c r="J9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
         <v>4.2</v>
@@ -2700,13 +2700,13 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>1.83</v>
@@ -2715,7 +2715,7 @@
         <v>1.44</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T9">
         <v>1.76</v>
@@ -2727,7 +2727,7 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X9">
         <v>18.5</v>
@@ -2754,7 +2754,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2784,7 +2784,7 @@
         <v>70</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9">
         <v>15.5</v>
@@ -2793,19 +2793,19 @@
         <v>30</v>
       </c>
       <c r="AS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
       </c>
       <c r="AU9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV9">
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2814,22 +2814,22 @@
         <v>9</v>
       </c>
       <c r="AZ9">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB9">
         <v>17</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="BD9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
         <v>9.6</v>
@@ -2847,13 +2847,13 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>9.6</v>
       </c>
       <c r="BN9">
         <v>4.8</v>
@@ -2865,37 +2865,37 @@
         <v>13</v>
       </c>
       <c r="BQ9">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW9">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY9">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="s">
         <v>124</v>
@@ -2921,7 +2921,7 @@
         <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -2957,10 +2957,10 @@
         <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U10">
         <v>2.14</v>
@@ -2969,10 +2969,10 @@
         <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="X10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y10">
         <v>29</v>
@@ -2990,7 +2990,7 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE10">
         <v>110</v>
@@ -3008,7 +3008,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK10">
         <v>16</v>
@@ -3026,7 +3026,7 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ10">
         <v>18</v>
@@ -3038,13 +3038,13 @@
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW10">
         <v>36</v>
@@ -3056,19 +3056,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA10">
         <v>34</v>
       </c>
       <c r="BB10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BE10">
         <v>38</v>
@@ -3080,13 +3080,13 @@
         <v>36</v>
       </c>
       <c r="BH10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
         <v>7.4</v>
@@ -3095,25 +3095,25 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BN10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO10">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ10">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
         <v>11</v>
@@ -3122,22 +3122,22 @@
         <v>7.6</v>
       </c>
       <c r="BV10">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BW10">
-        <v>38</v>
+        <v>11.5</v>
       </c>
       <c r="BX10">
         <v>55</v>
       </c>
       <c r="BY10">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BZ10">
         <v>15</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="s">
         <v>124</v>
@@ -3160,10 +3160,10 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G11">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H11">
         <v>6.2</v>
@@ -3172,13 +3172,13 @@
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M11">
         <v>1.01</v>
@@ -3187,22 +3187,22 @@
         <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q11">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="R11">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U11">
         <v>2.14</v>
@@ -3211,10 +3211,10 @@
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y11">
         <v>34</v>
@@ -3223,7 +3223,7 @@
         <v>70</v>
       </c>
       <c r="AA11">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB11">
         <v>13</v>
@@ -3232,10 +3232,10 @@
         <v>13.5</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE11">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF11">
         <v>12.5</v>
@@ -3244,13 +3244,13 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11">
         <v>80</v>
       </c>
       <c r="AJ11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK11">
         <v>17</v>
@@ -3262,10 +3262,10 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP11">
         <v>19.5</v>
@@ -3286,19 +3286,19 @@
         <v>9</v>
       </c>
       <c r="AV11">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
         <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
         <v>8</v>
       </c>
       <c r="AZ11">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
         <v>1.03</v>
@@ -3307,7 +3307,7 @@
         <v>11</v>
       </c>
       <c r="BC11">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
         <v>21</v>
@@ -3316,10 +3316,10 @@
         <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG11">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
         <v>4.6</v>
@@ -3331,13 +3331,13 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BN11">
         <v>4.5</v>
@@ -3349,37 +3349,37 @@
         <v>9.4</v>
       </c>
       <c r="BQ11">
+        <v>4.9</v>
+      </c>
+      <c r="BR11">
+        <v>21</v>
+      </c>
+      <c r="BS11">
         <v>7</v>
-      </c>
-      <c r="BR11">
-        <v>22</v>
-      </c>
-      <c r="BS11">
-        <v>15.5</v>
       </c>
       <c r="BT11">
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>36</v>
+        <v>8.6</v>
       </c>
       <c r="BZ11">
         <v>13</v>
       </c>
       <c r="CA11">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3405,16 +3405,16 @@
         <v>2.12</v>
       </c>
       <c r="G12">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
         <v>3.45</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.4</v>
@@ -3435,19 +3435,19 @@
         <v>3.05</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
         <v>1.84</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V12">
         <v>1.41</v>
@@ -3462,7 +3462,7 @@
         <v>25</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA12">
         <v>55</v>
@@ -3477,7 +3477,7 @@
         <v>16</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12">
         <v>21</v>
@@ -3489,10 +3489,10 @@
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK12">
         <v>20</v>
@@ -3522,19 +3522,19 @@
         <v>44</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AU12">
         <v>9.800000000000001</v>
       </c>
       <c r="AV12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>7.4</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3543,13 +3543,13 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB12">
         <v>23</v>
       </c>
       <c r="BC12">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD12">
         <v>20</v>
@@ -3567,7 +3567,7 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BJ12">
         <v>11</v>
@@ -3579,49 +3579,49 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>21</v>
+        <v>2.14</v>
       </c>
       <c r="BN12">
         <v>7.8</v>
       </c>
       <c r="BO12">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP12">
         <v>18.5</v>
       </c>
       <c r="BQ12">
-        <v>8.800000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="BR12">
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>12</v>
+        <v>2.04</v>
       </c>
       <c r="BT12">
         <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV12">
         <v>29</v>
       </c>
       <c r="BW12">
-        <v>13</v>
+        <v>2.04</v>
       </c>
       <c r="BX12">
         <v>34</v>
       </c>
       <c r="BY12">
-        <v>15.5</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12">
         <v>17</v>
       </c>
       <c r="CA12">
-        <v>7.6</v>
+        <v>1.95</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3647,16 +3647,16 @@
         <v>3.45</v>
       </c>
       <c r="G13">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H13">
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -3668,13 +3668,13 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
         <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
         <v>1.71</v>
@@ -3686,13 +3686,13 @@
         <v>2.78</v>
       </c>
       <c r="T13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U13">
         <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3749,7 +3749,7 @@
         <v>38</v>
       </c>
       <c r="AO13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP13">
         <v>17</v>
@@ -3788,10 +3788,10 @@
         <v>7.4</v>
       </c>
       <c r="BB13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC13">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BD13">
         <v>8</v>
@@ -3803,67 +3803,67 @@
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
         <v>7</v>
       </c>
       <c r="BO13">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP13">
         <v>25</v>
       </c>
       <c r="BQ13">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BT13">
         <v>5.3</v>
       </c>
       <c r="BU13">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BV13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA13">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3886,22 +3886,22 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G14">
         <v>1.6</v>
       </c>
       <c r="H14">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I14">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K14">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L14">
         <v>1.21</v>
@@ -3925,28 +3925,28 @@
         <v>1.99</v>
       </c>
       <c r="S14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T14">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="U14">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V14">
         <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X14">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="Y14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z14">
-        <v>510</v>
+        <v>60</v>
       </c>
       <c r="AA14">
         <v>1000</v>
@@ -3955,103 +3955,103 @@
         <v>19.5</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE14">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="AF14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH14">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI14">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ14">
         <v>18.5</v>
       </c>
       <c r="AK14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM14">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AN14">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AO14">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AP14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AR14">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AS14">
         <v>42</v>
       </c>
       <c r="AT14">
+        <v>16</v>
+      </c>
+      <c r="AU14">
+        <v>12</v>
+      </c>
+      <c r="AV14">
+        <v>18.5</v>
+      </c>
+      <c r="AW14">
+        <v>44</v>
+      </c>
+      <c r="AX14">
+        <v>13.5</v>
+      </c>
+      <c r="AY14">
+        <v>10</v>
+      </c>
+      <c r="AZ14">
         <v>15</v>
       </c>
-      <c r="AU14">
-        <v>11.5</v>
-      </c>
-      <c r="AV14">
-        <v>20</v>
-      </c>
-      <c r="AW14">
-        <v>28</v>
-      </c>
-      <c r="AX14">
+      <c r="BA14">
+        <v>40</v>
+      </c>
+      <c r="BB14">
+        <v>16.5</v>
+      </c>
+      <c r="BC14">
         <v>13</v>
       </c>
-      <c r="AY14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ14">
-        <v>14.5</v>
-      </c>
-      <c r="BA14">
-        <v>25</v>
-      </c>
-      <c r="BB14">
-        <v>15</v>
-      </c>
-      <c r="BC14">
-        <v>12.5</v>
-      </c>
       <c r="BD14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BE14">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BF14">
         <v>4.3</v>
       </c>
       <c r="BG14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ14">
         <v>9.199999999999999</v>
@@ -4105,7 +4105,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CA14">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>
@@ -4131,13 +4131,13 @@
         <v>1.75</v>
       </c>
       <c r="G15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H15">
         <v>4.7</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
         <v>4.2</v>
@@ -4149,10 +4149,10 @@
         <v>1.29</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O15">
         <v>1.2</v>
@@ -4173,7 +4173,7 @@
         <v>1.6</v>
       </c>
       <c r="U15">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
         <v>1.25</v>
@@ -4197,7 +4197,7 @@
         <v>13.5</v>
       </c>
       <c r="AC15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15">
         <v>20</v>
@@ -4248,7 +4248,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AU15">
         <v>9</v>
@@ -4260,22 +4260,22 @@
         <v>9</v>
       </c>
       <c r="AX15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY15">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BA15">
         <v>9</v>
       </c>
       <c r="BB15">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
         <v>21</v>
@@ -4284,7 +4284,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG15">
         <v>8.6</v>
@@ -4326,19 +4326,19 @@
         <v>15.5</v>
       </c>
       <c r="BT15">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU15">
         <v>6.4</v>
       </c>
       <c r="BV15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
         <v>24</v>
       </c>
       <c r="BX15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>26</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="CA15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4373,16 +4373,16 @@
         <v>2.42</v>
       </c>
       <c r="G16">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H16">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K16">
         <v>4.2</v>
@@ -4397,16 +4397,16 @@
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S16">
         <v>2.3</v>
@@ -4415,16 +4415,16 @@
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V16">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y16">
         <v>20</v>
@@ -4445,7 +4445,7 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF16">
         <v>21</v>
@@ -4466,7 +4466,7 @@
         <v>24</v>
       </c>
       <c r="AL16">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -4478,7 +4478,7 @@
         <v>16</v>
       </c>
       <c r="AP16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,7 +4487,7 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT16">
         <v>15.5</v>
@@ -4499,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4514,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="BB16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
@@ -4523,16 +4523,16 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF16">
         <v>10</v>
       </c>
       <c r="BG16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI16">
         <v>3.75</v>
@@ -4547,7 +4547,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
@@ -4559,13 +4559,13 @@
         <v>16.5</v>
       </c>
       <c r="BQ16">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="BR16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS16">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BT16">
         <v>6.8</v>
@@ -4574,22 +4574,22 @@
         <v>5.6</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BW16">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BX16">
         <v>26</v>
       </c>
       <c r="BY16">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BZ16">
         <v>15</v>
       </c>
       <c r="CA16">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="CB16" t="s">
         <v>124</v>
@@ -4645,19 +4645,19 @@
         <v>2.54</v>
       </c>
       <c r="Q17">
+        <v>1.6</v>
+      </c>
+      <c r="R17">
         <v>1.61</v>
-      </c>
-      <c r="R17">
-        <v>1.62</v>
       </c>
       <c r="S17">
         <v>2.52</v>
       </c>
       <c r="T17">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U17">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
         <v>1.35</v>
@@ -4684,7 +4684,7 @@
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE17">
         <v>38</v>
@@ -4702,7 +4702,7 @@
         <v>40</v>
       </c>
       <c r="AJ17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK17">
         <v>20</v>
@@ -4717,13 +4717,13 @@
         <v>10</v>
       </c>
       <c r="AO17">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP17">
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>16.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR17">
         <v>7.6</v>
@@ -4741,7 +4741,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX17">
         <v>13.5</v>
@@ -4759,7 +4759,7 @@
         <v>20</v>
       </c>
       <c r="BC17">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD17">
         <v>7.4</v>
@@ -4777,19 +4777,19 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BJ17">
         <v>12</v>
       </c>
       <c r="BK17">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>21</v>
+        <v>2.06</v>
       </c>
       <c r="BN17">
         <v>7</v>
@@ -4801,13 +4801,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>8.4</v>
+        <v>1.9</v>
       </c>
       <c r="BR17">
         <v>30</v>
       </c>
       <c r="BS17">
-        <v>14</v>
+        <v>1.98</v>
       </c>
       <c r="BT17">
         <v>9.800000000000001</v>
@@ -4819,19 +4819,19 @@
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>15.5</v>
+        <v>1.99</v>
       </c>
       <c r="BX17">
         <v>40</v>
       </c>
       <c r="BY17">
-        <v>18.5</v>
+        <v>2</v>
       </c>
       <c r="BZ17">
         <v>21</v>
       </c>
       <c r="CA17">
-        <v>10</v>
+        <v>1.92</v>
       </c>
       <c r="CB17" t="s">
         <v>124</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 11:21:35</t>
+    <t>2026-07-21 13:28:27</t>
   </si>
 </sst>
 </file>
@@ -994,13 +994,13 @@
         <v>1.92</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="M2">
         <v>1.11</v>
@@ -1012,10 +1012,10 @@
         <v>1.47</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
         <v>1.21</v>
@@ -1024,7 +1024,7 @@
         <v>4.7</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
         <v>1.7</v>
@@ -1063,7 +1063,7 @@
         <v>46</v>
       </c>
       <c r="AG2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH2">
         <v>32</v>
@@ -1093,25 +1093,25 @@
         <v>8.4</v>
       </c>
       <c r="AQ2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR2">
         <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT2">
         <v>12.5</v>
       </c>
       <c r="AU2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV2">
         <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2">
         <v>32</v>
@@ -1123,22 +1123,22 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
+        <v>8.4</v>
+      </c>
+      <c r="BC2">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC2">
-        <v>8</v>
-      </c>
       <c r="BD2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2">
         <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
@@ -1147,22 +1147,22 @@
         <v>2.96</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO2">
         <v>6.6</v>
@@ -1171,13 +1171,13 @@
         <v>65</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>4.3</v>
@@ -1189,19 +1189,19 @@
         <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>36</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1224,10 +1224,10 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -1239,10 +1239,10 @@
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1257,25 +1257,25 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
         <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T3">
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
         <v>1.31</v>
       </c>
       <c r="W3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X3">
         <v>19</v>
@@ -1287,16 +1287,16 @@
         <v>32</v>
       </c>
       <c r="AA3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>12</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
         <v>46</v>
@@ -1317,7 +1317,7 @@
         <v>23</v>
       </c>
       <c r="AK3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL3">
         <v>30</v>
@@ -1395,55 +1395,55 @@
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP3">
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
         <v>7.8</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
         <v>38</v>
       </c>
       <c r="BY3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1475,10 +1475,10 @@
         <v>4.1</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K4">
         <v>3.55</v>
@@ -1490,25 +1490,25 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
         <v>1.9</v>
@@ -1529,22 +1529,22 @@
         <v>29</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB4">
+        <v>7.6</v>
+      </c>
+      <c r="AC4">
         <v>7.8</v>
-      </c>
-      <c r="AC4">
-        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
         <v>17</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1553,7 +1553,7 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
         <v>26</v>
@@ -1568,34 +1568,34 @@
         <v>180</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1607,10 +1607,10 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
@@ -1619,19 +1619,19 @@
         <v>40</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BF4">
         <v>18</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI4">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -1682,7 +1682,7 @@
         <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA4">
         <v>12.5</v>
@@ -1708,13 +1708,13 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
         <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
         <v>3.65</v>
@@ -1723,7 +1723,7 @@
         <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1732,25 +1732,25 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
         <v>1.82</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
         <v>3.85</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2.08</v>
@@ -1762,13 +1762,13 @@
         <v>1.73</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
         <v>12.5</v>
       </c>
       <c r="Z5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA5">
         <v>75</v>
@@ -1777,16 +1777,16 @@
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
         <v>15</v>
       </c>
       <c r="AE5">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>12</v>
@@ -1795,7 +1795,7 @@
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>32</v>
@@ -1813,7 +1813,7 @@
         <v>22</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1825,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -1834,10 +1834,10 @@
         <v>7</v>
       </c>
       <c r="AV5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX5">
         <v>13</v>
@@ -1849,19 +1849,19 @@
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
@@ -1950,13 +1950,13 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G6">
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I6">
         <v>1.51</v>
@@ -1971,7 +1971,7 @@
         <v>1.39</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
         <v>3.95</v>
@@ -1983,25 +1983,25 @@
         <v>2.04</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>16</v>
@@ -2058,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6">
         <v>7.4</v>
@@ -2073,7 +2073,7 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2094,7 +2094,7 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC6">
         <v>13</v>
@@ -2106,10 +2106,10 @@
         <v>13</v>
       </c>
       <c r="BF6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
         <v>3.55</v>
@@ -2192,28 +2192,28 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H7">
+        <v>4.6</v>
+      </c>
+      <c r="I7">
         <v>4.9</v>
       </c>
-      <c r="I7">
-        <v>5.2</v>
-      </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>3.85</v>
       </c>
       <c r="L7">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
         <v>3.4</v>
@@ -2222,196 +2222,196 @@
         <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="X7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Y7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA7">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB7">
+        <v>8.6</v>
+      </c>
+      <c r="AC7">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC7">
-        <v>8.4</v>
-      </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE7">
         <v>70</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI7">
         <v>75</v>
       </c>
       <c r="AJ7">
+        <v>20</v>
+      </c>
+      <c r="AK7">
         <v>21</v>
-      </c>
-      <c r="AK7">
-        <v>22</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AX7">
+        <v>9.6</v>
+      </c>
+      <c r="AY7">
         <v>9.4</v>
       </c>
-      <c r="AY7">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ7">
+        <v>18.5</v>
+      </c>
+      <c r="BA7">
+        <v>11</v>
+      </c>
+      <c r="BB7">
         <v>17.5</v>
       </c>
-      <c r="BA7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB7">
-        <v>17</v>
-      </c>
       <c r="BC7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE7">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF7">
         <v>12</v>
       </c>
       <c r="BG7">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BH7">
         <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BO7">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>124</v>
@@ -2434,16 +2434,16 @@
         <v>114</v>
       </c>
       <c r="F8">
+        <v>3.6</v>
+      </c>
+      <c r="G8">
         <v>3.65</v>
       </c>
-      <c r="G8">
-        <v>3.75</v>
-      </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2458,16 +2458,16 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R8">
         <v>1.67</v>
@@ -2479,10 +2479,10 @@
         <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V8">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="W8">
         <v>1.37</v>
@@ -2506,7 +2506,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
         <v>18.5</v>
@@ -2515,13 +2515,13 @@
         <v>32</v>
       </c>
       <c r="AG8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2530,7 +2530,7 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2539,7 +2539,7 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AP8">
         <v>22</v>
@@ -2611,7 +2611,7 @@
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2676,7 +2676,7 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
         <v>1.88</v>
@@ -2706,10 +2706,10 @@
         <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2727,10 +2727,10 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>19</v>
@@ -2742,7 +2742,7 @@
         <v>120</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2784,7 +2784,7 @@
         <v>70</v>
       </c>
       <c r="AP9">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
         <v>15.5</v>
@@ -2793,7 +2793,7 @@
         <v>30</v>
       </c>
       <c r="AS9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
@@ -2805,31 +2805,31 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB9">
         <v>17</v>
       </c>
       <c r="BC9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF9">
         <v>9.6</v>
@@ -2853,7 +2853,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9">
         <v>4.8</v>
@@ -2877,10 +2877,10 @@
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
         <v>8.199999999999999</v>
@@ -2889,7 +2889,7 @@
         <v>46</v>
       </c>
       <c r="BY9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9">
         <v>21</v>
@@ -2918,7 +2918,7 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G10">
         <v>1.54</v>
@@ -2927,7 +2927,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>4.8</v>
@@ -2942,7 +2942,7 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
         <v>1.22</v>
@@ -2954,7 +2954,7 @@
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
         <v>2.68</v>
@@ -2966,7 +2966,7 @@
         <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -2996,7 +2996,7 @@
         <v>110</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK10">
         <v>16</v>
@@ -3020,13 +3020,13 @@
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10">
         <v>18</v>
@@ -3053,7 +3053,7 @@
         <v>9</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
         <v>18</v>
@@ -3065,10 +3065,10 @@
         <v>12.5</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE10">
         <v>38</v>
@@ -3160,10 +3160,10 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G11">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H11">
         <v>6.2</v>
@@ -3175,49 +3175,49 @@
         <v>4.7</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="S11">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T11">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U11">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="X11">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z11">
         <v>70</v>
@@ -3226,10 +3226,10 @@
         <v>190</v>
       </c>
       <c r="AB11">
+        <v>12.5</v>
+      </c>
+      <c r="AC11">
         <v>13</v>
-      </c>
-      <c r="AC11">
-        <v>13.5</v>
       </c>
       <c r="AD11">
         <v>29</v>
@@ -3238,7 +3238,7 @@
         <v>90</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3262,16 +3262,16 @@
         <v>100</v>
       </c>
       <c r="AN11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AO11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP11">
         <v>19.5</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR11">
         <v>1.03</v>
@@ -3307,7 +3307,7 @@
         <v>11</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD11">
         <v>21</v>
@@ -3316,52 +3316,52 @@
         <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG11">
         <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP11">
         <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT11">
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3373,13 +3373,13 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3402,22 +3402,22 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.23</v>
@@ -3435,7 +3435,7 @@
         <v>3.05</v>
       </c>
       <c r="Q12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R12">
         <v>1.84</v>
@@ -3444,16 +3444,16 @@
         <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="U12">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3462,46 +3462,46 @@
         <v>25</v>
       </c>
       <c r="Z12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>420</v>
       </c>
       <c r="AB12">
         <v>19</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12">
+        <v>34</v>
+      </c>
+      <c r="AF12">
+        <v>20</v>
+      </c>
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>14</v>
+      </c>
+      <c r="AI12">
+        <v>50</v>
+      </c>
+      <c r="AJ12">
         <v>32</v>
       </c>
-      <c r="AF12">
-        <v>21</v>
-      </c>
-      <c r="AG12">
-        <v>12.5</v>
-      </c>
-      <c r="AH12">
-        <v>14.5</v>
-      </c>
-      <c r="AI12">
-        <v>32</v>
-      </c>
-      <c r="AJ12">
-        <v>29</v>
-      </c>
       <c r="AK12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL12">
         <v>25</v>
       </c>
       <c r="AM12">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="AN12">
         <v>8.4</v>
@@ -3510,7 +3510,7 @@
         <v>16.5</v>
       </c>
       <c r="AP12">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3519,22 +3519,22 @@
         <v>25</v>
       </c>
       <c r="AS12">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AT12">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AX12">
-        <v>7.4</v>
+        <v>17</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3543,13 +3543,13 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>8.4</v>
+        <v>19.5</v>
       </c>
       <c r="BB12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC12">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
         <v>20</v>
@@ -3558,7 +3558,7 @@
         <v>34</v>
       </c>
       <c r="BF12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG12">
         <v>14.5</v>
@@ -3567,10 +3567,10 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BK12">
         <v>5.4</v>
@@ -3579,7 +3579,7 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="BN12">
         <v>7.8</v>
@@ -3588,40 +3588,40 @@
         <v>4.1</v>
       </c>
       <c r="BP12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ12">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BR12">
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BT12">
         <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
         <v>29</v>
       </c>
       <c r="BW12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="BX12">
         <v>34</v>
       </c>
       <c r="BY12">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="BZ12">
         <v>17</v>
       </c>
       <c r="CA12">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3647,16 +3647,16 @@
         <v>3.45</v>
       </c>
       <c r="G13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H13">
         <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -3677,22 +3677,22 @@
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
         <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U13">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3761,7 +3761,7 @@
         <v>13</v>
       </c>
       <c r="AS13">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT13">
         <v>15.5</v>
@@ -3785,19 +3785,19 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13">
         <v>8.4</v>
       </c>
       <c r="BC13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD13">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE13">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13">
         <v>21</v>
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="BO13">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
         <v>25</v>
@@ -3889,19 +3889,19 @@
         <v>1.59</v>
       </c>
       <c r="G14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
+        <v>5.4</v>
+      </c>
+      <c r="I14">
         <v>5.6</v>
-      </c>
-      <c r="I14">
-        <v>5.7</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
         <v>1.21</v>
@@ -3922,13 +3922,13 @@
         <v>1.38</v>
       </c>
       <c r="R14">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S14">
         <v>1.94</v>
       </c>
       <c r="T14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U14">
         <v>2.86</v>
@@ -3937,13 +3937,13 @@
         <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X14">
         <v>44</v>
       </c>
       <c r="Y14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -3952,7 +3952,7 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC14">
         <v>13</v>
@@ -3988,13 +3988,13 @@
         <v>55</v>
       </c>
       <c r="AN14">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO14">
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ14">
         <v>32</v>
@@ -4009,10 +4009,10 @@
         <v>16</v>
       </c>
       <c r="AU14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV14">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW14">
         <v>44</v>
@@ -4042,16 +4042,16 @@
         <v>42</v>
       </c>
       <c r="BF14">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
       </c>
       <c r="BI14">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ14">
         <v>9.199999999999999</v>
@@ -4093,7 +4093,7 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BX14">
         <v>34</v>
@@ -4134,10 +4134,10 @@
         <v>1.79</v>
       </c>
       <c r="H15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
         <v>4.2</v>
@@ -4152,16 +4152,16 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
         <v>2.6</v>
       </c>
       <c r="Q15">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R15">
         <v>1.64</v>
@@ -4173,7 +4173,7 @@
         <v>1.6</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V15">
         <v>1.25</v>
@@ -4248,7 +4248,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AT15">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AU15">
         <v>9</v>
@@ -4272,7 +4272,7 @@
         <v>9</v>
       </c>
       <c r="BB15">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BC15">
         <v>13.5</v>
@@ -4284,7 +4284,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF15">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
         <v>8.6</v>
@@ -4332,13 +4332,13 @@
         <v>6.4</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW15">
         <v>24</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY15">
         <v>26</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="CA15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4370,7 +4370,7 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G16">
         <v>2.5</v>
@@ -4379,7 +4379,7 @@
         <v>2.84</v>
       </c>
       <c r="I16">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J16">
         <v>3.95</v>
@@ -4406,7 +4406,7 @@
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S16">
         <v>2.3</v>
@@ -4415,7 +4415,7 @@
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V16">
         <v>1.51</v>
@@ -4424,7 +4424,7 @@
         <v>1.67</v>
       </c>
       <c r="X16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y16">
         <v>20</v>
@@ -4466,7 +4466,7 @@
         <v>24</v>
       </c>
       <c r="AL16">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM16">
         <v>55</v>
@@ -4478,7 +4478,7 @@
         <v>16</v>
       </c>
       <c r="AP16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,10 +4487,10 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4499,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4514,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="BB16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
@@ -4523,7 +4523,7 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF16">
         <v>10</v>
@@ -4621,46 +4621,46 @@
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J17">
         <v>3.95</v>
       </c>
       <c r="K17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O17">
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q17">
         <v>1.6</v>
       </c>
       <c r="R17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S17">
         <v>2.52</v>
       </c>
       <c r="T17">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.92</v>
@@ -4681,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>16</v>
@@ -4723,13 +4723,13 @@
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AR17">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS17">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT17">
         <v>12</v>
@@ -4741,7 +4741,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX17">
         <v>13.5</v>
@@ -4753,19 +4753,19 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB17">
         <v>20</v>
       </c>
       <c r="BC17">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE17">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17">
         <v>8.800000000000001</v>
@@ -4783,7 +4783,7 @@
         <v>12</v>
       </c>
       <c r="BK17">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BL17">
         <v>1000</v>
@@ -4795,19 +4795,19 @@
         <v>7</v>
       </c>
       <c r="BO17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP17">
         <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="BR17">
         <v>30</v>
       </c>
       <c r="BS17">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BT17">
         <v>9.800000000000001</v>
@@ -4819,10 +4819,10 @@
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="BX17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BY17">
         <v>2</v>
@@ -4831,7 +4831,7 @@
         <v>21</v>
       </c>
       <c r="CA17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CB17" t="s">
         <v>124</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 13:28:27</t>
+    <t>2026-07-21 15:35:26</t>
   </si>
 </sst>
 </file>
@@ -982,73 +982,73 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="G2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V2">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W2">
         <v>1.19</v>
       </c>
       <c r="X2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
         <v>10.5</v>
       </c>
       <c r="AA2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
         <v>8.4</v>
@@ -1069,7 +1069,7 @@
         <v>32</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
         <v>210</v>
@@ -1087,34 +1087,34 @@
         <v>190</v>
       </c>
       <c r="AO2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR2">
         <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV2">
         <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AX2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AY2">
         <v>19</v>
@@ -1123,46 +1123,46 @@
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD2">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2">
         <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO2">
         <v>6.6</v>
@@ -1171,37 +1171,37 @@
         <v>65</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
         <v>6.4</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1239,7 +1239,7 @@
         <v>3.9</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L3">
         <v>1.35</v>
@@ -1257,10 +1257,10 @@
         <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
         <v>2.9</v>
@@ -1272,7 +1272,7 @@
         <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.98</v>
@@ -1293,7 +1293,7 @@
         <v>12</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
         <v>16.5</v>
@@ -1475,7 +1475,7 @@
         <v>4.1</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J4">
         <v>3.4</v>
@@ -1493,13 +1493,13 @@
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1532,7 +1532,7 @@
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
@@ -1541,7 +1541,7 @@
         <v>17</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -1708,7 +1708,7 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
         <v>2.36</v>
@@ -1717,10 +1717,10 @@
         <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
         <v>3.5</v>
@@ -1729,34 +1729,34 @@
         <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
         <v>1.73</v>
@@ -1780,7 +1780,7 @@
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
         <v>55</v>
@@ -1789,19 +1789,19 @@
         <v>14.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5">
         <v>44</v>
@@ -1813,31 +1813,31 @@
         <v>22</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
         <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AX5">
         <v>13</v>
@@ -1846,28 +1846,28 @@
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA5">
         <v>10</v>
       </c>
       <c r="BB5">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC5">
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
@@ -1950,7 +1950,7 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G6">
         <v>8.800000000000001</v>
@@ -1962,10 +1962,10 @@
         <v>1.51</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -1974,7 +1974,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.31</v>
@@ -1998,13 +1998,13 @@
         <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="W6">
         <v>1.12</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
         <v>7.6</v>
@@ -2094,16 +2094,16 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF6">
         <v>11.5</v>
@@ -2157,7 +2157,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BW6">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BX6">
         <v>27</v>
@@ -2192,37 +2192,37 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G7">
         <v>1.91</v>
       </c>
       <c r="H7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
         <v>4.9</v>
       </c>
       <c r="J7">
+        <v>3.7</v>
+      </c>
+      <c r="K7">
         <v>3.8</v>
       </c>
-      <c r="K7">
-        <v>3.85</v>
-      </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M7">
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
@@ -2234,19 +2234,19 @@
         <v>3.7</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y7">
         <v>15</v>
@@ -2264,10 +2264,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF7">
         <v>11</v>
@@ -2276,7 +2276,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI7">
         <v>75</v>
@@ -2285,19 +2285,19 @@
         <v>20</v>
       </c>
       <c r="AK7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7">
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2306,10 +2306,10 @@
         <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AS7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2324,7 +2324,7 @@
         <v>55</v>
       </c>
       <c r="AX7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2333,10 +2333,10 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC7">
         <v>18</v>
@@ -2345,73 +2345,73 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF7">
         <v>12</v>
       </c>
       <c r="BG7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
         <v>4.7</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
         <v>44</v>
       </c>
       <c r="BW7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX7">
         <v>55</v>
       </c>
       <c r="BY7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>124</v>
@@ -2437,25 +2437,25 @@
         <v>3.6</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>1.28</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
         <v>5.9</v>
@@ -2473,7 +2473,7 @@
         <v>1.67</v>
       </c>
       <c r="S8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T8">
         <v>1.54</v>
@@ -2482,7 +2482,7 @@
         <v>2.74</v>
       </c>
       <c r="V8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W8">
         <v>1.37</v>
@@ -2500,7 +2500,7 @@
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC8">
         <v>9.800000000000001</v>
@@ -2515,7 +2515,7 @@
         <v>32</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
@@ -2530,7 +2530,7 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>55</v>
@@ -2551,7 +2551,7 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT8">
         <v>19</v>
@@ -2587,7 +2587,7 @@
         <v>30</v>
       </c>
       <c r="BE8">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF8">
         <v>20</v>
@@ -2679,19 +2679,19 @@
         <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H9">
         <v>4.6</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.37</v>
@@ -2700,7 +2700,7 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
         <v>1.28</v>
@@ -2727,7 +2727,7 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X9">
         <v>18</v>
@@ -2742,7 +2742,7 @@
         <v>120</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2784,16 +2784,16 @@
         <v>70</v>
       </c>
       <c r="AP9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
         <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
@@ -2805,7 +2805,7 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2814,28 +2814,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA9">
+        <v>9</v>
+      </c>
+      <c r="BB9">
+        <v>16.5</v>
+      </c>
+      <c r="BC9">
+        <v>16</v>
+      </c>
+      <c r="BD9">
+        <v>24</v>
+      </c>
+      <c r="BE9">
+        <v>9.6</v>
+      </c>
+      <c r="BF9">
         <v>9.4</v>
       </c>
-      <c r="BB9">
-        <v>17</v>
-      </c>
-      <c r="BC9">
-        <v>7</v>
-      </c>
-      <c r="BD9">
-        <v>8.4</v>
-      </c>
-      <c r="BE9">
-        <v>10</v>
-      </c>
-      <c r="BF9">
-        <v>9.6</v>
-      </c>
       <c r="BG9">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2847,13 +2847,13 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
         <v>4.8</v>
@@ -2865,37 +2865,37 @@
         <v>13</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
+        <v>40</v>
+      </c>
+      <c r="BW9">
+        <v>8</v>
+      </c>
+      <c r="BX9">
         <v>1000</v>
       </c>
-      <c r="BW9">
+      <c r="BY9">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BX9">
-        <v>46</v>
-      </c>
-      <c r="BY9">
-        <v>8.6</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="s">
         <v>124</v>
@@ -2918,7 +2918,7 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
         <v>1.54</v>
@@ -2930,7 +2930,7 @@
         <v>7.4</v>
       </c>
       <c r="J10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
         <v>2.4</v>
@@ -2954,10 +2954,10 @@
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T10">
         <v>1.82</v>
@@ -2966,7 +2966,7 @@
         <v>2.14</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -3011,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="AK10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10">
         <v>32</v>
@@ -3068,7 +3068,7 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BE10">
         <v>38</v>
@@ -3107,13 +3107,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BQ10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT10">
         <v>11</v>
@@ -3134,7 +3134,7 @@
         <v>11.5</v>
       </c>
       <c r="BZ10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA10">
         <v>8.4</v>
@@ -3160,7 +3160,7 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G11">
         <v>1.59</v>
@@ -3172,7 +3172,7 @@
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
         <v>5.4</v>
@@ -3402,7 +3402,7 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G12">
         <v>2.22</v>
@@ -3411,10 +3411,10 @@
         <v>3.25</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3441,7 +3441,7 @@
         <v>1.84</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T12">
         <v>1.44</v>
@@ -3453,7 +3453,7 @@
         <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
         <v>36</v>
@@ -3501,7 +3501,7 @@
         <v>25</v>
       </c>
       <c r="AM12">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AN12">
         <v>8.4</v>
@@ -3546,7 +3546,7 @@
         <v>19.5</v>
       </c>
       <c r="BB12">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BC12">
         <v>16.5</v>
@@ -3567,7 +3567,7 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ12">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>4.1</v>
       </c>
       <c r="BP12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ12">
         <v>2</v>
@@ -3597,7 +3597,7 @@
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BT12">
         <v>9.800000000000001</v>
@@ -3621,7 +3621,7 @@
         <v>17</v>
       </c>
       <c r="CA12">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3656,7 +3656,7 @@
         <v>2.2</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
         <v>4</v>
@@ -3671,13 +3671,13 @@
         <v>4.8</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13">
         <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R13">
         <v>1.52</v>
@@ -3692,7 +3692,7 @@
         <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W13">
         <v>1.37</v>
@@ -3827,7 +3827,7 @@
         <v>7</v>
       </c>
       <c r="BO13">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP13">
         <v>25</v>
@@ -3886,37 +3886,37 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H14">
+        <v>5.2</v>
+      </c>
+      <c r="I14">
         <v>5.4</v>
       </c>
-      <c r="I14">
-        <v>5.6</v>
-      </c>
       <c r="J14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K14">
         <v>5.3</v>
       </c>
       <c r="L14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M14">
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O14">
         <v>1.12</v>
       </c>
       <c r="P14">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
         <v>1.38</v>
@@ -3925,25 +3925,25 @@
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="U14">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X14">
         <v>44</v>
       </c>
       <c r="Y14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -3952,7 +3952,7 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC14">
         <v>13</v>
@@ -3964,7 +3964,7 @@
         <v>55</v>
       </c>
       <c r="AF14">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -3973,7 +3973,7 @@
         <v>16.5</v>
       </c>
       <c r="AI14">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AJ14">
         <v>18.5</v>
@@ -3988,7 +3988,7 @@
         <v>55</v>
       </c>
       <c r="AN14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO14">
         <v>32</v>
@@ -4000,7 +4000,7 @@
         <v>32</v>
       </c>
       <c r="AR14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AS14">
         <v>42</v>
@@ -4009,7 +4009,7 @@
         <v>16</v>
       </c>
       <c r="AU14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV14">
         <v>20</v>
@@ -4027,7 +4027,7 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="BB14">
         <v>16.5</v>
@@ -4045,7 +4045,7 @@
         <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
@@ -4069,13 +4069,13 @@
         <v>5.2</v>
       </c>
       <c r="BO14">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP14">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR14">
         <v>17.5</v>
@@ -4084,13 +4084,13 @@
         <v>12</v>
       </c>
       <c r="BT14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU14">
         <v>7.2</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW14">
         <v>24</v>
@@ -4131,46 +4131,46 @@
         <v>1.75</v>
       </c>
       <c r="G15">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H15">
+        <v>4.7</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>4.3</v>
+      </c>
+      <c r="K15">
         <v>4.6</v>
       </c>
-      <c r="I15">
-        <v>4.9</v>
-      </c>
-      <c r="J15">
-        <v>4.2</v>
-      </c>
-      <c r="K15">
-        <v>4.5</v>
-      </c>
       <c r="L15">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q15">
+        <v>1.56</v>
+      </c>
+      <c r="R15">
+        <v>1.68</v>
+      </c>
+      <c r="S15">
+        <v>2.4</v>
+      </c>
+      <c r="T15">
         <v>1.59</v>
-      </c>
-      <c r="R15">
-        <v>1.64</v>
-      </c>
-      <c r="S15">
-        <v>2.46</v>
-      </c>
-      <c r="T15">
-        <v>1.6</v>
       </c>
       <c r="U15">
         <v>2.52</v>
@@ -4182,10 +4182,10 @@
         <v>2.26</v>
       </c>
       <c r="X15">
+        <v>28</v>
+      </c>
+      <c r="Y15">
         <v>27</v>
-      </c>
-      <c r="Y15">
-        <v>26</v>
       </c>
       <c r="Z15">
         <v>46</v>
@@ -4206,34 +4206,34 @@
         <v>55</v>
       </c>
       <c r="AF15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG15">
         <v>10.5</v>
       </c>
       <c r="AH15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ15">
         <v>20</v>
       </c>
       <c r="AK15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM15">
         <v>65</v>
       </c>
       <c r="AN15">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP15">
         <v>21</v>
@@ -4242,10 +4242,10 @@
         <v>21</v>
       </c>
       <c r="AR15">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS15">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AT15">
         <v>11.5</v>
@@ -4257,49 +4257,49 @@
         <v>17</v>
       </c>
       <c r="AW15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX15">
         <v>12</v>
       </c>
       <c r="AY15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BA15">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB15">
         <v>16</v>
       </c>
       <c r="BC15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD15">
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG15">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI15">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BJ15">
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4314,22 +4314,22 @@
         <v>3.9</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ15">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BT15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV15">
         <v>34</v>
@@ -4338,16 +4338,16 @@
         <v>24</v>
       </c>
       <c r="BX15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
         <v>26</v>
       </c>
       <c r="BZ15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4373,16 +4373,16 @@
         <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H16">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I16">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <v>4.2</v>
@@ -4400,7 +4400,7 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
@@ -4421,7 +4421,7 @@
         <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4463,7 +4463,7 @@
         <v>42</v>
       </c>
       <c r="AK16">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL16">
         <v>29</v>
@@ -4478,7 +4478,7 @@
         <v>16</v>
       </c>
       <c r="AP16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,7 +4487,7 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT16">
         <v>15</v>
@@ -4499,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4514,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="BB16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
@@ -4523,7 +4523,7 @@
         <v>19</v>
       </c>
       <c r="BE16">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF16">
         <v>10</v>
@@ -4547,7 +4547,7 @@
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
@@ -4559,16 +4559,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR16">
         <v>23</v>
       </c>
       <c r="BS16">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU16">
         <v>5.6</v>
@@ -4577,19 +4577,19 @@
         <v>20</v>
       </c>
       <c r="BW16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX16">
         <v>26</v>
       </c>
       <c r="BY16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ16">
         <v>15</v>
       </c>
       <c r="CA16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB16" t="s">
         <v>124</v>
@@ -4615,7 +4615,7 @@
         <v>2.04</v>
       </c>
       <c r="G17">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H17">
         <v>3.55</v>
@@ -4639,22 +4639,22 @@
         <v>5.6</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P17">
         <v>2.56</v>
       </c>
       <c r="Q17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R17">
         <v>1.62</v>
       </c>
       <c r="S17">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U17">
         <v>2.54</v>
@@ -4663,7 +4663,7 @@
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X17">
         <v>25</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 15:35:26</t>
+    <t>2026-07-21 17:42:25</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
         <v>6.2</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="I2">
         <v>1.95</v>
@@ -1006,13 +1006,13 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
         <v>2.48</v>
@@ -1033,7 +1033,7 @@
         <v>2.04</v>
       </c>
       <c r="W2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
         <v>9.6</v>
@@ -1081,10 +1081,10 @@
         <v>130</v>
       </c>
       <c r="AM2">
+        <v>260</v>
+      </c>
+      <c r="AN2">
         <v>220</v>
-      </c>
-      <c r="AN2">
-        <v>190</v>
       </c>
       <c r="AO2">
         <v>21</v>
@@ -1099,40 +1099,40 @@
         <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV2">
         <v>8.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY2">
         <v>19</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>9.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE2">
         <v>9.199999999999999</v>
@@ -1153,7 +1153,7 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1248,31 +1248,31 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
         <v>1.49</v>
       </c>
       <c r="S3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U3">
         <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
         <v>1.98</v>
@@ -1290,7 +1290,7 @@
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>8.800000000000001</v>
@@ -1317,13 +1317,13 @@
         <v>23</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
         <v>30</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN3">
         <v>11</v>
@@ -1344,7 +1344,7 @@
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU3">
         <v>8.199999999999999</v>
@@ -1481,7 +1481,7 @@
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -1526,7 +1526,7 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AA4">
         <v>110</v>
@@ -1538,7 +1538,7 @@
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
         <v>65</v>
@@ -1589,7 +1589,7 @@
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
         <v>15.5</v>
@@ -1714,7 +1714,7 @@
         <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I5">
         <v>3.7</v>
@@ -1729,7 +1729,7 @@
         <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
         <v>3.35</v>
@@ -1747,19 +1747,19 @@
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.37</v>
       </c>
       <c r="W5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X5">
         <v>12.5</v>
@@ -1825,7 +1825,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1849,7 +1849,7 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB5">
         <v>8.4</v>
@@ -1858,7 +1858,7 @@
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE5">
         <v>10</v>
@@ -1956,16 +1956,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
         <v>1.51</v>
       </c>
       <c r="J6">
+        <v>4.5</v>
+      </c>
+      <c r="K6">
         <v>4.6</v>
-      </c>
-      <c r="K6">
-        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -1974,16 +1974,16 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
         <v>1.4</v>
@@ -1998,16 +1998,16 @@
         <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>15.5</v>
       </c>
       <c r="Y6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z6">
         <v>8.6</v>
@@ -2028,10 +2028,10 @@
         <v>17.5</v>
       </c>
       <c r="AF6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH6">
         <v>32</v>
@@ -2094,19 +2094,19 @@
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BE6">
         <v>13.5</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
@@ -2234,10 +2234,10 @@
         <v>3.7</v>
       </c>
       <c r="T7">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V7">
         <v>1.25</v>
@@ -2252,7 +2252,7 @@
         <v>15</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2306,7 +2306,7 @@
         <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS7">
         <v>12.5</v>
@@ -2336,7 +2336,7 @@
         <v>11.5</v>
       </c>
       <c r="BB7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC7">
         <v>18</v>
@@ -2351,7 +2351,7 @@
         <v>12</v>
       </c>
       <c r="BG7">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2363,13 +2363,13 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
         <v>4.7</v>
@@ -2387,31 +2387,31 @@
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV7">
         <v>44</v>
       </c>
       <c r="BW7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ7">
         <v>29</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>124</v>
@@ -2446,13 +2446,13 @@
         <v>2.08</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
         <v>1.03</v>
@@ -2464,22 +2464,22 @@
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S8">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U8">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="V8">
         <v>1.92</v>
@@ -2491,7 +2491,7 @@
         <v>26</v>
       </c>
       <c r="Y8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z8">
         <v>16.5</v>
@@ -2509,7 +2509,7 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AF8">
         <v>32</v>
@@ -2518,10 +2518,10 @@
         <v>16</v>
       </c>
       <c r="AH8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2530,10 +2530,10 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2542,7 +2542,7 @@
         <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2551,13 +2551,13 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8">
         <v>19</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2566,7 +2566,7 @@
         <v>16.5</v>
       </c>
       <c r="AX8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY8">
         <v>14</v>
@@ -2590,7 +2590,7 @@
         <v>46</v>
       </c>
       <c r="BF8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8">
         <v>8.6</v>
@@ -2605,13 +2605,13 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>50</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2620,16 +2620,16 @@
         <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ8">
-        <v>17.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>20</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>5.6</v>
@@ -2641,19 +2641,19 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>124</v>
@@ -2685,7 +2685,7 @@
         <v>4.6</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>3.9</v>
@@ -2709,7 +2709,7 @@
         <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2718,7 +2718,7 @@
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U9">
         <v>2.18</v>
@@ -2769,7 +2769,7 @@
         <v>21</v>
       </c>
       <c r="AK9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL9">
         <v>34</v>
@@ -2778,7 +2778,7 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO9">
         <v>70</v>
@@ -2793,7 +2793,7 @@
         <v>29</v>
       </c>
       <c r="AS9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
@@ -2805,7 +2805,7 @@
         <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2814,10 +2814,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB9">
         <v>16.5</v>
@@ -2826,16 +2826,16 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>8.4</v>
       </c>
       <c r="BE9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2847,55 +2847,55 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT9">
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
         <v>40</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="s">
         <v>124</v>
@@ -2918,13 +2918,13 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
         <v>7.4</v>
@@ -2933,7 +2933,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.32</v>
@@ -2948,40 +2948,40 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S10">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T10">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z10">
         <v>65</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
@@ -2990,10 +2990,10 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE10">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
@@ -3002,79 +3002,79 @@
         <v>10</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM10">
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AR10">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AS10">
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>9.6</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AW10">
         <v>36</v>
       </c>
       <c r="AX10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY10">
         <v>9</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA10">
         <v>34</v>
       </c>
       <c r="BB10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BE10">
         <v>38</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG10">
         <v>36</v>
@@ -3402,7 +3402,7 @@
         <v>118</v>
       </c>
       <c r="F12">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G12">
         <v>2.22</v>
@@ -3411,10 +3411,10 @@
         <v>3.25</v>
       </c>
       <c r="I12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3438,7 +3438,7 @@
         <v>1.45</v>
       </c>
       <c r="R12">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S12">
         <v>2.12</v>
@@ -3465,13 +3465,13 @@
         <v>34</v>
       </c>
       <c r="AA12">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="AB12">
         <v>19</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD12">
         <v>15.5</v>
@@ -3480,7 +3480,7 @@
         <v>34</v>
       </c>
       <c r="AF12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG12">
         <v>12</v>
@@ -3489,7 +3489,7 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
         <v>32</v>
@@ -3498,7 +3498,7 @@
         <v>19.5</v>
       </c>
       <c r="AL12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM12">
         <v>44</v>
@@ -3531,7 +3531,7 @@
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX12">
         <v>17</v>
@@ -3543,7 +3543,7 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB12">
         <v>19.5</v>
@@ -3647,19 +3647,19 @@
         <v>3.45</v>
       </c>
       <c r="G13">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H13">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.32</v>
@@ -3671,7 +3671,7 @@
         <v>4.8</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P13">
         <v>2.3</v>
@@ -3692,10 +3692,10 @@
         <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X13">
         <v>24</v>
@@ -3713,7 +3713,7 @@
         <v>21</v>
       </c>
       <c r="AC13">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD13">
         <v>11</v>
@@ -3761,7 +3761,7 @@
         <v>13</v>
       </c>
       <c r="AS13">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AT13">
         <v>15.5</v>
@@ -3785,7 +3785,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB13">
         <v>8.4</v>
@@ -3797,7 +3797,7 @@
         <v>8.4</v>
       </c>
       <c r="BE13">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF13">
         <v>21</v>
@@ -3886,19 +3886,19 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G14">
         <v>1.62</v>
       </c>
       <c r="H14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I14">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>5.3</v>
@@ -3934,7 +3934,7 @@
         <v>2.9</v>
       </c>
       <c r="V14">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W14">
         <v>2.6</v>
@@ -3943,7 +3943,7 @@
         <v>44</v>
       </c>
       <c r="Y14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -3952,10 +3952,10 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD14">
         <v>23</v>
@@ -3994,7 +3994,7 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AQ14">
         <v>32</v>
@@ -4039,13 +4039,13 @@
         <v>19</v>
       </c>
       <c r="BE14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF14">
         <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
@@ -4057,13 +4057,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>44</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
         <v>5.2</v>
@@ -4075,37 +4075,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ14">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
         <v>17.5</v>
       </c>
       <c r="BS14">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
         <v>10</v>
       </c>
       <c r="BU14">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>34</v>
       </c>
       <c r="BW14">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY14">
-        <v>23</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
         <v>9.800000000000001</v>
       </c>
       <c r="CA14">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>
@@ -4128,28 +4128,28 @@
         <v>121</v>
       </c>
       <c r="F15">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H15">
         <v>4.7</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J15">
         <v>4.3</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -4158,7 +4158,7 @@
         <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q15">
         <v>1.56</v>
@@ -4167,10 +4167,10 @@
         <v>1.68</v>
       </c>
       <c r="S15">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T15">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U15">
         <v>2.52</v>
@@ -4182,7 +4182,7 @@
         <v>2.26</v>
       </c>
       <c r="X15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y15">
         <v>27</v>
@@ -4194,7 +4194,7 @@
         <v>120</v>
       </c>
       <c r="AB15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC15">
         <v>10.5</v>
@@ -4224,7 +4224,7 @@
         <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM15">
         <v>65</v>
@@ -4233,7 +4233,7 @@
         <v>7.2</v>
       </c>
       <c r="AO15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP15">
         <v>21</v>
@@ -4257,7 +4257,7 @@
         <v>17</v>
       </c>
       <c r="AW15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX15">
         <v>12</v>
@@ -4269,10 +4269,10 @@
         <v>14</v>
       </c>
       <c r="BA15">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC15">
         <v>14</v>
@@ -4281,13 +4281,13 @@
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF15">
         <v>6.4</v>
       </c>
       <c r="BG15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH15">
         <v>4.7</v>
@@ -4299,13 +4299,13 @@
         <v>9.4</v>
       </c>
       <c r="BK15">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>21</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
         <v>5.1</v>
@@ -4317,37 +4317,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ15">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>21</v>
       </c>
       <c r="BS15">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
         <v>8.800000000000001</v>
       </c>
       <c r="BU15">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>34</v>
       </c>
       <c r="BW15">
-        <v>24</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>26</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
         <v>14</v>
       </c>
       <c r="CA15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4373,19 +4373,19 @@
         <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H16">
         <v>2.88</v>
       </c>
       <c r="I16">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.27</v>
@@ -4397,7 +4397,7 @@
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P16">
         <v>2.78</v>
@@ -4418,13 +4418,13 @@
         <v>2.84</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y16">
         <v>20</v>
@@ -4759,7 +4759,7 @@
         <v>20</v>
       </c>
       <c r="BC17">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BD17">
         <v>7.8</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 17:42:25</t>
+    <t>2026-07-21 19:49:04</t>
   </si>
 </sst>
 </file>
@@ -991,46 +991,46 @@
         <v>1.81</v>
       </c>
       <c r="I2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J2">
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W2">
         <v>1.2</v>
@@ -1039,7 +1039,7 @@
         <v>9.6</v>
       </c>
       <c r="Y2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z2">
         <v>10.5</v>
@@ -1057,7 +1057,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF2">
         <v>46</v>
@@ -1066,19 +1066,19 @@
         <v>25</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AK2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AL2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AM2">
         <v>260</v>
@@ -1087,121 +1087,121 @@
         <v>220</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP2">
         <v>8</v>
       </c>
       <c r="AQ2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
         <v>21</v>
       </c>
       <c r="AX2">
+        <v>34</v>
+      </c>
+      <c r="AY2">
+        <v>19.5</v>
+      </c>
+      <c r="AZ2">
+        <v>6.8</v>
+      </c>
+      <c r="BA2">
         <v>7.8</v>
       </c>
-      <c r="AY2">
-        <v>19</v>
-      </c>
-      <c r="AZ2">
+      <c r="BB2">
+        <v>8.6</v>
+      </c>
+      <c r="BC2">
+        <v>8.4</v>
+      </c>
+      <c r="BD2">
+        <v>8.4</v>
+      </c>
+      <c r="BE2">
+        <v>8.6</v>
+      </c>
+      <c r="BF2">
+        <v>8.6</v>
+      </c>
+      <c r="BG2">
+        <v>15</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.27</v>
+      </c>
+      <c r="BJ2">
+        <v>17.5</v>
+      </c>
+      <c r="BK2">
+        <v>1.19</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.27</v>
+      </c>
+      <c r="BN2">
+        <v>12.5</v>
+      </c>
+      <c r="BO2">
+        <v>5.4</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.26</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.27</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>2.88</v>
+      </c>
+      <c r="BV2">
         <v>21</v>
       </c>
-      <c r="BA2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG2">
-        <v>12.5</v>
-      </c>
-      <c r="BH2">
-        <v>2.9</v>
-      </c>
-      <c r="BI2">
-        <v>2.3</v>
-      </c>
-      <c r="BJ2">
-        <v>12.5</v>
-      </c>
-      <c r="BK2">
-        <v>5.8</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>10.5</v>
-      </c>
-      <c r="BN2">
-        <v>9</v>
-      </c>
-      <c r="BO2">
-        <v>6.6</v>
-      </c>
-      <c r="BP2">
-        <v>65</v>
-      </c>
-      <c r="BQ2">
-        <v>9.4</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>9.6</v>
-      </c>
-      <c r="BT2">
-        <v>4.4</v>
-      </c>
-      <c r="BU2">
-        <v>3.7</v>
-      </c>
-      <c r="BV2">
-        <v>15.5</v>
-      </c>
       <c r="BW2">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>8.6</v>
+        <v>1.25</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>1.27</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1251,7 +1251,7 @@
         <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
         <v>2.24</v>
@@ -1263,7 +1263,7 @@
         <v>1.49</v>
       </c>
       <c r="S3">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T3">
         <v>1.69</v>
@@ -1275,13 +1275,13 @@
         <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="X3">
         <v>19</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
         <v>32</v>
@@ -1299,7 +1299,7 @@
         <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AF3">
         <v>13.5</v>
@@ -1314,16 +1314,16 @@
         <v>48</v>
       </c>
       <c r="AJ3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>11</v>
@@ -1341,10 +1341,10 @@
         <v>28</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AT3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>8.199999999999999</v>
@@ -1353,7 +1353,7 @@
         <v>15</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AX3">
         <v>12</v>
@@ -1377,16 +1377,16 @@
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BF3">
         <v>10</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI3">
         <v>3.2</v>
@@ -1395,55 +1395,55 @@
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BP3">
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX3">
         <v>38</v>
       </c>
       <c r="BY3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>124</v>
@@ -1481,10 +1481,10 @@
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1508,7 +1508,7 @@
         <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U4">
         <v>1.9</v>
@@ -1526,28 +1526,28 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>570</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1565,16 +1565,16 @@
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>11</v>
@@ -1586,7 +1586,7 @@
         <v>55</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1610,19 +1610,19 @@
         <v>34</v>
       </c>
       <c r="BB4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BE4">
         <v>44</v>
       </c>
       <c r="BF4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
         <v>34</v>
@@ -1631,19 +1631,19 @@
         <v>2.96</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1652,40 +1652,40 @@
         <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>124</v>
@@ -1708,16 +1708,16 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
         <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J5">
         <v>3.4</v>
@@ -1726,19 +1726,19 @@
         <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
         <v>2.16</v>
@@ -1750,31 +1750,31 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>7.6</v>
@@ -1783,10 +1783,10 @@
         <v>16.5</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1801,16 +1801,16 @@
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM5">
         <v>130</v>
       </c>
       <c r="AN5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5">
         <v>60</v>
@@ -1819,13 +1819,13 @@
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1834,100 +1834,100 @@
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC5">
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ5">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BT5">
         <v>7</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="CB5" t="s">
         <v>124</v>
@@ -1959,7 +1959,7 @@
         <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1974,7 +1974,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.32</v>
@@ -1986,22 +1986,22 @@
         <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
         <v>2.94</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>15.5</v>
@@ -2010,13 +2010,13 @@
         <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA6">
         <v>13</v>
       </c>
       <c r="AB6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2025,31 +2025,31 @@
         <v>10.5</v>
       </c>
       <c r="AE6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG6">
         <v>32</v>
       </c>
       <c r="AH6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AK6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM6">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN6">
         <v>190</v>
@@ -2064,7 +2064,7 @@
         <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS6">
         <v>11.5</v>
@@ -2073,13 +2073,13 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX6">
         <v>60</v>
@@ -2088,88 +2088,88 @@
         <v>27</v>
       </c>
       <c r="AZ6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC6">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BE6">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BF6">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BT6">
         <v>3.85</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BW6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX6">
         <v>27</v>
       </c>
       <c r="BY6">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>124</v>
@@ -2195,13 +2195,13 @@
         <v>1.89</v>
       </c>
       <c r="G7">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2216,13 +2216,13 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
@@ -2231,7 +2231,7 @@
         <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T7">
         <v>1.9</v>
@@ -2240,16 +2240,16 @@
         <v>1.95</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X7">
         <v>14</v>
       </c>
       <c r="Y7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
         <v>36</v>
@@ -2258,31 +2258,31 @@
         <v>120</v>
       </c>
       <c r="AB7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AI7">
         <v>75</v>
       </c>
       <c r="AJ7">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AK7">
         <v>22</v>
@@ -2294,7 +2294,7 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO7">
         <v>100</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2333,25 +2333,25 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BB7">
         <v>19</v>
       </c>
       <c r="BC7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH7">
         <v>3.35</v>
@@ -2455,19 +2455,19 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
         <v>2.6</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
         <v>1.65</v>
@@ -2476,7 +2476,7 @@
         <v>2.44</v>
       </c>
       <c r="T8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U8">
         <v>2.68</v>
@@ -2488,19 +2488,19 @@
         <v>1.37</v>
       </c>
       <c r="X8">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y8">
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC8">
         <v>9.800000000000001</v>
@@ -2512,10 +2512,10 @@
         <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH8">
         <v>15</v>
@@ -2536,7 +2536,7 @@
         <v>60</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AO8">
         <v>9.4</v>
@@ -2548,7 +2548,7 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS8">
         <v>24</v>
@@ -2557,19 +2557,19 @@
         <v>19</v>
       </c>
       <c r="AU8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
         <v>10</v>
       </c>
       <c r="AW8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2581,10 +2581,10 @@
         <v>32</v>
       </c>
       <c r="BC8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE8">
         <v>46</v>
@@ -2605,13 +2605,13 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL8">
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2623,13 +2623,13 @@
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT8">
         <v>5.6</v>
@@ -2641,19 +2641,19 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8">
         <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>124</v>
@@ -2682,13 +2682,13 @@
         <v>1.87</v>
       </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
         <v>4.1</v>
@@ -2718,7 +2718,7 @@
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
         <v>2.18</v>
@@ -2736,10 +2736,10 @@
         <v>19</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA9">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB9">
         <v>10.5</v>
@@ -2748,10 +2748,10 @@
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF9">
         <v>12</v>
@@ -2763,7 +2763,7 @@
         <v>19</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
         <v>21</v>
@@ -2781,16 +2781,16 @@
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR9">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AS9">
         <v>10</v>
@@ -2802,10 +2802,10 @@
         <v>8</v>
       </c>
       <c r="AV9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2814,28 +2814,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC9">
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2859,7 +2859,7 @@
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
         <v>12.5</v>
@@ -2880,7 +2880,7 @@
         <v>4.8</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
         <v>8.6</v>
@@ -2918,25 +2918,25 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -2945,43 +2945,43 @@
         <v>5.2</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
         <v>1.81</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA10">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
@@ -2990,10 +2990,10 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
@@ -3008,25 +3008,25 @@
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK10">
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ10">
         <v>26</v>
@@ -3038,10 +3038,10 @@
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
         <v>23</v>
@@ -3068,76 +3068,76 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BE10">
         <v>38</v>
       </c>
       <c r="BF10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10">
         <v>36</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BI10">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BN10">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BP10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BT10">
         <v>11</v>
       </c>
       <c r="BU10">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="BV10">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BW10">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX10">
         <v>55</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
         <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
         <v>124</v>
@@ -3172,7 +3172,7 @@
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
         <v>5.4</v>
@@ -3202,7 +3202,7 @@
         <v>2.48</v>
       </c>
       <c r="T11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
         <v>2.08</v>
@@ -3223,7 +3223,7 @@
         <v>70</v>
       </c>
       <c r="AA11">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
@@ -3232,10 +3232,10 @@
         <v>13</v>
       </c>
       <c r="AD11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AF11">
         <v>12</v>
@@ -3244,22 +3244,22 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI11">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN11">
         <v>7.2</v>
@@ -3268,40 +3268,40 @@
         <v>100</v>
       </c>
       <c r="AP11">
+        <v>18</v>
+      </c>
+      <c r="AQ11">
+        <v>20</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11">
+        <v>8.6</v>
+      </c>
+      <c r="AV11">
         <v>19.5</v>
       </c>
-      <c r="AQ11">
-        <v>21</v>
-      </c>
-      <c r="AR11">
-        <v>1.03</v>
-      </c>
-      <c r="AS11">
-        <v>1.03</v>
-      </c>
-      <c r="AT11">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU11">
-        <v>9</v>
-      </c>
-      <c r="AV11">
-        <v>1.03</v>
-      </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AY11">
         <v>8</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3310,10 +3310,10 @@
         <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>1.05</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>5</v>
@@ -3414,7 +3414,7 @@
         <v>3.4</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3426,13 +3426,13 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O12">
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
         <v>1.45</v>
@@ -3441,31 +3441,31 @@
         <v>1.86</v>
       </c>
       <c r="S12">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U12">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X12">
+        <v>38</v>
+      </c>
+      <c r="Y12">
+        <v>27</v>
+      </c>
+      <c r="Z12">
         <v>36</v>
       </c>
-      <c r="Y12">
-        <v>25</v>
-      </c>
-      <c r="Z12">
-        <v>34</v>
-      </c>
       <c r="AA12">
-        <v>450</v>
+        <v>520</v>
       </c>
       <c r="AB12">
         <v>19</v>
@@ -3477,7 +3477,7 @@
         <v>15.5</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12">
         <v>21</v>
@@ -3486,7 +3486,7 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI12">
         <v>32</v>
@@ -3501,13 +3501,13 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN12">
         <v>8.4</v>
       </c>
       <c r="AO12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP12">
         <v>22</v>
@@ -3516,7 +3516,7 @@
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AS12">
         <v>29</v>
@@ -3528,10 +3528,10 @@
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX12">
         <v>17</v>
@@ -3540,22 +3540,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA12">
         <v>19</v>
       </c>
       <c r="BB12">
+        <v>20</v>
+      </c>
+      <c r="BC12">
+        <v>16</v>
+      </c>
+      <c r="BD12">
         <v>19.5</v>
       </c>
-      <c r="BC12">
-        <v>16.5</v>
-      </c>
-      <c r="BD12">
-        <v>20</v>
-      </c>
       <c r="BE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF12">
         <v>7.8</v>
@@ -3567,10 +3567,10 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BJ12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BK12">
         <v>5.4</v>
@@ -3579,49 +3579,49 @@
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BN12">
         <v>7.8</v>
       </c>
       <c r="BO12">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP12">
         <v>19</v>
       </c>
       <c r="BQ12">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BR12">
         <v>28</v>
       </c>
       <c r="BS12">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="BT12">
         <v>9.800000000000001</v>
       </c>
       <c r="BU12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV12">
         <v>29</v>
       </c>
       <c r="BW12">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BX12">
         <v>34</v>
       </c>
       <c r="BY12">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12">
         <v>17</v>
       </c>
       <c r="CA12">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3644,22 +3644,22 @@
         <v>119</v>
       </c>
       <c r="F13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G13">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H13">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="I13">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
         <v>3.75</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
         <v>1.32</v>
@@ -3668,13 +3668,13 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
         <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
         <v>1.71</v>
@@ -3686,46 +3686,46 @@
         <v>2.8</v>
       </c>
       <c r="T13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U13">
         <v>2.44</v>
       </c>
       <c r="V13">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z13">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AA13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB13">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AC13">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE13">
         <v>21</v>
       </c>
       <c r="AF13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH13">
         <v>15.5</v>
@@ -3734,136 +3734,136 @@
         <v>30</v>
       </c>
       <c r="AJ13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AO13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AP13">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU13">
         <v>8</v>
       </c>
       <c r="AV13">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY13">
         <v>13</v>
       </c>
       <c r="AZ13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA13">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BB13">
-        <v>8.4</v>
+        <v>50</v>
       </c>
       <c r="BC13">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD13">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BE13">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BF13">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3886,22 +3886,22 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H14">
         <v>5.3</v>
       </c>
       <c r="I14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
         <v>1.22</v>
@@ -3931,19 +3931,19 @@
         <v>1.49</v>
       </c>
       <c r="U14">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V14">
         <v>1.21</v>
       </c>
       <c r="W14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y14">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="Z14">
         <v>60</v>
@@ -3952,7 +3952,7 @@
         <v>1000</v>
       </c>
       <c r="AB14">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC14">
         <v>13.5</v>
@@ -3970,13 +3970,13 @@
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI14">
         <v>110</v>
       </c>
       <c r="AJ14">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK14">
         <v>14.5</v>
@@ -4000,7 +4000,7 @@
         <v>32</v>
       </c>
       <c r="AR14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS14">
         <v>42</v>
@@ -4027,13 +4027,13 @@
         <v>15</v>
       </c>
       <c r="BA14">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BB14">
         <v>16.5</v>
       </c>
       <c r="BC14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD14">
         <v>19</v>
@@ -4045,7 +4045,7 @@
         <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
@@ -4057,55 +4057,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN14">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO14">
         <v>3.9</v>
       </c>
       <c r="BP14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR14">
         <v>17.5</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT14">
         <v>10</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV14">
+        <v>36</v>
+      </c>
+      <c r="BW14">
+        <v>7.8</v>
+      </c>
+      <c r="BX14">
         <v>34</v>
       </c>
-      <c r="BW14">
-        <v>1.04</v>
-      </c>
-      <c r="BX14">
-        <v>32</v>
-      </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ14">
         <v>9.800000000000001</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>
@@ -4128,13 +4128,13 @@
         <v>121</v>
       </c>
       <c r="F15">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G15">
         <v>1.79</v>
       </c>
       <c r="H15">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I15">
         <v>4.9</v>
@@ -4164,34 +4164,34 @@
         <v>1.56</v>
       </c>
       <c r="R15">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T15">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U15">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W15">
         <v>2.26</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z15">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AA15">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
         <v>14</v>
@@ -4200,10 +4200,10 @@
         <v>10.5</v>
       </c>
       <c r="AD15">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AF15">
         <v>14</v>
@@ -4215,19 +4215,19 @@
         <v>16.5</v>
       </c>
       <c r="AI15">
-        <v>50</v>
+        <v>140</v>
       </c>
       <c r="AJ15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK15">
         <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
         <v>7.2</v>
@@ -4236,31 +4236,31 @@
         <v>44</v>
       </c>
       <c r="AP15">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AQ15">
         <v>21</v>
       </c>
       <c r="AR15">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AS15">
+        <v>38</v>
+      </c>
+      <c r="AT15">
+        <v>12</v>
+      </c>
+      <c r="AU15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV15">
+        <v>16.5</v>
+      </c>
+      <c r="AW15">
+        <v>26</v>
+      </c>
+      <c r="AX15">
         <v>11.5</v>
-      </c>
-      <c r="AT15">
-        <v>11.5</v>
-      </c>
-      <c r="AU15">
-        <v>9</v>
-      </c>
-      <c r="AV15">
-        <v>17</v>
-      </c>
-      <c r="AW15">
-        <v>10</v>
-      </c>
-      <c r="AX15">
-        <v>12</v>
       </c>
       <c r="AY15">
         <v>9.4</v>
@@ -4269,85 +4269,85 @@
         <v>14</v>
       </c>
       <c r="BA15">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="BB15">
         <v>16.5</v>
       </c>
       <c r="BC15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD15">
         <v>21</v>
       </c>
       <c r="BE15">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BF15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BH15">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.65</v>
+        <v>1.29</v>
       </c>
       <c r="BJ15">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BN15">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.9</v>
+        <v>1.29</v>
       </c>
       <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.29</v>
+      </c>
+      <c r="BR15">
+        <v>28</v>
+      </c>
+      <c r="BS15">
+        <v>1.24</v>
+      </c>
+      <c r="BT15">
         <v>11.5</v>
       </c>
-      <c r="BQ15">
-        <v>1.04</v>
-      </c>
-      <c r="BR15">
-        <v>21</v>
-      </c>
-      <c r="BS15">
-        <v>1.04</v>
-      </c>
-      <c r="BT15">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="BV15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BZ15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4370,7 +4370,7 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G16">
         <v>2.48</v>
@@ -4379,7 +4379,7 @@
         <v>2.88</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J16">
         <v>3.95</v>
@@ -4397,13 +4397,13 @@
         <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
         <v>2.78</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R16">
         <v>1.72</v>
@@ -4418,25 +4418,25 @@
         <v>2.84</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X16">
         <v>30</v>
       </c>
       <c r="Y16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z16">
         <v>26</v>
       </c>
       <c r="AA16">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC16">
         <v>10.5</v>
@@ -4445,7 +4445,7 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF16">
         <v>21</v>
@@ -4454,22 +4454,22 @@
         <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI16">
         <v>32</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AK16">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN16">
         <v>11.5</v>
@@ -4478,7 +4478,7 @@
         <v>16</v>
       </c>
       <c r="AP16">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4487,19 +4487,19 @@
         <v>20</v>
       </c>
       <c r="AS16">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AT16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16">
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AX16">
         <v>17.5</v>
@@ -4508,28 +4508,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ16">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA16">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="BB16">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BE16">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF16">
         <v>10</v>
       </c>
       <c r="BG16">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH16">
         <v>4.9</v>
@@ -4541,7 +4541,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
@@ -4571,7 +4571,7 @@
         <v>7</v>
       </c>
       <c r="BU16">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
         <v>20</v>
@@ -4589,7 +4589,7 @@
         <v>15</v>
       </c>
       <c r="CA16">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="s">
         <v>124</v>
@@ -4612,22 +4612,22 @@
         <v>123</v>
       </c>
       <c r="F17">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H17">
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4639,7 +4639,7 @@
         <v>5.6</v>
       </c>
       <c r="O17">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P17">
         <v>2.56</v>
@@ -4651,22 +4651,22 @@
         <v>1.62</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T17">
         <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="X17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y17">
         <v>21</v>
@@ -4675,76 +4675,76 @@
         <v>32</v>
       </c>
       <c r="AA17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC17">
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF17">
         <v>16</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK17">
         <v>20</v>
       </c>
       <c r="AL17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP17">
         <v>20</v>
       </c>
       <c r="AQ17">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR17">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="AS17">
-        <v>9.4</v>
+        <v>50</v>
       </c>
       <c r="AT17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU17">
         <v>8.6</v>
       </c>
       <c r="AV17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW17">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX17">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY17">
         <v>9.800000000000001</v>
@@ -4753,67 +4753,67 @@
         <v>13.5</v>
       </c>
       <c r="BA17">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BB17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BE17">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH17">
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BJ17">
         <v>12</v>
       </c>
       <c r="BK17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="BN17">
         <v>7</v>
       </c>
       <c r="BO17">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="BP17">
         <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="BR17">
         <v>30</v>
       </c>
       <c r="BS17">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="BT17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV17">
         <v>34</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -388,7 +388,7 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 19:49:04</t>
+    <t>2026-07-21 21:55:49</t>
   </si>
 </sst>
 </file>
@@ -994,7 +994,7 @@
         <v>1.94</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
         <v>3.65</v>
@@ -1006,7 +1006,7 @@
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
         <v>1.49</v>
@@ -1024,7 +1024,7 @@
         <v>4.8</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
         <v>1.7</v>
@@ -1039,13 +1039,13 @@
         <v>9.6</v>
       </c>
       <c r="Y2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB2">
         <v>14.5</v>
@@ -1057,10 +1057,10 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AG2">
         <v>25</v>
@@ -1087,7 +1087,7 @@
         <v>220</v>
       </c>
       <c r="AO2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP2">
         <v>8</v>
@@ -1099,7 +1099,7 @@
         <v>8.6</v>
       </c>
       <c r="AS2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT2">
         <v>11.5</v>
@@ -1114,31 +1114,31 @@
         <v>21</v>
       </c>
       <c r="AX2">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="AY2">
         <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BC2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BG2">
         <v>15</v>
@@ -1147,19 +1147,19 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BJ2">
         <v>17.5</v>
       </c>
       <c r="BK2">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BN2">
         <v>12.5</v>
@@ -1171,16 +1171,16 @@
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU2">
         <v>2.88</v>
@@ -1189,19 +1189,19 @@
         <v>21</v>
       </c>
       <c r="BW2">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1263,7 +1263,7 @@
         <v>1.49</v>
       </c>
       <c r="S3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T3">
         <v>1.69</v>
@@ -1272,7 +1272,7 @@
         <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.99</v>
@@ -1472,7 +1472,7 @@
         <v>2.12</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
         <v>4.4</v>
@@ -1496,10 +1496,10 @@
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1526,7 +1526,7 @@
         <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1541,13 +1541,13 @@
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1574,7 +1574,7 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
         <v>11</v>
@@ -1583,10 +1583,10 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
         <v>7</v>
@@ -1610,7 +1610,7 @@
         <v>34</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC4">
         <v>19</v>
@@ -1631,19 +1631,19 @@
         <v>2.96</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1652,16 +1652,16 @@
         <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
@@ -1673,19 +1673,19 @@
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>124</v>
@@ -1717,7 +1717,7 @@
         <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>3.4</v>
@@ -1729,16 +1729,16 @@
         <v>1.45</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
         <v>2.16</v>
@@ -1753,7 +1753,7 @@
         <v>1.91</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1762,7 +1762,7 @@
         <v>1.73</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>12</v>
@@ -1771,22 +1771,22 @@
         <v>24</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>820</v>
       </c>
       <c r="AB5">
         <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1795,37 +1795,37 @@
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5">
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="AT5">
         <v>8.4</v>
@@ -1837,37 +1837,37 @@
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AX5">
         <v>12</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BC5">
         <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BF5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1894,7 +1894,7 @@
         <v>4.4</v>
       </c>
       <c r="BP5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ5">
         <v>6.6</v>
@@ -1915,19 +1915,19 @@
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>124</v>
@@ -1950,10 +1950,10 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H6">
         <v>1.5</v>
@@ -1965,7 +1965,7 @@
         <v>4.5</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -1974,7 +1974,7 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
         <v>1.32</v>
@@ -1986,7 +1986,7 @@
         <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
         <v>3.35</v>
@@ -1998,19 +1998,19 @@
         <v>1.83</v>
       </c>
       <c r="V6">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y6">
         <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA6">
         <v>13</v>
@@ -2022,7 +2022,7 @@
         <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE6">
         <v>16.5</v>
@@ -2037,7 +2037,7 @@
         <v>27</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ6">
         <v>340</v>
@@ -2076,7 +2076,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>15</v>
@@ -2097,16 +2097,16 @@
         <v>16.5</v>
       </c>
       <c r="BC6">
+        <v>15.5</v>
+      </c>
+      <c r="BD6">
+        <v>15</v>
+      </c>
+      <c r="BE6">
+        <v>15.5</v>
+      </c>
+      <c r="BF6">
         <v>16</v>
-      </c>
-      <c r="BD6">
-        <v>15.5</v>
-      </c>
-      <c r="BE6">
-        <v>16</v>
-      </c>
-      <c r="BF6">
-        <v>16.5</v>
       </c>
       <c r="BG6">
         <v>7.4</v>
@@ -2192,7 +2192,7 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G7">
         <v>1.94</v>
@@ -2222,13 +2222,13 @@
         <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
         <v>3.75</v>
@@ -2264,7 +2264,7 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE7">
         <v>70</v>
@@ -2294,7 +2294,7 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO7">
         <v>100</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2345,7 +2345,7 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF7">
         <v>13</v>
@@ -2393,7 +2393,7 @@
         <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BV7">
         <v>44</v>
@@ -2461,7 +2461,7 @@
         <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
         <v>2.6</v>
@@ -2509,19 +2509,19 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF8">
         <v>30</v>
       </c>
       <c r="AG8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH8">
         <v>15</v>
       </c>
       <c r="AI8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2533,10 +2533,10 @@
         <v>38</v>
       </c>
       <c r="AM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN8">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AO8">
         <v>9.4</v>
@@ -2587,7 +2587,7 @@
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF8">
         <v>21</v>
@@ -2611,7 +2611,7 @@
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2629,7 +2629,7 @@
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
         <v>5.6</v>
@@ -2641,16 +2641,16 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA8">
         <v>6</v>
@@ -2679,7 +2679,7 @@
         <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2688,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K9">
         <v>4.1</v>
@@ -2727,16 +2727,16 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
         <v>18</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z9">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA9">
         <v>130</v>
@@ -2790,7 +2790,7 @@
         <v>16</v>
       </c>
       <c r="AR9">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AS9">
         <v>10</v>
@@ -2805,7 +2805,7 @@
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB9">
         <v>17</v>
@@ -2829,13 +2829,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2877,7 +2877,7 @@
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV9">
         <v>1000</v>
@@ -2927,7 +2927,7 @@
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -2966,7 +2966,7 @@
         <v>2.18</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -2978,7 +2978,7 @@
         <v>28</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA10">
         <v>200</v>
@@ -2990,13 +2990,13 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE10">
         <v>90</v>
       </c>
       <c r="AF10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>100</v>
       </c>
       <c r="AN10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
         <v>90</v>
@@ -3038,7 +3038,7 @@
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>9.800000000000001</v>
@@ -3059,10 +3059,10 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
@@ -3101,7 +3101,7 @@
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP10">
         <v>9.6</v>
@@ -3274,10 +3274,10 @@
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT11">
         <v>8.199999999999999</v>
@@ -3289,7 +3289,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX11">
         <v>8</v>
@@ -3301,7 +3301,7 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3310,16 +3310,16 @@
         <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF11">
         <v>5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH11">
         <v>4.5</v>
@@ -3405,7 +3405,7 @@
         <v>2.14</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
         <v>3.25</v>
@@ -3414,7 +3414,7 @@
         <v>3.4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3426,7 +3426,7 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O12">
         <v>1.14</v>
@@ -3450,16 +3450,16 @@
         <v>3.15</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
         <v>38</v>
       </c>
       <c r="Y12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z12">
         <v>36</v>
@@ -3468,7 +3468,7 @@
         <v>520</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC12">
         <v>11</v>
@@ -3492,7 +3492,7 @@
         <v>32</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AK12">
         <v>19.5</v>
@@ -3501,7 +3501,7 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AN12">
         <v>8.4</v>
@@ -3540,13 +3540,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA12">
         <v>19</v>
       </c>
       <c r="BB12">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BC12">
         <v>16</v>
@@ -3555,7 +3555,7 @@
         <v>19.5</v>
       </c>
       <c r="BE12">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BF12">
         <v>7.8</v>
@@ -3647,19 +3647,19 @@
         <v>3.4</v>
       </c>
       <c r="G13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I13">
         <v>2.26</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
         <v>1.32</v>
@@ -3668,7 +3668,7 @@
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>1.24</v>
@@ -3677,7 +3677,7 @@
         <v>2.32</v>
       </c>
       <c r="Q13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
         <v>1.52</v>
@@ -3689,10 +3689,10 @@
         <v>1.61</v>
       </c>
       <c r="U13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W13">
         <v>1.4</v>
@@ -3710,10 +3710,10 @@
         <v>28</v>
       </c>
       <c r="AB13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD13">
         <v>11.5</v>
@@ -3746,7 +3746,7 @@
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO13">
         <v>12.5</v>
@@ -3788,7 +3788,7 @@
         <v>27</v>
       </c>
       <c r="BB13">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC13">
         <v>30</v>
@@ -3803,7 +3803,7 @@
         <v>23</v>
       </c>
       <c r="BG13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3931,7 +3931,7 @@
         <v>1.49</v>
       </c>
       <c r="U14">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="V14">
         <v>1.21</v>
@@ -3994,7 +3994,7 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AQ14">
         <v>32</v>
@@ -4045,7 +4045,7 @@
         <v>4.5</v>
       </c>
       <c r="BG14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
@@ -4134,7 +4134,7 @@
         <v>1.79</v>
       </c>
       <c r="H15">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I15">
         <v>4.9</v>
@@ -4149,7 +4149,7 @@
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -4176,7 +4176,7 @@
         <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
         <v>2.26</v>
@@ -4188,7 +4188,7 @@
         <v>26</v>
       </c>
       <c r="Z15">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4203,10 +4203,10 @@
         <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AF15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG15">
         <v>10.5</v>
@@ -4218,7 +4218,7 @@
         <v>140</v>
       </c>
       <c r="AJ15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK15">
         <v>16.5</v>
@@ -4239,7 +4239,7 @@
         <v>18.5</v>
       </c>
       <c r="AQ15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR15">
         <v>30</v>
@@ -4248,7 +4248,7 @@
         <v>38</v>
       </c>
       <c r="AT15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
@@ -4269,10 +4269,10 @@
         <v>14</v>
       </c>
       <c r="BA15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB15">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC15">
         <v>13.5</v>
@@ -4293,61 +4293,61 @@
         <v>1000</v>
       </c>
       <c r="BI15">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="BJ15">
         <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO15">
-        <v>1.29</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ15">
-        <v>1.29</v>
+        <v>1.87</v>
       </c>
       <c r="BR15">
         <v>28</v>
       </c>
       <c r="BS15">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="BT15">
         <v>11.5</v>
       </c>
       <c r="BU15">
-        <v>1.16</v>
+        <v>1.79</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW15">
-        <v>1.29</v>
+        <v>2.02</v>
       </c>
       <c r="BX15">
         <v>48</v>
       </c>
       <c r="BY15">
-        <v>1.26</v>
+        <v>2.04</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA15">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="CB15" t="s">
         <v>124</v>
@@ -4370,10 +4370,10 @@
         <v>122</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H16">
         <v>2.88</v>
@@ -4394,7 +4394,7 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O16">
         <v>1.17</v>
@@ -4502,7 +4502,7 @@
         <v>6.8</v>
       </c>
       <c r="AX16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4544,7 +4544,7 @@
         <v>4.5</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM16">
         <v>8.4</v>
@@ -4612,7 +4612,7 @@
         <v>123</v>
       </c>
       <c r="F17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G17">
         <v>2.14</v>
@@ -4621,7 +4621,7 @@
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4636,13 +4636,13 @@
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O17">
         <v>1.2</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q17">
         <v>1.61</v>
@@ -4657,10 +4657,10 @@
         <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.88</v>
@@ -4669,19 +4669,19 @@
         <v>24</v>
       </c>
       <c r="Y17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z17">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB17">
         <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD17">
         <v>15.5</v>
@@ -4699,7 +4699,7 @@
         <v>15.5</v>
       </c>
       <c r="AI17">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ17">
         <v>27</v>
@@ -4720,7 +4720,7 @@
         <v>26</v>
       </c>
       <c r="AP17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ17">
         <v>18</v>
@@ -4732,7 +4732,7 @@
         <v>50</v>
       </c>
       <c r="AT17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU17">
         <v>8.6</v>
@@ -4741,13 +4741,13 @@
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX17">
         <v>14</v>
       </c>
       <c r="AY17">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
         <v>13.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="145">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>US United Soccer League</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
     <t>2026-07-23</t>
   </si>
   <si>
@@ -292,6 +295,15 @@
     <t>02:30:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Manta FC</t>
   </si>
   <si>
@@ -322,12 +334,12 @@
     <t>Colorado Switchbacks FC</t>
   </si>
   <si>
+    <t>Austin FC</t>
+  </si>
+  <si>
     <t>Colorado</t>
   </si>
   <si>
-    <t>Austin FC</t>
-  </si>
-  <si>
     <t>San Jose Earthquakes</t>
   </si>
   <si>
@@ -340,6 +352,30 @@
     <t>LA Galaxy</t>
   </si>
   <si>
+    <t>Orense Sporting Club</t>
+  </si>
+  <si>
+    <t>CD Leones del Norte</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>Sarmiento de Junin</t>
+  </si>
+  <si>
+    <t>Belgrano</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>Botafogo FR</t>
+  </si>
+  <si>
+    <t>Cuiaba</t>
+  </si>
+  <si>
     <t>LDU</t>
   </si>
   <si>
@@ -370,12 +406,12 @@
     <t>Miami FC</t>
   </si>
   <si>
+    <t>Seattle Sounders</t>
+  </si>
+  <si>
     <t>San Diego FC</t>
   </si>
   <si>
-    <t>Seattle Sounders</t>
-  </si>
-  <si>
     <t>Orlando City</t>
   </si>
   <si>
@@ -388,7 +424,31 @@
     <t>St Louis City SC</t>
   </si>
   <si>
-    <t>2026-07-21 21:55:49</t>
+    <t>Aucas</t>
+  </si>
+  <si>
+    <t>Guayaquil City</t>
+  </si>
+  <si>
+    <t>Sao Bernardo</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>2026-07-22 00:03:14</t>
   </si>
 </sst>
 </file>
@@ -720,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -970,16 +1030,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>5.2</v>
@@ -991,7 +1051,7 @@
         <v>1.81</v>
       </c>
       <c r="I2">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J2">
         <v>3.2</v>
@@ -1009,7 +1069,7 @@
         <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
         <v>1.55</v>
@@ -1021,7 +1081,7 @@
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T2">
         <v>2.2</v>
@@ -1060,7 +1120,7 @@
         <v>26</v>
       </c>
       <c r="AF2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AG2">
         <v>25</v>
@@ -1114,22 +1174,22 @@
         <v>21</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="AY2">
         <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>10</v>
       </c>
       <c r="BC2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BD2">
         <v>9.800000000000001</v>
@@ -1162,7 +1222,7 @@
         <v>1.67</v>
       </c>
       <c r="BN2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BO2">
         <v>5.4</v>
@@ -1180,7 +1240,7 @@
         <v>1.67</v>
       </c>
       <c r="BT2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU2">
         <v>2.88</v>
@@ -1195,16 +1255,16 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CB2" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1212,16 +1272,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="F3">
         <v>1.99</v>
@@ -1248,13 +1308,13 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
         <v>1.76</v>
@@ -1266,7 +1326,7 @@
         <v>2.92</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
         <v>2.38</v>
@@ -1281,7 +1341,7 @@
         <v>19</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>32</v>
@@ -1302,7 +1362,7 @@
         <v>120</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1320,13 +1380,13 @@
         <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
         <v>38</v>
@@ -1413,7 +1473,7 @@
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
         <v>25</v>
@@ -1425,7 +1485,7 @@
         <v>7.6</v>
       </c>
       <c r="BU3">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
         <v>30</v>
@@ -1446,7 +1506,7 @@
         <v>7.2</v>
       </c>
       <c r="CB3" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1454,16 +1514,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F4">
         <v>2.08</v>
@@ -1568,13 +1628,13 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO4">
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>11</v>
@@ -1583,7 +1643,7 @@
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1610,7 +1670,7 @@
         <v>34</v>
       </c>
       <c r="BB4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC4">
         <v>19</v>
@@ -1688,7 +1748,7 @@
         <v>12.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1696,16 +1756,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="F5">
         <v>2.32</v>
@@ -1714,10 +1774,10 @@
         <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J5">
         <v>3.4</v>
@@ -1732,7 +1792,7 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
         <v>1.38</v>
@@ -1741,7 +1801,7 @@
         <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1750,28 +1810,28 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
         <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
         <v>1.73</v>
       </c>
       <c r="X5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5">
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA5">
-        <v>820</v>
+        <v>65</v>
       </c>
       <c r="AB5">
         <v>9.199999999999999</v>
@@ -1780,10 +1840,10 @@
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>14</v>
@@ -1795,7 +1855,7 @@
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ5">
         <v>32</v>
@@ -1807,67 +1867,67 @@
         <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN5">
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP5">
         <v>11</v>
       </c>
       <c r="AQ5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV5">
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AX5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE5">
         <v>40</v>
       </c>
       <c r="BF5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1930,7 +1990,7 @@
         <v>8</v>
       </c>
       <c r="CB5" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1938,28 +1998,28 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="F6">
         <v>8.199999999999999</v>
       </c>
       <c r="G6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
         <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -1980,25 +2040,25 @@
         <v>1.32</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
         <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
         <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W6">
         <v>1.13</v>
@@ -2034,10 +2094,10 @@
         <v>32</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
         <v>340</v>
@@ -2049,19 +2109,19 @@
         <v>140</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN6">
         <v>190</v>
       </c>
       <c r="AO6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AP6">
         <v>13.5</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AR6">
         <v>7.8</v>
@@ -2094,22 +2154,22 @@
         <v>34</v>
       </c>
       <c r="BB6">
+        <v>17</v>
+      </c>
+      <c r="BC6">
+        <v>17</v>
+      </c>
+      <c r="BD6">
         <v>16.5</v>
       </c>
-      <c r="BC6">
-        <v>15.5</v>
-      </c>
-      <c r="BD6">
-        <v>15</v>
-      </c>
       <c r="BE6">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF6">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
         <v>3.6</v>
@@ -2172,7 +2232,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2180,25 +2240,25 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="G7">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7">
         <v>4.8</v>
@@ -2216,7 +2276,7 @@
         <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
         <v>1.35</v>
@@ -2228,16 +2288,16 @@
         <v>2.04</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.75</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>1.26</v>
@@ -2246,13 +2306,13 @@
         <v>2.06</v>
       </c>
       <c r="X7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y7">
         <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2264,13 +2324,13 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
         <v>70</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2282,7 +2342,7 @@
         <v>75</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
         <v>22</v>
@@ -2294,10 +2354,10 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2309,7 +2369,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2339,82 +2399,82 @@
         <v>19</v>
       </c>
       <c r="BC7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG7">
         <v>55</v>
       </c>
       <c r="BH7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BV7">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BW7">
         <v>8.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
         <v>8.6</v>
       </c>
       <c r="BZ7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2422,19 +2482,19 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
         <v>3.7</v>
@@ -2455,13 +2515,13 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
         <v>2.6</v>
@@ -2473,10 +2533,10 @@
         <v>1.65</v>
       </c>
       <c r="S8">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U8">
         <v>2.68</v>
@@ -2494,16 +2554,16 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2533,7 +2593,7 @@
         <v>38</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2566,7 +2626,7 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY8">
         <v>14.5</v>
@@ -2656,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="CB8" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2664,16 +2724,16 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="F9">
         <v>1.83</v>
@@ -2700,16 +2760,16 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
         <v>1.44</v>
@@ -2754,7 +2814,7 @@
         <v>70</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>10.5</v>
@@ -2763,7 +2823,7 @@
         <v>19</v>
       </c>
       <c r="AI9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
         <v>21</v>
@@ -2781,7 +2841,7 @@
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP9">
         <v>14.5</v>
@@ -2793,7 +2853,7 @@
         <v>32</v>
       </c>
       <c r="AS9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
@@ -2805,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2817,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB9">
         <v>17</v>
@@ -2826,16 +2886,16 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2847,58 +2907,58 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU9">
+        <v>4.8</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>8.4</v>
+      </c>
+      <c r="BX9">
+        <v>48</v>
+      </c>
+      <c r="BY9">
         <v>8.6</v>
-      </c>
-      <c r="BU9">
-        <v>6.4</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>8.6</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2906,28 +2966,28 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F10">
         <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
         <v>6.8</v>
       </c>
       <c r="I10">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -2942,10 +3002,10 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
         <v>2.44</v>
@@ -2966,7 +3026,7 @@
         <v>2.18</v>
       </c>
       <c r="V10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
         <v>2.84</v>
@@ -2975,13 +3035,13 @@
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="AA10">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
         <v>10.5</v>
@@ -2996,7 +3056,7 @@
         <v>90</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG10">
         <v>10</v>
@@ -3014,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM10">
         <v>100</v>
@@ -3059,10 +3119,10 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BB10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
@@ -3074,7 +3134,7 @@
         <v>38</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG10">
         <v>36</v>
@@ -3089,7 +3149,7 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3140,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="CB10" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3148,19 +3208,19 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G11">
         <v>1.59</v>
@@ -3169,13 +3229,13 @@
         <v>6.2</v>
       </c>
       <c r="I11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>4.6</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L11">
         <v>1.26</v>
@@ -3184,7 +3244,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>1.2</v>
@@ -3193,10 +3253,10 @@
         <v>2.38</v>
       </c>
       <c r="Q11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11">
         <v>2.48</v>
@@ -3205,7 +3265,7 @@
         <v>1.75</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V11">
         <v>1.13</v>
@@ -3223,7 +3283,7 @@
         <v>70</v>
       </c>
       <c r="AA11">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
@@ -3244,7 +3304,7 @@
         <v>12</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11">
         <v>85</v>
@@ -3256,7 +3316,7 @@
         <v>18</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -3265,7 +3325,7 @@
         <v>7.2</v>
       </c>
       <c r="AO11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP11">
         <v>18</v>
@@ -3274,10 +3334,10 @@
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT11">
         <v>8.199999999999999</v>
@@ -3289,7 +3349,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX11">
         <v>8</v>
@@ -3301,7 +3361,7 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3313,16 +3373,16 @@
         <v>4.5</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF11">
         <v>5</v>
       </c>
       <c r="BG11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
         <v>3.5</v>
@@ -3331,13 +3391,13 @@
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN11">
         <v>4.4</v>
@@ -3349,40 +3409,40 @@
         <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR11">
         <v>22</v>
       </c>
       <c r="BS11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT11">
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11">
         <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3390,241 +3450,241 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>3.45</v>
       </c>
       <c r="H12">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="I12">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L12">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N12">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q12">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="R12">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="T12">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="U12">
-        <v>3.15</v>
+        <v>2.46</v>
       </c>
       <c r="V12">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Y12">
+        <v>13</v>
+      </c>
+      <c r="Z12">
+        <v>16</v>
+      </c>
+      <c r="AA12">
+        <v>28</v>
+      </c>
+      <c r="AB12">
+        <v>17</v>
+      </c>
+      <c r="AC12">
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <v>11.5</v>
+      </c>
+      <c r="AE12">
+        <v>21</v>
+      </c>
+      <c r="AF12">
+        <v>27</v>
+      </c>
+      <c r="AG12">
+        <v>15</v>
+      </c>
+      <c r="AH12">
+        <v>15.5</v>
+      </c>
+      <c r="AI12">
+        <v>30</v>
+      </c>
+      <c r="AJ12">
+        <v>60</v>
+      </c>
+      <c r="AK12">
+        <v>36</v>
+      </c>
+      <c r="AL12">
+        <v>40</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
         <v>26</v>
       </c>
-      <c r="Z12">
-        <v>36</v>
-      </c>
-      <c r="AA12">
-        <v>520</v>
-      </c>
-      <c r="AB12">
-        <v>19.5</v>
-      </c>
-      <c r="AC12">
-        <v>11</v>
-      </c>
-      <c r="AD12">
-        <v>15.5</v>
-      </c>
-      <c r="AE12">
-        <v>32</v>
-      </c>
-      <c r="AF12">
-        <v>21</v>
-      </c>
-      <c r="AG12">
-        <v>12</v>
-      </c>
-      <c r="AH12">
-        <v>13.5</v>
-      </c>
-      <c r="AI12">
-        <v>32</v>
-      </c>
-      <c r="AJ12">
+      <c r="AO12">
+        <v>12.5</v>
+      </c>
+      <c r="AP12">
+        <v>17.5</v>
+      </c>
+      <c r="AQ12">
+        <v>11.5</v>
+      </c>
+      <c r="AR12">
+        <v>14</v>
+      </c>
+      <c r="AS12">
+        <v>25</v>
+      </c>
+      <c r="AT12">
+        <v>15</v>
+      </c>
+      <c r="AU12">
+        <v>8</v>
+      </c>
+      <c r="AV12">
+        <v>10</v>
+      </c>
+      <c r="AW12">
+        <v>18.5</v>
+      </c>
+      <c r="AX12">
+        <v>23</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>14</v>
+      </c>
+      <c r="BA12">
+        <v>27</v>
+      </c>
+      <c r="BB12">
         <v>50</v>
       </c>
-      <c r="AK12">
-        <v>19.5</v>
-      </c>
-      <c r="AL12">
-        <v>24</v>
-      </c>
-      <c r="AM12">
-        <v>44</v>
-      </c>
-      <c r="AN12">
-        <v>8.4</v>
-      </c>
-      <c r="AO12">
-        <v>17</v>
-      </c>
-      <c r="AP12">
-        <v>22</v>
-      </c>
-      <c r="AQ12">
-        <v>20</v>
-      </c>
-      <c r="AR12">
-        <v>20</v>
-      </c>
-      <c r="AS12">
-        <v>29</v>
-      </c>
-      <c r="AT12">
-        <v>16.5</v>
-      </c>
-      <c r="AU12">
-        <v>9.6</v>
-      </c>
-      <c r="AV12">
-        <v>13.5</v>
-      </c>
-      <c r="AW12">
-        <v>19</v>
-      </c>
-      <c r="AX12">
-        <v>17</v>
-      </c>
-      <c r="AY12">
-        <v>10.5</v>
-      </c>
-      <c r="AZ12">
-        <v>12</v>
-      </c>
-      <c r="BA12">
-        <v>19</v>
-      </c>
-      <c r="BB12">
-        <v>25</v>
-      </c>
       <c r="BC12">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BD12">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="BE12">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BF12">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BG12">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>2.18</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3632,241 +3692,241 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F13">
+        <v>2.08</v>
+      </c>
+      <c r="G13">
+        <v>2.12</v>
+      </c>
+      <c r="H13">
         <v>3.4</v>
       </c>
-      <c r="G13">
-        <v>3.45</v>
-      </c>
-      <c r="H13">
-        <v>2.22</v>
-      </c>
       <c r="I13">
-        <v>2.26</v>
+        <v>3.55</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P13">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="U13">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="X13">
+        <v>38</v>
+      </c>
+      <c r="Y13">
+        <v>28</v>
+      </c>
+      <c r="Z13">
+        <v>36</v>
+      </c>
+      <c r="AA13">
+        <v>590</v>
+      </c>
+      <c r="AB13">
+        <v>19</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>16</v>
+      </c>
+      <c r="AE13">
+        <v>34</v>
+      </c>
+      <c r="AF13">
         <v>20</v>
       </c>
-      <c r="Y13">
-        <v>13</v>
-      </c>
-      <c r="Z13">
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13">
+        <v>13.5</v>
+      </c>
+      <c r="AI13">
+        <v>32</v>
+      </c>
+      <c r="AJ13">
+        <v>32</v>
+      </c>
+      <c r="AK13">
+        <v>18.5</v>
+      </c>
+      <c r="AL13">
+        <v>25</v>
+      </c>
+      <c r="AM13">
+        <v>44</v>
+      </c>
+      <c r="AN13">
+        <v>8</v>
+      </c>
+      <c r="AO13">
+        <v>18</v>
+      </c>
+      <c r="AP13">
+        <v>22</v>
+      </c>
+      <c r="AQ13">
+        <v>21</v>
+      </c>
+      <c r="AR13">
+        <v>21</v>
+      </c>
+      <c r="AS13">
+        <v>29</v>
+      </c>
+      <c r="AT13">
+        <v>16.5</v>
+      </c>
+      <c r="AU13">
+        <v>9.6</v>
+      </c>
+      <c r="AV13">
+        <v>13.5</v>
+      </c>
+      <c r="AW13">
+        <v>20</v>
+      </c>
+      <c r="AX13">
+        <v>16.5</v>
+      </c>
+      <c r="AY13">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>20</v>
+      </c>
+      <c r="BB13">
+        <v>19</v>
+      </c>
+      <c r="BC13">
         <v>16</v>
       </c>
-      <c r="AA13">
-        <v>28</v>
-      </c>
-      <c r="AB13">
-        <v>17</v>
-      </c>
-      <c r="AC13">
-        <v>9</v>
-      </c>
-      <c r="AD13">
-        <v>11.5</v>
-      </c>
-      <c r="AE13">
-        <v>21</v>
-      </c>
-      <c r="AF13">
-        <v>27</v>
-      </c>
-      <c r="AG13">
+      <c r="BD13">
+        <v>19</v>
+      </c>
+      <c r="BE13">
+        <v>24</v>
+      </c>
+      <c r="BF13">
+        <v>7.2</v>
+      </c>
+      <c r="BG13">
         <v>15</v>
       </c>
-      <c r="AH13">
-        <v>15.5</v>
-      </c>
-      <c r="AI13">
-        <v>30</v>
-      </c>
-      <c r="AJ13">
-        <v>60</v>
-      </c>
-      <c r="AK13">
-        <v>36</v>
-      </c>
-      <c r="AL13">
-        <v>40</v>
-      </c>
-      <c r="AM13">
-        <v>70</v>
-      </c>
-      <c r="AN13">
+      <c r="BH13">
+        <v>5.4</v>
+      </c>
+      <c r="BI13">
+        <v>4.1</v>
+      </c>
+      <c r="BJ13">
+        <v>8.6</v>
+      </c>
+      <c r="BK13">
+        <v>4.5</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN13">
+        <v>6</v>
+      </c>
+      <c r="BO13">
+        <v>4.9</v>
+      </c>
+      <c r="BP13">
+        <v>14</v>
+      </c>
+      <c r="BQ13">
+        <v>5.7</v>
+      </c>
+      <c r="BR13">
+        <v>20</v>
+      </c>
+      <c r="BS13">
+        <v>6.4</v>
+      </c>
+      <c r="BT13">
+        <v>7.8</v>
+      </c>
+      <c r="BU13">
+        <v>4.3</v>
+      </c>
+      <c r="BV13">
+        <v>23</v>
+      </c>
+      <c r="BW13">
+        <v>6.6</v>
+      </c>
+      <c r="BX13">
         <v>26</v>
       </c>
-      <c r="AO13">
+      <c r="BY13">
+        <v>7</v>
+      </c>
+      <c r="BZ13">
         <v>12.5</v>
       </c>
-      <c r="AP13">
-        <v>17.5</v>
-      </c>
-      <c r="AQ13">
-        <v>11.5</v>
-      </c>
-      <c r="AR13">
-        <v>14</v>
-      </c>
-      <c r="AS13">
-        <v>23</v>
-      </c>
-      <c r="AT13">
-        <v>15</v>
-      </c>
-      <c r="AU13">
-        <v>8</v>
-      </c>
-      <c r="AV13">
-        <v>10</v>
-      </c>
-      <c r="AW13">
-        <v>18.5</v>
-      </c>
-      <c r="AX13">
-        <v>23</v>
-      </c>
-      <c r="AY13">
-        <v>13</v>
-      </c>
-      <c r="AZ13">
-        <v>14</v>
-      </c>
-      <c r="BA13">
-        <v>27</v>
-      </c>
-      <c r="BB13">
-        <v>48</v>
-      </c>
-      <c r="BC13">
-        <v>30</v>
-      </c>
-      <c r="BD13">
-        <v>34</v>
-      </c>
-      <c r="BE13">
-        <v>55</v>
-      </c>
-      <c r="BF13">
-        <v>23</v>
-      </c>
-      <c r="BG13">
-        <v>11.5</v>
-      </c>
-      <c r="BH13">
-        <v>1000</v>
-      </c>
-      <c r="BI13">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13">
-        <v>1000</v>
-      </c>
-      <c r="BK13">
-        <v>1.04</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>1.04</v>
-      </c>
-      <c r="BN13">
-        <v>1000</v>
-      </c>
-      <c r="BO13">
-        <v>1.04</v>
-      </c>
-      <c r="BP13">
-        <v>1000</v>
-      </c>
-      <c r="BQ13">
-        <v>1.04</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>1.04</v>
-      </c>
-      <c r="BT13">
-        <v>1000</v>
-      </c>
-      <c r="BU13">
-        <v>1.04</v>
-      </c>
-      <c r="BV13">
-        <v>1000</v>
-      </c>
-      <c r="BW13">
-        <v>1.04</v>
-      </c>
-      <c r="BX13">
-        <v>1000</v>
-      </c>
-      <c r="BY13">
-        <v>1.04</v>
-      </c>
-      <c r="BZ13">
-        <v>1000</v>
-      </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3874,16 +3934,16 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F14">
         <v>1.59</v>
@@ -3901,7 +3961,7 @@
         <v>5.1</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
         <v>1.22</v>
@@ -3910,7 +3970,7 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O14">
         <v>1.12</v>
@@ -3919,13 +3979,13 @@
         <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R14">
         <v>2</v>
       </c>
       <c r="S14">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T14">
         <v>1.49</v>
@@ -3943,13 +4003,13 @@
         <v>40</v>
       </c>
       <c r="Y14">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Z14">
         <v>60</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB14">
         <v>18</v>
@@ -3976,7 +4036,7 @@
         <v>110</v>
       </c>
       <c r="AJ14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK14">
         <v>14.5</v>
@@ -3994,7 +4054,7 @@
         <v>32</v>
       </c>
       <c r="AP14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AQ14">
         <v>32</v>
@@ -4042,10 +4102,10 @@
         <v>44</v>
       </c>
       <c r="BF14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BH14">
         <v>5.8</v>
@@ -4108,7 +4168,7 @@
         <v>4.9</v>
       </c>
       <c r="CB14" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4116,16 +4176,16 @@
         <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F15">
         <v>1.76</v>
@@ -4134,7 +4194,7 @@
         <v>1.79</v>
       </c>
       <c r="H15">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
         <v>4.9</v>
@@ -4149,22 +4209,22 @@
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O15">
         <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q15">
         <v>1.56</v>
       </c>
       <c r="R15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S15">
         <v>2.4</v>
@@ -4182,13 +4242,13 @@
         <v>2.26</v>
       </c>
       <c r="X15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y15">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4203,10 +4263,10 @@
         <v>19.5</v>
       </c>
       <c r="AE15">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="AF15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG15">
         <v>10.5</v>
@@ -4224,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="AL15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM15">
         <v>1000</v>
@@ -4233,7 +4293,7 @@
         <v>7.2</v>
       </c>
       <c r="AO15">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AP15">
         <v>18.5</v>
@@ -4242,13 +4302,13 @@
         <v>23</v>
       </c>
       <c r="AR15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS15">
         <v>38</v>
       </c>
       <c r="AT15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
@@ -4287,7 +4347,7 @@
         <v>6.6</v>
       </c>
       <c r="BG15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4311,7 +4371,7 @@
         <v>6.4</v>
       </c>
       <c r="BO15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP15">
         <v>15.5</v>
@@ -4350,7 +4410,7 @@
         <v>1.91</v>
       </c>
       <c r="CB15" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4358,16 +4418,16 @@
         <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="F16">
         <v>2.4</v>
@@ -4376,7 +4436,7 @@
         <v>2.46</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I16">
         <v>2.96</v>
@@ -4400,10 +4460,10 @@
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
         <v>1.72</v>
@@ -4424,19 +4484,19 @@
         <v>1.68</v>
       </c>
       <c r="X16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA16">
         <v>48</v>
       </c>
       <c r="AB16">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
         <v>10.5</v>
@@ -4445,7 +4505,7 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF16">
         <v>21</v>
@@ -4460,13 +4520,13 @@
         <v>32</v>
       </c>
       <c r="AJ16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK16">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM16">
         <v>60</v>
@@ -4478,7 +4538,7 @@
         <v>16</v>
       </c>
       <c r="AP16">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16">
         <v>17</v>
@@ -4499,10 +4559,10 @@
         <v>12</v>
       </c>
       <c r="AW16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4511,19 +4571,19 @@
         <v>12</v>
       </c>
       <c r="BA16">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB16">
-        <v>7.2</v>
+        <v>27</v>
       </c>
       <c r="BC16">
         <v>18.5</v>
       </c>
       <c r="BD16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE16">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF16">
         <v>10</v>
@@ -4532,22 +4592,22 @@
         <v>13.5</v>
       </c>
       <c r="BH16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI16">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL16">
         <v>70</v>
       </c>
       <c r="BM16">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
@@ -4556,19 +4616,19 @@
         <v>4.7</v>
       </c>
       <c r="BP16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ16">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR16">
         <v>23</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
         <v>5.2</v>
@@ -4577,22 +4637,22 @@
         <v>20</v>
       </c>
       <c r="BW16">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BX16">
         <v>26</v>
       </c>
       <c r="BY16">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="CA16">
         <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4600,49 +4660,49 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F17">
+        <v>2.1</v>
+      </c>
+      <c r="G17">
         <v>2.12</v>
-      </c>
-      <c r="G17">
-        <v>2.14</v>
       </c>
       <c r="H17">
         <v>3.55</v>
       </c>
       <c r="I17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q17">
         <v>1.61</v>
@@ -4657,13 +4717,13 @@
         <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X17">
         <v>24</v>
@@ -4675,13 +4735,13 @@
         <v>30</v>
       </c>
       <c r="AA17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
         <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD17">
         <v>15.5</v>
@@ -4711,7 +4771,7 @@
         <v>28</v>
       </c>
       <c r="AM17">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN17">
         <v>10.5</v>
@@ -4741,7 +4801,7 @@
         <v>14</v>
       </c>
       <c r="AW17">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX17">
         <v>14</v>
@@ -4771,70 +4831,2006 @@
         <v>9</v>
       </c>
       <c r="BG17">
+        <v>22</v>
+      </c>
+      <c r="BH17">
+        <v>4.5</v>
+      </c>
+      <c r="BI17">
+        <v>3.5</v>
+      </c>
+      <c r="BJ17">
+        <v>9</v>
+      </c>
+      <c r="BK17">
+        <v>4.8</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN17">
+        <v>5.5</v>
+      </c>
+      <c r="BO17">
+        <v>4.6</v>
+      </c>
+      <c r="BP17">
+        <v>14</v>
+      </c>
+      <c r="BQ17">
+        <v>5.9</v>
+      </c>
+      <c r="BR17">
+        <v>23</v>
+      </c>
+      <c r="BS17">
+        <v>7</v>
+      </c>
+      <c r="BT17">
+        <v>7.6</v>
+      </c>
+      <c r="BU17">
+        <v>4.4</v>
+      </c>
+      <c r="BV17">
+        <v>26</v>
+      </c>
+      <c r="BW17">
+        <v>7.4</v>
+      </c>
+      <c r="BX17">
+        <v>32</v>
+      </c>
+      <c r="BY17">
+        <v>7.8</v>
+      </c>
+      <c r="BZ17">
+        <v>16.5</v>
+      </c>
+      <c r="CA17">
+        <v>6.4</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18">
+        <v>2.62</v>
+      </c>
+      <c r="G18">
+        <v>3.05</v>
+      </c>
+      <c r="H18">
+        <v>2.82</v>
+      </c>
+      <c r="I18">
+        <v>3.5</v>
+      </c>
+      <c r="J18">
+        <v>2.88</v>
+      </c>
+      <c r="K18">
+        <v>3.3</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>2.52</v>
+      </c>
+      <c r="O18">
+        <v>1.37</v>
+      </c>
+      <c r="P18">
+        <v>1.57</v>
+      </c>
+      <c r="Q18">
+        <v>2.04</v>
+      </c>
+      <c r="R18">
+        <v>1.27</v>
+      </c>
+      <c r="S18">
+        <v>2.34</v>
+      </c>
+      <c r="T18">
+        <v>1.11</v>
+      </c>
+      <c r="U18">
+        <v>1.11</v>
+      </c>
+      <c r="V18">
+        <v>1.4</v>
+      </c>
+      <c r="W18">
+        <v>1.49</v>
+      </c>
+      <c r="X18">
+        <v>16</v>
+      </c>
+      <c r="Y18">
+        <v>970</v>
+      </c>
+      <c r="Z18">
+        <v>970</v>
+      </c>
+      <c r="AA18">
+        <v>75</v>
+      </c>
+      <c r="AB18">
+        <v>13.5</v>
+      </c>
+      <c r="AC18">
+        <v>10.5</v>
+      </c>
+      <c r="AD18">
+        <v>20</v>
+      </c>
+      <c r="AE18">
+        <v>55</v>
+      </c>
+      <c r="AF18">
+        <v>25</v>
+      </c>
+      <c r="AG18">
+        <v>18.5</v>
+      </c>
+      <c r="AH18">
+        <v>950</v>
+      </c>
+      <c r="AI18">
+        <v>85</v>
+      </c>
+      <c r="AJ18">
+        <v>65</v>
+      </c>
+      <c r="AK18">
+        <v>50</v>
+      </c>
+      <c r="AL18">
+        <v>75</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>50</v>
+      </c>
+      <c r="AO18">
+        <v>60</v>
+      </c>
+      <c r="AP18">
+        <v>1.91</v>
+      </c>
+      <c r="AQ18">
+        <v>2.5</v>
+      </c>
+      <c r="AR18">
+        <v>13</v>
+      </c>
+      <c r="AS18">
+        <v>3.25</v>
+      </c>
+      <c r="AT18">
+        <v>1.87</v>
+      </c>
+      <c r="AU18">
+        <v>1.8</v>
+      </c>
+      <c r="AV18">
+        <v>2.94</v>
+      </c>
+      <c r="AW18">
+        <v>3.2</v>
+      </c>
+      <c r="AX18">
+        <v>3</v>
+      </c>
+      <c r="AY18">
+        <v>2.9</v>
+      </c>
+      <c r="AZ18">
+        <v>3.05</v>
+      </c>
+      <c r="BA18">
+        <v>3.3</v>
+      </c>
+      <c r="BB18">
+        <v>3.25</v>
+      </c>
+      <c r="BC18">
+        <v>3.2</v>
+      </c>
+      <c r="BD18">
+        <v>3.25</v>
+      </c>
+      <c r="BE18">
+        <v>2.16</v>
+      </c>
+      <c r="BF18">
+        <v>3.2</v>
+      </c>
+      <c r="BG18">
+        <v>3.25</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.74</v>
+      </c>
+      <c r="BJ18">
+        <v>15</v>
+      </c>
+      <c r="BK18">
+        <v>1.56</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.74</v>
+      </c>
+      <c r="BN18">
+        <v>7.8</v>
+      </c>
+      <c r="BO18">
+        <v>1.42</v>
+      </c>
+      <c r="BP18">
+        <v>34</v>
+      </c>
+      <c r="BQ18">
+        <v>1.66</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.69</v>
+      </c>
+      <c r="BT18">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU18">
+        <v>1.44</v>
+      </c>
+      <c r="BV18">
+        <v>38</v>
+      </c>
+      <c r="BW18">
+        <v>1.67</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.69</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.69</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19">
+        <v>1.81</v>
+      </c>
+      <c r="G19">
+        <v>1.93</v>
+      </c>
+      <c r="H19">
+        <v>5.2</v>
+      </c>
+      <c r="I19">
+        <v>6.2</v>
+      </c>
+      <c r="J19">
+        <v>3.3</v>
+      </c>
+      <c r="K19">
+        <v>3.75</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>2.58</v>
+      </c>
+      <c r="O19">
+        <v>1.52</v>
+      </c>
+      <c r="P19">
+        <v>1.54</v>
+      </c>
+      <c r="Q19">
+        <v>2.36</v>
+      </c>
+      <c r="R19">
+        <v>1.18</v>
+      </c>
+      <c r="S19">
+        <v>5.1</v>
+      </c>
+      <c r="T19">
+        <v>1.99</v>
+      </c>
+      <c r="U19">
+        <v>1.58</v>
+      </c>
+      <c r="V19">
+        <v>1.2</v>
+      </c>
+      <c r="W19">
+        <v>2.06</v>
+      </c>
+      <c r="X19">
+        <v>12.5</v>
+      </c>
+      <c r="Y19">
+        <v>18.5</v>
+      </c>
+      <c r="Z19">
+        <v>55</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>6.6</v>
+      </c>
+      <c r="AC19">
+        <v>10</v>
+      </c>
+      <c r="AD19">
+        <v>950</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>10.5</v>
+      </c>
+      <c r="AG19">
+        <v>970</v>
+      </c>
+      <c r="AH19">
+        <v>950</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>23</v>
+      </c>
+      <c r="AK19">
+        <v>26</v>
+      </c>
+      <c r="AL19">
+        <v>60</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>22</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ19">
+        <v>12</v>
+      </c>
+      <c r="AR19">
+        <v>4.8</v>
+      </c>
+      <c r="AS19">
+        <v>3.4</v>
+      </c>
+      <c r="AT19">
+        <v>2.92</v>
+      </c>
+      <c r="AU19">
+        <v>7</v>
+      </c>
+      <c r="AV19">
+        <v>20</v>
+      </c>
+      <c r="AW19">
+        <v>3.4</v>
+      </c>
+      <c r="AX19">
+        <v>8.4</v>
+      </c>
+      <c r="AY19">
+        <v>3.35</v>
+      </c>
+      <c r="AZ19">
+        <v>4.5</v>
+      </c>
+      <c r="BA19">
+        <v>3.4</v>
+      </c>
+      <c r="BB19">
+        <v>18</v>
+      </c>
+      <c r="BC19">
         <v>21</v>
       </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>2.08</v>
-      </c>
-      <c r="BJ17">
+      <c r="BD19">
+        <v>3.8</v>
+      </c>
+      <c r="BE19">
+        <v>3.4</v>
+      </c>
+      <c r="BF19">
+        <v>17.5</v>
+      </c>
+      <c r="BG19">
+        <v>3.4</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.04</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.04</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.04</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.04</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.04</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.04</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.04</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.04</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.04</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.04</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20">
+        <v>2.06</v>
+      </c>
+      <c r="G20">
+        <v>2.32</v>
+      </c>
+      <c r="H20">
+        <v>3.85</v>
+      </c>
+      <c r="I20">
+        <v>5.6</v>
+      </c>
+      <c r="J20">
+        <v>1.03</v>
+      </c>
+      <c r="K20">
+        <v>3.9</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.01</v>
+      </c>
+      <c r="N20">
+        <v>2.52</v>
+      </c>
+      <c r="O20">
+        <v>1.46</v>
+      </c>
+      <c r="P20">
+        <v>1.49</v>
+      </c>
+      <c r="Q20">
+        <v>2.06</v>
+      </c>
+      <c r="R20">
+        <v>1.19</v>
+      </c>
+      <c r="S20">
+        <v>4</v>
+      </c>
+      <c r="T20">
+        <v>1.11</v>
+      </c>
+      <c r="U20">
+        <v>1.67</v>
+      </c>
+      <c r="V20">
+        <v>1.21</v>
+      </c>
+      <c r="W20">
+        <v>1.75</v>
+      </c>
+      <c r="X20">
+        <v>1000</v>
+      </c>
+      <c r="Y20">
+        <v>1000</v>
+      </c>
+      <c r="Z20">
+        <v>1000</v>
+      </c>
+      <c r="AA20">
+        <v>1000</v>
+      </c>
+      <c r="AB20">
+        <v>1000</v>
+      </c>
+      <c r="AC20">
+        <v>1000</v>
+      </c>
+      <c r="AD20">
+        <v>1000</v>
+      </c>
+      <c r="AE20">
+        <v>1000</v>
+      </c>
+      <c r="AF20">
+        <v>1000</v>
+      </c>
+      <c r="AG20">
+        <v>1000</v>
+      </c>
+      <c r="AH20">
+        <v>1000</v>
+      </c>
+      <c r="AI20">
+        <v>1000</v>
+      </c>
+      <c r="AJ20">
+        <v>1000</v>
+      </c>
+      <c r="AK20">
+        <v>1000</v>
+      </c>
+      <c r="AL20">
+        <v>1000</v>
+      </c>
+      <c r="AM20">
+        <v>1000</v>
+      </c>
+      <c r="AN20">
+        <v>1000</v>
+      </c>
+      <c r="AO20">
+        <v>1000</v>
+      </c>
+      <c r="AP20">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20">
+        <v>1.01</v>
+      </c>
+      <c r="AR20">
+        <v>1.01</v>
+      </c>
+      <c r="AS20">
+        <v>1.01</v>
+      </c>
+      <c r="AT20">
+        <v>1.01</v>
+      </c>
+      <c r="AU20">
+        <v>1.01</v>
+      </c>
+      <c r="AV20">
+        <v>1.01</v>
+      </c>
+      <c r="AW20">
+        <v>1.01</v>
+      </c>
+      <c r="AX20">
+        <v>1.01</v>
+      </c>
+      <c r="AY20">
+        <v>1.01</v>
+      </c>
+      <c r="AZ20">
+        <v>1.01</v>
+      </c>
+      <c r="BA20">
+        <v>1.01</v>
+      </c>
+      <c r="BB20">
+        <v>1.01</v>
+      </c>
+      <c r="BC20">
+        <v>1.01</v>
+      </c>
+      <c r="BD20">
+        <v>1.01</v>
+      </c>
+      <c r="BE20">
+        <v>1.01</v>
+      </c>
+      <c r="BF20">
+        <v>1.01</v>
+      </c>
+      <c r="BG20">
+        <v>1.01</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.04</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.04</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.04</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.04</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.04</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.04</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.04</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.04</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.04</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
+        <v>1.04</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21">
+        <v>4.9</v>
+      </c>
+      <c r="G21">
+        <v>5.4</v>
+      </c>
+      <c r="H21">
+        <v>2.04</v>
+      </c>
+      <c r="I21">
+        <v>2.1</v>
+      </c>
+      <c r="J21">
+        <v>2.94</v>
+      </c>
+      <c r="K21">
+        <v>3.15</v>
+      </c>
+      <c r="L21">
+        <v>1.01</v>
+      </c>
+      <c r="M21">
+        <v>1.16</v>
+      </c>
+      <c r="N21">
+        <v>2.24</v>
+      </c>
+      <c r="O21">
+        <v>1.56</v>
+      </c>
+      <c r="P21">
+        <v>1.41</v>
+      </c>
+      <c r="Q21">
+        <v>3.05</v>
+      </c>
+      <c r="R21">
+        <v>1.14</v>
+      </c>
+      <c r="S21">
+        <v>5.5</v>
+      </c>
+      <c r="T21">
+        <v>2.22</v>
+      </c>
+      <c r="U21">
+        <v>1.48</v>
+      </c>
+      <c r="V21">
+        <v>1.9</v>
+      </c>
+      <c r="W21">
+        <v>1.22</v>
+      </c>
+      <c r="X21">
+        <v>8.4</v>
+      </c>
+      <c r="Y21">
+        <v>7</v>
+      </c>
+      <c r="Z21">
         <v>12</v>
       </c>
-      <c r="BK17">
-        <v>1.78</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
+      <c r="AA21">
+        <v>32</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>8.6</v>
+      </c>
+      <c r="AD21">
+        <v>14.5</v>
+      </c>
+      <c r="AE21">
+        <v>46</v>
+      </c>
+      <c r="AF21">
+        <v>42</v>
+      </c>
+      <c r="AG21">
+        <v>26</v>
+      </c>
+      <c r="AH21">
+        <v>950</v>
+      </c>
+      <c r="AI21">
+        <v>95</v>
+      </c>
+      <c r="AJ21">
+        <v>1000</v>
+      </c>
+      <c r="AK21">
+        <v>1000</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>1000</v>
+      </c>
+      <c r="AN21">
+        <v>1000</v>
+      </c>
+      <c r="AO21">
+        <v>38</v>
+      </c>
+      <c r="AP21">
+        <v>3</v>
+      </c>
+      <c r="AQ21">
+        <v>5.2</v>
+      </c>
+      <c r="AR21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS21">
+        <v>19.5</v>
+      </c>
+      <c r="AT21">
+        <v>3.45</v>
+      </c>
+      <c r="AU21">
+        <v>3</v>
+      </c>
+      <c r="AV21">
+        <v>9.6</v>
+      </c>
+      <c r="AW21">
+        <v>4.2</v>
+      </c>
+      <c r="AX21">
+        <v>23</v>
+      </c>
+      <c r="AY21">
+        <v>15</v>
+      </c>
+      <c r="AZ21">
+        <v>4.1</v>
+      </c>
+      <c r="BA21">
+        <v>4.4</v>
+      </c>
+      <c r="BB21">
+        <v>4.7</v>
+      </c>
+      <c r="BC21">
+        <v>4.7</v>
+      </c>
+      <c r="BD21">
+        <v>4.7</v>
+      </c>
+      <c r="BE21">
+        <v>4.7</v>
+      </c>
+      <c r="BF21">
+        <v>4.7</v>
+      </c>
+      <c r="BG21">
+        <v>22</v>
+      </c>
+      <c r="BH21">
+        <v>1000</v>
+      </c>
+      <c r="BI21">
         <v>2.04</v>
       </c>
-      <c r="BN17">
+      <c r="BJ21">
+        <v>18.5</v>
+      </c>
+      <c r="BK21">
+        <v>1.51</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>1.65</v>
+      </c>
+      <c r="BN21">
+        <v>11.5</v>
+      </c>
+      <c r="BO21">
+        <v>1.44</v>
+      </c>
+      <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>1.62</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>1.65</v>
+      </c>
+      <c r="BT21">
+        <v>5.8</v>
+      </c>
+      <c r="BU21">
+        <v>3.05</v>
+      </c>
+      <c r="BV21">
+        <v>25</v>
+      </c>
+      <c r="BW21">
+        <v>1.55</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>1.61</v>
+      </c>
+      <c r="BZ21">
+        <v>1000</v>
+      </c>
+      <c r="CA21">
+        <v>1.61</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>116</v>
+      </c>
+      <c r="E22" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22">
+        <v>2.8</v>
+      </c>
+      <c r="G22">
+        <v>2.92</v>
+      </c>
+      <c r="H22">
+        <v>3.15</v>
+      </c>
+      <c r="I22">
+        <v>3.3</v>
+      </c>
+      <c r="J22">
+        <v>2.92</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>2.24</v>
+      </c>
+      <c r="O22">
+        <v>1.68</v>
+      </c>
+      <c r="P22">
+        <v>1.43</v>
+      </c>
+      <c r="Q22">
+        <v>3.05</v>
+      </c>
+      <c r="R22">
+        <v>1.13</v>
+      </c>
+      <c r="S22">
         <v>7</v>
       </c>
-      <c r="BO17">
+      <c r="T22">
+        <v>2.3</v>
+      </c>
+      <c r="U22">
+        <v>1.6</v>
+      </c>
+      <c r="V22">
+        <v>1.43</v>
+      </c>
+      <c r="W22">
+        <v>1.52</v>
+      </c>
+      <c r="X22">
+        <v>8</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>18</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>18</v>
+      </c>
+      <c r="AG22">
+        <v>15.5</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.21</v>
+      </c>
+      <c r="AQ22">
+        <v>1.43</v>
+      </c>
+      <c r="AR22">
+        <v>1.43</v>
+      </c>
+      <c r="AS22">
+        <v>1.43</v>
+      </c>
+      <c r="AT22">
+        <v>1.43</v>
+      </c>
+      <c r="AU22">
+        <v>1.43</v>
+      </c>
+      <c r="AV22">
+        <v>1.33</v>
+      </c>
+      <c r="AW22">
+        <v>1.43</v>
+      </c>
+      <c r="AX22">
+        <v>1.33</v>
+      </c>
+      <c r="AY22">
+        <v>11</v>
+      </c>
+      <c r="AZ22">
+        <v>1.43</v>
+      </c>
+      <c r="BA22">
+        <v>1.43</v>
+      </c>
+      <c r="BB22">
+        <v>1.43</v>
+      </c>
+      <c r="BC22">
+        <v>1.43</v>
+      </c>
+      <c r="BD22">
+        <v>1.43</v>
+      </c>
+      <c r="BE22">
+        <v>1.43</v>
+      </c>
+      <c r="BF22">
+        <v>1.43</v>
+      </c>
+      <c r="BG22">
+        <v>1.43</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.66</v>
+      </c>
+      <c r="BJ22">
+        <v>17.5</v>
+      </c>
+      <c r="BK22">
+        <v>1.51</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.66</v>
+      </c>
+      <c r="BN22">
+        <v>7</v>
+      </c>
+      <c r="BO22">
+        <v>3.7</v>
+      </c>
+      <c r="BP22">
+        <v>36</v>
+      </c>
+      <c r="BQ22">
+        <v>1.59</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.63</v>
+      </c>
+      <c r="BT22">
+        <v>8.6</v>
+      </c>
+      <c r="BU22">
+        <v>4.3</v>
+      </c>
+      <c r="BV22">
+        <v>50</v>
+      </c>
+      <c r="BW22">
+        <v>1.61</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.63</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.63</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23">
+        <v>1.55</v>
+      </c>
+      <c r="G23">
+        <v>1.57</v>
+      </c>
+      <c r="H23">
+        <v>8</v>
+      </c>
+      <c r="I23">
+        <v>8.4</v>
+      </c>
+      <c r="J23">
+        <v>4.2</v>
+      </c>
+      <c r="K23">
+        <v>4.4</v>
+      </c>
+      <c r="L23">
+        <v>1.34</v>
+      </c>
+      <c r="M23">
+        <v>1.08</v>
+      </c>
+      <c r="N23">
+        <v>3.6</v>
+      </c>
+      <c r="O23">
+        <v>1.35</v>
+      </c>
+      <c r="P23">
+        <v>1.92</v>
+      </c>
+      <c r="Q23">
+        <v>2.04</v>
+      </c>
+      <c r="R23">
+        <v>1.33</v>
+      </c>
+      <c r="S23">
+        <v>3.7</v>
+      </c>
+      <c r="T23">
+        <v>2.14</v>
+      </c>
+      <c r="U23">
+        <v>1.81</v>
+      </c>
+      <c r="V23">
+        <v>1.13</v>
+      </c>
+      <c r="W23">
+        <v>2.74</v>
+      </c>
+      <c r="X23">
+        <v>14</v>
+      </c>
+      <c r="Y23">
+        <v>22</v>
+      </c>
+      <c r="Z23">
+        <v>860</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>7.4</v>
+      </c>
+      <c r="AC23">
+        <v>9.4</v>
+      </c>
+      <c r="AD23">
+        <v>32</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG23">
+        <v>10.5</v>
+      </c>
+      <c r="AH23">
+        <v>26</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>14</v>
+      </c>
+      <c r="AK23">
+        <v>18</v>
+      </c>
+      <c r="AL23">
+        <v>50</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>9.6</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>12</v>
+      </c>
+      <c r="AQ23">
+        <v>19.5</v>
+      </c>
+      <c r="AR23">
+        <v>30</v>
+      </c>
+      <c r="AS23">
+        <v>50</v>
+      </c>
+      <c r="AT23">
+        <v>6.8</v>
+      </c>
+      <c r="AU23">
+        <v>8.4</v>
+      </c>
+      <c r="AV23">
+        <v>20</v>
+      </c>
+      <c r="AW23">
+        <v>42</v>
+      </c>
+      <c r="AX23">
+        <v>7.6</v>
+      </c>
+      <c r="AY23">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23">
+        <v>23</v>
+      </c>
+      <c r="BA23">
+        <v>42</v>
+      </c>
+      <c r="BB23">
+        <v>12</v>
+      </c>
+      <c r="BC23">
+        <v>15.5</v>
+      </c>
+      <c r="BD23">
+        <v>36</v>
+      </c>
+      <c r="BE23">
+        <v>46</v>
+      </c>
+      <c r="BF23">
+        <v>8.6</v>
+      </c>
+      <c r="BG23">
+        <v>95</v>
+      </c>
+      <c r="BH23">
+        <v>3.4</v>
+      </c>
+      <c r="BI23">
+        <v>2.82</v>
+      </c>
+      <c r="BJ23">
+        <v>12</v>
+      </c>
+      <c r="BK23">
+        <v>7</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>15.5</v>
+      </c>
+      <c r="BN23">
+        <v>3.85</v>
+      </c>
+      <c r="BO23">
+        <v>3.1</v>
+      </c>
+      <c r="BP23">
+        <v>10</v>
+      </c>
+      <c r="BQ23">
+        <v>6.2</v>
+      </c>
+      <c r="BR23">
+        <v>29</v>
+      </c>
+      <c r="BS23">
+        <v>10.5</v>
+      </c>
+      <c r="BT23">
+        <v>11</v>
+      </c>
+      <c r="BU23">
+        <v>6.6</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>13.5</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>14</v>
+      </c>
+      <c r="BZ23">
+        <v>21</v>
+      </c>
+      <c r="CA23">
+        <v>9.4</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24">
+        <v>1.75</v>
+      </c>
+      <c r="G24">
+        <v>1.85</v>
+      </c>
+      <c r="H24">
+        <v>5</v>
+      </c>
+      <c r="I24">
+        <v>5.6</v>
+      </c>
+      <c r="J24">
+        <v>3.75</v>
+      </c>
+      <c r="K24">
+        <v>4.2</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.05</v>
+      </c>
+      <c r="N24">
         <v>3.9</v>
       </c>
-      <c r="BP17">
-        <v>18.5</v>
-      </c>
-      <c r="BQ17">
-        <v>1.88</v>
-      </c>
-      <c r="BR17">
-        <v>30</v>
-      </c>
-      <c r="BS17">
-        <v>1.96</v>
-      </c>
-      <c r="BT17">
-        <v>10</v>
-      </c>
-      <c r="BU17">
-        <v>4.9</v>
-      </c>
-      <c r="BV17">
-        <v>34</v>
-      </c>
-      <c r="BW17">
-        <v>1.98</v>
-      </c>
-      <c r="BX17">
-        <v>44</v>
-      </c>
-      <c r="BY17">
-        <v>2</v>
-      </c>
-      <c r="BZ17">
-        <v>21</v>
-      </c>
-      <c r="CA17">
-        <v>1.91</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>124</v>
+      <c r="O24">
+        <v>1.28</v>
+      </c>
+      <c r="P24">
+        <v>1.99</v>
+      </c>
+      <c r="Q24">
+        <v>1.87</v>
+      </c>
+      <c r="R24">
+        <v>1.39</v>
+      </c>
+      <c r="S24">
+        <v>2.92</v>
+      </c>
+      <c r="T24">
+        <v>1.82</v>
+      </c>
+      <c r="U24">
+        <v>2.06</v>
+      </c>
+      <c r="V24">
+        <v>1.21</v>
+      </c>
+      <c r="W24">
+        <v>2.16</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>1000</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>9.6</v>
+      </c>
+      <c r="AC24">
+        <v>8.6</v>
+      </c>
+      <c r="AD24">
+        <v>1000</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>1000</v>
+      </c>
+      <c r="AG24">
+        <v>1000</v>
+      </c>
+      <c r="AH24">
+        <v>1000</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>1000</v>
+      </c>
+      <c r="AK24">
+        <v>1000</v>
+      </c>
+      <c r="AL24">
+        <v>1000</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.28</v>
+      </c>
+      <c r="AQ24">
+        <v>1.28</v>
+      </c>
+      <c r="AR24">
+        <v>1.29</v>
+      </c>
+      <c r="AS24">
+        <v>1.29</v>
+      </c>
+      <c r="AT24">
+        <v>8</v>
+      </c>
+      <c r="AU24">
+        <v>1.12</v>
+      </c>
+      <c r="AV24">
+        <v>1.28</v>
+      </c>
+      <c r="AW24">
+        <v>1.29</v>
+      </c>
+      <c r="AX24">
+        <v>1.29</v>
+      </c>
+      <c r="AY24">
+        <v>1.28</v>
+      </c>
+      <c r="AZ24">
+        <v>1.28</v>
+      </c>
+      <c r="BA24">
+        <v>1.29</v>
+      </c>
+      <c r="BB24">
+        <v>1.29</v>
+      </c>
+      <c r="BC24">
+        <v>1.29</v>
+      </c>
+      <c r="BD24">
+        <v>1.29</v>
+      </c>
+      <c r="BE24">
+        <v>1.29</v>
+      </c>
+      <c r="BF24">
+        <v>1.29</v>
+      </c>
+      <c r="BG24">
+        <v>1.29</v>
+      </c>
+      <c r="BH24">
+        <v>4.2</v>
+      </c>
+      <c r="BI24">
+        <v>2.9</v>
+      </c>
+      <c r="BJ24">
+        <v>13.5</v>
+      </c>
+      <c r="BK24">
+        <v>2.88</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>3.65</v>
+      </c>
+      <c r="BN24">
+        <v>5.9</v>
+      </c>
+      <c r="BO24">
+        <v>3.15</v>
+      </c>
+      <c r="BP24">
+        <v>16</v>
+      </c>
+      <c r="BQ24">
+        <v>2.98</v>
+      </c>
+      <c r="BR24">
+        <v>36</v>
+      </c>
+      <c r="BS24">
+        <v>3.3</v>
+      </c>
+      <c r="BT24">
+        <v>11.5</v>
+      </c>
+      <c r="BU24">
+        <v>2.78</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>3.4</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>3.45</v>
+      </c>
+      <c r="BZ24">
+        <v>29</v>
+      </c>
+      <c r="CA24">
+        <v>3.25</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25">
+        <v>1.93</v>
+      </c>
+      <c r="G25">
+        <v>2.2</v>
+      </c>
+      <c r="H25">
+        <v>4.1</v>
+      </c>
+      <c r="I25">
+        <v>5.5</v>
+      </c>
+      <c r="J25">
+        <v>2.76</v>
+      </c>
+      <c r="K25">
+        <v>3.6</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>2.52</v>
+      </c>
+      <c r="O25">
+        <v>1.48</v>
+      </c>
+      <c r="P25">
+        <v>1.5</v>
+      </c>
+      <c r="Q25">
+        <v>2.52</v>
+      </c>
+      <c r="R25">
+        <v>1.17</v>
+      </c>
+      <c r="S25">
+        <v>2.52</v>
+      </c>
+      <c r="T25">
+        <v>1.11</v>
+      </c>
+      <c r="U25">
+        <v>1.72</v>
+      </c>
+      <c r="V25">
+        <v>1.24</v>
+      </c>
+      <c r="W25">
+        <v>1.83</v>
+      </c>
+      <c r="X25">
+        <v>10.5</v>
+      </c>
+      <c r="Y25">
+        <v>14.5</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>24</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>14</v>
+      </c>
+      <c r="AG25">
+        <v>13.5</v>
+      </c>
+      <c r="AH25">
+        <v>950</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.41</v>
+      </c>
+      <c r="AQ25">
+        <v>1.46</v>
+      </c>
+      <c r="AR25">
+        <v>1.63</v>
+      </c>
+      <c r="AS25">
+        <v>1.63</v>
+      </c>
+      <c r="AT25">
+        <v>1.62</v>
+      </c>
+      <c r="AU25">
+        <v>1.62</v>
+      </c>
+      <c r="AV25">
+        <v>1.52</v>
+      </c>
+      <c r="AW25">
+        <v>1.63</v>
+      </c>
+      <c r="AX25">
+        <v>1.46</v>
+      </c>
+      <c r="AY25">
+        <v>1.45</v>
+      </c>
+      <c r="AZ25">
+        <v>1.54</v>
+      </c>
+      <c r="BA25">
+        <v>1.63</v>
+      </c>
+      <c r="BB25">
+        <v>1.63</v>
+      </c>
+      <c r="BC25">
+        <v>1.63</v>
+      </c>
+      <c r="BD25">
+        <v>1.63</v>
+      </c>
+      <c r="BE25">
+        <v>1.63</v>
+      </c>
+      <c r="BF25">
+        <v>1.63</v>
+      </c>
+      <c r="BG25">
+        <v>1.63</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.04</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.04</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.04</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.04</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.04</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.04</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.04</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.04</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.04</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.04</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="149">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>US United Soccer League</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>02:30:00</t>
   </si>
   <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -334,10 +340,16 @@
     <t>Colorado Switchbacks FC</t>
   </si>
   <si>
+    <t>Colorado</t>
+  </si>
+  <si>
     <t>Austin FC</t>
   </si>
   <si>
-    <t>Colorado</t>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
+    <t>Portland Timbers</t>
   </si>
   <si>
     <t>San Jose Earthquakes</t>
@@ -346,10 +358,7 @@
     <t>Los Angeles FC</t>
   </si>
   <si>
-    <t>Portland Timbers</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
+    <t>Leiknir R</t>
   </si>
   <si>
     <t>Orense Sporting Club</t>
@@ -406,10 +415,16 @@
     <t>Miami FC</t>
   </si>
   <si>
+    <t>San Diego FC</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
-    <t>San Diego FC</t>
+    <t>St Louis City SC</t>
+  </si>
+  <si>
+    <t>FC Dallas</t>
   </si>
   <si>
     <t>Orlando City</t>
@@ -418,10 +433,7 @@
     <t>Real Salt Lake</t>
   </si>
   <si>
-    <t>FC Dallas</t>
-  </si>
-  <si>
-    <t>St Louis City SC</t>
+    <t>Throttur</t>
   </si>
   <si>
     <t>Aucas</t>
@@ -448,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 00:03:14</t>
+    <t>2026-07-22 02:10:19</t>
   </si>
 </sst>
 </file>
@@ -780,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1030,70 +1042,70 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
         <v>5.2</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I2">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
         <v>5</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
         <v>1.7</v>
       </c>
       <c r="V2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="W2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X2">
         <v>9.6</v>
@@ -1102,7 +1114,7 @@
         <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA2">
         <v>22</v>
@@ -1120,7 +1132,7 @@
         <v>26</v>
       </c>
       <c r="AF2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG2">
         <v>25</v>
@@ -1132,25 +1144,25 @@
         <v>70</v>
       </c>
       <c r="AJ2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK2">
         <v>130</v>
       </c>
       <c r="AL2">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN2">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AO2">
         <v>21</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
         <v>5.6</v>
@@ -1183,88 +1195,88 @@
         <v>7.4</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC2">
+        <v>9.4</v>
+      </c>
+      <c r="BD2">
+        <v>9.4</v>
+      </c>
+      <c r="BE2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF2">
         <v>9.6</v>
-      </c>
-      <c r="BD2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE2">
-        <v>10</v>
-      </c>
-      <c r="BF2">
-        <v>10</v>
       </c>
       <c r="BG2">
         <v>15</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="BI2">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.53</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.67</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BO2">
         <v>5.4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ2">
-        <v>1.64</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.67</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="BV2">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BW2">
-        <v>1.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY2">
-        <v>1.62</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.62</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1272,58 +1284,58 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F3">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="G3">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I3">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J3">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K3">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
         <v>1.35</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S3">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T3">
         <v>1.68</v>
@@ -1332,118 +1344,118 @@
         <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP3">
         <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AX3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BB3">
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD3">
         <v>27</v>
       </c>
       <c r="BE3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>4</v>
@@ -1461,52 +1473,52 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
         <v>14</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BW3">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3">
         <v>19.5</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1514,22 +1526,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
         <v>4.2</v>
@@ -1541,58 +1553,58 @@
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>42</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1601,7 +1613,7 @@
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>560</v>
+        <v>600</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -1613,7 +1625,7 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
         <v>26</v>
@@ -1634,28 +1646,28 @@
         <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS4">
         <v>36</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1667,22 +1679,22 @@
         <v>19</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BC4">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE4">
         <v>44</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG4">
         <v>34</v>
@@ -1748,7 +1760,7 @@
         <v>12.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1756,61 +1768,61 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J5">
         <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O5">
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q5">
         <v>2.18</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
         <v>2.04</v>
@@ -1819,7 +1831,7 @@
         <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X5">
         <v>12.5</v>
@@ -1834,10 +1846,10 @@
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>15.5</v>
@@ -1846,7 +1858,7 @@
         <v>48</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1855,13 +1867,13 @@
         <v>19</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5">
         <v>44</v>
@@ -1945,7 +1957,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
@@ -1957,16 +1969,16 @@
         <v>18</v>
       </c>
       <c r="BQ5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
         <v>5.7</v>
@@ -1975,22 +1987,22 @@
         <v>32</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1998,25 +2010,25 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G6">
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I6">
         <v>1.51</v>
@@ -2025,7 +2037,7 @@
         <v>4.5</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -2034,79 +2046,79 @@
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
         <v>2.04</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
         <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
         <v>2.96</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
         <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA6">
         <v>13</v>
       </c>
       <c r="AB6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG6">
         <v>32</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI6">
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AK6">
         <v>140</v>
       </c>
       <c r="AL6">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM6">
         <v>190</v>
@@ -2115,13 +2127,13 @@
         <v>190</v>
       </c>
       <c r="AO6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
         <v>7.8</v>
@@ -2133,13 +2145,13 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX6">
         <v>60</v>
@@ -2148,25 +2160,25 @@
         <v>27</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC6">
         <v>17</v>
       </c>
       <c r="BD6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BE6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BF6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
@@ -2232,7 +2244,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2240,28 +2252,28 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F7">
         <v>1.89</v>
       </c>
       <c r="G7">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2270,40 +2282,40 @@
         <v>3.8</v>
       </c>
       <c r="L7">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
         <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2312,7 +2324,7 @@
         <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2324,7 +2336,7 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE7">
         <v>70</v>
@@ -2339,7 +2351,7 @@
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
         <v>21</v>
@@ -2354,10 +2366,10 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2369,7 +2381,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2405,31 +2417,31 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
@@ -2441,40 +2453,40 @@
         <v>14</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
         <v>6</v>
       </c>
       <c r="BV7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2482,19 +2494,19 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
         <v>3.7</v>
@@ -2515,10 +2527,10 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
         <v>1.2</v>
@@ -2554,7 +2566,7 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
         <v>26</v>
@@ -2563,7 +2575,7 @@
         <v>19.5</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2575,13 +2587,13 @@
         <v>30</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH8">
         <v>15</v>
       </c>
       <c r="AI8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2599,16 +2611,16 @@
         <v>24</v>
       </c>
       <c r="AO8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
         <v>24</v>
@@ -2656,7 +2668,7 @@
         <v>8.6</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
         <v>3.5</v>
@@ -2665,13 +2677,13 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
@@ -2683,16 +2695,16 @@
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT8">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
         <v>4.1</v>
@@ -2701,22 +2713,22 @@
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX8">
         <v>22</v>
       </c>
       <c r="BY8">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ8">
         <v>15</v>
       </c>
       <c r="CA8">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2724,19 +2736,19 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G9">
         <v>1.86</v>
@@ -2763,10 +2775,10 @@
         <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
         <v>1.84</v>
@@ -2793,7 +2805,7 @@
         <v>18</v>
       </c>
       <c r="Y9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2802,7 +2814,7 @@
         <v>130</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2865,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="AW9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2877,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB9">
         <v>17</v>
@@ -2895,7 +2907,7 @@
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH9">
         <v>3.85</v>
@@ -2907,13 +2919,13 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
@@ -2925,16 +2937,16 @@
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
         <v>4.8</v>
@@ -2943,22 +2955,22 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2966,25 +2978,25 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G10">
         <v>1.55</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>7.2</v>
@@ -2993,7 +3005,7 @@
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3002,25 +3014,25 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q10">
         <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S10">
         <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
         <v>2.18</v>
@@ -3029,7 +3041,7 @@
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3038,7 +3050,7 @@
         <v>29</v>
       </c>
       <c r="Z10">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3065,7 +3077,7 @@
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ10">
         <v>14</v>
@@ -3077,7 +3089,7 @@
         <v>29</v>
       </c>
       <c r="AM10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN10">
         <v>6.4</v>
@@ -3086,7 +3098,7 @@
         <v>90</v>
       </c>
       <c r="AP10">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
         <v>26</v>
@@ -3098,10 +3110,10 @@
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV10">
         <v>23</v>
@@ -3110,7 +3122,7 @@
         <v>36</v>
       </c>
       <c r="AX10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY10">
         <v>9</v>
@@ -3131,16 +3143,16 @@
         <v>26</v>
       </c>
       <c r="BE10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10">
         <v>36</v>
       </c>
       <c r="BH10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI10">
         <v>3.3</v>
@@ -3149,13 +3161,13 @@
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
@@ -3167,40 +3179,40 @@
         <v>9.6</v>
       </c>
       <c r="BQ10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BR10">
         <v>23</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV10">
         <v>55</v>
       </c>
       <c r="BW10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX10">
         <v>55</v>
       </c>
       <c r="BY10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ10">
         <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3208,70 +3220,70 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F11">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G11">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="H11">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K11">
         <v>5.3</v>
       </c>
       <c r="L11">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="Q11">
+        <v>1.58</v>
+      </c>
+      <c r="R11">
         <v>1.6</v>
-      </c>
-      <c r="R11">
-        <v>1.55</v>
       </c>
       <c r="S11">
         <v>2.48</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="X11">
         <v>28</v>
@@ -3283,7 +3295,7 @@
         <v>70</v>
       </c>
       <c r="AA11">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
@@ -3298,7 +3310,7 @@
         <v>100</v>
       </c>
       <c r="AF11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
         <v>12</v>
@@ -3310,10 +3322,10 @@
         <v>85</v>
       </c>
       <c r="AJ11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AK11">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL11">
         <v>34</v>
@@ -3322,10 +3334,10 @@
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP11">
         <v>18</v>
@@ -3334,10 +3346,10 @@
         <v>20</v>
       </c>
       <c r="AR11">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AS11">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT11">
         <v>8.199999999999999</v>
@@ -3349,7 +3361,7 @@
         <v>19.5</v>
       </c>
       <c r="AW11">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX11">
         <v>8</v>
@@ -3361,7 +3373,7 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3370,79 +3382,79 @@
         <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE11">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BF11">
         <v>5</v>
       </c>
       <c r="BG11">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
+        <v>10.5</v>
+      </c>
+      <c r="BN11">
+        <v>4.3</v>
+      </c>
+      <c r="BO11">
+        <v>3.4</v>
+      </c>
+      <c r="BP11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ11">
+        <v>5</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>7.6</v>
+      </c>
+      <c r="BT11">
+        <v>11.5</v>
+      </c>
+      <c r="BU11">
+        <v>5.8</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
         <v>10</v>
       </c>
-      <c r="BN11">
-        <v>4.4</v>
-      </c>
-      <c r="BO11">
-        <v>3.45</v>
-      </c>
-      <c r="BP11">
-        <v>9.4</v>
-      </c>
-      <c r="BQ11">
-        <v>5.1</v>
-      </c>
-      <c r="BR11">
-        <v>22</v>
-      </c>
-      <c r="BS11">
-        <v>7.4</v>
-      </c>
-      <c r="BT11">
-        <v>11</v>
-      </c>
-      <c r="BU11">
-        <v>5.5</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>9.4</v>
-      </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ11">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA11">
         <v>6</v>
       </c>
       <c r="CB11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3450,241 +3462,241 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F12">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="G12">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="H12">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>2.26</v>
+        <v>3.55</v>
       </c>
       <c r="J12">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="O12">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P12">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="Q12">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="S12">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="T12">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="U12">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="X12">
+        <v>38</v>
+      </c>
+      <c r="Y12">
+        <v>28</v>
+      </c>
+      <c r="Z12">
+        <v>38</v>
+      </c>
+      <c r="AA12">
+        <v>650</v>
+      </c>
+      <c r="AB12">
+        <v>19</v>
+      </c>
+      <c r="AC12">
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <v>16</v>
+      </c>
+      <c r="AE12">
+        <v>36</v>
+      </c>
+      <c r="AF12">
         <v>20</v>
       </c>
-      <c r="Y12">
-        <v>13</v>
-      </c>
-      <c r="Z12">
+      <c r="AG12">
+        <v>12</v>
+      </c>
+      <c r="AH12">
+        <v>13.5</v>
+      </c>
+      <c r="AI12">
+        <v>34</v>
+      </c>
+      <c r="AJ12">
+        <v>46</v>
+      </c>
+      <c r="AK12">
+        <v>18.5</v>
+      </c>
+      <c r="AL12">
+        <v>24</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>7.8</v>
+      </c>
+      <c r="AO12">
+        <v>18.5</v>
+      </c>
+      <c r="AP12">
+        <v>22</v>
+      </c>
+      <c r="AQ12">
+        <v>17.5</v>
+      </c>
+      <c r="AR12">
+        <v>21</v>
+      </c>
+      <c r="AS12">
+        <v>30</v>
+      </c>
+      <c r="AT12">
+        <v>16.5</v>
+      </c>
+      <c r="AU12">
+        <v>9.6</v>
+      </c>
+      <c r="AV12">
+        <v>14</v>
+      </c>
+      <c r="AW12">
+        <v>26</v>
+      </c>
+      <c r="AX12">
+        <v>17</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>12</v>
+      </c>
+      <c r="BA12">
+        <v>20</v>
+      </c>
+      <c r="BB12">
+        <v>19</v>
+      </c>
+      <c r="BC12">
         <v>16</v>
       </c>
-      <c r="AA12">
-        <v>28</v>
-      </c>
-      <c r="AB12">
-        <v>17</v>
-      </c>
-      <c r="AC12">
+      <c r="BD12">
+        <v>16</v>
+      </c>
+      <c r="BE12">
+        <v>24</v>
+      </c>
+      <c r="BF12">
+        <v>7.2</v>
+      </c>
+      <c r="BG12">
+        <v>15.5</v>
+      </c>
+      <c r="BH12">
+        <v>5.4</v>
+      </c>
+      <c r="BI12">
+        <v>4.1</v>
+      </c>
+      <c r="BJ12">
+        <v>8.6</v>
+      </c>
+      <c r="BK12">
+        <v>4.7</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
         <v>9</v>
       </c>
-      <c r="AD12">
-        <v>11.5</v>
-      </c>
-      <c r="AE12">
-        <v>21</v>
-      </c>
-      <c r="AF12">
-        <v>27</v>
-      </c>
-      <c r="AG12">
-        <v>15</v>
-      </c>
-      <c r="AH12">
-        <v>15.5</v>
-      </c>
-      <c r="AI12">
-        <v>30</v>
-      </c>
-      <c r="AJ12">
-        <v>60</v>
-      </c>
-      <c r="AK12">
-        <v>36</v>
-      </c>
-      <c r="AL12">
-        <v>40</v>
-      </c>
-      <c r="AM12">
-        <v>1000</v>
-      </c>
-      <c r="AN12">
+      <c r="BN12">
+        <v>5.9</v>
+      </c>
+      <c r="BO12">
+        <v>4.9</v>
+      </c>
+      <c r="BP12">
+        <v>13.5</v>
+      </c>
+      <c r="BQ12">
+        <v>5.9</v>
+      </c>
+      <c r="BR12">
+        <v>19.5</v>
+      </c>
+      <c r="BS12">
+        <v>6.8</v>
+      </c>
+      <c r="BT12">
+        <v>7.8</v>
+      </c>
+      <c r="BU12">
+        <v>4.5</v>
+      </c>
+      <c r="BV12">
+        <v>23</v>
+      </c>
+      <c r="BW12">
+        <v>7.2</v>
+      </c>
+      <c r="BX12">
         <v>26</v>
       </c>
-      <c r="AO12">
-        <v>12.5</v>
-      </c>
-      <c r="AP12">
-        <v>17.5</v>
-      </c>
-      <c r="AQ12">
-        <v>11.5</v>
-      </c>
-      <c r="AR12">
-        <v>14</v>
-      </c>
-      <c r="AS12">
-        <v>25</v>
-      </c>
-      <c r="AT12">
-        <v>15</v>
-      </c>
-      <c r="AU12">
-        <v>8</v>
-      </c>
-      <c r="AV12">
-        <v>10</v>
-      </c>
-      <c r="AW12">
-        <v>18.5</v>
-      </c>
-      <c r="AX12">
-        <v>23</v>
-      </c>
-      <c r="AY12">
-        <v>13</v>
-      </c>
-      <c r="AZ12">
-        <v>14</v>
-      </c>
-      <c r="BA12">
-        <v>27</v>
-      </c>
-      <c r="BB12">
-        <v>50</v>
-      </c>
-      <c r="BC12">
-        <v>30</v>
-      </c>
-      <c r="BD12">
-        <v>34</v>
-      </c>
-      <c r="BE12">
-        <v>55</v>
-      </c>
-      <c r="BF12">
-        <v>23</v>
-      </c>
-      <c r="BG12">
-        <v>11.5</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3692,241 +3704,241 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F13">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="G13">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="H13">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="I13">
-        <v>3.55</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L13">
+        <v>1.33</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13">
         <v>1.24</v>
       </c>
-      <c r="M13">
-        <v>1.02</v>
-      </c>
-      <c r="N13">
-        <v>7.6</v>
-      </c>
-      <c r="O13">
-        <v>1.14</v>
-      </c>
       <c r="P13">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q13">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
-        <v>2.08</v>
+        <v>2.82</v>
       </c>
       <c r="T13">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="U13">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
+        <v>1.8</v>
+      </c>
+      <c r="W13">
         <v>1.4</v>
       </c>
-      <c r="W13">
-        <v>1.89</v>
-      </c>
       <c r="X13">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="Y13">
+        <v>13</v>
+      </c>
+      <c r="Z13">
+        <v>16</v>
+      </c>
+      <c r="AA13">
         <v>28</v>
       </c>
-      <c r="Z13">
-        <v>36</v>
-      </c>
-      <c r="AA13">
-        <v>590</v>
-      </c>
       <c r="AB13">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AE13">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AF13">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AG13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH13">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI13">
         <v>32</v>
       </c>
       <c r="AJ13">
+        <v>60</v>
+      </c>
+      <c r="AK13">
+        <v>34</v>
+      </c>
+      <c r="AL13">
+        <v>40</v>
+      </c>
+      <c r="AM13">
+        <v>70</v>
+      </c>
+      <c r="AN13">
+        <v>26</v>
+      </c>
+      <c r="AO13">
+        <v>13</v>
+      </c>
+      <c r="AP13">
+        <v>17.5</v>
+      </c>
+      <c r="AQ13">
+        <v>11.5</v>
+      </c>
+      <c r="AR13">
+        <v>14</v>
+      </c>
+      <c r="AS13">
+        <v>25</v>
+      </c>
+      <c r="AT13">
+        <v>15</v>
+      </c>
+      <c r="AU13">
+        <v>8</v>
+      </c>
+      <c r="AV13">
+        <v>10</v>
+      </c>
+      <c r="AW13">
+        <v>18.5</v>
+      </c>
+      <c r="AX13">
+        <v>23</v>
+      </c>
+      <c r="AY13">
+        <v>13</v>
+      </c>
+      <c r="AZ13">
+        <v>14</v>
+      </c>
+      <c r="BA13">
+        <v>27</v>
+      </c>
+      <c r="BB13">
+        <v>48</v>
+      </c>
+      <c r="BC13">
+        <v>30</v>
+      </c>
+      <c r="BD13">
+        <v>34</v>
+      </c>
+      <c r="BE13">
+        <v>55</v>
+      </c>
+      <c r="BF13">
+        <v>23</v>
+      </c>
+      <c r="BG13">
+        <v>11.5</v>
+      </c>
+      <c r="BH13">
+        <v>4.1</v>
+      </c>
+      <c r="BI13">
+        <v>3.25</v>
+      </c>
+      <c r="BJ13">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK13">
+        <v>5.6</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>13</v>
+      </c>
+      <c r="BN13">
+        <v>6.8</v>
+      </c>
+      <c r="BO13">
+        <v>5.2</v>
+      </c>
+      <c r="BP13">
+        <v>24</v>
+      </c>
+      <c r="BQ13">
+        <v>9.4</v>
+      </c>
+      <c r="BR13">
         <v>32</v>
       </c>
-      <c r="AK13">
+      <c r="BS13">
+        <v>10.5</v>
+      </c>
+      <c r="BT13">
+        <v>5.4</v>
+      </c>
+      <c r="BU13">
+        <v>4.1</v>
+      </c>
+      <c r="BV13">
+        <v>15</v>
+      </c>
+      <c r="BW13">
+        <v>7.6</v>
+      </c>
+      <c r="BX13">
+        <v>24</v>
+      </c>
+      <c r="BY13">
+        <v>9.4</v>
+      </c>
+      <c r="BZ13">
         <v>18.5</v>
       </c>
-      <c r="AL13">
-        <v>25</v>
-      </c>
-      <c r="AM13">
-        <v>44</v>
-      </c>
-      <c r="AN13">
-        <v>8</v>
-      </c>
-      <c r="AO13">
-        <v>18</v>
-      </c>
-      <c r="AP13">
-        <v>22</v>
-      </c>
-      <c r="AQ13">
-        <v>21</v>
-      </c>
-      <c r="AR13">
-        <v>21</v>
-      </c>
-      <c r="AS13">
-        <v>29</v>
-      </c>
-      <c r="AT13">
-        <v>16.5</v>
-      </c>
-      <c r="AU13">
-        <v>9.6</v>
-      </c>
-      <c r="AV13">
-        <v>13.5</v>
-      </c>
-      <c r="AW13">
-        <v>20</v>
-      </c>
-      <c r="AX13">
-        <v>16.5</v>
-      </c>
-      <c r="AY13">
-        <v>10.5</v>
-      </c>
-      <c r="AZ13">
-        <v>12</v>
-      </c>
-      <c r="BA13">
-        <v>20</v>
-      </c>
-      <c r="BB13">
-        <v>19</v>
-      </c>
-      <c r="BC13">
-        <v>16</v>
-      </c>
-      <c r="BD13">
-        <v>19</v>
-      </c>
-      <c r="BE13">
-        <v>24</v>
-      </c>
-      <c r="BF13">
-        <v>7.2</v>
-      </c>
-      <c r="BG13">
-        <v>15</v>
-      </c>
-      <c r="BH13">
-        <v>5.4</v>
-      </c>
-      <c r="BI13">
-        <v>4.1</v>
-      </c>
-      <c r="BJ13">
-        <v>8.6</v>
-      </c>
-      <c r="BK13">
-        <v>4.5</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN13">
-        <v>6</v>
-      </c>
-      <c r="BO13">
-        <v>4.9</v>
-      </c>
-      <c r="BP13">
-        <v>14</v>
-      </c>
-      <c r="BQ13">
-        <v>5.7</v>
-      </c>
-      <c r="BR13">
-        <v>20</v>
-      </c>
-      <c r="BS13">
-        <v>6.4</v>
-      </c>
-      <c r="BT13">
-        <v>7.8</v>
-      </c>
-      <c r="BU13">
-        <v>4.3</v>
-      </c>
-      <c r="BV13">
-        <v>23</v>
-      </c>
-      <c r="BW13">
-        <v>6.6</v>
-      </c>
-      <c r="BX13">
-        <v>26</v>
-      </c>
-      <c r="BY13">
-        <v>7</v>
-      </c>
-      <c r="BZ13">
-        <v>12.5</v>
-      </c>
       <c r="CA13">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3934,187 +3946,187 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F14">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
+        <v>2.12</v>
+      </c>
+      <c r="H14">
+        <v>3.55</v>
+      </c>
+      <c r="I14">
+        <v>3.7</v>
+      </c>
+      <c r="J14">
+        <v>3.95</v>
+      </c>
+      <c r="K14">
+        <v>4.2</v>
+      </c>
+      <c r="L14">
+        <v>1.3</v>
+      </c>
+      <c r="M14">
+        <v>1.04</v>
+      </c>
+      <c r="N14">
+        <v>5.7</v>
+      </c>
+      <c r="O14">
+        <v>1.19</v>
+      </c>
+      <c r="P14">
+        <v>2.56</v>
+      </c>
+      <c r="Q14">
         <v>1.61</v>
       </c>
-      <c r="H14">
-        <v>5.3</v>
-      </c>
-      <c r="I14">
-        <v>5.7</v>
-      </c>
-      <c r="J14">
-        <v>5.1</v>
-      </c>
-      <c r="K14">
-        <v>5.3</v>
-      </c>
-      <c r="L14">
-        <v>1.22</v>
-      </c>
-      <c r="M14">
-        <v>1.02</v>
-      </c>
-      <c r="N14">
-        <v>8.6</v>
-      </c>
-      <c r="O14">
-        <v>1.12</v>
-      </c>
-      <c r="P14">
-        <v>3.5</v>
-      </c>
-      <c r="Q14">
+      <c r="R14">
+        <v>1.62</v>
+      </c>
+      <c r="S14">
+        <v>2.52</v>
+      </c>
+      <c r="T14">
+        <v>1.57</v>
+      </c>
+      <c r="U14">
+        <v>2.6</v>
+      </c>
+      <c r="V14">
         <v>1.37</v>
       </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>1.94</v>
-      </c>
-      <c r="T14">
-        <v>1.49</v>
-      </c>
-      <c r="U14">
-        <v>2.92</v>
-      </c>
-      <c r="V14">
-        <v>1.21</v>
-      </c>
       <c r="W14">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="X14">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Y14">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AA14">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AB14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD14">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AE14">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AF14">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI14">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="AJ14">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AK14">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
+        <v>28</v>
+      </c>
+      <c r="AM14">
+        <v>60</v>
+      </c>
+      <c r="AN14">
+        <v>10.5</v>
+      </c>
+      <c r="AO14">
+        <v>24</v>
+      </c>
+      <c r="AP14">
+        <v>21</v>
+      </c>
+      <c r="AQ14">
+        <v>18</v>
+      </c>
+      <c r="AR14">
+        <v>26</v>
+      </c>
+      <c r="AS14">
+        <v>50</v>
+      </c>
+      <c r="AT14">
+        <v>13</v>
+      </c>
+      <c r="AU14">
+        <v>8.6</v>
+      </c>
+      <c r="AV14">
+        <v>14</v>
+      </c>
+      <c r="AW14">
         <v>22</v>
       </c>
-      <c r="AM14">
-        <v>55</v>
-      </c>
-      <c r="AN14">
-        <v>4.9</v>
-      </c>
-      <c r="AO14">
-        <v>32</v>
-      </c>
-      <c r="AP14">
-        <v>32</v>
-      </c>
-      <c r="AQ14">
-        <v>32</v>
-      </c>
-      <c r="AR14">
-        <v>48</v>
-      </c>
-      <c r="AS14">
-        <v>42</v>
-      </c>
-      <c r="AT14">
-        <v>16</v>
-      </c>
-      <c r="AU14">
-        <v>12</v>
-      </c>
-      <c r="AV14">
-        <v>20</v>
-      </c>
-      <c r="AW14">
-        <v>44</v>
-      </c>
       <c r="AX14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY14">
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BB14">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BC14">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BE14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BF14">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BG14">
         <v>22</v>
       </c>
       <c r="BH14">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BI14">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="BJ14">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK14">
         <v>4.8</v>
@@ -4123,52 +4135,52 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO14">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BP14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BQ14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BR14">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BS14">
+        <v>7.2</v>
+      </c>
+      <c r="BT14">
+        <v>7.6</v>
+      </c>
+      <c r="BU14">
+        <v>4.4</v>
+      </c>
+      <c r="BV14">
+        <v>26</v>
+      </c>
+      <c r="BW14">
+        <v>7.4</v>
+      </c>
+      <c r="BX14">
+        <v>32</v>
+      </c>
+      <c r="BY14">
+        <v>8</v>
+      </c>
+      <c r="BZ14">
+        <v>16</v>
+      </c>
+      <c r="CA14">
         <v>6.4</v>
       </c>
-      <c r="BT14">
-        <v>10</v>
-      </c>
-      <c r="BU14">
-        <v>5</v>
-      </c>
-      <c r="BV14">
-        <v>36</v>
-      </c>
-      <c r="BW14">
-        <v>7.8</v>
-      </c>
-      <c r="BX14">
-        <v>34</v>
-      </c>
-      <c r="BY14">
-        <v>7.8</v>
-      </c>
-      <c r="BZ14">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="CA14">
-        <v>4.9</v>
-      </c>
       <c r="CB14" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4176,241 +4188,241 @@
         <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F15">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="G15">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="I15">
-        <v>4.9</v>
+        <v>2.96</v>
       </c>
       <c r="J15">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q15">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="S15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T15">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="U15">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="X15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y15">
+        <v>20</v>
+      </c>
+      <c r="Z15">
+        <v>25</v>
+      </c>
+      <c r="AA15">
+        <v>48</v>
+      </c>
+      <c r="AB15">
+        <v>18</v>
+      </c>
+      <c r="AC15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD15">
+        <v>13.5</v>
+      </c>
+      <c r="AE15">
+        <v>28</v>
+      </c>
+      <c r="AF15">
+        <v>21</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>14.5</v>
+      </c>
+      <c r="AI15">
+        <v>32</v>
+      </c>
+      <c r="AJ15">
         <v>36</v>
       </c>
-      <c r="Z15">
-        <v>46</v>
-      </c>
-      <c r="AA15">
-        <v>1000</v>
-      </c>
-      <c r="AB15">
-        <v>14</v>
-      </c>
-      <c r="AC15">
-        <v>10.5</v>
-      </c>
-      <c r="AD15">
-        <v>19.5</v>
-      </c>
-      <c r="AE15">
-        <v>55</v>
-      </c>
-      <c r="AF15">
-        <v>14</v>
-      </c>
-      <c r="AG15">
-        <v>10.5</v>
-      </c>
-      <c r="AH15">
-        <v>16.5</v>
-      </c>
-      <c r="AI15">
-        <v>140</v>
-      </c>
-      <c r="AJ15">
+      <c r="AK15">
+        <v>23</v>
+      </c>
+      <c r="AL15">
+        <v>28</v>
+      </c>
+      <c r="AM15">
+        <v>180</v>
+      </c>
+      <c r="AN15">
+        <v>11.5</v>
+      </c>
+      <c r="AO15">
+        <v>15.5</v>
+      </c>
+      <c r="AP15">
+        <v>19</v>
+      </c>
+      <c r="AQ15">
+        <v>17.5</v>
+      </c>
+      <c r="AR15">
         <v>20</v>
       </c>
-      <c r="AK15">
-        <v>16.5</v>
-      </c>
-      <c r="AL15">
-        <v>26</v>
-      </c>
-      <c r="AM15">
-        <v>1000</v>
-      </c>
-      <c r="AN15">
-        <v>7.2</v>
-      </c>
-      <c r="AO15">
-        <v>85</v>
-      </c>
-      <c r="AP15">
-        <v>18.5</v>
-      </c>
-      <c r="AQ15">
-        <v>23</v>
-      </c>
-      <c r="AR15">
-        <v>32</v>
-      </c>
       <c r="AS15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT15">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AW15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AX15">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15">
+        <v>28</v>
+      </c>
+      <c r="BC15">
+        <v>18.5</v>
+      </c>
+      <c r="BD15">
+        <v>18</v>
+      </c>
+      <c r="BE15">
+        <v>27</v>
+      </c>
+      <c r="BF15">
+        <v>10</v>
+      </c>
+      <c r="BG15">
+        <v>13.5</v>
+      </c>
+      <c r="BH15">
+        <v>4.8</v>
+      </c>
+      <c r="BI15">
+        <v>3.8</v>
+      </c>
+      <c r="BJ15">
+        <v>8.6</v>
+      </c>
+      <c r="BK15">
+        <v>4.9</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN15">
+        <v>6.2</v>
+      </c>
+      <c r="BO15">
+        <v>4.7</v>
+      </c>
+      <c r="BP15">
         <v>16</v>
       </c>
-      <c r="BC15">
-        <v>13.5</v>
-      </c>
-      <c r="BD15">
-        <v>21</v>
-      </c>
-      <c r="BE15">
-        <v>30</v>
-      </c>
-      <c r="BF15">
+      <c r="BQ15">
         <v>6.6</v>
       </c>
-      <c r="BG15">
-        <v>30</v>
-      </c>
-      <c r="BH15">
-        <v>1000</v>
-      </c>
-      <c r="BI15">
-        <v>2.12</v>
-      </c>
-      <c r="BJ15">
-        <v>12.5</v>
-      </c>
-      <c r="BK15">
-        <v>1.82</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>2.08</v>
-      </c>
-      <c r="BN15">
-        <v>6.4</v>
-      </c>
-      <c r="BO15">
-        <v>3.7</v>
-      </c>
-      <c r="BP15">
-        <v>15.5</v>
-      </c>
-      <c r="BQ15">
-        <v>1.87</v>
-      </c>
       <c r="BR15">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BS15">
-        <v>1.98</v>
+        <v>7.6</v>
       </c>
       <c r="BT15">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>1.79</v>
+        <v>5.2</v>
       </c>
       <c r="BV15">
-        <v>46</v>
+        <v>19.5</v>
       </c>
       <c r="BW15">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BX15">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="BY15">
-        <v>2.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA15">
-        <v>1.91</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB15" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4418,241 +4430,241 @@
         <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F16">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="G16">
-        <v>2.46</v>
+        <v>1.61</v>
       </c>
       <c r="H16">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="I16">
-        <v>2.96</v>
+        <v>5.7</v>
       </c>
       <c r="J16">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="L16">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="M16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N16">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="O16">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="S16">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="T16">
         <v>1.49</v>
       </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
-        <v>1.68</v>
+        <v>2.64</v>
       </c>
       <c r="X16">
+        <v>44</v>
+      </c>
+      <c r="Y16">
+        <v>80</v>
+      </c>
+      <c r="Z16">
+        <v>60</v>
+      </c>
+      <c r="AA16">
+        <v>140</v>
+      </c>
+      <c r="AB16">
+        <v>18</v>
+      </c>
+      <c r="AC16">
+        <v>13.5</v>
+      </c>
+      <c r="AD16">
+        <v>23</v>
+      </c>
+      <c r="AE16">
+        <v>55</v>
+      </c>
+      <c r="AF16">
+        <v>15.5</v>
+      </c>
+      <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>17</v>
+      </c>
+      <c r="AI16">
+        <v>110</v>
+      </c>
+      <c r="AJ16">
+        <v>18.5</v>
+      </c>
+      <c r="AK16">
+        <v>14.5</v>
+      </c>
+      <c r="AL16">
+        <v>22</v>
+      </c>
+      <c r="AM16">
+        <v>55</v>
+      </c>
+      <c r="AN16">
+        <v>4.7</v>
+      </c>
+      <c r="AO16">
         <v>32</v>
       </c>
-      <c r="Y16">
+      <c r="AP16">
+        <v>26</v>
+      </c>
+      <c r="AQ16">
+        <v>32</v>
+      </c>
+      <c r="AR16">
+        <v>48</v>
+      </c>
+      <c r="AS16">
+        <v>42</v>
+      </c>
+      <c r="AT16">
+        <v>16</v>
+      </c>
+      <c r="AU16">
+        <v>12</v>
+      </c>
+      <c r="AV16">
         <v>20</v>
       </c>
-      <c r="Z16">
-        <v>25</v>
-      </c>
-      <c r="AA16">
-        <v>48</v>
-      </c>
-      <c r="AB16">
-        <v>18.5</v>
-      </c>
-      <c r="AC16">
-        <v>10.5</v>
-      </c>
-      <c r="AD16">
-        <v>14</v>
-      </c>
-      <c r="AE16">
-        <v>28</v>
-      </c>
-      <c r="AF16">
-        <v>21</v>
-      </c>
-      <c r="AG16">
+      <c r="AW16">
+        <v>44</v>
+      </c>
+      <c r="AX16">
+        <v>13.5</v>
+      </c>
+      <c r="AY16">
+        <v>10</v>
+      </c>
+      <c r="AZ16">
+        <v>15</v>
+      </c>
+      <c r="BA16">
+        <v>38</v>
+      </c>
+      <c r="BB16">
+        <v>16.5</v>
+      </c>
+      <c r="BC16">
         <v>12.5</v>
       </c>
-      <c r="AH16">
-        <v>14.5</v>
-      </c>
-      <c r="AI16">
-        <v>32</v>
-      </c>
-      <c r="AJ16">
-        <v>38</v>
-      </c>
-      <c r="AK16">
-        <v>23</v>
-      </c>
-      <c r="AL16">
-        <v>29</v>
-      </c>
-      <c r="AM16">
-        <v>60</v>
-      </c>
-      <c r="AN16">
-        <v>11.5</v>
-      </c>
-      <c r="AO16">
-        <v>16</v>
-      </c>
-      <c r="AP16">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ16">
-        <v>17</v>
-      </c>
-      <c r="AR16">
-        <v>20</v>
-      </c>
-      <c r="AS16">
-        <v>32</v>
-      </c>
-      <c r="AT16">
-        <v>15.5</v>
-      </c>
-      <c r="AU16">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV16">
-        <v>12</v>
-      </c>
-      <c r="AW16">
-        <v>8</v>
-      </c>
-      <c r="AX16">
-        <v>17.5</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>12</v>
-      </c>
-      <c r="BA16">
-        <v>8.4</v>
-      </c>
-      <c r="BB16">
-        <v>27</v>
-      </c>
-      <c r="BC16">
-        <v>18.5</v>
-      </c>
       <c r="BD16">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BE16">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="BF16">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="BG16">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BH16">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BI16">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ16">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16">
         <v>4.8</v>
       </c>
       <c r="BL16">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO16">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="BP16">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BQ16">
+        <v>5</v>
+      </c>
+      <c r="BR16">
+        <v>17.5</v>
+      </c>
+      <c r="BS16">
         <v>6.4</v>
       </c>
-      <c r="BR16">
-        <v>23</v>
-      </c>
-      <c r="BS16">
-        <v>7.4</v>
-      </c>
       <c r="BT16">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV16">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BW16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BY16">
         <v>7.8</v>
       </c>
       <c r="BZ16">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="CB16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4660,276 +4672,276 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F17">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="H17">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="I17">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O17">
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="Q17">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="R17">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="S17">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="T17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
         <v>2.58</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="X17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Y17">
+        <v>27</v>
+      </c>
+      <c r="Z17">
+        <v>44</v>
+      </c>
+      <c r="AA17">
+        <v>110</v>
+      </c>
+      <c r="AB17">
+        <v>13.5</v>
+      </c>
+      <c r="AC17">
+        <v>10.5</v>
+      </c>
+      <c r="AD17">
+        <v>19.5</v>
+      </c>
+      <c r="AE17">
+        <v>160</v>
+      </c>
+      <c r="AF17">
+        <v>14</v>
+      </c>
+      <c r="AG17">
+        <v>10.5</v>
+      </c>
+      <c r="AH17">
+        <v>16.5</v>
+      </c>
+      <c r="AI17">
+        <v>55</v>
+      </c>
+      <c r="AJ17">
         <v>20</v>
       </c>
-      <c r="Z17">
-        <v>30</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
+      <c r="AK17">
+        <v>16.5</v>
+      </c>
+      <c r="AL17">
+        <v>26</v>
+      </c>
+      <c r="AM17">
+        <v>1000</v>
+      </c>
+      <c r="AN17">
+        <v>7.2</v>
+      </c>
+      <c r="AO17">
+        <v>85</v>
+      </c>
+      <c r="AP17">
+        <v>18.5</v>
+      </c>
+      <c r="AQ17">
+        <v>22</v>
+      </c>
+      <c r="AR17">
+        <v>34</v>
+      </c>
+      <c r="AS17">
+        <v>38</v>
+      </c>
+      <c r="AT17">
+        <v>12</v>
+      </c>
+      <c r="AU17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV17">
+        <v>16.5</v>
+      </c>
+      <c r="AW17">
+        <v>42</v>
+      </c>
+      <c r="AX17">
+        <v>11.5</v>
+      </c>
+      <c r="AY17">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17">
+        <v>14</v>
+      </c>
+      <c r="BA17">
+        <v>40</v>
+      </c>
+      <c r="BB17">
+        <v>17.5</v>
+      </c>
+      <c r="BC17">
         <v>14.5</v>
       </c>
-      <c r="AC17">
-        <v>9.4</v>
-      </c>
-      <c r="AD17">
-        <v>15.5</v>
-      </c>
-      <c r="AE17">
-        <v>36</v>
-      </c>
-      <c r="AF17">
-        <v>16</v>
-      </c>
-      <c r="AG17">
-        <v>11</v>
-      </c>
-      <c r="AH17">
-        <v>15.5</v>
-      </c>
-      <c r="AI17">
-        <v>38</v>
-      </c>
-      <c r="AJ17">
-        <v>27</v>
-      </c>
-      <c r="AK17">
-        <v>20</v>
-      </c>
-      <c r="AL17">
-        <v>28</v>
-      </c>
-      <c r="AM17">
-        <v>60</v>
-      </c>
-      <c r="AN17">
-        <v>10.5</v>
-      </c>
-      <c r="AO17">
-        <v>26</v>
-      </c>
-      <c r="AP17">
+      <c r="BD17">
         <v>21</v>
-      </c>
-      <c r="AQ17">
-        <v>18</v>
-      </c>
-      <c r="AR17">
-        <v>26</v>
-      </c>
-      <c r="AS17">
-        <v>50</v>
-      </c>
-      <c r="AT17">
-        <v>13</v>
-      </c>
-      <c r="AU17">
-        <v>8.6</v>
-      </c>
-      <c r="AV17">
-        <v>14</v>
-      </c>
-      <c r="AW17">
-        <v>22</v>
-      </c>
-      <c r="AX17">
-        <v>14</v>
-      </c>
-      <c r="AY17">
-        <v>10</v>
-      </c>
-      <c r="AZ17">
-        <v>13.5</v>
-      </c>
-      <c r="BA17">
-        <v>32</v>
-      </c>
-      <c r="BB17">
-        <v>23</v>
-      </c>
-      <c r="BC17">
-        <v>17</v>
-      </c>
-      <c r="BD17">
-        <v>24</v>
       </c>
       <c r="BE17">
         <v>50</v>
       </c>
       <c r="BF17">
+        <v>6.6</v>
+      </c>
+      <c r="BG17">
+        <v>23</v>
+      </c>
+      <c r="BH17">
+        <v>4.8</v>
+      </c>
+      <c r="BI17">
+        <v>3.75</v>
+      </c>
+      <c r="BJ17">
+        <v>9.4</v>
+      </c>
+      <c r="BK17">
+        <v>4.9</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
         <v>9</v>
       </c>
-      <c r="BG17">
-        <v>22</v>
-      </c>
-      <c r="BH17">
-        <v>4.5</v>
-      </c>
-      <c r="BI17">
-        <v>3.5</v>
-      </c>
-      <c r="BJ17">
-        <v>9</v>
-      </c>
-      <c r="BK17">
-        <v>4.8</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BN17">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BO17">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="BR17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT17">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV17">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BW17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX17">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BY17">
         <v>7.8</v>
       </c>
       <c r="BZ17">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA17">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB17" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F18">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="G18">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H18">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="I18">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J18">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="K18">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4938,205 +4950,205 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="O18">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="P18">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="R18">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S18">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="T18">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
         <v>1000</v>
       </c>
       <c r="AN18">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5144,420 +5156,420 @@
         <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F19">
-        <v>1.81</v>
+        <v>2.62</v>
       </c>
       <c r="G19">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="H19">
-        <v>5.2</v>
+        <v>2.88</v>
       </c>
       <c r="I19">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="J19">
+        <v>3.05</v>
+      </c>
+      <c r="K19">
         <v>3.3</v>
-      </c>
-      <c r="K19">
-        <v>3.75</v>
       </c>
       <c r="L19">
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O19">
+        <v>1.42</v>
+      </c>
+      <c r="P19">
+        <v>1.68</v>
+      </c>
+      <c r="Q19">
+        <v>2.22</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>4.2</v>
+      </c>
+      <c r="T19">
+        <v>1.87</v>
+      </c>
+      <c r="U19">
+        <v>1.96</v>
+      </c>
+      <c r="V19">
+        <v>1.45</v>
+      </c>
+      <c r="W19">
         <v>1.52</v>
       </c>
-      <c r="P19">
-        <v>1.54</v>
-      </c>
-      <c r="Q19">
-        <v>2.36</v>
-      </c>
-      <c r="R19">
-        <v>1.18</v>
-      </c>
-      <c r="S19">
-        <v>5.1</v>
-      </c>
-      <c r="T19">
-        <v>1.99</v>
-      </c>
-      <c r="U19">
-        <v>1.58</v>
-      </c>
-      <c r="V19">
-        <v>1.2</v>
-      </c>
-      <c r="W19">
-        <v>2.06</v>
-      </c>
       <c r="X19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y19">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z19">
+        <v>970</v>
+      </c>
+      <c r="AA19">
         <v>55</v>
       </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
       <c r="AB19">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD19">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF19">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
         <v>970</v>
       </c>
-      <c r="AH19">
-        <v>950</v>
-      </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ19">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AK19">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AL19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP19">
+        <v>9.4</v>
+      </c>
+      <c r="AQ19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR19">
+        <v>7</v>
+      </c>
+      <c r="AS19">
+        <v>8</v>
+      </c>
+      <c r="AT19">
+        <v>8.4</v>
+      </c>
+      <c r="AU19">
+        <v>6.4</v>
+      </c>
+      <c r="AV19">
+        <v>11.5</v>
+      </c>
+      <c r="AW19">
+        <v>7.6</v>
+      </c>
+      <c r="AX19">
+        <v>15</v>
+      </c>
+      <c r="AY19">
+        <v>11</v>
+      </c>
+      <c r="AZ19">
+        <v>16.5</v>
+      </c>
+      <c r="BA19">
+        <v>8</v>
+      </c>
+      <c r="BB19">
+        <v>7.8</v>
+      </c>
+      <c r="BC19">
+        <v>7.4</v>
+      </c>
+      <c r="BD19">
+        <v>8</v>
+      </c>
+      <c r="BE19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF19">
+        <v>7.4</v>
+      </c>
+      <c r="BG19">
+        <v>7.6</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.74</v>
+      </c>
+      <c r="BJ19">
+        <v>15</v>
+      </c>
+      <c r="BK19">
+        <v>1.56</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.74</v>
+      </c>
+      <c r="BN19">
+        <v>7.8</v>
+      </c>
+      <c r="BO19">
+        <v>1.42</v>
+      </c>
+      <c r="BP19">
+        <v>34</v>
+      </c>
+      <c r="BQ19">
+        <v>1.66</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.69</v>
+      </c>
+      <c r="BT19">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ19">
-        <v>12</v>
-      </c>
-      <c r="AR19">
-        <v>4.8</v>
-      </c>
-      <c r="AS19">
-        <v>3.4</v>
-      </c>
-      <c r="AT19">
-        <v>2.92</v>
-      </c>
-      <c r="AU19">
-        <v>7</v>
-      </c>
-      <c r="AV19">
-        <v>20</v>
-      </c>
-      <c r="AW19">
-        <v>3.4</v>
-      </c>
-      <c r="AX19">
-        <v>8.4</v>
-      </c>
-      <c r="AY19">
-        <v>3.35</v>
-      </c>
-      <c r="AZ19">
-        <v>4.5</v>
-      </c>
-      <c r="BA19">
-        <v>3.4</v>
-      </c>
-      <c r="BB19">
-        <v>18</v>
-      </c>
-      <c r="BC19">
-        <v>21</v>
-      </c>
-      <c r="BD19">
-        <v>3.8</v>
-      </c>
-      <c r="BE19">
-        <v>3.4</v>
-      </c>
-      <c r="BF19">
-        <v>17.5</v>
-      </c>
-      <c r="BG19">
-        <v>3.4</v>
-      </c>
-      <c r="BH19">
-        <v>1000</v>
-      </c>
-      <c r="BI19">
-        <v>1.04</v>
-      </c>
-      <c r="BJ19">
-        <v>1000</v>
-      </c>
-      <c r="BK19">
-        <v>1.04</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>1.04</v>
-      </c>
-      <c r="BN19">
-        <v>1000</v>
-      </c>
-      <c r="BO19">
-        <v>1.04</v>
-      </c>
-      <c r="BP19">
-        <v>1000</v>
-      </c>
-      <c r="BQ19">
-        <v>1.04</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>1.04</v>
-      </c>
-      <c r="BT19">
-        <v>1000</v>
-      </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>1.69</v>
       </c>
       <c r="CB19" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F20">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="G20">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="H20">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="I20">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J20">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L20">
         <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="Q20">
+        <v>2.42</v>
+      </c>
+      <c r="R20">
+        <v>1.2</v>
+      </c>
+      <c r="S20">
+        <v>5</v>
+      </c>
+      <c r="T20">
+        <v>2.18</v>
+      </c>
+      <c r="U20">
+        <v>1.69</v>
+      </c>
+      <c r="V20">
+        <v>1.2</v>
+      </c>
+      <c r="W20">
         <v>2.06</v>
       </c>
-      <c r="R20">
-        <v>1.19</v>
-      </c>
-      <c r="S20">
-        <v>4</v>
-      </c>
-      <c r="T20">
-        <v>1.11</v>
-      </c>
-      <c r="U20">
-        <v>1.67</v>
-      </c>
-      <c r="V20">
-        <v>1.21</v>
-      </c>
-      <c r="W20">
-        <v>1.75</v>
-      </c>
       <c r="X20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5620,733 +5632,733 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F21">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="H21">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J21">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="L21">
         <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>2.24</v>
+        <v>2.86</v>
       </c>
       <c r="O21">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="P21">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="Q21">
-        <v>3.05</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S21">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="T21">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="U21">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="V21">
-        <v>1.9</v>
+        <v>1.26</v>
       </c>
       <c r="W21">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="X21">
+        <v>10.5</v>
+      </c>
+      <c r="Y21">
+        <v>13</v>
+      </c>
+      <c r="Z21">
+        <v>32</v>
+      </c>
+      <c r="AA21">
+        <v>130</v>
+      </c>
+      <c r="AB21">
+        <v>7.8</v>
+      </c>
+      <c r="AC21">
+        <v>7.8</v>
+      </c>
+      <c r="AD21">
+        <v>19</v>
+      </c>
+      <c r="AE21">
+        <v>95</v>
+      </c>
+      <c r="AF21">
+        <v>13</v>
+      </c>
+      <c r="AG21">
+        <v>12</v>
+      </c>
+      <c r="AH21">
+        <v>23</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
+      </c>
+      <c r="AJ21">
+        <v>29</v>
+      </c>
+      <c r="AK21">
+        <v>29</v>
+      </c>
+      <c r="AL21">
+        <v>55</v>
+      </c>
+      <c r="AM21">
+        <v>190</v>
+      </c>
+      <c r="AN21">
+        <v>25</v>
+      </c>
+      <c r="AO21">
+        <v>120</v>
+      </c>
+      <c r="AP21">
+        <v>9</v>
+      </c>
+      <c r="AQ21">
+        <v>10.5</v>
+      </c>
+      <c r="AR21">
+        <v>19</v>
+      </c>
+      <c r="AS21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT21">
+        <v>6.4</v>
+      </c>
+      <c r="AU21">
+        <v>6.4</v>
+      </c>
+      <c r="AV21">
+        <v>15.5</v>
+      </c>
+      <c r="AW21">
+        <v>7.8</v>
+      </c>
+      <c r="AX21">
+        <v>9.4</v>
+      </c>
+      <c r="AY21">
+        <v>9.4</v>
+      </c>
+      <c r="AZ21">
+        <v>18.5</v>
+      </c>
+      <c r="BA21">
+        <v>8</v>
+      </c>
+      <c r="BB21">
+        <v>22</v>
+      </c>
+      <c r="BC21">
+        <v>22</v>
+      </c>
+      <c r="BD21">
+        <v>40</v>
+      </c>
+      <c r="BE21">
         <v>8.4</v>
       </c>
-      <c r="Y21">
-        <v>7</v>
-      </c>
-      <c r="Z21">
-        <v>12</v>
-      </c>
-      <c r="AA21">
-        <v>32</v>
-      </c>
-      <c r="AB21">
-        <v>13</v>
-      </c>
-      <c r="AC21">
-        <v>8.6</v>
-      </c>
-      <c r="AD21">
-        <v>14.5</v>
-      </c>
-      <c r="AE21">
-        <v>46</v>
-      </c>
-      <c r="AF21">
-        <v>42</v>
-      </c>
-      <c r="AG21">
-        <v>26</v>
-      </c>
-      <c r="AH21">
-        <v>950</v>
-      </c>
-      <c r="AI21">
-        <v>95</v>
-      </c>
-      <c r="AJ21">
-        <v>1000</v>
-      </c>
-      <c r="AK21">
-        <v>1000</v>
-      </c>
-      <c r="AL21">
-        <v>1000</v>
-      </c>
-      <c r="AM21">
-        <v>1000</v>
-      </c>
-      <c r="AN21">
-        <v>1000</v>
-      </c>
-      <c r="AO21">
-        <v>38</v>
-      </c>
-      <c r="AP21">
-        <v>3</v>
-      </c>
-      <c r="AQ21">
-        <v>5.2</v>
-      </c>
-      <c r="AR21">
+      <c r="BF21">
+        <v>20</v>
+      </c>
+      <c r="BG21">
         <v>8.199999999999999</v>
       </c>
-      <c r="AS21">
-        <v>19.5</v>
-      </c>
-      <c r="AT21">
-        <v>3.45</v>
-      </c>
-      <c r="AU21">
-        <v>3</v>
-      </c>
-      <c r="AV21">
-        <v>9.6</v>
-      </c>
-      <c r="AW21">
-        <v>4.2</v>
-      </c>
-      <c r="AX21">
-        <v>23</v>
-      </c>
-      <c r="AY21">
-        <v>15</v>
-      </c>
-      <c r="AZ21">
-        <v>4.1</v>
-      </c>
-      <c r="BA21">
-        <v>4.4</v>
-      </c>
-      <c r="BB21">
-        <v>4.7</v>
-      </c>
-      <c r="BC21">
-        <v>4.7</v>
-      </c>
-      <c r="BD21">
-        <v>4.7</v>
-      </c>
-      <c r="BE21">
-        <v>4.7</v>
-      </c>
-      <c r="BF21">
-        <v>4.7</v>
-      </c>
-      <c r="BG21">
-        <v>22</v>
-      </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F22">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>2.92</v>
+        <v>5.4</v>
       </c>
       <c r="H22">
+        <v>2.04</v>
+      </c>
+      <c r="I22">
+        <v>2.1</v>
+      </c>
+      <c r="J22">
+        <v>3.05</v>
+      </c>
+      <c r="K22">
         <v>3.15</v>
-      </c>
-      <c r="I22">
-        <v>3.3</v>
-      </c>
-      <c r="J22">
-        <v>2.92</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
       </c>
       <c r="L22">
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O22">
         <v>1.68</v>
       </c>
       <c r="P22">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q22">
         <v>3.05</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S22">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="U22">
         <v>1.6</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="W22">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD22">
+        <v>13</v>
+      </c>
+      <c r="AE22">
+        <v>36</v>
+      </c>
+      <c r="AF22">
+        <v>38</v>
+      </c>
+      <c r="AG22">
+        <v>23</v>
+      </c>
+      <c r="AH22">
+        <v>32</v>
+      </c>
+      <c r="AI22">
+        <v>95</v>
+      </c>
+      <c r="AJ22">
+        <v>190</v>
+      </c>
+      <c r="AK22">
+        <v>130</v>
+      </c>
+      <c r="AL22">
+        <v>170</v>
+      </c>
+      <c r="AM22">
+        <v>370</v>
+      </c>
+      <c r="AN22">
+        <v>260</v>
+      </c>
+      <c r="AO22">
+        <v>38</v>
+      </c>
+      <c r="AP22">
+        <v>6.4</v>
+      </c>
+      <c r="AQ22">
+        <v>5.4</v>
+      </c>
+      <c r="AR22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS22">
+        <v>19.5</v>
+      </c>
+      <c r="AT22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU22">
+        <v>6.6</v>
+      </c>
+      <c r="AV22">
+        <v>11</v>
+      </c>
+      <c r="AW22">
+        <v>25</v>
+      </c>
+      <c r="AX22">
+        <v>23</v>
+      </c>
+      <c r="AY22">
+        <v>19</v>
+      </c>
+      <c r="AZ22">
+        <v>20</v>
+      </c>
+      <c r="BA22">
+        <v>12</v>
+      </c>
+      <c r="BB22">
+        <v>13</v>
+      </c>
+      <c r="BC22">
+        <v>12.5</v>
+      </c>
+      <c r="BD22">
+        <v>12.5</v>
+      </c>
+      <c r="BE22">
+        <v>13.5</v>
+      </c>
+      <c r="BF22">
+        <v>13</v>
+      </c>
+      <c r="BG22">
+        <v>22</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.42</v>
+      </c>
+      <c r="BJ22">
         <v>18</v>
       </c>
-      <c r="AE22">
-        <v>1000</v>
-      </c>
-      <c r="AF22">
-        <v>18</v>
-      </c>
-      <c r="AG22">
-        <v>15.5</v>
-      </c>
-      <c r="AH22">
-        <v>1000</v>
-      </c>
-      <c r="AI22">
-        <v>1000</v>
-      </c>
-      <c r="AJ22">
-        <v>1000</v>
-      </c>
-      <c r="AK22">
-        <v>1000</v>
-      </c>
-      <c r="AL22">
-        <v>1000</v>
-      </c>
-      <c r="AM22">
-        <v>1000</v>
-      </c>
-      <c r="AN22">
-        <v>1000</v>
-      </c>
-      <c r="AO22">
-        <v>1000</v>
-      </c>
-      <c r="AP22">
-        <v>1.21</v>
-      </c>
-      <c r="AQ22">
-        <v>1.43</v>
-      </c>
-      <c r="AR22">
-        <v>1.43</v>
-      </c>
-      <c r="AS22">
-        <v>1.43</v>
-      </c>
-      <c r="AT22">
-        <v>1.43</v>
-      </c>
-      <c r="AU22">
-        <v>1.43</v>
-      </c>
-      <c r="AV22">
-        <v>1.33</v>
-      </c>
-      <c r="AW22">
-        <v>1.43</v>
-      </c>
-      <c r="AX22">
-        <v>1.33</v>
-      </c>
-      <c r="AY22">
-        <v>11</v>
-      </c>
-      <c r="AZ22">
-        <v>1.43</v>
-      </c>
-      <c r="BA22">
-        <v>1.43</v>
-      </c>
-      <c r="BB22">
-        <v>1.43</v>
-      </c>
-      <c r="BC22">
-        <v>1.43</v>
-      </c>
-      <c r="BD22">
-        <v>1.43</v>
-      </c>
-      <c r="BE22">
-        <v>1.43</v>
-      </c>
-      <c r="BF22">
-        <v>1.43</v>
-      </c>
-      <c r="BG22">
-        <v>1.43</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.66</v>
-      </c>
-      <c r="BJ22">
-        <v>17.5</v>
-      </c>
       <c r="BK22">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="BN22">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BP22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="BT22">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU22">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="BV22">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BW22">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="CB22" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F23">
-        <v>1.55</v>
+        <v>2.82</v>
       </c>
       <c r="G23">
+        <v>2.9</v>
+      </c>
+      <c r="H23">
+        <v>3.15</v>
+      </c>
+      <c r="I23">
+        <v>3.2</v>
+      </c>
+      <c r="J23">
+        <v>2.92</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.14</v>
+      </c>
+      <c r="N23">
+        <v>2.28</v>
+      </c>
+      <c r="O23">
+        <v>1.69</v>
+      </c>
+      <c r="P23">
+        <v>1.43</v>
+      </c>
+      <c r="Q23">
+        <v>3.05</v>
+      </c>
+      <c r="R23">
+        <v>1.14</v>
+      </c>
+      <c r="S23">
+        <v>7</v>
+      </c>
+      <c r="T23">
+        <v>2.34</v>
+      </c>
+      <c r="U23">
+        <v>1.64</v>
+      </c>
+      <c r="V23">
+        <v>1.45</v>
+      </c>
+      <c r="W23">
+        <v>1.52</v>
+      </c>
+      <c r="X23">
+        <v>7.8</v>
+      </c>
+      <c r="Y23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z23">
+        <v>21</v>
+      </c>
+      <c r="AA23">
+        <v>70</v>
+      </c>
+      <c r="AB23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23">
+        <v>15.5</v>
+      </c>
+      <c r="AE23">
+        <v>60</v>
+      </c>
+      <c r="AF23">
+        <v>970</v>
+      </c>
+      <c r="AG23">
+        <v>970</v>
+      </c>
+      <c r="AH23">
+        <v>34</v>
+      </c>
+      <c r="AI23">
+        <v>95</v>
+      </c>
+      <c r="AJ23">
+        <v>65</v>
+      </c>
+      <c r="AK23">
+        <v>60</v>
+      </c>
+      <c r="AL23">
+        <v>110</v>
+      </c>
+      <c r="AM23">
+        <v>320</v>
+      </c>
+      <c r="AN23">
+        <v>80</v>
+      </c>
+      <c r="AO23">
+        <v>85</v>
+      </c>
+      <c r="AP23">
+        <v>6.6</v>
+      </c>
+      <c r="AQ23">
+        <v>6.4</v>
+      </c>
+      <c r="AR23">
+        <v>15.5</v>
+      </c>
+      <c r="AS23">
+        <v>6.4</v>
+      </c>
+      <c r="AT23">
+        <v>6.6</v>
+      </c>
+      <c r="AU23">
+        <v>6.8</v>
+      </c>
+      <c r="AV23">
+        <v>12.5</v>
+      </c>
+      <c r="AW23">
+        <v>6.4</v>
+      </c>
+      <c r="AX23">
+        <v>15</v>
+      </c>
+      <c r="AY23">
+        <v>13</v>
+      </c>
+      <c r="AZ23">
+        <v>5.9</v>
+      </c>
+      <c r="BA23">
+        <v>6.6</v>
+      </c>
+      <c r="BB23">
+        <v>6.4</v>
+      </c>
+      <c r="BC23">
+        <v>6.4</v>
+      </c>
+      <c r="BD23">
+        <v>6.6</v>
+      </c>
+      <c r="BE23">
+        <v>7</v>
+      </c>
+      <c r="BF23">
+        <v>6.6</v>
+      </c>
+      <c r="BG23">
+        <v>6.6</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.62</v>
+      </c>
+      <c r="BJ23">
+        <v>17.5</v>
+      </c>
+      <c r="BK23">
+        <v>1.49</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.62</v>
+      </c>
+      <c r="BN23">
+        <v>7.6</v>
+      </c>
+      <c r="BO23">
+        <v>3.7</v>
+      </c>
+      <c r="BP23">
+        <v>40</v>
+      </c>
+      <c r="BQ23">
+        <v>1.56</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.6</v>
+      </c>
+      <c r="BT23">
+        <v>8.6</v>
+      </c>
+      <c r="BU23">
+        <v>4.3</v>
+      </c>
+      <c r="BV23">
+        <v>46</v>
+      </c>
+      <c r="BW23">
         <v>1.57</v>
       </c>
-      <c r="H23">
-        <v>8</v>
-      </c>
-      <c r="I23">
-        <v>8.4</v>
-      </c>
-      <c r="J23">
-        <v>4.2</v>
-      </c>
-      <c r="K23">
-        <v>4.4</v>
-      </c>
-      <c r="L23">
-        <v>1.34</v>
-      </c>
-      <c r="M23">
-        <v>1.08</v>
-      </c>
-      <c r="N23">
-        <v>3.6</v>
-      </c>
-      <c r="O23">
-        <v>1.35</v>
-      </c>
-      <c r="P23">
-        <v>1.92</v>
-      </c>
-      <c r="Q23">
-        <v>2.04</v>
-      </c>
-      <c r="R23">
-        <v>1.33</v>
-      </c>
-      <c r="S23">
-        <v>3.7</v>
-      </c>
-      <c r="T23">
-        <v>2.14</v>
-      </c>
-      <c r="U23">
-        <v>1.81</v>
-      </c>
-      <c r="V23">
-        <v>1.13</v>
-      </c>
-      <c r="W23">
-        <v>2.74</v>
-      </c>
-      <c r="X23">
-        <v>14</v>
-      </c>
-      <c r="Y23">
-        <v>22</v>
-      </c>
-      <c r="Z23">
-        <v>860</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>7.4</v>
-      </c>
-      <c r="AC23">
-        <v>9.4</v>
-      </c>
-      <c r="AD23">
-        <v>32</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG23">
-        <v>10.5</v>
-      </c>
-      <c r="AH23">
-        <v>26</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>14</v>
-      </c>
-      <c r="AK23">
-        <v>18</v>
-      </c>
-      <c r="AL23">
-        <v>50</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>9.6</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>12</v>
-      </c>
-      <c r="AQ23">
-        <v>19.5</v>
-      </c>
-      <c r="AR23">
-        <v>30</v>
-      </c>
-      <c r="AS23">
-        <v>50</v>
-      </c>
-      <c r="AT23">
-        <v>6.8</v>
-      </c>
-      <c r="AU23">
-        <v>8.4</v>
-      </c>
-      <c r="AV23">
-        <v>20</v>
-      </c>
-      <c r="AW23">
-        <v>42</v>
-      </c>
-      <c r="AX23">
-        <v>7.6</v>
-      </c>
-      <c r="AY23">
-        <v>9.4</v>
-      </c>
-      <c r="AZ23">
-        <v>23</v>
-      </c>
-      <c r="BA23">
-        <v>42</v>
-      </c>
-      <c r="BB23">
-        <v>12</v>
-      </c>
-      <c r="BC23">
-        <v>15.5</v>
-      </c>
-      <c r="BD23">
-        <v>36</v>
-      </c>
-      <c r="BE23">
-        <v>46</v>
-      </c>
-      <c r="BF23">
-        <v>8.6</v>
-      </c>
-      <c r="BG23">
-        <v>95</v>
-      </c>
-      <c r="BH23">
-        <v>3.4</v>
-      </c>
-      <c r="BI23">
-        <v>2.82</v>
-      </c>
-      <c r="BJ23">
-        <v>12</v>
-      </c>
-      <c r="BK23">
-        <v>7</v>
-      </c>
-      <c r="BL23">
-        <v>1000</v>
-      </c>
-      <c r="BM23">
-        <v>15.5</v>
-      </c>
-      <c r="BN23">
-        <v>3.85</v>
-      </c>
-      <c r="BO23">
-        <v>3.1</v>
-      </c>
-      <c r="BP23">
-        <v>10</v>
-      </c>
-      <c r="BQ23">
-        <v>6.2</v>
-      </c>
-      <c r="BR23">
-        <v>29</v>
-      </c>
-      <c r="BS23">
-        <v>10.5</v>
-      </c>
-      <c r="BT23">
-        <v>11</v>
-      </c>
-      <c r="BU23">
-        <v>6.6</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>13.5</v>
-      </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>14</v>
+        <v>1.6</v>
       </c>
       <c r="BZ23">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="CB23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6354,483 +6366,725 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F24">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="G24">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="J24">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="K24">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M24">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="Q24">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="R24">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S24">
-        <v>2.92</v>
+        <v>3.65</v>
       </c>
       <c r="T24">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="W24">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
+        <v>7.4</v>
+      </c>
+      <c r="AC24">
+        <v>9.4</v>
+      </c>
+      <c r="AD24">
+        <v>32</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG24">
+        <v>10.5</v>
+      </c>
+      <c r="AH24">
+        <v>26</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>14</v>
+      </c>
+      <c r="AK24">
+        <v>18</v>
+      </c>
+      <c r="AL24">
+        <v>50</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
         <v>9.6</v>
       </c>
-      <c r="AC24">
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>12</v>
+      </c>
+      <c r="AQ24">
+        <v>19.5</v>
+      </c>
+      <c r="AR24">
+        <v>30</v>
+      </c>
+      <c r="AS24">
+        <v>50</v>
+      </c>
+      <c r="AT24">
+        <v>6.8</v>
+      </c>
+      <c r="AU24">
+        <v>8.4</v>
+      </c>
+      <c r="AV24">
+        <v>20</v>
+      </c>
+      <c r="AW24">
+        <v>15.5</v>
+      </c>
+      <c r="AX24">
+        <v>7.6</v>
+      </c>
+      <c r="AY24">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24">
+        <v>23</v>
+      </c>
+      <c r="BA24">
+        <v>42</v>
+      </c>
+      <c r="BB24">
+        <v>12</v>
+      </c>
+      <c r="BC24">
+        <v>15.5</v>
+      </c>
+      <c r="BD24">
+        <v>26</v>
+      </c>
+      <c r="BE24">
+        <v>16</v>
+      </c>
+      <c r="BF24">
         <v>8.6</v>
       </c>
-      <c r="AD24">
-        <v>1000</v>
-      </c>
-      <c r="AE24">
-        <v>1000</v>
-      </c>
-      <c r="AF24">
-        <v>1000</v>
-      </c>
-      <c r="AG24">
-        <v>1000</v>
-      </c>
-      <c r="AH24">
-        <v>1000</v>
-      </c>
-      <c r="AI24">
-        <v>1000</v>
-      </c>
-      <c r="AJ24">
-        <v>1000</v>
-      </c>
-      <c r="AK24">
-        <v>1000</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>1000</v>
-      </c>
-      <c r="AN24">
-        <v>1000</v>
-      </c>
-      <c r="AO24">
-        <v>1000</v>
-      </c>
-      <c r="AP24">
-        <v>1.28</v>
-      </c>
-      <c r="AQ24">
-        <v>1.28</v>
-      </c>
-      <c r="AR24">
-        <v>1.29</v>
-      </c>
-      <c r="AS24">
-        <v>1.29</v>
-      </c>
-      <c r="AT24">
-        <v>8</v>
-      </c>
-      <c r="AU24">
-        <v>1.12</v>
-      </c>
-      <c r="AV24">
-        <v>1.28</v>
-      </c>
-      <c r="AW24">
-        <v>1.29</v>
-      </c>
-      <c r="AX24">
-        <v>1.29</v>
-      </c>
-      <c r="AY24">
-        <v>1.28</v>
-      </c>
-      <c r="AZ24">
-        <v>1.28</v>
-      </c>
-      <c r="BA24">
-        <v>1.29</v>
-      </c>
-      <c r="BB24">
-        <v>1.29</v>
-      </c>
-      <c r="BC24">
-        <v>1.29</v>
-      </c>
-      <c r="BD24">
-        <v>1.29</v>
-      </c>
-      <c r="BE24">
-        <v>1.29</v>
-      </c>
-      <c r="BF24">
-        <v>1.29</v>
-      </c>
       <c r="BG24">
-        <v>1.29</v>
+        <v>95</v>
       </c>
       <c r="BH24">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="BI24">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BJ24">
+        <v>12</v>
+      </c>
+      <c r="BK24">
+        <v>7</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>15.5</v>
+      </c>
+      <c r="BN24">
+        <v>3.85</v>
+      </c>
+      <c r="BO24">
+        <v>3.1</v>
+      </c>
+      <c r="BP24">
+        <v>10</v>
+      </c>
+      <c r="BQ24">
+        <v>6.2</v>
+      </c>
+      <c r="BR24">
+        <v>29</v>
+      </c>
+      <c r="BS24">
+        <v>10.5</v>
+      </c>
+      <c r="BT24">
+        <v>11</v>
+      </c>
+      <c r="BU24">
+        <v>6.6</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
         <v>13.5</v>
       </c>
-      <c r="BK24">
-        <v>2.88</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>3.65</v>
-      </c>
-      <c r="BN24">
-        <v>5.9</v>
-      </c>
-      <c r="BO24">
-        <v>3.15</v>
-      </c>
-      <c r="BP24">
-        <v>16</v>
-      </c>
-      <c r="BQ24">
-        <v>2.98</v>
-      </c>
-      <c r="BR24">
-        <v>36</v>
-      </c>
-      <c r="BS24">
-        <v>3.3</v>
-      </c>
-      <c r="BT24">
-        <v>11.5</v>
-      </c>
-      <c r="BU24">
-        <v>2.78</v>
-      </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
-        <v>3.4</v>
-      </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="BZ24">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="CA24">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="CB24" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F25">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="G25">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>5.6</v>
+      </c>
+      <c r="J25">
+        <v>3.7</v>
+      </c>
+      <c r="K25">
         <v>4.1</v>
       </c>
-      <c r="I25">
-        <v>5.5</v>
-      </c>
-      <c r="J25">
-        <v>2.76</v>
-      </c>
-      <c r="K25">
-        <v>3.6</v>
-      </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="O25">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="P25">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="Q25">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="R25">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="S25">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="U25">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="V25">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W25">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="X25">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y25">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD25">
         <v>24</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF25">
+        <v>12.5</v>
+      </c>
+      <c r="AG25">
+        <v>12</v>
+      </c>
+      <c r="AH25">
+        <v>22</v>
+      </c>
+      <c r="AI25">
+        <v>80</v>
+      </c>
+      <c r="AJ25">
+        <v>22</v>
+      </c>
+      <c r="AK25">
+        <v>22</v>
+      </c>
+      <c r="AL25">
+        <v>40</v>
+      </c>
+      <c r="AM25">
+        <v>120</v>
+      </c>
+      <c r="AN25">
+        <v>13</v>
+      </c>
+      <c r="AO25">
+        <v>85</v>
+      </c>
+      <c r="AP25">
         <v>14</v>
       </c>
-      <c r="AG25">
+      <c r="AQ25">
+        <v>14</v>
+      </c>
+      <c r="AR25">
+        <v>5.4</v>
+      </c>
+      <c r="AS25">
+        <v>5.9</v>
+      </c>
+      <c r="AT25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU25">
+        <v>7.8</v>
+      </c>
+      <c r="AV25">
+        <v>14.5</v>
+      </c>
+      <c r="AW25">
+        <v>5.7</v>
+      </c>
+      <c r="AX25">
+        <v>9.6</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>4.8</v>
+      </c>
+      <c r="BA25">
+        <v>5.7</v>
+      </c>
+      <c r="BB25">
+        <v>16</v>
+      </c>
+      <c r="BC25">
+        <v>15</v>
+      </c>
+      <c r="BD25">
+        <v>5.3</v>
+      </c>
+      <c r="BE25">
+        <v>5.9</v>
+      </c>
+      <c r="BF25">
+        <v>9.6</v>
+      </c>
+      <c r="BG25">
+        <v>5.8</v>
+      </c>
+      <c r="BH25">
+        <v>3.65</v>
+      </c>
+      <c r="BI25">
+        <v>3.3</v>
+      </c>
+      <c r="BJ25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK25">
+        <v>6.4</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>14.5</v>
+      </c>
+      <c r="BN25">
+        <v>4.5</v>
+      </c>
+      <c r="BO25">
+        <v>4</v>
+      </c>
+      <c r="BP25">
+        <v>12</v>
+      </c>
+      <c r="BQ25">
+        <v>7.8</v>
+      </c>
+      <c r="BR25">
+        <v>36</v>
+      </c>
+      <c r="BS25">
+        <v>10</v>
+      </c>
+      <c r="BT25">
+        <v>8.4</v>
+      </c>
+      <c r="BU25">
+        <v>5.6</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>11.5</v>
+      </c>
+      <c r="BX25">
+        <v>65</v>
+      </c>
+      <c r="BY25">
+        <v>12</v>
+      </c>
+      <c r="BZ25">
+        <v>21</v>
+      </c>
+      <c r="CA25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>122</v>
+      </c>
+      <c r="E26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26">
+        <v>1.93</v>
+      </c>
+      <c r="G26">
+        <v>2.2</v>
+      </c>
+      <c r="H26">
+        <v>4.1</v>
+      </c>
+      <c r="I26">
+        <v>5.5</v>
+      </c>
+      <c r="J26">
+        <v>2.76</v>
+      </c>
+      <c r="K26">
+        <v>3.6</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>2.52</v>
+      </c>
+      <c r="O26">
+        <v>1.48</v>
+      </c>
+      <c r="P26">
+        <v>1.5</v>
+      </c>
+      <c r="Q26">
+        <v>2.52</v>
+      </c>
+      <c r="R26">
+        <v>1.17</v>
+      </c>
+      <c r="S26">
+        <v>2.52</v>
+      </c>
+      <c r="T26">
+        <v>1.11</v>
+      </c>
+      <c r="U26">
+        <v>1.69</v>
+      </c>
+      <c r="V26">
+        <v>1.24</v>
+      </c>
+      <c r="W26">
+        <v>1.83</v>
+      </c>
+      <c r="X26">
+        <v>10.5</v>
+      </c>
+      <c r="Y26">
+        <v>14.5</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>24</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>14</v>
+      </c>
+      <c r="AG26">
         <v>13.5</v>
       </c>
-      <c r="AH25">
+      <c r="AH26">
         <v>950</v>
       </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
         <v>1.41</v>
       </c>
-      <c r="AQ25">
+      <c r="AQ26">
         <v>1.46</v>
       </c>
-      <c r="AR25">
+      <c r="AR26">
         <v>1.63</v>
       </c>
-      <c r="AS25">
+      <c r="AS26">
         <v>1.63</v>
       </c>
-      <c r="AT25">
+      <c r="AT26">
         <v>1.62</v>
       </c>
-      <c r="AU25">
+      <c r="AU26">
         <v>1.62</v>
       </c>
-      <c r="AV25">
+      <c r="AV26">
         <v>1.52</v>
       </c>
-      <c r="AW25">
+      <c r="AW26">
         <v>1.63</v>
       </c>
-      <c r="AX25">
+      <c r="AX26">
         <v>1.46</v>
       </c>
-      <c r="AY25">
+      <c r="AY26">
         <v>1.45</v>
       </c>
-      <c r="AZ25">
+      <c r="AZ26">
         <v>1.54</v>
       </c>
-      <c r="BA25">
+      <c r="BA26">
         <v>1.63</v>
       </c>
-      <c r="BB25">
+      <c r="BB26">
         <v>1.63</v>
       </c>
-      <c r="BC25">
+      <c r="BC26">
         <v>1.63</v>
       </c>
-      <c r="BD25">
+      <c r="BD26">
         <v>1.63</v>
       </c>
-      <c r="BE25">
+      <c r="BE26">
         <v>1.63</v>
       </c>
-      <c r="BF25">
+      <c r="BF26">
         <v>1.63</v>
       </c>
-      <c r="BG25">
+      <c r="BG26">
         <v>1.63</v>
       </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
         <v>1.04</v>
       </c>
-      <c r="BJ25">
-        <v>1000</v>
-      </c>
-      <c r="BK25">
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
         <v>1.04</v>
       </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
         <v>1.04</v>
       </c>
-      <c r="BN25">
-        <v>1000</v>
-      </c>
-      <c r="BO25">
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
         <v>1.04</v>
       </c>
-      <c r="BP25">
-        <v>1000</v>
-      </c>
-      <c r="BQ25">
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
         <v>1.04</v>
       </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
         <v>1.04</v>
       </c>
-      <c r="BT25">
-        <v>1000</v>
-      </c>
-      <c r="BU25">
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
         <v>1.04</v>
       </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
         <v>1.04</v>
       </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
         <v>1.04</v>
       </c>
-      <c r="BZ25">
-        <v>1000</v>
-      </c>
-      <c r="CA25">
+      <c r="BZ26">
+        <v>1000</v>
+      </c>
+      <c r="CA26">
         <v>1.04</v>
       </c>
-      <c r="CB25" t="s">
-        <v>144</v>
+      <c r="CB26" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 02:10:19</t>
+    <t>2026-07-22 04:17:51</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1057,7 @@
         <v>5.2</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H2">
         <v>1.82</v>
@@ -1069,7 +1069,7 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.54</v>
@@ -1105,10 +1105,10 @@
         <v>2.1</v>
       </c>
       <c r="W2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y2">
         <v>6.6</v>
@@ -1132,10 +1132,10 @@
         <v>26</v>
       </c>
       <c r="AF2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AG2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH2">
         <v>27</v>
@@ -1159,7 +1159,7 @@
         <v>200</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2">
         <v>8.199999999999999</v>
@@ -1192,25 +1192,25 @@
         <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA2">
         <v>8.6</v>
       </c>
       <c r="BB2">
+        <v>9.4</v>
+      </c>
+      <c r="BC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE2">
         <v>9.6</v>
       </c>
-      <c r="BC2">
+      <c r="BF2">
         <v>9.4</v>
-      </c>
-      <c r="BD2">
-        <v>9.4</v>
-      </c>
-      <c r="BE2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF2">
-        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>15</v>
@@ -1296,10 +1296,10 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3">
         <v>3.8</v>
@@ -1314,31 +1314,31 @@
         <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.06</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U3">
         <v>2.38</v>
@@ -1347,7 +1347,7 @@
         <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
         <v>17.5</v>
@@ -1368,7 +1368,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
         <v>42</v>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>46</v>
@@ -1395,19 +1395,19 @@
         <v>32</v>
       </c>
       <c r="AM3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>12</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR3">
         <v>25</v>
@@ -1416,10 +1416,10 @@
         <v>55</v>
       </c>
       <c r="AT3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV3">
         <v>14</v>
@@ -1437,7 +1437,7 @@
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB3">
         <v>21</v>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BI3">
         <v>3.2</v>
@@ -1473,7 +1473,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1482,22 +1482,22 @@
         <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR3">
         <v>25</v>
       </c>
       <c r="BS3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
         <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
         <v>28</v>
@@ -1509,10 +1509,10 @@
         <v>36</v>
       </c>
       <c r="BY3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="CA3">
         <v>7.8</v>
@@ -1538,22 +1538,22 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
         <v>4.2</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J4">
         <v>3.4</v>
       </c>
       <c r="K4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L4">
         <v>1.51</v>
@@ -1583,37 +1583,37 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V4">
         <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y4">
         <v>13</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4">
         <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
@@ -1625,7 +1625,7 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
         <v>26</v>
@@ -1643,31 +1643,31 @@
         <v>22</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AS4">
         <v>36</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
@@ -1676,19 +1676,19 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB4">
         <v>23</v>
       </c>
       <c r="BC4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE4">
         <v>44</v>
@@ -1709,13 +1709,13 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1727,7 +1727,7 @@
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>36</v>
@@ -1751,10 +1751,10 @@
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="CA4">
         <v>12.5</v>
@@ -1786,7 +1786,7 @@
         <v>2.38</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I5">
         <v>3.6</v>
@@ -1795,7 +1795,7 @@
         <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1807,13 +1807,13 @@
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
         <v>1.31</v>
@@ -1822,13 +1822,13 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
         <v>1.72</v>
@@ -1846,7 +1846,7 @@
         <v>65</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1858,7 +1858,7 @@
         <v>48</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1900,7 +1900,7 @@
         <v>55</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
         <v>7</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="AW5">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AX5">
         <v>13</v>
@@ -2022,7 +2022,7 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="G6">
         <v>8.800000000000001</v>
@@ -2031,13 +2031,13 @@
         <v>1.49</v>
       </c>
       <c r="I6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="J6">
         <v>4.5</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
         <v>1.39</v>
@@ -2052,64 +2052,64 @@
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA6">
         <v>13</v>
       </c>
       <c r="AB6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
       </c>
       <c r="AD6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AE6">
         <v>16</v>
       </c>
       <c r="AF6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ6">
         <v>330</v>
@@ -2121,7 +2121,7 @@
         <v>130</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN6">
         <v>190</v>
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
         <v>7.8</v>
@@ -2145,7 +2145,7 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
@@ -2160,25 +2160,25 @@
         <v>27</v>
       </c>
       <c r="AZ6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BD6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BE6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BF6">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
@@ -2294,7 +2294,7 @@
         <v>1.36</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2306,7 +2306,7 @@
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U7">
         <v>1.94</v>
@@ -2321,10 +2321,10 @@
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA7">
         <v>120</v>
@@ -2336,7 +2336,7 @@
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE7">
         <v>70</v>
@@ -2357,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2369,7 +2369,7 @@
         <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2396,7 +2396,7 @@
         <v>55</v>
       </c>
       <c r="AX7">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2411,7 +2411,7 @@
         <v>19</v>
       </c>
       <c r="BC7">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD7">
         <v>34</v>
@@ -2423,25 +2423,25 @@
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="BH7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
@@ -2453,28 +2453,28 @@
         <v>14</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS7">
         <v>7.8</v>
       </c>
       <c r="BT7">
+        <v>8.6</v>
+      </c>
+      <c r="BU7">
+        <v>6.2</v>
+      </c>
+      <c r="BV7">
+        <v>46</v>
+      </c>
+      <c r="BW7">
         <v>8.4</v>
       </c>
-      <c r="BU7">
-        <v>6</v>
-      </c>
-      <c r="BV7">
-        <v>44</v>
-      </c>
-      <c r="BW7">
-        <v>8.6</v>
-      </c>
       <c r="BX7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY7">
         <v>8.800000000000001</v>
@@ -2483,7 +2483,7 @@
         <v>27</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>148</v>
@@ -2506,16 +2506,16 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2527,13 +2527,13 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
         <v>2.6</v>
@@ -2548,13 +2548,13 @@
         <v>2.46</v>
       </c>
       <c r="T8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U8">
         <v>2.68</v>
       </c>
       <c r="V8">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W8">
         <v>1.37</v>
@@ -2572,7 +2572,7 @@
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
@@ -2587,10 +2587,10 @@
         <v>30</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
         <v>26</v>
@@ -2614,7 +2614,7 @@
         <v>9.6</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2638,7 +2638,7 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY8">
         <v>14.5</v>
@@ -2656,7 +2656,7 @@
         <v>32</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE8">
         <v>48</v>
@@ -2748,10 +2748,10 @@
         <v>130</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2775,10 +2775,10 @@
         <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
         <v>1.84</v>
@@ -2799,10 +2799,10 @@
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y9">
         <v>19</v>
@@ -2811,7 +2811,7 @@
         <v>40</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB9">
         <v>9.800000000000001</v>
@@ -2823,7 +2823,7 @@
         <v>20</v>
       </c>
       <c r="AE9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF9">
         <v>11.5</v>
@@ -2856,16 +2856,16 @@
         <v>65</v>
       </c>
       <c r="AP9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
         <v>16</v>
       </c>
       <c r="AR9">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT9">
         <v>8.800000000000001</v>
@@ -2898,10 +2898,10 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
@@ -2990,22 +2990,22 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
         <v>7.2</v>
       </c>
       <c r="J10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3014,34 +3014,34 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3050,13 +3050,13 @@
         <v>29</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
         <v>11</v>
@@ -3071,16 +3071,16 @@
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
         <v>15</v>
@@ -3092,10 +3092,10 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO10">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP10">
         <v>20</v>
@@ -3140,34 +3140,34 @@
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE10">
         <v>36</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BH10">
         <v>4.3</v>
       </c>
       <c r="BI10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
@@ -3179,37 +3179,37 @@
         <v>9.6</v>
       </c>
       <c r="BQ10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT10">
         <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV10">
         <v>55</v>
       </c>
       <c r="BW10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3241,7 +3241,7 @@
         <v>7.2</v>
       </c>
       <c r="I11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>4.9</v>
@@ -3262,7 +3262,7 @@
         <v>1.19</v>
       </c>
       <c r="P11">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
         <v>1.58</v>
@@ -3271,16 +3271,16 @@
         <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
         <v>2.96</v>
@@ -3400,7 +3400,7 @@
         <v>3.6</v>
       </c>
       <c r="BJ11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
         <v>5.6</v>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3421,37 +3421,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT11">
         <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11">
         <v>12.5</v>
       </c>
       <c r="CA11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,19 +3474,19 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
         <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3522,13 +3522,13 @@
         <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y12">
         <v>28</v>
@@ -3537,10 +3537,10 @@
         <v>38</v>
       </c>
       <c r="AA12">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC12">
         <v>11</v>
@@ -3549,16 +3549,16 @@
         <v>16</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>20</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AI12">
         <v>34</v>
@@ -3573,7 +3573,7 @@
         <v>24</v>
       </c>
       <c r="AM12">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AN12">
         <v>7.8</v>
@@ -3582,13 +3582,13 @@
         <v>18.5</v>
       </c>
       <c r="AP12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ12">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AR12">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS12">
         <v>30</v>
@@ -3603,10 +3603,10 @@
         <v>14</v>
       </c>
       <c r="AW12">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AX12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3618,13 +3618,13 @@
         <v>20</v>
       </c>
       <c r="BB12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC12">
         <v>16</v>
       </c>
       <c r="BD12">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BE12">
         <v>24</v>
@@ -3639,7 +3639,7 @@
         <v>5.4</v>
       </c>
       <c r="BI12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
@@ -3728,7 +3728,7 @@
         <v>2.26</v>
       </c>
       <c r="J13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
         <v>3.9</v>
@@ -3749,7 +3749,7 @@
         <v>2.34</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R13">
         <v>1.52</v>
@@ -3761,10 +3761,10 @@
         <v>1.61</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
         <v>1.4</v>
@@ -3785,7 +3785,7 @@
         <v>17</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13">
         <v>11.5</v>
@@ -3797,7 +3797,7 @@
         <v>26</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH13">
         <v>15.5</v>
@@ -3824,7 +3824,7 @@
         <v>13</v>
       </c>
       <c r="AP13">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
@@ -3881,19 +3881,19 @@
         <v>4.1</v>
       </c>
       <c r="BI13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ13">
         <v>8.800000000000001</v>
       </c>
       <c r="BK13">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN13">
         <v>6.8</v>
@@ -3905,13 +3905,13 @@
         <v>24</v>
       </c>
       <c r="BQ13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT13">
         <v>5.4</v>
@@ -3920,22 +3920,22 @@
         <v>4.1</v>
       </c>
       <c r="BV13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX13">
         <v>24</v>
       </c>
       <c r="BY13">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="CA13">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3964,7 +3964,7 @@
         <v>2.12</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I14">
         <v>3.7</v>
@@ -3973,7 +3973,7 @@
         <v>3.95</v>
       </c>
       <c r="K14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>1.3</v>
@@ -3985,7 +3985,7 @@
         <v>5.7</v>
       </c>
       <c r="O14">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P14">
         <v>2.56</v>
@@ -3997,13 +3997,13 @@
         <v>1.62</v>
       </c>
       <c r="S14">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T14">
         <v>1.57</v>
       </c>
       <c r="U14">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
         <v>1.37</v>
@@ -4015,7 +4015,7 @@
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z14">
         <v>30</v>
@@ -4027,7 +4027,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD14">
         <v>15.5</v>
@@ -4051,7 +4051,7 @@
         <v>26</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4087,7 +4087,7 @@
         <v>14</v>
       </c>
       <c r="AW14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX14">
         <v>14</v>
@@ -4099,7 +4099,7 @@
         <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB14">
         <v>23</v>
@@ -4206,7 +4206,7 @@
         <v>2.44</v>
       </c>
       <c r="H15">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
         <v>2.96</v>
@@ -4236,7 +4236,7 @@
         <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S15">
         <v>2.3</v>
@@ -4245,7 +4245,7 @@
         <v>1.49</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="V15">
         <v>1.51</v>
@@ -4254,7 +4254,7 @@
         <v>1.69</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y15">
         <v>20</v>
@@ -4275,52 +4275,52 @@
         <v>13.5</v>
       </c>
       <c r="AE15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF15">
         <v>21</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15">
         <v>14.5</v>
       </c>
       <c r="AI15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ15">
         <v>36</v>
       </c>
       <c r="AK15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="AN15">
         <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AQ15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT15">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU15">
         <v>9.199999999999999</v>
@@ -4329,31 +4329,31 @@
         <v>12</v>
       </c>
       <c r="AW15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BE15">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BF15">
         <v>10</v>
@@ -4365,7 +4365,7 @@
         <v>4.8</v>
       </c>
       <c r="BI15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BJ15">
         <v>8.6</v>
@@ -4442,19 +4442,19 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H16">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5.3</v>
@@ -4469,7 +4469,7 @@
         <v>8.6</v>
       </c>
       <c r="O16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P16">
         <v>3.55</v>
@@ -4484,22 +4484,22 @@
         <v>1.93</v>
       </c>
       <c r="T16">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
         <v>1.21</v>
       </c>
       <c r="W16">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="X16">
         <v>44</v>
       </c>
       <c r="Y16">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z16">
         <v>60</v>
@@ -4511,7 +4511,7 @@
         <v>18</v>
       </c>
       <c r="AC16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD16">
         <v>23</v>
@@ -4532,7 +4532,7 @@
         <v>110</v>
       </c>
       <c r="AJ16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK16">
         <v>14.5</v>
@@ -4592,7 +4592,7 @@
         <v>12.5</v>
       </c>
       <c r="BD16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE16">
         <v>42</v>
@@ -4601,67 +4601,67 @@
         <v>4.4</v>
       </c>
       <c r="BG16">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BH16">
         <v>5.8</v>
       </c>
       <c r="BI16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ16">
         <v>9.199999999999999</v>
       </c>
       <c r="BK16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16">
         <v>5.3</v>
       </c>
       <c r="BO16">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP16">
         <v>10</v>
       </c>
       <c r="BQ16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
         <v>10</v>
       </c>
       <c r="BU16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX16">
+        <v>32</v>
+      </c>
+      <c r="BY16">
         <v>8</v>
-      </c>
-      <c r="BX16">
-        <v>34</v>
-      </c>
-      <c r="BY16">
-        <v>7.8</v>
       </c>
       <c r="BZ16">
         <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,7 +4684,7 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G17">
         <v>1.79</v>
@@ -4702,34 +4702,34 @@
         <v>4.5</v>
       </c>
       <c r="L17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M17">
         <v>1.04</v>
       </c>
       <c r="N17">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="Q17">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S17">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U17">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
         <v>1.25</v>
@@ -4738,10 +4738,10 @@
         <v>2.26</v>
       </c>
       <c r="X17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z17">
         <v>44</v>
@@ -4750,7 +4750,7 @@
         <v>110</v>
       </c>
       <c r="AB17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
@@ -4762,7 +4762,7 @@
         <v>160</v>
       </c>
       <c r="AF17">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG17">
         <v>10.5</v>
@@ -4789,10 +4789,10 @@
         <v>7.2</v>
       </c>
       <c r="AO17">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AP17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ17">
         <v>22</v>
@@ -4804,7 +4804,7 @@
         <v>38</v>
       </c>
       <c r="AT17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU17">
         <v>9.199999999999999</v>
@@ -4843,10 +4843,10 @@
         <v>6.6</v>
       </c>
       <c r="BG17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BH17">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BI17">
         <v>3.75</v>
@@ -4855,16 +4855,16 @@
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO17">
         <v>4.3</v>
@@ -4873,37 +4873,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR17">
         <v>21</v>
       </c>
       <c r="BS17">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT17">
         <v>8.800000000000001</v>
       </c>
       <c r="BU17">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BV17">
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX17">
         <v>36</v>
       </c>
       <c r="BY17">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ17">
         <v>13.5</v>
       </c>
       <c r="CA17">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,112 +4926,112 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="J18">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.25</v>
+        <v>3.45</v>
       </c>
       <c r="O18">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q18">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="S18">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AP18">
         <v>1.01</v>
@@ -5070,7 +5070,7 @@
         <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC18">
         <v>1.01</v>
@@ -5079,7 +5079,7 @@
         <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5088,13 +5088,13 @@
         <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI18">
         <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5106,7 +5106,7 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
@@ -5124,25 +5124,25 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU18">
         <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5168,10 +5168,10 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G19">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H19">
         <v>2.88</v>
@@ -5186,22 +5186,22 @@
         <v>3.3</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
         <v>3</v>
       </c>
       <c r="O19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P19">
         <v>1.68</v>
       </c>
       <c r="Q19">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
         <v>1.25</v>
@@ -5222,7 +5222,7 @@
         <v>1.52</v>
       </c>
       <c r="X19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y19">
         <v>10.5</v>
@@ -5285,7 +5285,7 @@
         <v>7</v>
       </c>
       <c r="AS19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19">
         <v>8.4</v>
@@ -5309,85 +5309,85 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB19">
         <v>8</v>
       </c>
-      <c r="BB19">
+      <c r="BC19">
+        <v>7.6</v>
+      </c>
+      <c r="BD19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE19">
+        <v>9</v>
+      </c>
+      <c r="BF19">
+        <v>7.6</v>
+      </c>
+      <c r="BG19">
         <v>7.8</v>
       </c>
-      <c r="BC19">
-        <v>7.4</v>
-      </c>
-      <c r="BD19">
-        <v>8</v>
-      </c>
-      <c r="BE19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF19">
-        <v>7.4</v>
-      </c>
-      <c r="BG19">
-        <v>7.6</v>
-      </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI19">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>1.56</v>
+        <v>6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.74</v>
+        <v>12.5</v>
       </c>
       <c r="BN19">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO19">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="BP19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.66</v>
+        <v>8.6</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.69</v>
+        <v>10</v>
       </c>
       <c r="BT19">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BU19">
-        <v>1.44</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.67</v>
+        <v>9</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.69</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.69</v>
+        <v>10</v>
       </c>
       <c r="CB19" t="s">
         <v>148</v>
@@ -5416,7 +5416,7 @@
         <v>1.94</v>
       </c>
       <c r="H20">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I20">
         <v>6.2</v>
@@ -5428,10 +5428,10 @@
         <v>3.75</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
         <v>2.62</v>
@@ -5440,7 +5440,7 @@
         <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q20">
         <v>2.42</v>
@@ -5449,7 +5449,7 @@
         <v>1.2</v>
       </c>
       <c r="S20">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T20">
         <v>2.18</v>
@@ -5461,7 +5461,7 @@
         <v>1.2</v>
       </c>
       <c r="W20">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X20">
         <v>10.5</v>
@@ -5572,64 +5572,64 @@
         <v>8.4</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI20">
-        <v>1.04</v>
+        <v>2.36</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK20">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO20">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ20">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS20">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU20">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA20">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB20" t="s">
         <v>148</v>
@@ -5655,10 +5655,10 @@
         <v>2.06</v>
       </c>
       <c r="G21">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I21">
         <v>4.8</v>
@@ -5670,7 +5670,7 @@
         <v>3.6</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M21">
         <v>1.1</v>
@@ -5679,7 +5679,7 @@
         <v>2.86</v>
       </c>
       <c r="O21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P21">
         <v>1.6</v>
@@ -5691,19 +5691,19 @@
         <v>1.22</v>
       </c>
       <c r="S21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U21">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X21">
         <v>10.5</v>
@@ -5778,7 +5778,7 @@
         <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW21">
         <v>7.8</v>
@@ -5796,10 +5796,10 @@
         <v>8</v>
       </c>
       <c r="BB21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD21">
         <v>40</v>
@@ -5814,64 +5814,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="s">
         <v>148</v>
@@ -5894,25 +5894,25 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G22">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I22">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="M22">
         <v>1.16</v>
@@ -5936,13 +5936,13 @@
         <v>6.8</v>
       </c>
       <c r="T22">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U22">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V22">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="W22">
         <v>1.23</v>
@@ -5954,13 +5954,13 @@
         <v>6</v>
       </c>
       <c r="Z22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC22">
         <v>7.6</v>
@@ -5978,10 +5978,10 @@
         <v>23</v>
       </c>
       <c r="AH22">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AI22">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ22">
         <v>190</v>
@@ -5999,7 +5999,7 @@
         <v>260</v>
       </c>
       <c r="AO22">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP22">
         <v>6.4</v>
@@ -6014,7 +6014,7 @@
         <v>19.5</v>
       </c>
       <c r="AT22">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU22">
         <v>6.6</v>
@@ -6032,88 +6032,88 @@
         <v>19</v>
       </c>
       <c r="AZ22">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BA22">
+        <v>11</v>
+      </c>
+      <c r="BB22">
         <v>12</v>
       </c>
-      <c r="BB22">
-        <v>13</v>
-      </c>
       <c r="BC22">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD22">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE22">
+        <v>12</v>
+      </c>
+      <c r="BF22">
+        <v>12</v>
+      </c>
+      <c r="BG22">
+        <v>9.4</v>
+      </c>
+      <c r="BH22">
+        <v>2.46</v>
+      </c>
+      <c r="BI22">
+        <v>2.26</v>
+      </c>
+      <c r="BJ22">
         <v>13.5</v>
       </c>
-      <c r="BF22">
-        <v>13</v>
-      </c>
-      <c r="BG22">
-        <v>22</v>
-      </c>
-      <c r="BH22">
-        <v>1000</v>
-      </c>
-      <c r="BI22">
-        <v>1.42</v>
-      </c>
-      <c r="BJ22">
-        <v>18</v>
-      </c>
       <c r="BK22">
-        <v>1.32</v>
+        <v>8.4</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.42</v>
+        <v>16</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO22">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ22">
-        <v>1.42</v>
+        <v>13.5</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.42</v>
+        <v>14.5</v>
       </c>
       <c r="BT22">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BU22">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="BV22">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BW22">
-        <v>1.35</v>
+        <v>8.6</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY22">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA22">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="CB22" t="s">
         <v>148</v>
@@ -6136,19 +6136,19 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G23">
         <v>2.9</v>
       </c>
       <c r="H23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I23">
         <v>3.2</v>
       </c>
       <c r="J23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -6166,19 +6166,19 @@
         <v>1.69</v>
       </c>
       <c r="P23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q23">
         <v>3.05</v>
       </c>
       <c r="R23">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S23">
         <v>7</v>
       </c>
       <c r="T23">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U23">
         <v>1.64</v>
@@ -6205,7 +6205,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD23">
         <v>15.5</v>
@@ -6253,7 +6253,7 @@
         <v>15.5</v>
       </c>
       <c r="AS23">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT23">
         <v>6.6</v>
@@ -6274,10 +6274,10 @@
         <v>13</v>
       </c>
       <c r="AZ23">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB23">
         <v>6.4</v>
@@ -6286,7 +6286,7 @@
         <v>6.4</v>
       </c>
       <c r="BD23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE23">
         <v>7</v>
@@ -6301,10 +6301,10 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BJ23">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BK23">
         <v>1.49</v>
@@ -6313,7 +6313,7 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BN23">
         <v>7.6</v>
@@ -6322,10 +6322,10 @@
         <v>3.7</v>
       </c>
       <c r="BP23">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BQ23">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BR23">
         <v>1000</v>
@@ -6343,19 +6343,19 @@
         <v>46</v>
       </c>
       <c r="BW23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6378,10 +6378,10 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G24">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H24">
         <v>8</v>
@@ -6402,7 +6402,7 @@
         <v>1.08</v>
       </c>
       <c r="N24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O24">
         <v>1.35</v>
@@ -6417,22 +6417,22 @@
         <v>1.33</v>
       </c>
       <c r="S24">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T24">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V24">
         <v>1.13</v>
       </c>
       <c r="W24">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y24">
         <v>22</v>
@@ -6450,7 +6450,7 @@
         <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AE24">
         <v>1000</v>
@@ -6462,7 +6462,7 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AI24">
         <v>1000</v>
@@ -6480,7 +6480,7 @@
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24">
         <v>1000</v>
@@ -6495,28 +6495,28 @@
         <v>30</v>
       </c>
       <c r="AS24">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AT24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU24">
         <v>8.4</v>
       </c>
       <c r="AV24">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AW24">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="AX24">
         <v>7.6</v>
       </c>
       <c r="AY24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA24">
         <v>42</v>
@@ -6531,7 +6531,7 @@
         <v>26</v>
       </c>
       <c r="BE24">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="BF24">
         <v>8.6</v>
@@ -6623,10 +6623,10 @@
         <v>1.75</v>
       </c>
       <c r="G25">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H25">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I25">
         <v>5.6</v>
@@ -6671,7 +6671,7 @@
         <v>1.21</v>
       </c>
       <c r="W25">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X25">
         <v>18.5</v>
@@ -6833,7 +6833,7 @@
         <v>65</v>
       </c>
       <c r="BY25">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25">
         <v>21</v>
@@ -6862,226 +6862,226 @@
         <v>147</v>
       </c>
       <c r="F26">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="G26">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H26">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I26">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J26">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N26">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P26">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q26">
         <v>2.52</v>
       </c>
       <c r="R26">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S26">
-        <v>2.52</v>
+        <v>5.1</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U26">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V26">
         <v>1.24</v>
       </c>
       <c r="W26">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X26">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y26">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD26">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF26">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH26">
         <v>950</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP26">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="AQ26">
-        <v>1.46</v>
+        <v>10</v>
       </c>
       <c r="AR26">
-        <v>1.63</v>
+        <v>5.6</v>
       </c>
       <c r="AS26">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="AT26">
-        <v>1.62</v>
+        <v>5.9</v>
       </c>
       <c r="AU26">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>1.52</v>
+        <v>16.5</v>
       </c>
       <c r="AW26">
-        <v>1.63</v>
+        <v>6</v>
       </c>
       <c r="AX26">
-        <v>1.46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY26">
-        <v>1.45</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>1.54</v>
+        <v>20</v>
       </c>
       <c r="BA26">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="BB26">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="BC26">
-        <v>1.63</v>
+        <v>5.5</v>
       </c>
       <c r="BD26">
-        <v>1.63</v>
+        <v>6</v>
       </c>
       <c r="BE26">
-        <v>1.63</v>
+        <v>6.4</v>
       </c>
       <c r="BF26">
-        <v>1.63</v>
+        <v>20</v>
       </c>
       <c r="BG26">
-        <v>1.63</v>
+        <v>6.2</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 04:17:51</t>
+    <t>2026-07-22 06:25:20</t>
   </si>
 </sst>
 </file>
@@ -1054,22 +1054,22 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G2">
         <v>6.2</v>
       </c>
       <c r="H2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L2">
         <v>1.54</v>
@@ -1081,10 +1081,10 @@
         <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
         <v>2.56</v>
@@ -1096,184 +1096,184 @@
         <v>5</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W2">
         <v>1.2</v>
       </c>
       <c r="X2">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.9</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,10 +1296,10 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
         <v>3.8</v>
@@ -1314,7 +1314,7 @@
         <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
         <v>1.06</v>
@@ -1323,34 +1323,34 @@
         <v>4.6</v>
       </c>
       <c r="O3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S3">
         <v>3</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V3">
         <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3">
         <v>17</v>
@@ -1362,16 +1362,16 @@
         <v>75</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1380,16 +1380,16 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI3">
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL3">
         <v>32</v>
@@ -1398,7 +1398,7 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
         <v>36</v>
@@ -1407,43 +1407,43 @@
         <v>16</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
         <v>14</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="BB3">
         <v>21</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD3">
         <v>27</v>
@@ -1455,67 +1455,67 @@
         <v>11</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BH3">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,16 +1538,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
         <v>3.4</v>
@@ -1556,7 +1556,7 @@
         <v>3.45</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1565,13 +1565,13 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1583,67 +1583,67 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X4">
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z4">
         <v>30</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>85</v>
       </c>
       <c r="AJ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
@@ -1664,13 +1664,13 @@
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1679,85 +1679,85 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC4">
         <v>23</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE4">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BH4">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1780,25 +1780,25 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G5">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
         <v>3.45</v>
       </c>
       <c r="I5">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
         <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1807,7 +1807,7 @@
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P5">
         <v>1.84</v>
@@ -1822,82 +1822,82 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="U5">
         <v>2.06</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X5">
         <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z5">
         <v>23</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>520</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
         <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>27</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
         <v>11</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -1906,25 +1906,25 @@
         <v>7</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW5">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX5">
         <v>13</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB5">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BC5">
         <v>23</v>
@@ -1939,67 +1939,67 @@
         <v>20</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,19 +2022,19 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="G6">
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K6">
         <v>4.7</v>
@@ -2049,46 +2049,46 @@
         <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
         <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
         <v>3.35</v>
       </c>
       <c r="T6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="W6">
         <v>1.13</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AA6">
         <v>13</v>
       </c>
       <c r="AB6">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AC6">
         <v>10.5</v>
@@ -2097,22 +2097,22 @@
         <v>10</v>
       </c>
       <c r="AE6">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AF6">
         <v>70</v>
       </c>
       <c r="AG6">
+        <v>32</v>
+      </c>
+      <c r="AH6">
         <v>30</v>
       </c>
-      <c r="AH6">
-        <v>34</v>
-      </c>
       <c r="AI6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AJ6">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AK6">
         <v>140</v>
@@ -2130,13 +2130,13 @@
         <v>7.8</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6">
         <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS6">
         <v>11.5</v>
@@ -2145,103 +2145,103 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AW6">
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>60</v>
+        <v>14.5</v>
       </c>
       <c r="AY6">
         <v>27</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>14.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC6">
-        <v>15</v>
+        <v>5.3</v>
       </c>
       <c r="BD6">
-        <v>16</v>
+        <v>5.3</v>
       </c>
       <c r="BE6">
-        <v>14</v>
+        <v>5.3</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2264,16 +2264,16 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2291,64 +2291,64 @@
         <v>3.55</v>
       </c>
       <c r="O7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T7">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB7">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC7">
         <v>8.4</v>
       </c>
       <c r="AD7">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE7">
         <v>70</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI7">
         <v>80</v>
@@ -2366,13 +2366,13 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP7">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ7">
         <v>13.5</v>
@@ -2381,7 +2381,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>4.9</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2393,10 +2393,10 @@
         <v>16.5</v>
       </c>
       <c r="AW7">
-        <v>55</v>
+        <v>4.7</v>
       </c>
       <c r="AX7">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2405,85 +2405,85 @@
         <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>4.8</v>
       </c>
       <c r="BB7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BC7">
-        <v>17.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>148</v>
@@ -2506,16 +2506,16 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2536,7 +2536,7 @@
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q8">
         <v>1.6</v>
@@ -2548,13 +2548,13 @@
         <v>2.46</v>
       </c>
       <c r="T8">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W8">
         <v>1.37</v>
@@ -2563,37 +2563,37 @@
         <v>24</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA8">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC8">
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG8">
         <v>15.5</v>
       </c>
       <c r="AH8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2608,13 +2608,13 @@
         <v>60</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AO8">
         <v>9.6</v>
       </c>
       <c r="AP8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2629,10 +2629,10 @@
         <v>19</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW8">
         <v>17</v>
@@ -2641,7 +2641,7 @@
         <v>27</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2653,79 +2653,79 @@
         <v>32</v>
       </c>
       <c r="BC8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BF8">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="BG8">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2751,7 +2751,7 @@
         <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2772,202 +2772,202 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
         <v>1.84</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>950</v>
+      </c>
+      <c r="AC9">
+        <v>950</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>24</v>
+      </c>
+      <c r="AG9">
+        <v>950</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
         <v>18.5</v>
       </c>
-      <c r="Y9">
-        <v>19</v>
-      </c>
-      <c r="Z9">
-        <v>40</v>
-      </c>
-      <c r="AA9">
-        <v>120</v>
-      </c>
-      <c r="AB9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC9">
-        <v>9</v>
-      </c>
-      <c r="AD9">
-        <v>20</v>
-      </c>
-      <c r="AE9">
-        <v>60</v>
-      </c>
-      <c r="AF9">
-        <v>11.5</v>
-      </c>
-      <c r="AG9">
-        <v>10.5</v>
-      </c>
-      <c r="AH9">
-        <v>19</v>
-      </c>
-      <c r="AI9">
-        <v>65</v>
-      </c>
-      <c r="AJ9">
-        <v>21</v>
-      </c>
-      <c r="AK9">
-        <v>19</v>
-      </c>
-      <c r="AL9">
-        <v>34</v>
-      </c>
-      <c r="AM9">
-        <v>110</v>
-      </c>
-      <c r="AN9">
-        <v>10.5</v>
-      </c>
       <c r="AO9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>1.39</v>
       </c>
       <c r="AQ9">
-        <v>16</v>
+        <v>1.39</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>1.4</v>
       </c>
       <c r="AS9">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="AT9">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AU9">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AV9">
-        <v>16</v>
+        <v>1.39</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="AX9">
-        <v>10</v>
+        <v>1.32</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>1.39</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="BB9">
-        <v>17</v>
+        <v>1.4</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>1.4</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>1.4</v>
       </c>
       <c r="BF9">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>1.4</v>
       </c>
       <c r="BH9">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2990,13 +2990,13 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G10">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I10">
         <v>7.2</v>
@@ -3008,7 +3008,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M10">
         <v>1.04</v>
@@ -3023,34 +3023,34 @@
         <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R10">
         <v>1.59</v>
       </c>
       <c r="S10">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V10">
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -3071,13 +3071,13 @@
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
         <v>14.5</v>
@@ -3086,25 +3086,25 @@
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
         <v>80</v>
       </c>
       <c r="AP10">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AQ10">
         <v>26</v>
       </c>
       <c r="AR10">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AS10">
         <v>46</v>
@@ -3116,10 +3116,10 @@
         <v>10</v>
       </c>
       <c r="AV10">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AW10">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3137,7 +3137,7 @@
         <v>13</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD10">
         <v>25</v>
@@ -3149,67 +3149,67 @@
         <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH10">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3232,25 +3232,25 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3268,190 +3268,190 @@
         <v>1.58</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S11">
         <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,16 +3474,16 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12">
         <v>4.2</v>
@@ -3522,22 +3522,22 @@
         <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y12">
         <v>28</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB12">
         <v>19.5</v>
@@ -3546,13 +3546,13 @@
         <v>11</v>
       </c>
       <c r="AD12">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
         <v>34</v>
       </c>
       <c r="AF12">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG12">
         <v>11.5</v>
@@ -3561,52 +3561,52 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AJ12">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AK12">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO12">
         <v>18.5</v>
       </c>
       <c r="AP12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AQ12">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR12">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS12">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AT12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AU12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV12">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3615,85 +3615,85 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BB12">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BE12">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BF12">
         <v>7.2</v>
       </c>
       <c r="BG12">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH12">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3716,58 +3716,58 @@
         <v>134</v>
       </c>
       <c r="F13">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G13">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="I13">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O13">
         <v>1.24</v>
       </c>
       <c r="P13">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S13">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T13">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X13">
         <v>20</v>
@@ -3776,16 +3776,16 @@
         <v>13</v>
       </c>
       <c r="Z13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA13">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AB13">
         <v>17</v>
       </c>
       <c r="AC13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD13">
         <v>11.5</v>
@@ -3794,22 +3794,22 @@
         <v>22</v>
       </c>
       <c r="AF13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG13">
         <v>14</v>
       </c>
       <c r="AH13">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI13">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AJ13">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL13">
         <v>40</v>
@@ -3818,13 +3818,13 @@
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
@@ -3839,7 +3839,7 @@
         <v>15</v>
       </c>
       <c r="AU13">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV13">
         <v>10</v>
@@ -3851,7 +3851,7 @@
         <v>23</v>
       </c>
       <c r="AY13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13">
         <v>14</v>
@@ -3860,7 +3860,7 @@
         <v>27</v>
       </c>
       <c r="BB13">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="BC13">
         <v>30</v>
@@ -3869,73 +3869,73 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF13">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BG13">
         <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3982,28 +3982,28 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O14">
         <v>1.2</v>
       </c>
       <c r="P14">
+        <v>2.54</v>
+      </c>
+      <c r="Q14">
+        <v>1.62</v>
+      </c>
+      <c r="R14">
+        <v>1.61</v>
+      </c>
+      <c r="S14">
         <v>2.56</v>
       </c>
-      <c r="Q14">
-        <v>1.61</v>
-      </c>
-      <c r="R14">
-        <v>1.62</v>
-      </c>
-      <c r="S14">
-        <v>2.54</v>
-      </c>
       <c r="T14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V14">
         <v>1.37</v>
@@ -4021,13 +4021,13 @@
         <v>30</v>
       </c>
       <c r="AA14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
         <v>15.5</v>
@@ -4048,7 +4048,7 @@
         <v>38</v>
       </c>
       <c r="AJ14">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AK14">
         <v>20</v>
@@ -4063,7 +4063,7 @@
         <v>10.5</v>
       </c>
       <c r="AO14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP14">
         <v>21</v>
@@ -4075,16 +4075,16 @@
         <v>26</v>
       </c>
       <c r="AS14">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW14">
         <v>32</v>
@@ -4105,79 +4105,79 @@
         <v>23</v>
       </c>
       <c r="BC14">
+        <v>17</v>
+      </c>
+      <c r="BD14">
+        <v>18.5</v>
+      </c>
+      <c r="BE14">
+        <v>29</v>
+      </c>
+      <c r="BF14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG14">
         <v>17.5</v>
       </c>
-      <c r="BD14">
-        <v>24</v>
-      </c>
-      <c r="BE14">
-        <v>50</v>
-      </c>
-      <c r="BF14">
-        <v>9</v>
-      </c>
-      <c r="BG14">
-        <v>22</v>
-      </c>
       <c r="BH14">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4206,13 +4206,13 @@
         <v>2.44</v>
       </c>
       <c r="H15">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I15">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
         <v>4.1</v>
@@ -4242,13 +4242,13 @@
         <v>2.3</v>
       </c>
       <c r="T15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="U15">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.69</v>
@@ -4257,25 +4257,25 @@
         <v>29</v>
       </c>
       <c r="Y15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z15">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AA15">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AB15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF15">
         <v>21</v>
@@ -4284,7 +4284,7 @@
         <v>12</v>
       </c>
       <c r="AH15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI15">
         <v>30</v>
@@ -4302,10 +4302,10 @@
         <v>50</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP15">
         <v>23</v>
@@ -4314,7 +4314,7 @@
         <v>18</v>
       </c>
       <c r="AR15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS15">
         <v>38</v>
@@ -4323,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="AU15">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV15">
         <v>12</v>
@@ -4335,10 +4335,10 @@
         <v>18</v>
       </c>
       <c r="AY15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA15">
         <v>26</v>
@@ -4353,7 +4353,7 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BF15">
         <v>10</v>
@@ -4362,64 +4362,64 @@
         <v>13.5</v>
       </c>
       <c r="BH15">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4460,7 +4460,7 @@
         <v>5.3</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M16">
         <v>1.02</v>
@@ -4481,13 +4481,13 @@
         <v>2.02</v>
       </c>
       <c r="S16">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="T16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V16">
         <v>1.21</v>
@@ -4496,7 +4496,7 @@
         <v>2.6</v>
       </c>
       <c r="X16">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="Y16">
         <v>75</v>
@@ -4505,16 +4505,16 @@
         <v>60</v>
       </c>
       <c r="AA16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC16">
         <v>14</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AE16">
         <v>55</v>
@@ -4526,37 +4526,37 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
         <v>110</v>
       </c>
       <c r="AJ16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AK16">
         <v>14.5</v>
       </c>
       <c r="AL16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AN16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO16">
         <v>32</v>
       </c>
       <c r="AP16">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AQ16">
         <v>32</v>
       </c>
       <c r="AR16">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AS16">
         <v>42</v>
@@ -4571,13 +4571,13 @@
         <v>20</v>
       </c>
       <c r="AW16">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="AX16">
         <v>13.5</v>
       </c>
       <c r="AY16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ16">
         <v>15</v>
@@ -4592,76 +4592,76 @@
         <v>12.5</v>
       </c>
       <c r="BD16">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE16">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BF16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH16">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,19 +4684,19 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G17">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
         <v>4.5</v>
@@ -4705,16 +4705,16 @@
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>6</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q17">
         <v>1.57</v>
@@ -4726,40 +4726,40 @@
         <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="U17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y17">
         <v>26</v>
       </c>
       <c r="Z17">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE17">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AF17">
         <v>13.5</v>
@@ -4768,7 +4768,7 @@
         <v>10.5</v>
       </c>
       <c r="AH17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI17">
         <v>55</v>
@@ -4777,43 +4777,43 @@
         <v>20</v>
       </c>
       <c r="AK17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN17">
         <v>7.2</v>
       </c>
       <c r="AO17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP17">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ17">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AR17">
         <v>34</v>
       </c>
       <c r="AS17">
+        <v>65</v>
+      </c>
+      <c r="AT17">
+        <v>12</v>
+      </c>
+      <c r="AU17">
+        <v>9.4</v>
+      </c>
+      <c r="AV17">
+        <v>17</v>
+      </c>
+      <c r="AW17">
         <v>38</v>
-      </c>
-      <c r="AT17">
-        <v>11.5</v>
-      </c>
-      <c r="AU17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV17">
-        <v>16.5</v>
-      </c>
-      <c r="AW17">
-        <v>42</v>
       </c>
       <c r="AX17">
         <v>11.5</v>
@@ -4822,88 +4822,88 @@
         <v>9.4</v>
       </c>
       <c r="AZ17">
+        <v>14.5</v>
+      </c>
+      <c r="BA17">
+        <v>36</v>
+      </c>
+      <c r="BB17">
+        <v>16.5</v>
+      </c>
+      <c r="BC17">
         <v>14</v>
       </c>
-      <c r="BA17">
-        <v>40</v>
-      </c>
-      <c r="BB17">
-        <v>17.5</v>
-      </c>
-      <c r="BC17">
-        <v>14.5</v>
-      </c>
       <c r="BD17">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE17">
         <v>50</v>
       </c>
       <c r="BF17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH17">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,112 +4926,112 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="G18">
-        <v>6.4</v>
+        <v>200</v>
       </c>
       <c r="H18">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="I18">
-        <v>1.78</v>
+        <v>200</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="K18">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L18">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="O18">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P18">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q18">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="R18">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="S18">
-        <v>2.14</v>
+        <v>1.14</v>
       </c>
       <c r="T18">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
         <v>1.01</v>
@@ -5070,7 +5070,7 @@
         <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
         <v>1.01</v>
@@ -5079,7 +5079,7 @@
         <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5088,13 +5088,13 @@
         <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
         <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
         <v>1.01</v>
@@ -5106,7 +5106,7 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
         <v>1.01</v>
@@ -5124,25 +5124,25 @@
         <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
         <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
         <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
         <v>1.01</v>
       </c>
       <c r="BZ18">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
         <v>1.01</v>
@@ -5168,226 +5168,226 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.64</v>
+        <v>2.12</v>
       </c>
       <c r="G19">
-        <v>2.92</v>
+        <v>990</v>
       </c>
       <c r="H19">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="I19">
-        <v>3.2</v>
+        <v>990</v>
       </c>
       <c r="J19">
-        <v>3.05</v>
+        <v>1.93</v>
       </c>
       <c r="K19">
         <v>3.3</v>
       </c>
       <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.08</v>
+      </c>
+      <c r="N19">
+        <v>1.24</v>
+      </c>
+      <c r="O19">
         <v>1.4</v>
       </c>
-      <c r="M19">
-        <v>1.1</v>
-      </c>
-      <c r="N19">
-        <v>3</v>
-      </c>
-      <c r="O19">
-        <v>1.43</v>
-      </c>
       <c r="P19">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="R19">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S19">
-        <v>4.2</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>7</v>
+        <v>1.13</v>
       </c>
       <c r="AS19">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="AT19">
-        <v>8.4</v>
+        <v>1.13</v>
       </c>
       <c r="AU19">
-        <v>6.4</v>
+        <v>1.13</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>1.13</v>
       </c>
       <c r="AW19">
-        <v>7.6</v>
+        <v>1.13</v>
       </c>
       <c r="AX19">
-        <v>15</v>
+        <v>1.13</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>1.13</v>
       </c>
       <c r="AZ19">
-        <v>16.5</v>
+        <v>1.13</v>
       </c>
       <c r="BA19">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="BB19">
-        <v>8</v>
+        <v>1.13</v>
       </c>
       <c r="BC19">
-        <v>7.6</v>
+        <v>1.13</v>
       </c>
       <c r="BD19">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="BE19">
-        <v>9</v>
+        <v>1.13</v>
       </c>
       <c r="BF19">
-        <v>7.6</v>
+        <v>1.13</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>1.13</v>
       </c>
       <c r="BH19">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.5</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
         <v>148</v>
@@ -5410,226 +5410,226 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="G20">
-        <v>1.94</v>
+        <v>990</v>
       </c>
       <c r="H20">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="I20">
-        <v>6.2</v>
+        <v>70</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>1.24</v>
       </c>
       <c r="K20">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L20">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="O20">
         <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="Q20">
-        <v>2.42</v>
+        <v>1.02</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>4.9</v>
+        <v>1.05</v>
       </c>
       <c r="T20">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="U20">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W20">
-        <v>2.04</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
         <v>1000</v>
       </c>
       <c r="BW20">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
         <v>148</v>
@@ -5652,226 +5652,226 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="G21">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H21">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="I21">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J21">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L21">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
+        <v>1.08</v>
+      </c>
+      <c r="N21">
         <v>1.1</v>
-      </c>
-      <c r="N21">
-        <v>2.86</v>
       </c>
       <c r="O21">
         <v>1.46</v>
       </c>
       <c r="P21">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>1.02</v>
       </c>
       <c r="R21">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S21">
-        <v>4.5</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
       <c r="V21">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="W21">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>148</v>
@@ -5894,226 +5894,226 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="G22">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="I22">
         <v>2.14</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="K22">
         <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>2.28</v>
+        <v>1.43</v>
       </c>
       <c r="O22">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="P22">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="R22">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S22">
-        <v>6.8</v>
+        <v>1.05</v>
       </c>
       <c r="T22">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="U22">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="V22">
         <v>1.87</v>
       </c>
       <c r="W22">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN22">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP22">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT22">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV22">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX22">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="s">
         <v>148</v>
@@ -6136,7 +6136,7 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G23">
         <v>2.9</v>
@@ -6145,7 +6145,7 @@
         <v>3.1</v>
       </c>
       <c r="I23">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J23">
         <v>2.94</v>
@@ -6157,205 +6157,205 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O23">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="P23">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q23">
-        <v>3.05</v>
+        <v>1.65</v>
       </c>
       <c r="R23">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S23">
-        <v>7</v>
+        <v>1.05</v>
       </c>
       <c r="T23">
-        <v>2.36</v>
+        <v>1.82</v>
       </c>
       <c r="U23">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
         <v>1.52</v>
       </c>
       <c r="X23">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6396,19 +6396,19 @@
         <v>4.4</v>
       </c>
       <c r="L24">
+        <v>1.35</v>
+      </c>
+      <c r="M24">
+        <v>1.06</v>
+      </c>
+      <c r="N24">
+        <v>3.6</v>
+      </c>
+      <c r="O24">
         <v>1.34</v>
       </c>
-      <c r="M24">
-        <v>1.08</v>
-      </c>
-      <c r="N24">
-        <v>3.55</v>
-      </c>
-      <c r="O24">
-        <v>1.35</v>
-      </c>
       <c r="P24">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
@@ -6417,13 +6417,13 @@
         <v>1.33</v>
       </c>
       <c r="S24">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="T24">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
         <v>1.13</v>
@@ -6432,25 +6432,25 @@
         <v>2.78</v>
       </c>
       <c r="X24">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Y24">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Z24">
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="AA24">
         <v>1000</v>
       </c>
       <c r="AB24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC24">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD24">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AE24">
         <v>1000</v>
@@ -6462,46 +6462,46 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI24">
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK24">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL24">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AM24">
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ24">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR24">
         <v>30</v>
       </c>
       <c r="AS24">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="AT24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU24">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV24">
         <v>24</v>
@@ -6510,22 +6510,22 @@
         <v>42</v>
       </c>
       <c r="AX24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24">
         <v>42</v>
       </c>
       <c r="BB24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC24">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD24">
         <v>26</v>
@@ -6534,70 +6534,70 @@
         <v>46</v>
       </c>
       <c r="BF24">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BG24">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="BH24">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN24">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP24">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="s">
         <v>148</v>
@@ -6620,226 +6620,226 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G25">
-        <v>1.84</v>
+        <v>3.3</v>
       </c>
       <c r="H25">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I25">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J25">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L25">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>1.96</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P25">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q25">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S25">
-        <v>3.2</v>
+        <v>1.27</v>
       </c>
       <c r="T25">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
         <v>1.21</v>
       </c>
       <c r="W25">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="X25">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z25">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA25">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB25">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC25">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD25">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF25">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI25">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK25">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL25">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM25">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN25">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO25">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP25">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR25">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS25">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT25">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU25">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV25">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX25">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY25">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA25">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB25">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC25">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD25">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE25">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF25">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG25">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK25">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN25">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO25">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP25">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ25">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BR25">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS25">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT25">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU25">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX25">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY25">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA25">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="s">
         <v>148</v>
@@ -6862,226 +6862,226 @@
         <v>147</v>
       </c>
       <c r="F26">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H26">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="I26">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>3.05</v>
+        <v>1.12</v>
       </c>
       <c r="K26">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L26">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>1.96</v>
+      </c>
+      <c r="O26">
+        <v>1.01</v>
+      </c>
+      <c r="P26">
+        <v>1.46</v>
+      </c>
+      <c r="Q26">
+        <v>1.49</v>
+      </c>
+      <c r="R26">
+        <v>1.17</v>
+      </c>
+      <c r="S26">
+        <v>1.05</v>
+      </c>
+      <c r="T26">
         <v>1.11</v>
       </c>
-      <c r="N26">
-        <v>2.66</v>
-      </c>
-      <c r="O26">
-        <v>1.5</v>
-      </c>
-      <c r="P26">
-        <v>1.54</v>
-      </c>
-      <c r="Q26">
-        <v>2.52</v>
-      </c>
-      <c r="R26">
-        <v>1.19</v>
-      </c>
-      <c r="S26">
-        <v>5.1</v>
-      </c>
-      <c r="T26">
-        <v>2.12</v>
-      </c>
       <c r="U26">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="W26">
-        <v>1.86</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN26">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP26">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT26">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 06:25:20</t>
+    <t>2026-07-22 08:32:45</t>
   </si>
 </sst>
 </file>
@@ -1054,31 +1054,31 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="I2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
         <v>1.52</v>
@@ -1087,193 +1087,193 @@
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W2">
         <v>1.2</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1311,19 +1311,19 @@
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
         <v>4.6</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
         <v>2.22</v>
@@ -1341,16 +1341,16 @@
         <v>1.68</v>
       </c>
       <c r="U3">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y3">
         <v>17</v>
@@ -1359,19 +1359,19 @@
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE3">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1380,55 +1380,55 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL3">
         <v>32</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN3">
         <v>12.5</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP3">
         <v>16</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT3">
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
         <v>9.800000000000001</v>
@@ -1437,85 +1437,85 @@
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BF3">
         <v>11</v>
       </c>
       <c r="BG3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,7 +1538,7 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
         <v>2.1</v>
@@ -1547,10 +1547,10 @@
         <v>4.3</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.45</v>
@@ -1565,13 +1565,13 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
         <v>1.26</v>
@@ -1583,10 +1583,10 @@
         <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
         <v>1.9</v>
@@ -1595,67 +1595,67 @@
         <v>11</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
         <v>30</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AL4">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>12</v>
       </c>
       <c r="AR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS4">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AT4">
         <v>7.2</v>
@@ -1664,13 +1664,13 @@
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1682,82 +1682,82 @@
         <v>36</v>
       </c>
       <c r="BB4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4">
         <v>23</v>
       </c>
       <c r="BD4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG4">
         <v>70</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>18</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1798,7 +1798,7 @@
         <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -1807,10 +1807,10 @@
         <v>3.5</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
         <v>2.16</v>
@@ -1822,7 +1822,7 @@
         <v>4</v>
       </c>
       <c r="T5">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
         <v>2.06</v>
@@ -1837,22 +1837,22 @@
         <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
         <v>23</v>
       </c>
       <c r="AA5">
-        <v>520</v>
+        <v>65</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
         <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE5">
         <v>44</v>
@@ -1861,22 +1861,22 @@
         <v>14.5</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI5">
         <v>60</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5">
         <v>27</v>
       </c>
       <c r="AL5">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="AM5">
         <v>110</v>
@@ -1888,16 +1888,16 @@
         <v>46</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
         <v>11</v>
       </c>
       <c r="AR5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -1921,10 +1921,10 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BC5">
         <v>23</v>
@@ -1933,73 +1933,73 @@
         <v>38</v>
       </c>
       <c r="BE5">
+        <v>48</v>
+      </c>
+      <c r="BF5">
+        <v>21</v>
+      </c>
+      <c r="BG5">
         <v>40</v>
       </c>
-      <c r="BF5">
-        <v>20</v>
-      </c>
-      <c r="BG5">
-        <v>38</v>
-      </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2028,10 +2028,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H6">
+        <v>1.49</v>
+      </c>
+      <c r="I6">
         <v>1.5</v>
-      </c>
-      <c r="I6">
-        <v>1.51</v>
       </c>
       <c r="J6">
         <v>4.6</v>
@@ -2040,7 +2040,7 @@
         <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -2049,7 +2049,7 @@
         <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6">
         <v>2.06</v>
@@ -2067,76 +2067,76 @@
         <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y6">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA6">
         <v>13</v>
       </c>
       <c r="AB6">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AF6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AG6">
         <v>32</v>
       </c>
       <c r="AH6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI6">
         <v>42</v>
       </c>
       <c r="AJ6">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AK6">
         <v>140</v>
       </c>
       <c r="AL6">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AM6">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN6">
         <v>190</v>
       </c>
       <c r="AO6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AP6">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
         <v>7.4</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS6">
         <v>11.5</v>
@@ -2145,103 +2145,103 @@
         <v>23</v>
       </c>
       <c r="AU6">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AY6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ6">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BA6">
         <v>34</v>
       </c>
       <c r="BB6">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BC6">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BD6">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BE6">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="BF6">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>16.5</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>14.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2264,13 +2264,13 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G7">
         <v>1.87</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I7">
         <v>5.2</v>
@@ -2288,31 +2288,31 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
         <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
         <v>2.14</v>
@@ -2321,34 +2321,34 @@
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z7">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA7">
         <v>130</v>
       </c>
       <c r="AB7">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF7">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>22</v>
       </c>
       <c r="AI7">
         <v>80</v>
@@ -2363,16 +2363,16 @@
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN7">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP7">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7">
         <v>13.5</v>
@@ -2381,7 +2381,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>4.9</v>
+        <v>12</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2390,100 +2390,100 @@
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>4.7</v>
+        <v>60</v>
       </c>
       <c r="AX7">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
       </c>
       <c r="AZ7">
+        <v>19.5</v>
+      </c>
+      <c r="BA7">
+        <v>34</v>
+      </c>
+      <c r="BB7">
+        <v>18</v>
+      </c>
+      <c r="BC7">
         <v>18.5</v>
-      </c>
-      <c r="BA7">
-        <v>4.8</v>
-      </c>
-      <c r="BB7">
-        <v>8</v>
-      </c>
-      <c r="BC7">
-        <v>4.1</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>148</v>
@@ -2512,7 +2512,7 @@
         <v>3.7</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I8">
         <v>2.08</v>
@@ -2530,25 +2530,25 @@
         <v>1.03</v>
       </c>
       <c r="N8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q8">
         <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S8">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T8">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="U8">
         <v>2.7</v>
@@ -2566,10 +2566,10 @@
         <v>14.5</v>
       </c>
       <c r="Z8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA8">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AB8">
         <v>21</v>
@@ -2578,13 +2578,13 @@
         <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG8">
         <v>15.5</v>
@@ -2593,7 +2593,7 @@
         <v>15</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AJ8">
         <v>70</v>
@@ -2602,25 +2602,25 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM8">
         <v>60</v>
       </c>
       <c r="AN8">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AO8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ8">
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8">
         <v>24</v>
@@ -2629,10 +2629,10 @@
         <v>19</v>
       </c>
       <c r="AU8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>17</v>
@@ -2641,7 +2641,7 @@
         <v>27</v>
       </c>
       <c r="AY8">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2653,79 +2653,79 @@
         <v>32</v>
       </c>
       <c r="BC8">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BD8">
         <v>34</v>
       </c>
       <c r="BE8">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BG8">
         <v>9</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2760,7 +2760,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.1</v>
@@ -2772,28 +2772,28 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R9">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
         <v>3.15</v>
       </c>
       <c r="T9">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U9">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V9">
         <v>1.25</v>
@@ -2802,172 +2802,172 @@
         <v>2.16</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB9">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN9">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP9">
-        <v>1.39</v>
+        <v>15</v>
       </c>
       <c r="AQ9">
-        <v>1.39</v>
+        <v>15.5</v>
       </c>
       <c r="AR9">
-        <v>1.4</v>
+        <v>32</v>
       </c>
       <c r="AS9">
-        <v>1.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU9">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AV9">
-        <v>1.39</v>
+        <v>16</v>
       </c>
       <c r="AW9">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX9">
-        <v>1.32</v>
+        <v>10</v>
       </c>
       <c r="AY9">
-        <v>1.29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>1.39</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB9">
-        <v>1.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC9">
-        <v>1.4</v>
+        <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>1.4</v>
+        <v>27</v>
       </c>
       <c r="BE9">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="BF9">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG9">
-        <v>1.4</v>
+        <v>44</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2990,10 +2990,10 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H10">
         <v>6.6</v>
@@ -3023,7 +3023,7 @@
         <v>2.5</v>
       </c>
       <c r="Q10">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R10">
         <v>1.59</v>
@@ -3035,25 +3035,25 @@
         <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z10">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB10">
         <v>11</v>
@@ -3062,7 +3062,7 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE10">
         <v>90</v>
@@ -3071,13 +3071,13 @@
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
         <v>21</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ10">
         <v>14.5</v>
@@ -3086,25 +3086,25 @@
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO10">
         <v>80</v>
       </c>
       <c r="AP10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
         <v>26</v>
       </c>
       <c r="AR10">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AS10">
         <v>46</v>
@@ -3116,10 +3116,10 @@
         <v>10</v>
       </c>
       <c r="AV10">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AW10">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3131,13 +3131,13 @@
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB10">
         <v>13</v>
       </c>
       <c r="BC10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
         <v>25</v>
@@ -3149,67 +3149,67 @@
         <v>5.8</v>
       </c>
       <c r="BG10">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3232,25 +3232,25 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H11">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K11">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.03</v>
@@ -3265,7 +3265,7 @@
         <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R11">
         <v>1.59</v>
@@ -3274,184 +3274,184 @@
         <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3504,13 +3504,13 @@
         <v>1.14</v>
       </c>
       <c r="P12">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q12">
         <v>1.44</v>
       </c>
       <c r="R12">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S12">
         <v>2.08</v>
@@ -3531,16 +3531,16 @@
         <v>36</v>
       </c>
       <c r="Y12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA12">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB12">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC12">
         <v>11</v>
@@ -3561,10 +3561,10 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AJ12">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK12">
         <v>17.5</v>
@@ -3573,28 +3573,28 @@
         <v>23</v>
       </c>
       <c r="AM12">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AN12">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AO12">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP12">
         <v>28</v>
       </c>
       <c r="AQ12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR12">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS12">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AT12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU12">
         <v>10</v>
@@ -3603,97 +3603,97 @@
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AX12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>29</v>
+      </c>
+      <c r="BB12">
+        <v>24</v>
+      </c>
+      <c r="BC12">
+        <v>16</v>
+      </c>
+      <c r="BD12">
+        <v>20</v>
+      </c>
+      <c r="BE12">
+        <v>38</v>
+      </c>
+      <c r="BF12">
+        <v>7</v>
+      </c>
+      <c r="BG12">
+        <v>16.5</v>
+      </c>
+      <c r="BH12">
+        <v>5.4</v>
+      </c>
+      <c r="BI12">
+        <v>4.2</v>
+      </c>
+      <c r="BJ12">
+        <v>8.6</v>
+      </c>
+      <c r="BK12">
+        <v>4.7</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>9</v>
+      </c>
+      <c r="BN12">
+        <v>5.8</v>
+      </c>
+      <c r="BO12">
+        <v>4.5</v>
+      </c>
+      <c r="BP12">
+        <v>13</v>
+      </c>
+      <c r="BQ12">
+        <v>5.8</v>
+      </c>
+      <c r="BR12">
+        <v>19.5</v>
+      </c>
+      <c r="BS12">
+        <v>6.8</v>
+      </c>
+      <c r="BT12">
+        <v>8</v>
+      </c>
+      <c r="BU12">
+        <v>6</v>
+      </c>
+      <c r="BV12">
+        <v>24</v>
+      </c>
+      <c r="BW12">
+        <v>7.4</v>
+      </c>
+      <c r="BX12">
+        <v>26</v>
+      </c>
+      <c r="BY12">
+        <v>7.6</v>
+      </c>
+      <c r="BZ12">
         <v>12</v>
       </c>
-      <c r="BA12">
-        <v>25</v>
-      </c>
-      <c r="BB12">
-        <v>22</v>
-      </c>
-      <c r="BC12">
-        <v>15.5</v>
-      </c>
-      <c r="BD12">
-        <v>18</v>
-      </c>
-      <c r="BE12">
-        <v>36</v>
-      </c>
-      <c r="BF12">
-        <v>7.2</v>
-      </c>
-      <c r="BG12">
-        <v>13.5</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3722,79 +3722,79 @@
         <v>3.45</v>
       </c>
       <c r="H13">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I13">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
         <v>3.85</v>
       </c>
       <c r="L13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q13">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R13">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S13">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="T13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X13">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AA13">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AB13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC13">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13">
         <v>11.5</v>
       </c>
       <c r="AE13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF13">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG13">
         <v>14</v>
@@ -3803,16 +3803,16 @@
         <v>16</v>
       </c>
       <c r="AI13">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AJ13">
         <v>60</v>
       </c>
       <c r="AK13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL13">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM13">
         <v>70</v>
@@ -3842,25 +3842,25 @@
         <v>7.6</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX13">
         <v>23</v>
       </c>
       <c r="AY13">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA13">
         <v>27</v>
       </c>
       <c r="BB13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BC13">
         <v>30</v>
@@ -3869,73 +3869,73 @@
         <v>34</v>
       </c>
       <c r="BE13">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BF13">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BG13">
         <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI13">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK13">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO13">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ13">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS13">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BU13">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW13">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY13">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA13">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,16 +3958,16 @@
         <v>135</v>
       </c>
       <c r="F14">
+        <v>2.06</v>
+      </c>
+      <c r="G14">
         <v>2.1</v>
       </c>
-      <c r="G14">
-        <v>2.12</v>
-      </c>
       <c r="H14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I14">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J14">
         <v>3.95</v>
@@ -3991,16 +3991,16 @@
         <v>2.54</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R14">
         <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T14">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U14">
         <v>2.64</v>
@@ -4009,7 +4009,7 @@
         <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X14">
         <v>24</v>
@@ -4024,10 +4024,10 @@
         <v>70</v>
       </c>
       <c r="AB14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD14">
         <v>15.5</v>
@@ -4036,7 +4036,7 @@
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4048,10 +4048,10 @@
         <v>38</v>
       </c>
       <c r="AJ14">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AK14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4060,31 +4060,31 @@
         <v>60</v>
       </c>
       <c r="AN14">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ14">
         <v>18</v>
       </c>
       <c r="AR14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AS14">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW14">
         <v>32</v>
@@ -4093,7 +4093,7 @@
         <v>14</v>
       </c>
       <c r="AY14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14">
         <v>13.5</v>
@@ -4108,76 +4108,76 @@
         <v>17</v>
       </c>
       <c r="BD14">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BE14">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF14">
         <v>9.199999999999999</v>
       </c>
       <c r="BG14">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4203,10 +4203,10 @@
         <v>2.4</v>
       </c>
       <c r="G15">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H15">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I15">
         <v>2.98</v>
@@ -4224,31 +4224,31 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="Q15">
         <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S15">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T15">
         <v>1.48</v>
       </c>
       <c r="U15">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
         <v>1.69</v>
@@ -4257,16 +4257,16 @@
         <v>29</v>
       </c>
       <c r="Y15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z15">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AA15">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AB15">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4275,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="AE15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF15">
         <v>21</v>
@@ -4290,7 +4290,7 @@
         <v>30</v>
       </c>
       <c r="AJ15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK15">
         <v>22</v>
@@ -4302,13 +4302,13 @@
         <v>50</v>
       </c>
       <c r="AN15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AP15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ15">
         <v>18</v>
@@ -4323,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV15">
         <v>12</v>
@@ -4335,10 +4335,10 @@
         <v>18</v>
       </c>
       <c r="AY15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA15">
         <v>26</v>
@@ -4353,7 +4353,7 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF15">
         <v>10</v>
@@ -4362,64 +4362,64 @@
         <v>13.5</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4454,10 +4454,10 @@
         <v>5.6</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L16">
         <v>1.21</v>
@@ -4466,7 +4466,7 @@
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16">
         <v>1.11</v>
@@ -4475,19 +4475,19 @@
         <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R16">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T16">
         <v>1.48</v>
       </c>
       <c r="U16">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="V16">
         <v>1.21</v>
@@ -4496,67 +4496,67 @@
         <v>2.6</v>
       </c>
       <c r="X16">
-        <v>140</v>
+        <v>42</v>
       </c>
       <c r="Y16">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Z16">
         <v>60</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB16">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD16">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AE16">
         <v>55</v>
       </c>
       <c r="AF16">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG16">
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AK16">
         <v>14.5</v>
       </c>
       <c r="AL16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM16">
-        <v>190</v>
+        <v>55</v>
       </c>
       <c r="AN16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO16">
         <v>32</v>
       </c>
       <c r="AP16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR16">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AS16">
         <v>42</v>
@@ -4571,13 +4571,13 @@
         <v>20</v>
       </c>
       <c r="AW16">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AX16">
         <v>13.5</v>
       </c>
       <c r="AY16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ16">
         <v>15</v>
@@ -4592,76 +4592,76 @@
         <v>12.5</v>
       </c>
       <c r="BD16">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE16">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BF16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG16">
         <v>25</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,7 +4684,7 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G17">
         <v>1.78</v>
@@ -4696,7 +4696,7 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
         <v>4.5</v>
@@ -4705,13 +4705,13 @@
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
         <v>6</v>
       </c>
       <c r="O17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
         <v>2.66</v>
@@ -4726,10 +4726,10 @@
         <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
         <v>1.25</v>
@@ -4738,28 +4738,28 @@
         <v>2.28</v>
       </c>
       <c r="X17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Y17">
         <v>26</v>
       </c>
       <c r="Z17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA17">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC17">
         <v>10.5</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE17">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF17">
         <v>13.5</v>
@@ -4768,40 +4768,40 @@
         <v>10.5</v>
       </c>
       <c r="AH17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK17">
         <v>16</v>
       </c>
       <c r="AL17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM17">
-        <v>75</v>
+        <v>920</v>
       </c>
       <c r="AN17">
         <v>7.2</v>
       </c>
       <c r="AO17">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP17">
         <v>22</v>
       </c>
       <c r="AQ17">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AR17">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS17">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AT17">
         <v>12</v>
@@ -4810,13 +4810,13 @@
         <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17">
         <v>9.4</v>
@@ -4825,85 +4825,85 @@
         <v>14.5</v>
       </c>
       <c r="BA17">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB17">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD17">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BE17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF17">
         <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI17">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BM17">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,226 +4926,226 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G18">
-        <v>200</v>
+        <v>6.8</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="I18">
-        <v>200</v>
+        <v>1.71</v>
       </c>
       <c r="J18">
-        <v>1.02</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.02</v>
+        <v>4.7</v>
       </c>
       <c r="O18">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q18">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="R18">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S18">
-        <v>1.14</v>
+        <v>2.12</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="CB18" t="s">
         <v>148</v>
@@ -5168,226 +5168,226 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="G19">
-        <v>990</v>
+        <v>2.84</v>
       </c>
       <c r="H19">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="I19">
-        <v>990</v>
+        <v>3.3</v>
       </c>
       <c r="J19">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
         <v>3.3</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="R19">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>4.3</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V19">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y19">
+        <v>14.5</v>
+      </c>
+      <c r="Z19">
+        <v>23</v>
+      </c>
+      <c r="AA19">
+        <v>55</v>
+      </c>
+      <c r="AB19">
+        <v>11.5</v>
+      </c>
+      <c r="AC19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19">
+        <v>17</v>
+      </c>
+      <c r="AE19">
+        <v>40</v>
+      </c>
+      <c r="AF19">
         <v>970</v>
       </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP19">
-        <v>1.13</v>
+        <v>9.4</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR19">
-        <v>1.13</v>
+        <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="AT19">
-        <v>1.13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU19">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="AV19">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="AW19">
-        <v>1.13</v>
+        <v>32</v>
       </c>
       <c r="AX19">
-        <v>1.13</v>
+        <v>15</v>
       </c>
       <c r="AY19">
-        <v>1.13</v>
+        <v>3.85</v>
       </c>
       <c r="AZ19">
-        <v>1.13</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="BB19">
-        <v>1.13</v>
+        <v>28</v>
       </c>
       <c r="BC19">
-        <v>1.13</v>
+        <v>4.8</v>
       </c>
       <c r="BD19">
-        <v>1.13</v>
+        <v>5.1</v>
       </c>
       <c r="BE19">
-        <v>1.13</v>
+        <v>5.4</v>
       </c>
       <c r="BF19">
-        <v>1.13</v>
+        <v>4.8</v>
       </c>
       <c r="BG19">
-        <v>1.13</v>
+        <v>4.9</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="CB19" t="s">
         <v>148</v>
@@ -5410,166 +5410,166 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G20">
-        <v>990</v>
+        <v>1.9</v>
       </c>
       <c r="H20">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="I20">
-        <v>70</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
-        <v>1.24</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N20">
-        <v>1.56</v>
+        <v>2.68</v>
       </c>
       <c r="O20">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P20">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="Q20">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="R20">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S20">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="T20">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="U20">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="V20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>2.1</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5652,226 +5652,226 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
         <v>2.18</v>
       </c>
       <c r="H21">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I21">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J21">
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M21">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N21">
-        <v>1.1</v>
+        <v>2.86</v>
       </c>
       <c r="O21">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P21">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Q21">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S21">
-        <v>1.48</v>
+        <v>4.6</v>
       </c>
       <c r="T21">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="W21">
         <v>1.84</v>
       </c>
       <c r="X21">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y21">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z21">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH21">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK21">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN21">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP21">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT21">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU21">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY21">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD21">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF21">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI21">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK21">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO21">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ21">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS21">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU21">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW21">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY21">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA21">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB21" t="s">
         <v>148</v>
@@ -5894,166 +5894,166 @@
         <v>143</v>
       </c>
       <c r="F22">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="H22">
-        <v>1.64</v>
+        <v>2.04</v>
       </c>
       <c r="I22">
         <v>2.14</v>
       </c>
       <c r="J22">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="K22">
         <v>3.15</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N22">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="O22">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q22">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="R22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S22">
-        <v>1.05</v>
+        <v>7.4</v>
       </c>
       <c r="T22">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="V22">
         <v>1.87</v>
       </c>
       <c r="W22">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y22">
         <v>1000</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW22">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX22">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY22">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ22">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA22">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BB22">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC22">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BE22">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6136,7 +6136,7 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="G23">
         <v>2.9</v>
@@ -6145,43 +6145,43 @@
         <v>3.1</v>
       </c>
       <c r="I23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J23">
         <v>2.94</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
+        <v>3.05</v>
+      </c>
+      <c r="R23">
+        <v>1.14</v>
+      </c>
+      <c r="S23">
+        <v>7</v>
+      </c>
+      <c r="T23">
+        <v>2.38</v>
+      </c>
+      <c r="U23">
         <v>1.65</v>
-      </c>
-      <c r="R23">
-        <v>1.12</v>
-      </c>
-      <c r="S23">
-        <v>1.05</v>
-      </c>
-      <c r="T23">
-        <v>1.82</v>
-      </c>
-      <c r="U23">
-        <v>1.31</v>
       </c>
       <c r="V23">
         <v>1.43</v>
@@ -6190,172 +6190,172 @@
         <v>1.52</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>710</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI23">
         <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AL23">
         <v>1000</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>520</v>
       </c>
       <c r="AO23">
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW23">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6384,10 +6384,10 @@
         <v>1.56</v>
       </c>
       <c r="H24">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
         <v>4.2</v>
@@ -6396,28 +6396,28 @@
         <v>4.4</v>
       </c>
       <c r="L24">
+        <v>1.41</v>
+      </c>
+      <c r="M24">
+        <v>1.08</v>
+      </c>
+      <c r="N24">
+        <v>3.65</v>
+      </c>
+      <c r="O24">
         <v>1.35</v>
       </c>
-      <c r="M24">
-        <v>1.06</v>
-      </c>
-      <c r="N24">
-        <v>3.6</v>
-      </c>
-      <c r="O24">
-        <v>1.34</v>
-      </c>
       <c r="P24">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S24">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="T24">
         <v>2.14</v>
@@ -6432,49 +6432,49 @@
         <v>2.78</v>
       </c>
       <c r="X24">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y24">
+        <v>23</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>7.4</v>
+      </c>
+      <c r="AC24">
+        <v>9.4</v>
+      </c>
+      <c r="AD24">
         <v>30</v>
       </c>
-      <c r="Z24">
-        <v>790</v>
-      </c>
-      <c r="AA24">
-        <v>1000</v>
-      </c>
-      <c r="AB24">
-        <v>7.6</v>
-      </c>
-      <c r="AC24">
-        <v>10</v>
-      </c>
-      <c r="AD24">
-        <v>38</v>
-      </c>
       <c r="AE24">
         <v>1000</v>
       </c>
       <c r="AF24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI24">
         <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK24">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL24">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM24">
         <v>1000</v>
@@ -6486,46 +6486,46 @@
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ24">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR24">
         <v>30</v>
       </c>
       <c r="AS24">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AT24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU24">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV24">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW24">
         <v>42</v>
       </c>
       <c r="AX24">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY24">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA24">
         <v>42</v>
       </c>
       <c r="BB24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC24">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD24">
         <v>26</v>
@@ -6534,70 +6534,70 @@
         <v>46</v>
       </c>
       <c r="BF24">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG24">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI24">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK24">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO24">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ24">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS24">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU24">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA24">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB24" t="s">
         <v>148</v>
@@ -6620,226 +6620,226 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="G25">
+        <v>1.84</v>
+      </c>
+      <c r="H25">
+        <v>5.1</v>
+      </c>
+      <c r="I25">
+        <v>5.5</v>
+      </c>
+      <c r="J25">
+        <v>3.85</v>
+      </c>
+      <c r="K25">
+        <v>4.1</v>
+      </c>
+      <c r="L25">
+        <v>1.37</v>
+      </c>
+      <c r="M25">
+        <v>1.06</v>
+      </c>
+      <c r="N25">
+        <v>4.3</v>
+      </c>
+      <c r="O25">
+        <v>1.28</v>
+      </c>
+      <c r="P25">
+        <v>2.08</v>
+      </c>
+      <c r="Q25">
+        <v>1.86</v>
+      </c>
+      <c r="R25">
+        <v>1.42</v>
+      </c>
+      <c r="S25">
+        <v>3.15</v>
+      </c>
+      <c r="T25">
+        <v>1.79</v>
+      </c>
+      <c r="U25">
+        <v>2.16</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>2.2</v>
+      </c>
+      <c r="X25">
+        <v>21</v>
+      </c>
+      <c r="Y25">
+        <v>26</v>
+      </c>
+      <c r="Z25">
+        <v>95</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>9.4</v>
+      </c>
+      <c r="AC25">
+        <v>8.6</v>
+      </c>
+      <c r="AD25">
+        <v>21</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>11.5</v>
+      </c>
+      <c r="AG25">
+        <v>10</v>
+      </c>
+      <c r="AH25">
+        <v>24</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>24</v>
+      </c>
+      <c r="AK25">
+        <v>18.5</v>
+      </c>
+      <c r="AL25">
+        <v>70</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>11</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>14</v>
+      </c>
+      <c r="AQ25">
+        <v>16.5</v>
+      </c>
+      <c r="AR25">
+        <v>29</v>
+      </c>
+      <c r="AS25">
+        <v>40</v>
+      </c>
+      <c r="AT25">
+        <v>8.6</v>
+      </c>
+      <c r="AU25">
+        <v>7.8</v>
+      </c>
+      <c r="AV25">
+        <v>17.5</v>
+      </c>
+      <c r="AW25">
+        <v>44</v>
+      </c>
+      <c r="AX25">
+        <v>10</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>14</v>
+      </c>
+      <c r="BA25">
+        <v>42</v>
+      </c>
+      <c r="BB25">
+        <v>17</v>
+      </c>
+      <c r="BC25">
+        <v>13.5</v>
+      </c>
+      <c r="BD25">
+        <v>22</v>
+      </c>
+      <c r="BE25">
+        <v>60</v>
+      </c>
+      <c r="BF25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG25">
+        <v>32</v>
+      </c>
+      <c r="BH25">
+        <v>3.65</v>
+      </c>
+      <c r="BI25">
         <v>3.3</v>
       </c>
-      <c r="H25">
-        <v>5</v>
-      </c>
-      <c r="I25">
-        <v>5.7</v>
-      </c>
-      <c r="J25">
-        <v>2</v>
-      </c>
-      <c r="K25">
-        <v>1000</v>
-      </c>
-      <c r="L25">
-        <v>1.33</v>
-      </c>
-      <c r="M25">
-        <v>1.05</v>
-      </c>
-      <c r="N25">
-        <v>1.96</v>
-      </c>
-      <c r="O25">
-        <v>1.26</v>
-      </c>
-      <c r="P25">
-        <v>1.86</v>
-      </c>
-      <c r="Q25">
-        <v>1.26</v>
-      </c>
-      <c r="R25">
-        <v>1.21</v>
-      </c>
-      <c r="S25">
-        <v>1.27</v>
-      </c>
-      <c r="T25">
-        <v>1.11</v>
-      </c>
-      <c r="U25">
-        <v>1.11</v>
-      </c>
-      <c r="V25">
-        <v>1.21</v>
-      </c>
-      <c r="W25">
-        <v>1.43</v>
-      </c>
-      <c r="X25">
-        <v>1000</v>
-      </c>
-      <c r="Y25">
-        <v>1000</v>
-      </c>
-      <c r="Z25">
-        <v>1000</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
-        <v>1000</v>
-      </c>
-      <c r="AC25">
-        <v>1000</v>
-      </c>
-      <c r="AD25">
-        <v>1000</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>1000</v>
-      </c>
-      <c r="AH25">
-        <v>1000</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25">
-        <v>1.01</v>
-      </c>
-      <c r="AR25">
-        <v>1.01</v>
-      </c>
-      <c r="AS25">
-        <v>1.01</v>
-      </c>
-      <c r="AT25">
-        <v>1.01</v>
-      </c>
-      <c r="AU25">
-        <v>1.01</v>
-      </c>
-      <c r="AV25">
-        <v>1.01</v>
-      </c>
-      <c r="AW25">
-        <v>1.01</v>
-      </c>
-      <c r="AX25">
-        <v>1.01</v>
-      </c>
-      <c r="AY25">
-        <v>1.01</v>
-      </c>
-      <c r="AZ25">
-        <v>1.01</v>
-      </c>
-      <c r="BA25">
-        <v>1.01</v>
-      </c>
-      <c r="BB25">
-        <v>1.01</v>
-      </c>
-      <c r="BC25">
-        <v>1.01</v>
-      </c>
-      <c r="BD25">
-        <v>1.01</v>
-      </c>
-      <c r="BE25">
-        <v>1.01</v>
-      </c>
-      <c r="BF25">
-        <v>1.01</v>
-      </c>
-      <c r="BG25">
-        <v>1.01</v>
-      </c>
-      <c r="BH25">
-        <v>1000</v>
-      </c>
-      <c r="BI25">
-        <v>1.04</v>
-      </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK25">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL25">
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO25">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ25">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR25">
         <v>1000</v>
       </c>
       <c r="BS25">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU25">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV25">
         <v>1000</v>
       </c>
       <c r="BW25">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX25">
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ25">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA25">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB25" t="s">
         <v>148</v>
@@ -6862,226 +6862,226 @@
         <v>147</v>
       </c>
       <c r="F26">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="G26">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H26">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="K26">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N26">
-        <v>1.96</v>
+        <v>2.66</v>
       </c>
       <c r="O26">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P26">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>2.54</v>
       </c>
       <c r="R26">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S26">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U26">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V26">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI26">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK26">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO26">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ26">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR26">
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU26">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV26">
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB26" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 08:32:45</t>
+    <t>2026-07-22 10:40:06</t>
   </si>
 </sst>
 </file>
@@ -1054,226 +1054,226 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="I2">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
         <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O2">
         <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q2">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
         <v>2.06</v>
       </c>
       <c r="W2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
         <v>11</v>
       </c>
       <c r="Y2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AK2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL2">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AM2">
+        <v>240</v>
+      </c>
+      <c r="AN2">
         <v>270</v>
       </c>
-      <c r="AN2">
-        <v>210</v>
-      </c>
       <c r="AO2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
         <v>5.4</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AY2">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AZ2">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>8.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BC2">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BD2">
-        <v>8.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BH2">
         <v>2.88</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>4.3</v>
       </c>
       <c r="BU2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW2">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
+        <v>38</v>
+      </c>
+      <c r="BY2">
+        <v>10</v>
+      </c>
+      <c r="BZ2">
         <v>40</v>
       </c>
-      <c r="BY2">
-        <v>9.6</v>
-      </c>
-      <c r="BZ2">
-        <v>38</v>
-      </c>
       <c r="CA2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1311,10 +1311,10 @@
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1323,31 +1323,31 @@
         <v>4.6</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U3">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X3">
         <v>18</v>
@@ -1359,7 +1359,7 @@
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>11.5</v>
@@ -1374,13 +1374,13 @@
         <v>42</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
         <v>46</v>
@@ -1398,19 +1398,19 @@
         <v>75</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
         <v>15</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS3">
         <v>60</v>
@@ -1419,10 +1419,10 @@
         <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW3">
         <v>34</v>
@@ -1431,13 +1431,13 @@
         <v>13</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB3">
         <v>23</v>
@@ -1446,31 +1446,31 @@
         <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>3.9</v>
       </c>
       <c r="BI3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3">
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM3">
         <v>10</v>
@@ -1479,16 +1479,16 @@
         <v>5.3</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP3">
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS3">
         <v>7.8</v>
@@ -1509,7 +1509,7 @@
         <v>36</v>
       </c>
       <c r="BY3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
         <v>21</v>
@@ -1544,7 +1544,7 @@
         <v>2.1</v>
       </c>
       <c r="H4">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
         <v>4.5</v>
@@ -1565,7 +1565,7 @@
         <v>3.15</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
         <v>1.7</v>
@@ -1586,28 +1586,28 @@
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
         <v>1.9</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB4">
         <v>7.6</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>17.5</v>
@@ -1625,22 +1625,22 @@
         <v>22</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
         <v>25</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4">
         <v>90</v>
@@ -1652,19 +1652,19 @@
         <v>12</v>
       </c>
       <c r="AR4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS4">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>55</v>
@@ -1679,7 +1679,7 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB4">
         <v>23</v>
@@ -1697,46 +1697,46 @@
         <v>19.5</v>
       </c>
       <c r="BG4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BN4">
         <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP4">
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU4">
         <v>5.6</v>
@@ -1745,19 +1745,19 @@
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1783,10 +1783,10 @@
         <v>2.38</v>
       </c>
       <c r="G5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
         <v>3.5</v>
@@ -1804,19 +1804,19 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S5">
         <v>4</v>
@@ -1825,19 +1825,19 @@
         <v>1.89</v>
       </c>
       <c r="U5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
         <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X5">
         <v>12.5</v>
       </c>
       <c r="Y5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
         <v>23</v>
@@ -1849,13 +1849,13 @@
         <v>9.4</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF5">
         <v>14.5</v>
@@ -1876,7 +1876,7 @@
         <v>27</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>130</v>
       </c>
       <c r="AM5">
         <v>110</v>
@@ -1885,7 +1885,7 @@
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP5">
         <v>11</v>
@@ -1897,7 +1897,7 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -1927,13 +1927,13 @@
         <v>29</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD5">
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="BF5">
         <v>21</v>
@@ -1942,64 +1942,64 @@
         <v>40</v>
       </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
         <v>19</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="BR5">
         <v>36</v>
       </c>
       <c r="BS5">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV5">
         <v>30</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,10 +2022,10 @@
         <v>127</v>
       </c>
       <c r="F6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G6">
         <v>8.6</v>
-      </c>
-      <c r="G6">
-        <v>8.800000000000001</v>
       </c>
       <c r="H6">
         <v>1.49</v>
@@ -2037,13 +2037,13 @@
         <v>4.6</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
         <v>4.1</v>
@@ -2052,37 +2052,37 @@
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
         <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V6">
         <v>3</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z6">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA6">
         <v>13</v>
@@ -2091,7 +2091,7 @@
         <v>25</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>9.800000000000001</v>
@@ -2100,7 +2100,7 @@
         <v>16</v>
       </c>
       <c r="AF6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG6">
         <v>32</v>
@@ -2109,16 +2109,16 @@
         <v>27</v>
       </c>
       <c r="AI6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AK6">
         <v>140</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AM6">
         <v>170</v>
@@ -2127,16 +2127,16 @@
         <v>190</v>
       </c>
       <c r="AO6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP6">
         <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS6">
         <v>11.5</v>
@@ -2154,7 +2154,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AY6">
         <v>28</v>
@@ -2163,85 +2163,85 @@
         <v>24</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BF6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG6">
         <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BT6">
         <v>3.85</v>
       </c>
       <c r="BU6">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BV6">
         <v>9.199999999999999</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6">
         <v>17</v>
       </c>
       <c r="CA6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2267,13 +2267,13 @@
         <v>1.86</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H7">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>3.7</v>
@@ -2288,34 +2288,34 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
+        <v>2.1</v>
+      </c>
+      <c r="R7">
+        <v>1.32</v>
+      </c>
+      <c r="S7">
+        <v>3.85</v>
+      </c>
+      <c r="T7">
+        <v>1.96</v>
+      </c>
+      <c r="U7">
+        <v>1.95</v>
+      </c>
+      <c r="V7">
+        <v>1.25</v>
+      </c>
+      <c r="W7">
         <v>2.12</v>
-      </c>
-      <c r="R7">
-        <v>1.31</v>
-      </c>
-      <c r="S7">
-        <v>3.9</v>
-      </c>
-      <c r="T7">
-        <v>1.95</v>
-      </c>
-      <c r="U7">
-        <v>1.92</v>
-      </c>
-      <c r="V7">
-        <v>1.23</v>
-      </c>
-      <c r="W7">
-        <v>2.14</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2336,13 +2336,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE7">
         <v>75</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2363,7 +2363,7 @@
         <v>42</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
         <v>14.5</v>
@@ -2378,10 +2378,10 @@
         <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2396,13 +2396,13 @@
         <v>60</v>
       </c>
       <c r="AX7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
         <v>34</v>
@@ -2411,25 +2411,25 @@
         <v>18</v>
       </c>
       <c r="BC7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ7">
         <v>11</v>
@@ -2441,31 +2441,31 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU7">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV7">
         <v>46</v>
@@ -2480,7 +2480,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="CA7">
         <v>7.6</v>
@@ -2506,16 +2506,16 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H8">
         <v>2.06</v>
       </c>
       <c r="I8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2527,7 +2527,7 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.9</v>
@@ -2539,7 +2539,7 @@
         <v>2.64</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
         <v>1.66</v>
@@ -2554,7 +2554,7 @@
         <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W8">
         <v>1.37</v>
@@ -2572,10 +2572,10 @@
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>11.5</v>
@@ -2596,7 +2596,7 @@
         <v>26</v>
       </c>
       <c r="AJ8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK8">
         <v>36</v>
@@ -2614,7 +2614,7 @@
         <v>9.4</v>
       </c>
       <c r="AP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
         <v>13</v>
@@ -2629,7 +2629,7 @@
         <v>19</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2641,7 +2641,7 @@
         <v>27</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2653,10 +2653,10 @@
         <v>32</v>
       </c>
       <c r="BC8">
+        <v>30</v>
+      </c>
+      <c r="BD8">
         <v>32</v>
-      </c>
-      <c r="BD8">
-        <v>34</v>
       </c>
       <c r="BE8">
         <v>48</v>
@@ -2668,7 +2668,7 @@
         <v>9</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
         <v>3.5</v>
@@ -2683,25 +2683,25 @@
         <v>75</v>
       </c>
       <c r="BM8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN8">
         <v>7.6</v>
       </c>
       <c r="BO8">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BP8">
         <v>25</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR8">
         <v>30</v>
       </c>
       <c r="BS8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT8">
         <v>5.5</v>
@@ -2710,7 +2710,7 @@
         <v>4.1</v>
       </c>
       <c r="BV8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW8">
         <v>6</v>
@@ -2725,7 +2725,7 @@
         <v>15.5</v>
       </c>
       <c r="CA8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2748,22 +2748,22 @@
         <v>130</v>
       </c>
       <c r="F9">
+        <v>1.82</v>
+      </c>
+      <c r="G9">
         <v>1.83</v>
-      </c>
-      <c r="G9">
-        <v>1.86</v>
       </c>
       <c r="H9">
         <v>4.7</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
         <v>1.37</v>
@@ -2772,46 +2772,46 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T9">
         <v>1.77</v>
       </c>
       <c r="U9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y9">
         <v>19.5</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>10.5</v>
@@ -2820,7 +2820,7 @@
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE9">
         <v>65</v>
@@ -2832,7 +2832,7 @@
         <v>10</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI9">
         <v>65</v>
@@ -2841,13 +2841,13 @@
         <v>21</v>
       </c>
       <c r="AK9">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN9">
         <v>10.5</v>
@@ -2856,61 +2856,61 @@
         <v>65</v>
       </c>
       <c r="AP9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AR9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS9">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW9">
+        <v>40</v>
+      </c>
+      <c r="AX9">
         <v>10.5</v>
-      </c>
-      <c r="AX9">
-        <v>10</v>
       </c>
       <c r="AY9">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>50</v>
       </c>
       <c r="BB9">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
         <v>15.5</v>
       </c>
       <c r="BD9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE9">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BF9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
         <v>3.05</v>
@@ -2919,55 +2919,55 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT9">
         <v>8.6</v>
       </c>
       <c r="BU9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
         <v>40</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BX9">
         <v>46</v>
       </c>
       <c r="BY9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2990,31 +2990,31 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I10">
         <v>7.2</v>
       </c>
       <c r="J10">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O10">
         <v>1.21</v>
@@ -3032,7 +3032,7 @@
         <v>2.6</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U10">
         <v>2.2</v>
@@ -3041,7 +3041,7 @@
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3053,7 +3053,7 @@
         <v>60</v>
       </c>
       <c r="AA10">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
         <v>11</v>
@@ -3065,7 +3065,7 @@
         <v>25</v>
       </c>
       <c r="AE10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
@@ -3080,7 +3080,7 @@
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK10">
         <v>15</v>
@@ -3092,13 +3092,13 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
         <v>80</v>
       </c>
       <c r="AP10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ10">
         <v>26</v>
@@ -3119,19 +3119,19 @@
         <v>23</v>
       </c>
       <c r="AW10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
         <v>18.5</v>
       </c>
       <c r="BA10">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3146,13 +3146,13 @@
         <v>36</v>
       </c>
       <c r="BF10">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG10">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BH10">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI10">
         <v>3.35</v>
@@ -3167,19 +3167,19 @@
         <v>110</v>
       </c>
       <c r="BM10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
       </c>
       <c r="BO10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP10">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BR10">
         <v>22</v>
@@ -3191,25 +3191,25 @@
         <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX10">
         <v>50</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
         <v>14</v>
       </c>
       <c r="CA10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3241,13 +3241,13 @@
         <v>7.2</v>
       </c>
       <c r="I11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>4.9</v>
       </c>
       <c r="K11">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>1.29</v>
@@ -3268,19 +3268,19 @@
         <v>1.59</v>
       </c>
       <c r="R11">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
         <v>2.5</v>
       </c>
       <c r="T11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
         <v>2.96</v>
@@ -3289,10 +3289,10 @@
         <v>29</v>
       </c>
       <c r="Y11">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="Z11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA11">
         <v>250</v>
@@ -3301,40 +3301,40 @@
         <v>12</v>
       </c>
       <c r="AC11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD11">
         <v>34</v>
       </c>
       <c r="AE11">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI11">
         <v>100</v>
       </c>
       <c r="AJ11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AL11">
         <v>36</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO11">
         <v>120</v>
@@ -3343,25 +3343,25 @@
         <v>19</v>
       </c>
       <c r="AQ11">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="AR11">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AS11">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT11">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11">
         <v>9.199999999999999</v>
       </c>
       <c r="AV11">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="AW11">
-        <v>5.1</v>
+        <v>55</v>
       </c>
       <c r="AX11">
         <v>7.8</v>
@@ -3373,25 +3373,25 @@
         <v>17</v>
       </c>
       <c r="BA11">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="BB11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC11">
         <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BE11">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>5.1</v>
+        <v>55</v>
       </c>
       <c r="BH11">
         <v>4.5</v>
@@ -3400,58 +3400,58 @@
         <v>3.55</v>
       </c>
       <c r="BJ11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
       </c>
       <c r="BO11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP11">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT11">
         <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>12.5</v>
       </c>
       <c r="CA11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,61 +3474,61 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="G12">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I12">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J12">
         <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M12">
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P12">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q12">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="R12">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="S12">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="T12">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="U12">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X12">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y12">
         <v>27</v>
@@ -3537,22 +3537,22 @@
         <v>36</v>
       </c>
       <c r="AA12">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB12">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
         <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG12">
         <v>11.5</v>
@@ -3561,10 +3561,10 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="AJ12">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK12">
         <v>17.5</v>
@@ -3573,16 +3573,16 @@
         <v>23</v>
       </c>
       <c r="AM12">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AN12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO12">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AQ12">
         <v>23</v>
@@ -3591,13 +3591,13 @@
         <v>30</v>
       </c>
       <c r="AS12">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT12">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12">
         <v>14.5</v>
@@ -3606,10 +3606,10 @@
         <v>29</v>
       </c>
       <c r="AX12">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ12">
         <v>13</v>
@@ -3618,10 +3618,10 @@
         <v>29</v>
       </c>
       <c r="BB12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD12">
         <v>20</v>
@@ -3633,49 +3633,49 @@
         <v>7</v>
       </c>
       <c r="BG12">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH12">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BJ12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP12">
         <v>13</v>
       </c>
       <c r="BQ12">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR12">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BS12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BV12">
         <v>24</v>
@@ -3684,16 +3684,16 @@
         <v>7.4</v>
       </c>
       <c r="BX12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CA12">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3716,25 +3716,25 @@
         <v>134</v>
       </c>
       <c r="F13">
+        <v>3.2</v>
+      </c>
+      <c r="G13">
         <v>3.35</v>
       </c>
-      <c r="G13">
-        <v>3.45</v>
-      </c>
       <c r="H13">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I13">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13">
         <v>1.05</v>
@@ -3749,40 +3749,40 @@
         <v>2.24</v>
       </c>
       <c r="Q13">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13">
         <v>2.94</v>
       </c>
       <c r="T13">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U13">
         <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X13">
         <v>19</v>
       </c>
       <c r="Y13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AA13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AB13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
@@ -3794,34 +3794,34 @@
         <v>23</v>
       </c>
       <c r="AF13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG13">
         <v>14</v>
       </c>
       <c r="AH13">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL13">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO13">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP13">
         <v>17</v>
@@ -3836,34 +3836,34 @@
         <v>25</v>
       </c>
       <c r="AT13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU13">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW13">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY13">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA13">
         <v>27</v>
       </c>
       <c r="BB13">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BC13">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD13">
         <v>34</v>
@@ -3872,13 +3872,13 @@
         <v>60</v>
       </c>
       <c r="BF13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG13">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI13">
         <v>3.15</v>
@@ -3887,55 +3887,55 @@
         <v>9</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BP13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BQ13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BU13">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BV13">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BW13">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ13">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,16 +3958,16 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="G14">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="H14">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I14">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J14">
         <v>3.95</v>
@@ -3982,7 +3982,7 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O14">
         <v>1.2</v>
@@ -3994,7 +3994,7 @@
         <v>1.61</v>
       </c>
       <c r="R14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
         <v>2.54</v>
@@ -4006,25 +4006,25 @@
         <v>2.64</v>
       </c>
       <c r="V14">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X14">
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC14">
         <v>9.4</v>
@@ -4036,7 +4036,7 @@
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4048,10 +4048,10 @@
         <v>38</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4060,46 +4060,46 @@
         <v>60</v>
       </c>
       <c r="AN14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
         <v>18</v>
       </c>
       <c r="AR14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX14">
         <v>14</v>
       </c>
       <c r="AY14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ14">
         <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB14">
         <v>23</v>
@@ -4111,13 +4111,13 @@
         <v>24</v>
       </c>
       <c r="BE14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF14">
         <v>9.199999999999999</v>
       </c>
       <c r="BG14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BH14">
         <v>4.5</v>
@@ -4129,55 +4129,55 @@
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM14">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN14">
         <v>5.4</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BP14">
         <v>14</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
         <v>23</v>
       </c>
       <c r="BS14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BW14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
         <v>32</v>
       </c>
       <c r="BY14">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ14">
         <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4200,19 +4200,19 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
         <v>2.92</v>
       </c>
       <c r="I15">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.1</v>
@@ -4230,13 +4230,13 @@
         <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q15">
         <v>1.52</v>
       </c>
       <c r="R15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S15">
         <v>2.28</v>
@@ -4284,7 +4284,7 @@
         <v>12</v>
       </c>
       <c r="AH15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI15">
         <v>30</v>
@@ -4296,7 +4296,7 @@
         <v>22</v>
       </c>
       <c r="AL15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM15">
         <v>50</v>
@@ -4308,7 +4308,7 @@
         <v>15.5</v>
       </c>
       <c r="AP15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ15">
         <v>18</v>
@@ -4371,55 +4371,55 @@
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL15">
         <v>65</v>
       </c>
       <c r="BM15">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN15">
         <v>6.2</v>
       </c>
       <c r="BO15">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP15">
         <v>16</v>
       </c>
       <c r="BQ15">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR15">
         <v>23</v>
       </c>
       <c r="BS15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU15">
         <v>5.2</v>
       </c>
       <c r="BV15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX15">
         <v>25</v>
       </c>
       <c r="BY15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ15">
         <v>14.5</v>
       </c>
       <c r="CA15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4442,16 +4442,16 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I16">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J16">
         <v>5.1</v>
@@ -4460,46 +4460,46 @@
         <v>5.2</v>
       </c>
       <c r="L16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="T16">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="U16">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
         <v>1.21</v>
       </c>
       <c r="W16">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y16">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Z16">
         <v>60</v>
@@ -4508,19 +4508,19 @@
         <v>140</v>
       </c>
       <c r="AB16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
         <v>13.5</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE16">
         <v>55</v>
       </c>
       <c r="AF16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4529,34 +4529,34 @@
         <v>16.5</v>
       </c>
       <c r="AI16">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AJ16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM16">
         <v>55</v>
       </c>
       <c r="AN16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AO16">
         <v>32</v>
       </c>
       <c r="AP16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AQ16">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AR16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS16">
         <v>42</v>
@@ -4583,28 +4583,28 @@
         <v>15</v>
       </c>
       <c r="BA16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB16">
         <v>16.5</v>
       </c>
       <c r="BC16">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD16">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BE16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG16">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH16">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BI16">
         <v>4.3</v>
@@ -4613,55 +4613,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK16">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BL16">
         <v>65</v>
       </c>
       <c r="BM16">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP16">
         <v>10</v>
       </c>
       <c r="BQ16">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BR16">
         <v>17.5</v>
       </c>
       <c r="BS16">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU16">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
         <v>36</v>
       </c>
       <c r="BW16">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY16">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA16">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,19 +4684,19 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G17">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
         <v>4.5</v>
@@ -4705,7 +4705,7 @@
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -4726,16 +4726,16 @@
         <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X17">
         <v>26</v>
@@ -4744,7 +4744,7 @@
         <v>26</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA17">
         <v>110</v>
@@ -4759,10 +4759,10 @@
         <v>19</v>
       </c>
       <c r="AE17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG17">
         <v>10.5</v>
@@ -4771,10 +4771,10 @@
         <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK17">
         <v>16</v>
@@ -4783,13 +4783,13 @@
         <v>26</v>
       </c>
       <c r="AM17">
-        <v>920</v>
+        <v>70</v>
       </c>
       <c r="AN17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP17">
         <v>22</v>
@@ -4816,7 +4816,7 @@
         <v>44</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY17">
         <v>9.4</v>
@@ -4831,7 +4831,7 @@
         <v>17.5</v>
       </c>
       <c r="BC17">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD17">
         <v>23</v>
@@ -4840,7 +4840,7 @@
         <v>55</v>
       </c>
       <c r="BF17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG17">
         <v>32</v>
@@ -4855,22 +4855,22 @@
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL17">
         <v>85</v>
       </c>
       <c r="BM17">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN17">
         <v>5</v>
       </c>
       <c r="BO17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP17">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ17">
         <v>5.4</v>
@@ -4879,31 +4879,31 @@
         <v>21</v>
       </c>
       <c r="BS17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT17">
         <v>9</v>
       </c>
       <c r="BU17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV17">
         <v>36</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ17">
         <v>14</v>
       </c>
       <c r="CA17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,7 +4926,7 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="G18">
         <v>6.8</v>
@@ -4935,52 +4935,52 @@
         <v>1.57</v>
       </c>
       <c r="I18">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J18">
         <v>4.3</v>
       </c>
       <c r="K18">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="Q18">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S18">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T18">
         <v>1.58</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V18">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y18">
         <v>16.5</v>
@@ -4989,7 +4989,7 @@
         <v>16</v>
       </c>
       <c r="AA18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AB18">
         <v>34</v>
@@ -5001,13 +5001,13 @@
         <v>13</v>
       </c>
       <c r="AE18">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AF18">
         <v>60</v>
       </c>
       <c r="AG18">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH18">
         <v>22</v>
@@ -5031,61 +5031,61 @@
         <v>55</v>
       </c>
       <c r="AO18">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AP18">
+        <v>21</v>
+      </c>
+      <c r="AQ18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR18">
+        <v>9.6</v>
+      </c>
+      <c r="AS18">
+        <v>12</v>
+      </c>
+      <c r="AT18">
+        <v>20</v>
+      </c>
+      <c r="AU18">
+        <v>8.6</v>
+      </c>
+      <c r="AV18">
+        <v>7.8</v>
+      </c>
+      <c r="AW18">
+        <v>11</v>
+      </c>
+      <c r="AX18">
+        <v>38</v>
+      </c>
+      <c r="AY18">
+        <v>15.5</v>
+      </c>
+      <c r="AZ18">
+        <v>13</v>
+      </c>
+      <c r="BA18">
+        <v>18.5</v>
+      </c>
+      <c r="BB18">
         <v>4.1</v>
       </c>
-      <c r="AQ18">
-        <v>3.6</v>
-      </c>
-      <c r="AR18">
-        <v>3.6</v>
-      </c>
-      <c r="AS18">
-        <v>3.7</v>
-      </c>
-      <c r="AT18">
+      <c r="BC18">
         <v>4</v>
       </c>
-      <c r="AU18">
-        <v>3.5</v>
-      </c>
-      <c r="AV18">
-        <v>3.4</v>
-      </c>
-      <c r="AW18">
-        <v>3.6</v>
-      </c>
-      <c r="AX18">
-        <v>4.3</v>
-      </c>
-      <c r="AY18">
+      <c r="BD18">
+        <v>4</v>
+      </c>
+      <c r="BE18">
+        <v>4</v>
+      </c>
+      <c r="BF18">
         <v>3.95</v>
       </c>
-      <c r="AZ18">
-        <v>3.8</v>
-      </c>
-      <c r="BA18">
-        <v>4</v>
-      </c>
-      <c r="BB18">
-        <v>4.5</v>
-      </c>
-      <c r="BC18">
-        <v>4.3</v>
-      </c>
-      <c r="BD18">
-        <v>4.3</v>
-      </c>
-      <c r="BE18">
-        <v>4.4</v>
-      </c>
-      <c r="BF18">
-        <v>4.2</v>
-      </c>
       <c r="BG18">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5171,10 +5171,10 @@
         <v>2.58</v>
       </c>
       <c r="G19">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H19">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I19">
         <v>3.3</v>
@@ -5186,7 +5186,7 @@
         <v>3.3</v>
       </c>
       <c r="L19">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M19">
         <v>1.1</v>
@@ -5198,7 +5198,7 @@
         <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
@@ -5213,19 +5213,19 @@
         <v>1.89</v>
       </c>
       <c r="U19">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V19">
         <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X19">
         <v>13</v>
       </c>
       <c r="Y19">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Z19">
         <v>23</v>
@@ -5285,7 +5285,7 @@
         <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT19">
         <v>8.199999999999999</v>
@@ -5303,31 +5303,31 @@
         <v>15</v>
       </c>
       <c r="AY19">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19">
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB19">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="BC19">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD19">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE19">
+        <v>6</v>
+      </c>
+      <c r="BF19">
         <v>5.4</v>
       </c>
-      <c r="BF19">
-        <v>4.8</v>
-      </c>
       <c r="BG19">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH19">
         <v>3.05</v>
@@ -5410,22 +5410,22 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
         <v>5.4</v>
       </c>
       <c r="I20">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K20">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L20">
         <v>1.5</v>
@@ -5434,43 +5434,43 @@
         <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P20">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q20">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R20">
         <v>1.2</v>
       </c>
       <c r="S20">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>15</v>
       </c>
       <c r="Z20">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA20">
         <v>200</v>
@@ -5494,7 +5494,7 @@
         <v>12.5</v>
       </c>
       <c r="AH20">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI20">
         <v>140</v>
@@ -5524,10 +5524,10 @@
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS20">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT20">
         <v>5.3</v>
@@ -5539,7 +5539,7 @@
         <v>19.5</v>
       </c>
       <c r="AW20">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX20">
         <v>8.4</v>
@@ -5548,10 +5548,10 @@
         <v>9</v>
       </c>
       <c r="AZ20">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BA20">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB20">
         <v>18</v>
@@ -5560,16 +5560,16 @@
         <v>21</v>
       </c>
       <c r="BD20">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BE20">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20">
         <v>16</v>
       </c>
       <c r="BG20">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5661,13 +5661,13 @@
         <v>4.2</v>
       </c>
       <c r="I21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21">
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21">
         <v>1.45</v>
@@ -5700,7 +5700,7 @@
         <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W21">
         <v>1.84</v>
@@ -5712,7 +5712,7 @@
         <v>13</v>
       </c>
       <c r="Z21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21">
         <v>130</v>
@@ -5724,7 +5724,7 @@
         <v>7.8</v>
       </c>
       <c r="AD21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE21">
         <v>90</v>
@@ -5766,10 +5766,10 @@
         <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS21">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT21">
         <v>6.2</v>
@@ -5781,7 +5781,7 @@
         <v>15.5</v>
       </c>
       <c r="AW21">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX21">
         <v>10</v>
@@ -5793,25 +5793,25 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD21">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21">
         <v>18</v>
       </c>
       <c r="BG21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH21">
         <v>2.98</v>
@@ -5835,7 +5835,7 @@
         <v>4.8</v>
       </c>
       <c r="BO21">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP21">
         <v>17.5</v>
@@ -5900,13 +5900,13 @@
         <v>5.3</v>
       </c>
       <c r="H22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I22">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>3.15</v>
@@ -5918,31 +5918,31 @@
         <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="O22">
         <v>1.7</v>
       </c>
       <c r="P22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q22">
         <v>3.15</v>
       </c>
       <c r="R22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S22">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="T22">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U22">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V22">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W22">
         <v>1.23</v>
@@ -5951,7 +5951,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="Z22">
         <v>11</v>
@@ -5975,10 +5975,10 @@
         <v>38</v>
       </c>
       <c r="AG22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH22">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AI22">
         <v>100</v>
@@ -5996,7 +5996,7 @@
         <v>390</v>
       </c>
       <c r="AN22">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AO22">
         <v>36</v>
@@ -6029,28 +6029,28 @@
         <v>24</v>
       </c>
       <c r="AY22">
-        <v>3.15</v>
+        <v>20</v>
       </c>
       <c r="AZ22">
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB22">
-        <v>3.55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC22">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="BD22">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="BE22">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="BF22">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG22">
         <v>26</v>
@@ -6059,61 +6059,61 @@
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BK22">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO22">
-        <v>1.04</v>
+        <v>1.44</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BU22">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW22">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="CB22" t="s">
         <v>148</v>
@@ -6136,28 +6136,28 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G23">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I23">
         <v>3.35</v>
       </c>
       <c r="J23">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="K23">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L23">
         <v>1.64</v>
       </c>
       <c r="M23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N23">
         <v>2.28</v>
@@ -6169,7 +6169,7 @@
         <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
         <v>1.14</v>
@@ -6178,49 +6178,49 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U23">
         <v>1.65</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y23">
         <v>8.4</v>
       </c>
       <c r="Z23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA23">
-        <v>710</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC23">
         <v>7.4</v>
       </c>
       <c r="AD23">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>350</v>
+        <v>610</v>
       </c>
       <c r="AF23">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG23">
         <v>15</v>
       </c>
       <c r="AH23">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6235,10 +6235,10 @@
         <v>1000</v>
       </c>
       <c r="AM23">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN23">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="AO23">
         <v>1000</v>
@@ -6247,10 +6247,10 @@
         <v>6.4</v>
       </c>
       <c r="AQ23">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS23">
         <v>30</v>
@@ -6259,16 +6259,16 @@
         <v>6.6</v>
       </c>
       <c r="AU23">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY23">
         <v>13</v>
@@ -6277,10 +6277,10 @@
         <v>19.5</v>
       </c>
       <c r="BA23">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB23">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC23">
         <v>27</v>
@@ -6295,7 +6295,7 @@
         <v>29</v>
       </c>
       <c r="BG23">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6378,10 +6378,10 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H24">
         <v>7.8</v>
@@ -6393,7 +6393,7 @@
         <v>4.2</v>
       </c>
       <c r="K24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>1.41</v>
@@ -6408,7 +6408,7 @@
         <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
@@ -6420,25 +6420,25 @@
         <v>3.7</v>
       </c>
       <c r="T24">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U24">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W24">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X24">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y24">
         <v>23</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA24">
         <v>1000</v>
@@ -6450,7 +6450,7 @@
         <v>9.4</v>
       </c>
       <c r="AD24">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE24">
         <v>1000</v>
@@ -6462,7 +6462,7 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI24">
         <v>1000</v>
@@ -6471,70 +6471,70 @@
         <v>14</v>
       </c>
       <c r="AK24">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL24">
         <v>60</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN24">
         <v>9.6</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP24">
         <v>12</v>
       </c>
       <c r="AQ24">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR24">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AS24">
         <v>95</v>
       </c>
       <c r="AT24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AW24">
         <v>42</v>
       </c>
       <c r="AX24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA24">
         <v>42</v>
       </c>
       <c r="BB24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD24">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BE24">
         <v>46</v>
       </c>
       <c r="BF24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24">
         <v>90</v>
@@ -6623,7 +6623,7 @@
         <v>1.78</v>
       </c>
       <c r="G25">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H25">
         <v>5.1</v>
@@ -6635,7 +6635,7 @@
         <v>3.85</v>
       </c>
       <c r="K25">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
         <v>1.37</v>
@@ -6644,7 +6644,7 @@
         <v>1.06</v>
       </c>
       <c r="N25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O25">
         <v>1.28</v>
@@ -6653,7 +6653,7 @@
         <v>2.08</v>
       </c>
       <c r="Q25">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R25">
         <v>1.42</v>
@@ -6662,10 +6662,10 @@
         <v>3.15</v>
       </c>
       <c r="T25">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V25">
         <v>1.22</v>
@@ -6674,7 +6674,7 @@
         <v>2.2</v>
       </c>
       <c r="X25">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Y25">
         <v>26</v>
@@ -6710,13 +6710,13 @@
         <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK25">
         <v>18.5</v>
       </c>
       <c r="AL25">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM25">
         <v>1000</v>
@@ -6734,7 +6734,7 @@
         <v>16.5</v>
       </c>
       <c r="AR25">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AS25">
         <v>40</v>
@@ -6743,13 +6743,13 @@
         <v>8.6</v>
       </c>
       <c r="AU25">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV25">
         <v>17.5</v>
       </c>
       <c r="AW25">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX25">
         <v>10</v>
@@ -6758,7 +6758,7 @@
         <v>9</v>
       </c>
       <c r="AZ25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA25">
         <v>42</v>
@@ -6767,13 +6767,13 @@
         <v>17</v>
       </c>
       <c r="BC25">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD25">
         <v>22</v>
       </c>
       <c r="BE25">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BF25">
         <v>9.800000000000001</v>
@@ -6865,7 +6865,7 @@
         <v>2.04</v>
       </c>
       <c r="G26">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H26">
         <v>4.2</v>
@@ -6886,13 +6886,13 @@
         <v>1.12</v>
       </c>
       <c r="N26">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O26">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P26">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q26">
         <v>2.54</v>
@@ -6901,10 +6901,10 @@
         <v>1.19</v>
       </c>
       <c r="S26">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U26">
         <v>1.73</v>
@@ -6913,7 +6913,7 @@
         <v>1.25</v>
       </c>
       <c r="W26">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X26">
         <v>10.5</v>
@@ -6970,7 +6970,7 @@
         <v>150</v>
       </c>
       <c r="AP26">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="AQ26">
         <v>10</v>
@@ -7024,7 +7024,7 @@
         <v>6.6</v>
       </c>
       <c r="BH26">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI26">
         <v>2.32</v>
@@ -7057,7 +7057,7 @@
         <v>1000</v>
       </c>
       <c r="BS26">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT26">
         <v>8</v>
@@ -7069,19 +7069,19 @@
         <v>1000</v>
       </c>
       <c r="BW26">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX26">
         <v>1000</v>
       </c>
       <c r="BY26">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ26">
         <v>1000</v>
       </c>
       <c r="CA26">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB26" t="s">
         <v>148</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 10:40:06</t>
+    <t>2026-07-22 12:47:32</t>
   </si>
 </sst>
 </file>
@@ -1054,13 +1054,13 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>5.4</v>
       </c>
       <c r="H2">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I2">
         <v>1.93</v>
@@ -1072,7 +1072,7 @@
         <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
         <v>1.11</v>
@@ -1099,7 +1099,7 @@
         <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V2">
         <v>2.06</v>
@@ -1141,7 +1141,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ2">
         <v>190</v>
@@ -1171,7 +1171,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT2">
         <v>11</v>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB2">
         <v>90</v>
@@ -1207,10 +1207,10 @@
         <v>65</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
         <v>18</v>
@@ -1219,7 +1219,7 @@
         <v>2.88</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1231,7 +1231,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
         <v>8.6</v>
@@ -1243,13 +1243,13 @@
         <v>65</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>4.3</v>
@@ -1258,7 +1258,7 @@
         <v>3.75</v>
       </c>
       <c r="BV2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
         <v>8.800000000000001</v>
@@ -1267,13 +1267,13 @@
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,16 +1296,16 @@
         <v>124</v>
       </c>
       <c r="F3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G3">
         <v>2.14</v>
       </c>
       <c r="H3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J3">
         <v>3.7</v>
@@ -1314,7 +1314,7 @@
         <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.05</v>
@@ -1326,40 +1326,40 @@
         <v>1.26</v>
       </c>
       <c r="P3">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R3">
         <v>1.47</v>
       </c>
       <c r="S3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T3">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>11.5</v>
@@ -1368,28 +1368,28 @@
         <v>8.4</v>
       </c>
       <c r="AD3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI3">
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL3">
         <v>32</v>
@@ -1404,7 +1404,7 @@
         <v>36</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
         <v>15</v>
@@ -1413,10 +1413,10 @@
         <v>25</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU3">
         <v>7.8</v>
@@ -1431,13 +1431,13 @@
         <v>13</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB3">
         <v>23</v>
@@ -1449,7 +1449,7 @@
         <v>29</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BF3">
         <v>11.5</v>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
       <c r="BH3">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI3">
         <v>3.1</v>
@@ -1467,13 +1467,13 @@
         <v>9.4</v>
       </c>
       <c r="BK3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BL3">
         <v>100</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1485,37 +1485,37 @@
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
         <v>27</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
         <v>5.6</v>
       </c>
       <c r="BV3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BW3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>36</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BZ3">
         <v>21</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,7 +1538,7 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
         <v>2.1</v>
@@ -1547,13 +1547,13 @@
         <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -1562,25 +1562,25 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
         <v>1.9</v>
@@ -1595,7 +1595,7 @@
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
         <v>32</v>
@@ -1604,22 +1604,22 @@
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1634,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1646,16 +1646,16 @@
         <v>90</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
         <v>12</v>
       </c>
       <c r="AR4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS4">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AT4">
         <v>7</v>
@@ -1664,7 +1664,7 @@
         <v>7</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
         <v>55</v>
@@ -1703,40 +1703,40 @@
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BN4">
         <v>4.6</v>
       </c>
       <c r="BO4">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP4">
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
         <v>5.6</v>
@@ -1745,19 +1745,19 @@
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1780,16 +1780,16 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
         <v>3.4</v>
@@ -1810,28 +1810,28 @@
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X5">
         <v>12.5</v>
@@ -1840,16 +1840,16 @@
         <v>12</v>
       </c>
       <c r="Z5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
         <v>14.5</v>
@@ -1858,7 +1858,7 @@
         <v>42</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
@@ -1867,10 +1867,10 @@
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>27</v>
@@ -1882,13 +1882,13 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO5">
         <v>44</v>
       </c>
       <c r="AP5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ5">
         <v>11</v>
@@ -1897,22 +1897,22 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
         <v>7</v>
       </c>
       <c r="AV5">
+        <v>13</v>
+      </c>
+      <c r="AW5">
+        <v>36</v>
+      </c>
+      <c r="AX5">
         <v>13.5</v>
-      </c>
-      <c r="AW5">
-        <v>38</v>
-      </c>
-      <c r="AX5">
-        <v>13</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
@@ -1921,7 +1921,7 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB5">
         <v>29</v>
@@ -1933,31 +1933,31 @@
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BF5">
         <v>21</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="BH5">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
@@ -1969,13 +1969,13 @@
         <v>19</v>
       </c>
       <c r="BQ5">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
@@ -1987,19 +1987,19 @@
         <v>30</v>
       </c>
       <c r="BW5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <v>44</v>
       </c>
       <c r="BY5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,10 +2022,10 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
         <v>1.49</v>
@@ -2037,70 +2037,70 @@
         <v>4.6</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T6">
         <v>2.12</v>
       </c>
       <c r="U6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V6">
         <v>3</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>15.5</v>
       </c>
       <c r="Y6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE6">
         <v>16</v>
       </c>
       <c r="AF6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AG6">
         <v>32</v>
@@ -2121,25 +2121,25 @@
         <v>130</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AN6">
         <v>190</v>
       </c>
       <c r="AO6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AP6">
         <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR6">
         <v>7.6</v>
       </c>
       <c r="AS6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>23</v>
@@ -2148,13 +2148,13 @@
         <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AY6">
         <v>28</v>
@@ -2166,25 +2166,25 @@
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BD6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BE6">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BF6">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI6">
         <v>3.2</v>
@@ -2196,7 +2196,7 @@
         <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM6">
         <v>19</v>
@@ -2208,13 +2208,13 @@
         <v>7.4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BQ6">
         <v>16.5</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS6">
         <v>16.5</v>
@@ -2232,16 +2232,16 @@
         <v>6.6</v>
       </c>
       <c r="BX6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BY6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6">
         <v>17</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2264,19 +2264,19 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G7">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H7">
         <v>4.8</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
         <v>3.8</v>
@@ -2300,7 +2300,7 @@
         <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S7">
         <v>3.85</v>
@@ -2309,7 +2309,7 @@
         <v>1.96</v>
       </c>
       <c r="U7">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
         <v>1.25</v>
@@ -2330,7 +2330,7 @@
         <v>130</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
         <v>8.199999999999999</v>
@@ -2381,7 +2381,7 @@
         <v>32</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2396,7 +2396,7 @@
         <v>60</v>
       </c>
       <c r="AX7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
@@ -2408,7 +2408,7 @@
         <v>34</v>
       </c>
       <c r="BB7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC7">
         <v>19</v>
@@ -2417,13 +2417,13 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
@@ -2435,13 +2435,13 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
@@ -2453,7 +2453,7 @@
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
         <v>30</v>
@@ -2480,7 +2480,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA7">
         <v>7.6</v>
@@ -2506,16 +2506,16 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2530,34 +2530,34 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q8">
         <v>1.59</v>
       </c>
       <c r="R8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S8">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T8">
         <v>1.56</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="V8">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W8">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X8">
         <v>24</v>
@@ -2581,13 +2581,13 @@
         <v>11.5</v>
       </c>
       <c r="AE8">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AF8">
         <v>30</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH8">
         <v>15</v>
@@ -2605,7 +2605,7 @@
         <v>36</v>
       </c>
       <c r="AM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN8">
         <v>24</v>
@@ -2620,7 +2620,7 @@
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
         <v>24</v>
@@ -2662,7 +2662,7 @@
         <v>48</v>
       </c>
       <c r="BF8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG8">
         <v>9</v>
@@ -2754,7 +2754,7 @@
         <v>1.83</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -2793,7 +2793,7 @@
         <v>1.77</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
         <v>1.25</v>
@@ -2802,10 +2802,10 @@
         <v>2.2</v>
       </c>
       <c r="X9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
         <v>38</v>
@@ -2820,25 +2820,25 @@
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH9">
         <v>18</v>
       </c>
       <c r="AI9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK9">
         <v>18</v>
@@ -2853,16 +2853,16 @@
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
         <v>17</v>
       </c>
       <c r="AR9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS9">
         <v>38</v>
@@ -2892,10 +2892,10 @@
         <v>50</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD9">
         <v>28</v>
@@ -2904,7 +2904,7 @@
         <v>36</v>
       </c>
       <c r="BF9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG9">
         <v>46</v>
@@ -2919,55 +2919,55 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BP9">
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT9">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX9">
         <v>46</v>
       </c>
       <c r="BY9">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2996,10 +2996,10 @@
         <v>1.56</v>
       </c>
       <c r="H10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -3017,46 +3017,46 @@
         <v>5.4</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
         <v>1.78</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V10">
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z10">
         <v>60</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
         <v>11</v>
@@ -3065,7 +3065,7 @@
         <v>25</v>
       </c>
       <c r="AE10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
@@ -3074,13 +3074,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI10">
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK10">
         <v>15</v>
@@ -3098,7 +3098,7 @@
         <v>80</v>
       </c>
       <c r="AP10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ10">
         <v>26</v>
@@ -3116,10 +3116,10 @@
         <v>10</v>
       </c>
       <c r="AV10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW10">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AX10">
         <v>9.6</v>
@@ -3128,10 +3128,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BB10">
         <v>13</v>
@@ -3143,31 +3143,31 @@
         <v>25</v>
       </c>
       <c r="BE10">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BF10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BH10">
         <v>4.4</v>
       </c>
       <c r="BI10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL10">
         <v>110</v>
       </c>
       <c r="BM10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN10">
         <v>4.5</v>
@@ -3179,37 +3179,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ10">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BR10">
         <v>22</v>
       </c>
       <c r="BS10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT10">
         <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV10">
         <v>55</v>
       </c>
       <c r="BW10">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BY10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3232,94 +3232,94 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G11">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M11">
         <v>1.03</v>
       </c>
       <c r="N11">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q11">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="R11">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U11">
         <v>2.06</v>
       </c>
       <c r="V11">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W11">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="X11">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y11">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z11">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA11">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AB11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE11">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
       </c>
       <c r="AG11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11">
         <v>24</v>
       </c>
       <c r="AI11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ11">
         <v>14</v>
@@ -3328,34 +3328,34 @@
         <v>16</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM11">
         <v>110</v>
       </c>
       <c r="AN11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP11">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
       </c>
       <c r="AU11">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV11">
         <v>22</v>
@@ -3364,52 +3364,52 @@
         <v>55</v>
       </c>
       <c r="AX11">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
       </c>
       <c r="BC11">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE11">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="BF11">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BH11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN11">
         <v>4.3</v>
@@ -3418,28 +3418,28 @@
         <v>3.4</v>
       </c>
       <c r="BP11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ11">
         <v>5.2</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS11">
         <v>7.8</v>
       </c>
       <c r="BT11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>1000</v>
@@ -3448,10 +3448,10 @@
         <v>10</v>
       </c>
       <c r="BZ11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,85 +3474,85 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="H12">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I12">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J12">
+        <v>4.1</v>
+      </c>
+      <c r="K12">
         <v>4.2</v>
       </c>
-      <c r="K12">
-        <v>4.4</v>
-      </c>
       <c r="L12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O12">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="Q12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="S12">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="T12">
         <v>1.48</v>
       </c>
       <c r="U12">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="X12">
+        <v>29</v>
+      </c>
+      <c r="Y12">
+        <v>23</v>
+      </c>
+      <c r="Z12">
         <v>32</v>
       </c>
-      <c r="Y12">
-        <v>27</v>
-      </c>
-      <c r="Z12">
-        <v>36</v>
-      </c>
       <c r="AA12">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB12">
+        <v>17</v>
+      </c>
+      <c r="AC12">
+        <v>10</v>
+      </c>
+      <c r="AD12">
+        <v>15</v>
+      </c>
+      <c r="AE12">
+        <v>34</v>
+      </c>
+      <c r="AF12">
         <v>17.5</v>
-      </c>
-      <c r="AC12">
-        <v>10.5</v>
-      </c>
-      <c r="AD12">
-        <v>16.5</v>
-      </c>
-      <c r="AE12">
-        <v>36</v>
-      </c>
-      <c r="AF12">
-        <v>18</v>
       </c>
       <c r="AG12">
         <v>11.5</v>
@@ -3561,52 +3561,52 @@
         <v>14</v>
       </c>
       <c r="AI12">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM12">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AN12">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AO12">
         <v>20</v>
       </c>
       <c r="AP12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ12">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AR12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS12">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
         <v>29</v>
       </c>
       <c r="AX12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3615,28 +3615,28 @@
         <v>13</v>
       </c>
       <c r="BA12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC12">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BD12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE12">
         <v>38</v>
       </c>
       <c r="BF12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH12">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI12">
         <v>3.95</v>
@@ -3645,55 +3645,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN12">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO12">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP12">
         <v>13</v>
       </c>
       <c r="BQ12">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12">
         <v>21</v>
       </c>
       <c r="BS12">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV12">
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX12">
         <v>28</v>
       </c>
       <c r="BY12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12">
         <v>13</v>
       </c>
       <c r="CA12">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3716,22 +3716,22 @@
         <v>134</v>
       </c>
       <c r="F13">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I13">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="J13">
         <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L13">
         <v>1.35</v>
@@ -3746,10 +3746,10 @@
         <v>1.25</v>
       </c>
       <c r="P13">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q13">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R13">
         <v>1.5</v>
@@ -3761,13 +3761,13 @@
         <v>1.64</v>
       </c>
       <c r="U13">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V13">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>19</v>
@@ -3779,10 +3779,10 @@
         <v>16.5</v>
       </c>
       <c r="AA13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC13">
         <v>8.4</v>
@@ -3791,7 +3791,7 @@
         <v>11.5</v>
       </c>
       <c r="AE13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF13">
         <v>24</v>
@@ -3821,31 +3821,31 @@
         <v>26</v>
       </c>
       <c r="AO13">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP13">
         <v>17</v>
       </c>
       <c r="AQ13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT13">
         <v>14</v>
       </c>
       <c r="AU13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW13">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AX13">
         <v>21</v>
@@ -3857,13 +3857,13 @@
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD13">
         <v>34</v>
@@ -3872,70 +3872,70 @@
         <v>60</v>
       </c>
       <c r="BF13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH13">
         <v>3.9</v>
       </c>
       <c r="BI13">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13">
         <v>9</v>
       </c>
       <c r="BK13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL13">
         <v>90</v>
       </c>
       <c r="BM13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN13">
         <v>6.6</v>
       </c>
       <c r="BO13">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BP13">
         <v>23</v>
       </c>
       <c r="BQ13">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT13">
         <v>5.5</v>
       </c>
       <c r="BU13">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BV13">
         <v>16</v>
       </c>
       <c r="BW13">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY13">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA13">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,19 +3958,19 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H14">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I14">
         <v>3.6</v>
       </c>
       <c r="J14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -3988,7 +3988,7 @@
         <v>1.2</v>
       </c>
       <c r="P14">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="Q14">
         <v>1.61</v>
@@ -3997,25 +3997,25 @@
         <v>1.62</v>
       </c>
       <c r="S14">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T14">
         <v>1.56</v>
       </c>
       <c r="U14">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X14">
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z14">
         <v>29</v>
@@ -4030,19 +4030,19 @@
         <v>9.4</v>
       </c>
       <c r="AD14">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE14">
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI14">
         <v>38</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="AK14">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4060,10 +4060,10 @@
         <v>60</v>
       </c>
       <c r="AN14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP14">
         <v>21</v>
@@ -4075,13 +4075,13 @@
         <v>26</v>
       </c>
       <c r="AS14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV14">
         <v>13.5</v>
@@ -4111,13 +4111,13 @@
         <v>24</v>
       </c>
       <c r="BE14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF14">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH14">
         <v>4.5</v>
@@ -4129,55 +4129,55 @@
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL14">
         <v>80</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BN14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BP14">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR14">
         <v>23</v>
       </c>
       <c r="BS14">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT14">
         <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV14">
         <v>25</v>
       </c>
       <c r="BW14">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX14">
         <v>32</v>
       </c>
       <c r="BY14">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ14">
         <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4203,16 +4203,16 @@
         <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H15">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
         <v>4.1</v>
@@ -4224,22 +4224,22 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T15">
         <v>1.48</v>
@@ -4248,10 +4248,10 @@
         <v>2.96</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X15">
         <v>29</v>
@@ -4296,7 +4296,7 @@
         <v>22</v>
       </c>
       <c r="AL15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM15">
         <v>50</v>
@@ -4308,7 +4308,7 @@
         <v>15.5</v>
       </c>
       <c r="AP15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ15">
         <v>18</v>
@@ -4317,7 +4317,7 @@
         <v>23</v>
       </c>
       <c r="AS15">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT15">
         <v>16</v>
@@ -4326,7 +4326,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW15">
         <v>23</v>
@@ -4353,13 +4353,13 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF15">
         <v>10</v>
       </c>
       <c r="BG15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH15">
         <v>4.9</v>
@@ -4371,13 +4371,13 @@
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL15">
         <v>65</v>
       </c>
       <c r="BM15">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN15">
         <v>6.2</v>
@@ -4395,28 +4395,28 @@
         <v>23</v>
       </c>
       <c r="BS15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT15">
         <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BV15">
         <v>19</v>
       </c>
       <c r="BW15">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX15">
         <v>25</v>
       </c>
       <c r="BY15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA15">
         <v>6.2</v>
@@ -4442,100 +4442,100 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G16">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H16">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I16">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5.2</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16">
         <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q16">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S16">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="T16">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W16">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X16">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y16">
         <v>36</v>
       </c>
       <c r="Z16">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA16">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG16">
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI16">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ16">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AK16">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL16">
         <v>21</v>
@@ -4547,16 +4547,16 @@
         <v>4.8</v>
       </c>
       <c r="AO16">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AQ16">
         <v>30</v>
       </c>
       <c r="AR16">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS16">
         <v>42</v>
@@ -4568,100 +4568,100 @@
         <v>12</v>
       </c>
       <c r="AV16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX16">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY16">
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB16">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC16">
         <v>13</v>
       </c>
       <c r="BD16">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BE16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF16">
         <v>4.5</v>
       </c>
       <c r="BG16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BH16">
         <v>5.7</v>
       </c>
       <c r="BI16">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK16">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM16">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN16">
         <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BP16">
         <v>10</v>
       </c>
       <c r="BQ16">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BR16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU16">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BV16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW16">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ16">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,22 +4684,22 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G17">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H17">
+        <v>4.7</v>
+      </c>
+      <c r="I17">
         <v>4.9</v>
-      </c>
-      <c r="I17">
-        <v>5.1</v>
       </c>
       <c r="J17">
         <v>4.4</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4714,40 +4714,40 @@
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S17">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
         <v>1.62</v>
       </c>
       <c r="U17">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
         <v>13</v>
@@ -4759,37 +4759,37 @@
         <v>19</v>
       </c>
       <c r="AE17">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF17">
         <v>13</v>
       </c>
       <c r="AG17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH17">
         <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AJ17">
         <v>19</v>
       </c>
       <c r="AK17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL17">
         <v>26</v>
       </c>
       <c r="AM17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN17">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP17">
         <v>22</v>
@@ -4798,16 +4798,16 @@
         <v>23</v>
       </c>
       <c r="AR17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS17">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT17">
         <v>12</v>
       </c>
       <c r="AU17">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17">
         <v>17.5</v>
@@ -4816,13 +4816,13 @@
         <v>44</v>
       </c>
       <c r="AX17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY17">
         <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA17">
         <v>42</v>
@@ -4831,7 +4831,7 @@
         <v>17.5</v>
       </c>
       <c r="BC17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD17">
         <v>23</v>
@@ -4840,10 +4840,10 @@
         <v>55</v>
       </c>
       <c r="BF17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH17">
         <v>4.7</v>
@@ -4861,7 +4861,7 @@
         <v>85</v>
       </c>
       <c r="BM17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN17">
         <v>5</v>
@@ -4870,7 +4870,7 @@
         <v>3.85</v>
       </c>
       <c r="BP17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ17">
         <v>5.4</v>
@@ -4879,7 +4879,7 @@
         <v>21</v>
       </c>
       <c r="BS17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT17">
         <v>9</v>
@@ -4888,22 +4888,22 @@
         <v>4.8</v>
       </c>
       <c r="BV17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW17">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX17">
         <v>38</v>
       </c>
       <c r="BY17">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ17">
         <v>14</v>
       </c>
       <c r="CA17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,7 +4926,7 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G18">
         <v>6.8</v>
@@ -4944,7 +4944,7 @@
         <v>5.2</v>
       </c>
       <c r="L18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
         <v>1.01</v>
@@ -4962,10 +4962,10 @@
         <v>1.49</v>
       </c>
       <c r="R18">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="S18">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T18">
         <v>1.58</v>
@@ -5037,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AQ18">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR18">
         <v>9.6</v>
@@ -5067,7 +5067,7 @@
         <v>13</v>
       </c>
       <c r="BA18">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB18">
         <v>4.1</v>
@@ -5168,7 +5168,7 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G19">
         <v>2.8</v>
@@ -5228,7 +5228,7 @@
         <v>11</v>
       </c>
       <c r="Z19">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA19">
         <v>55</v>
@@ -5237,7 +5237,7 @@
         <v>11.5</v>
       </c>
       <c r="AC19">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD19">
         <v>17</v>
@@ -5285,7 +5285,7 @@
         <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT19">
         <v>8.199999999999999</v>
@@ -5309,25 +5309,25 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB19">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BC19">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD19">
+        <v>6</v>
+      </c>
+      <c r="BE19">
+        <v>6.4</v>
+      </c>
+      <c r="BF19">
         <v>5.7</v>
       </c>
-      <c r="BE19">
-        <v>6</v>
-      </c>
-      <c r="BF19">
-        <v>5.4</v>
-      </c>
       <c r="BG19">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="BH19">
         <v>3.05</v>
@@ -5410,10 +5410,10 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H20">
         <v>5.4</v>
@@ -5422,10 +5422,10 @@
         <v>6.6</v>
       </c>
       <c r="J20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K20">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
         <v>1.5</v>
@@ -5434,34 +5434,34 @@
         <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O20">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q20">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S20">
         <v>5.1</v>
       </c>
       <c r="T20">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U20">
         <v>1.67</v>
       </c>
       <c r="V20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -5473,25 +5473,25 @@
         <v>48</v>
       </c>
       <c r="AA20">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AB20">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC20">
         <v>8.6</v>
       </c>
       <c r="AD20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE20">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AF20">
         <v>10</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
         <v>30</v>
@@ -5512,25 +5512,25 @@
         <v>260</v>
       </c>
       <c r="AN20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO20">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AP20">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AQ20">
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT20">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU20">
         <v>7</v>
@@ -5539,10 +5539,10 @@
         <v>19.5</v>
       </c>
       <c r="AW20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX20">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY20">
         <v>9</v>
@@ -5551,7 +5551,7 @@
         <v>7</v>
       </c>
       <c r="BA20">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20">
         <v>18</v>
@@ -5560,16 +5560,16 @@
         <v>21</v>
       </c>
       <c r="BD20">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE20">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF20">
         <v>16</v>
       </c>
       <c r="BG20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5667,7 +5667,7 @@
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L21">
         <v>1.45</v>
@@ -5700,7 +5700,7 @@
         <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
         <v>1.84</v>
@@ -5900,7 +5900,7 @@
         <v>5.3</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I22">
         <v>2.12</v>
@@ -5918,7 +5918,7 @@
         <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="O22">
         <v>1.7</v>
@@ -5927,7 +5927,7 @@
         <v>1.42</v>
       </c>
       <c r="Q22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
         <v>1.13</v>
@@ -5942,7 +5942,7 @@
         <v>1.57</v>
       </c>
       <c r="V22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W22">
         <v>1.23</v>
@@ -5951,34 +5951,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y22">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z22">
+        <v>10.5</v>
+      </c>
+      <c r="AA22">
+        <v>27</v>
+      </c>
+      <c r="AB22">
         <v>11</v>
       </c>
-      <c r="AA22">
-        <v>28</v>
-      </c>
-      <c r="AB22">
-        <v>13</v>
-      </c>
       <c r="AC22">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD22">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE22">
+        <v>48</v>
+      </c>
+      <c r="AF22">
         <v>36</v>
-      </c>
-      <c r="AF22">
-        <v>38</v>
       </c>
       <c r="AG22">
         <v>24</v>
       </c>
       <c r="AH22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI22">
         <v>100</v>
@@ -5999,22 +5999,22 @@
         <v>250</v>
       </c>
       <c r="AO22">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR22">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS22">
         <v>19.5</v>
       </c>
       <c r="AT22">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
         <v>6.6</v>
@@ -6035,25 +6035,25 @@
         <v>21</v>
       </c>
       <c r="BA22">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB22">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BC22">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD22">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BF22">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BG22">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6139,10 +6139,10 @@
         <v>2.78</v>
       </c>
       <c r="G23">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H23">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I23">
         <v>3.35</v>
@@ -6151,22 +6151,22 @@
         <v>2.86</v>
       </c>
       <c r="K23">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L23">
         <v>1.64</v>
       </c>
       <c r="M23">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N23">
         <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6178,7 +6178,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U23">
         <v>1.65</v>
@@ -6190,37 +6190,37 @@
         <v>1.53</v>
       </c>
       <c r="X23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y23">
         <v>8.4</v>
       </c>
       <c r="Z23">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA23">
         <v>1000</v>
       </c>
       <c r="AB23">
+        <v>7.4</v>
+      </c>
+      <c r="AC23">
         <v>7.2</v>
-      </c>
-      <c r="AC23">
-        <v>7.4</v>
       </c>
       <c r="AD23">
         <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>610</v>
+        <v>710</v>
       </c>
       <c r="AF23">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
         <v>15</v>
       </c>
       <c r="AH23">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AI23">
         <v>1000</v>
@@ -6229,7 +6229,7 @@
         <v>140</v>
       </c>
       <c r="AK23">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AL23">
         <v>1000</v>
@@ -6238,7 +6238,7 @@
         <v>310</v>
       </c>
       <c r="AN23">
-        <v>510</v>
+        <v>580</v>
       </c>
       <c r="AO23">
         <v>1000</v>
@@ -6253,7 +6253,7 @@
         <v>14</v>
       </c>
       <c r="AS23">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT23">
         <v>6.6</v>
@@ -6265,7 +6265,7 @@
         <v>14</v>
       </c>
       <c r="AW23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX23">
         <v>14</v>
@@ -6274,13 +6274,13 @@
         <v>13</v>
       </c>
       <c r="AZ23">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA23">
         <v>40</v>
       </c>
       <c r="BB23">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC23">
         <v>27</v>
@@ -6301,22 +6301,22 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BJ23">
         <v>17.5</v>
       </c>
       <c r="BK23">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BN23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO23">
         <v>3.8</v>
@@ -6325,13 +6325,13 @@
         <v>40</v>
       </c>
       <c r="BQ23">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BT23">
         <v>8.199999999999999</v>
@@ -6349,13 +6349,13 @@
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6408,7 +6408,7 @@
         <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
@@ -6420,10 +6420,10 @@
         <v>3.7</v>
       </c>
       <c r="T24">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U24">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V24">
         <v>1.14</v>
@@ -6474,7 +6474,7 @@
         <v>17.5</v>
       </c>
       <c r="AL24">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AM24">
         <v>180</v>
@@ -6620,7 +6620,7 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G25">
         <v>1.83</v>
@@ -6632,10 +6632,10 @@
         <v>5.5</v>
       </c>
       <c r="J25">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>1.37</v>
@@ -6650,7 +6650,7 @@
         <v>1.28</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q25">
         <v>1.88</v>
@@ -6659,7 +6659,7 @@
         <v>1.42</v>
       </c>
       <c r="S25">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T25">
         <v>1.8</v>
@@ -6862,22 +6862,22 @@
         <v>147</v>
       </c>
       <c r="F26">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H26">
         <v>4.2</v>
       </c>
       <c r="I26">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -6889,10 +6889,10 @@
         <v>2.62</v>
       </c>
       <c r="O26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P26">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q26">
         <v>2.54</v>
@@ -6901,7 +6901,7 @@
         <v>1.19</v>
       </c>
       <c r="S26">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T26">
         <v>2.14</v>
@@ -6910,16 +6910,16 @@
         <v>1.73</v>
       </c>
       <c r="V26">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W26">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X26">
         <v>10.5</v>
       </c>
       <c r="Y26">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z26">
         <v>34</v>
@@ -6946,7 +6946,7 @@
         <v>12</v>
       </c>
       <c r="AH26">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI26">
         <v>120</v>
@@ -6976,10 +6976,10 @@
         <v>10</v>
       </c>
       <c r="AR26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS26">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT26">
         <v>5.9</v>
@@ -6991,7 +6991,7 @@
         <v>16.5</v>
       </c>
       <c r="AW26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX26">
         <v>9.800000000000001</v>
@@ -7003,25 +7003,25 @@
         <v>20</v>
       </c>
       <c r="BA26">
+        <v>6.8</v>
+      </c>
+      <c r="BB26">
+        <v>5.7</v>
+      </c>
+      <c r="BC26">
+        <v>5.8</v>
+      </c>
+      <c r="BD26">
         <v>6.4</v>
       </c>
-      <c r="BB26">
-        <v>5.5</v>
-      </c>
-      <c r="BC26">
-        <v>5.6</v>
-      </c>
-      <c r="BD26">
-        <v>6.2</v>
-      </c>
       <c r="BE26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF26">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG26">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH26">
         <v>2.82</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 12:47:32</t>
+    <t>2026-07-22 14:55:41</t>
   </si>
 </sst>
 </file>
@@ -1054,22 +1054,22 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G2">
         <v>5.4</v>
       </c>
       <c r="H2">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I2">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.53</v>
@@ -1093,16 +1093,16 @@
         <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
         <v>1.72</v>
       </c>
       <c r="V2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="W2">
         <v>1.22</v>
@@ -1117,7 +1117,7 @@
         <v>11</v>
       </c>
       <c r="AA2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB2">
         <v>13.5</v>
@@ -1129,7 +1129,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF2">
         <v>40</v>
@@ -1144,7 +1144,7 @@
         <v>70</v>
       </c>
       <c r="AJ2">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AK2">
         <v>120</v>
@@ -1156,13 +1156,13 @@
         <v>240</v>
       </c>
       <c r="AN2">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AO2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
         <v>5.4</v>
@@ -1171,7 +1171,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AT2">
         <v>11</v>
@@ -1183,7 +1183,7 @@
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX2">
         <v>30</v>
@@ -1201,79 +1201,79 @@
         <v>90</v>
       </c>
       <c r="BC2">
+        <v>50</v>
+      </c>
+      <c r="BD2">
         <v>55</v>
       </c>
-      <c r="BD2">
-        <v>65</v>
-      </c>
       <c r="BE2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>48</v>
       </c>
       <c r="BG2">
         <v>18</v>
       </c>
       <c r="BH2">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BP2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU2">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="BV2">
         <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BX2">
         <v>38</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>38</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1299,13 +1299,13 @@
         <v>2.12</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H3">
         <v>3.75</v>
       </c>
       <c r="I3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
         <v>3.7</v>
@@ -1320,49 +1320,49 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O3">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q3">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R3">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T3">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3">
         <v>8.4</v>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1380,7 +1380,7 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3">
         <v>46</v>
@@ -1395,19 +1395,19 @@
         <v>32</v>
       </c>
       <c r="AM3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AP3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR3">
         <v>25</v>
@@ -1419,7 +1419,7 @@
         <v>11</v>
       </c>
       <c r="AU3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3">
         <v>14</v>
@@ -1428,13 +1428,13 @@
         <v>34</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA3">
         <v>40</v>
@@ -1446,76 +1446,76 @@
         <v>18.5</v>
       </c>
       <c r="BD3">
+        <v>28</v>
+      </c>
+      <c r="BE3">
+        <v>55</v>
+      </c>
+      <c r="BF3">
+        <v>11</v>
+      </c>
+      <c r="BG3">
         <v>29</v>
-      </c>
-      <c r="BE3">
-        <v>36</v>
-      </c>
-      <c r="BF3">
-        <v>11.5</v>
-      </c>
-      <c r="BG3">
-        <v>30</v>
       </c>
       <c r="BH3">
         <v>3.85</v>
       </c>
       <c r="BI3">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK3">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BL3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO3">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
+        <v>26</v>
+      </c>
+      <c r="BS3">
+        <v>10</v>
+      </c>
+      <c r="BT3">
+        <v>7</v>
+      </c>
+      <c r="BU3">
+        <v>6.4</v>
+      </c>
+      <c r="BV3">
         <v>27</v>
       </c>
-      <c r="BS3">
-        <v>8.4</v>
-      </c>
-      <c r="BT3">
-        <v>7.2</v>
-      </c>
-      <c r="BU3">
-        <v>5.6</v>
-      </c>
-      <c r="BV3">
-        <v>28</v>
-      </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>36</v>
       </c>
       <c r="BY3">
+        <v>11</v>
+      </c>
+      <c r="BZ3">
+        <v>20</v>
+      </c>
+      <c r="CA3">
         <v>9</v>
-      </c>
-      <c r="BZ3">
-        <v>21</v>
-      </c>
-      <c r="CA3">
-        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1541,7 +1541,7 @@
         <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H4">
         <v>4.4</v>
@@ -1571,7 +1571,7 @@
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
         <v>1.25</v>
@@ -1586,10 +1586,10 @@
         <v>1.9</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X4">
         <v>10.5</v>
@@ -1607,7 +1607,7 @@
         <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
         <v>18</v>
@@ -1619,7 +1619,7 @@
         <v>11</v>
       </c>
       <c r="AG4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
         <v>22</v>
@@ -1655,13 +1655,13 @@
         <v>28</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT4">
         <v>7</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>17</v>
@@ -1694,7 +1694,7 @@
         <v>44</v>
       </c>
       <c r="BF4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG4">
         <v>75</v>
@@ -1703,7 +1703,7 @@
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -1712,16 +1712,16 @@
         <v>6.8</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BM4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
         <v>16</v>
@@ -1736,19 +1736,19 @@
         <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU4">
         <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW4">
         <v>13</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY4">
         <v>14.5</v>
@@ -1780,13 +1780,13 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I5">
         <v>3.35</v>
@@ -1810,7 +1810,7 @@
         <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q5">
         <v>2.12</v>
@@ -1819,7 +1819,7 @@
         <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T5">
         <v>1.86</v>
@@ -1831,7 +1831,7 @@
         <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X5">
         <v>12.5</v>
@@ -1849,7 +1849,7 @@
         <v>9.6</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD5">
         <v>14.5</v>
@@ -1876,13 +1876,13 @@
         <v>27</v>
       </c>
       <c r="AL5">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO5">
         <v>44</v>
@@ -1897,13 +1897,13 @@
         <v>20</v>
       </c>
       <c r="AS5">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AT5">
         <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV5">
         <v>13</v>
@@ -1912,7 +1912,7 @@
         <v>36</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
@@ -1933,7 +1933,7 @@
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="BF5">
         <v>21</v>
@@ -1942,64 +1942,64 @@
         <v>32</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BW5">
         <v>10.5</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,25 +2022,25 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="I6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2052,16 +2052,16 @@
         <v>1.3</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
         <v>1.41</v>
       </c>
       <c r="S6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T6">
         <v>2.12</v>
@@ -2070,19 +2070,19 @@
         <v>1.87</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="W6">
         <v>1.12</v>
       </c>
       <c r="X6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA6">
         <v>12.5</v>
@@ -2094,13 +2094,13 @@
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6">
         <v>16</v>
       </c>
       <c r="AF6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG6">
         <v>32</v>
@@ -2115,7 +2115,7 @@
         <v>300</v>
       </c>
       <c r="AK6">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AL6">
         <v>130</v>
@@ -2124,7 +2124,7 @@
         <v>210</v>
       </c>
       <c r="AN6">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AO6">
         <v>7.6</v>
@@ -2139,25 +2139,25 @@
         <v>7.6</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU6">
         <v>9.6</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AY6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ6">
         <v>24</v>
@@ -2166,10 +2166,10 @@
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC6">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="BD6">
         <v>25</v>
@@ -2178,16 +2178,16 @@
         <v>26</v>
       </c>
       <c r="BF6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH6">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
         <v>11.5</v>
@@ -2196,10 +2196,10 @@
         <v>7.4</v>
       </c>
       <c r="BL6">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="BM6">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
@@ -2211,37 +2211,37 @@
         <v>80</v>
       </c>
       <c r="BQ6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BR6">
         <v>80</v>
       </c>
       <c r="BS6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BT6">
         <v>3.85</v>
       </c>
       <c r="BU6">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BV6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY6">
         <v>12</v>
       </c>
       <c r="BZ6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2264,22 +2264,22 @@
         <v>128</v>
       </c>
       <c r="F7">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="G7">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
+        <v>3.7</v>
+      </c>
+      <c r="K7">
         <v>3.75</v>
-      </c>
-      <c r="K7">
-        <v>3.8</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2288,7 +2288,7 @@
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O7">
         <v>1.37</v>
@@ -2303,7 +2303,7 @@
         <v>1.33</v>
       </c>
       <c r="S7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
         <v>1.96</v>
@@ -2315,22 +2315,22 @@
         <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X7">
         <v>13</v>
       </c>
       <c r="Y7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AA7">
         <v>130</v>
       </c>
       <c r="AB7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>8.199999999999999</v>
@@ -2357,7 +2357,7 @@
         <v>21</v>
       </c>
       <c r="AK7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2378,7 +2378,7 @@
         <v>13.5</v>
       </c>
       <c r="AR7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS7">
         <v>14.5</v>
@@ -2393,19 +2393,19 @@
         <v>17.5</v>
       </c>
       <c r="AW7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7">
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BB7">
         <v>18.5</v>
@@ -2423,7 +2423,7 @@
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
@@ -2435,13 +2435,13 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
@@ -2453,28 +2453,28 @@
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR7">
         <v>30</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT7">
         <v>8.6</v>
       </c>
       <c r="BU7">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV7">
         <v>46</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY7">
         <v>8.800000000000001</v>
@@ -2483,7 +2483,7 @@
         <v>27</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
         <v>148</v>
@@ -2506,13 +2506,13 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G8">
         <v>3.6</v>
       </c>
       <c r="H8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I8">
         <v>2.12</v>
@@ -2524,76 +2524,76 @@
         <v>4.2</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
+        <v>1.63</v>
+      </c>
+      <c r="R8">
+        <v>1.62</v>
+      </c>
+      <c r="S8">
+        <v>2.56</v>
+      </c>
+      <c r="T8">
         <v>1.59</v>
       </c>
-      <c r="R8">
-        <v>1.67</v>
-      </c>
-      <c r="S8">
-        <v>2.42</v>
-      </c>
-      <c r="T8">
-        <v>1.56</v>
-      </c>
       <c r="U8">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="V8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W8">
         <v>1.38</v>
       </c>
       <c r="X8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA8">
         <v>26</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG8">
         <v>15</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ8">
         <v>65</v>
@@ -2602,22 +2602,22 @@
         <v>36</v>
       </c>
       <c r="AL8">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AP8">
         <v>21</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
         <v>14.5</v>
@@ -2626,10 +2626,10 @@
         <v>24</v>
       </c>
       <c r="AT8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>17</v>
       </c>
       <c r="AX8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY8">
         <v>14</v>
@@ -2647,85 +2647,85 @@
         <v>13.5</v>
       </c>
       <c r="BA8">
+        <v>24</v>
+      </c>
+      <c r="BB8">
+        <v>55</v>
+      </c>
+      <c r="BC8">
+        <v>32</v>
+      </c>
+      <c r="BD8">
+        <v>34</v>
+      </c>
+      <c r="BE8">
+        <v>50</v>
+      </c>
+      <c r="BF8">
         <v>23</v>
       </c>
-      <c r="BB8">
-        <v>32</v>
-      </c>
-      <c r="BC8">
-        <v>30</v>
-      </c>
-      <c r="BD8">
-        <v>32</v>
-      </c>
-      <c r="BE8">
-        <v>48</v>
-      </c>
-      <c r="BF8">
-        <v>20</v>
-      </c>
       <c r="BG8">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BI8">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BJ8">
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BM8">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BN8">
+        <v>7.2</v>
+      </c>
+      <c r="BO8">
+        <v>6.4</v>
+      </c>
+      <c r="BP8">
+        <v>26</v>
+      </c>
+      <c r="BQ8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR8">
+        <v>32</v>
+      </c>
+      <c r="BS8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT8">
+        <v>5.2</v>
+      </c>
+      <c r="BU8">
+        <v>4.8</v>
+      </c>
+      <c r="BV8">
+        <v>14.5</v>
+      </c>
+      <c r="BW8">
+        <v>7.2</v>
+      </c>
+      <c r="BX8">
+        <v>23</v>
+      </c>
+      <c r="BY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ8">
+        <v>16.5</v>
+      </c>
+      <c r="CA8">
         <v>7.6</v>
-      </c>
-      <c r="BO8">
-        <v>6.2</v>
-      </c>
-      <c r="BP8">
-        <v>25</v>
-      </c>
-      <c r="BQ8">
-        <v>7.4</v>
-      </c>
-      <c r="BR8">
-        <v>30</v>
-      </c>
-      <c r="BS8">
-        <v>7.8</v>
-      </c>
-      <c r="BT8">
-        <v>5.5</v>
-      </c>
-      <c r="BU8">
-        <v>4.1</v>
-      </c>
-      <c r="BV8">
-        <v>13.5</v>
-      </c>
-      <c r="BW8">
-        <v>6</v>
-      </c>
-      <c r="BX8">
-        <v>22</v>
-      </c>
-      <c r="BY8">
-        <v>7.2</v>
-      </c>
-      <c r="BZ8">
-        <v>15.5</v>
-      </c>
-      <c r="CA8">
-        <v>6.2</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2748,13 +2748,13 @@
         <v>130</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
         <v>4.9</v>
@@ -2781,7 +2781,7 @@
         <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>1.46</v>
@@ -2790,16 +2790,16 @@
         <v>3.05</v>
       </c>
       <c r="T9">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X9">
         <v>17.5</v>
@@ -2814,7 +2814,7 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2826,7 +2826,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>9.6</v>
@@ -2877,16 +2877,16 @@
         <v>17</v>
       </c>
       <c r="AW9">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY9">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
         <v>50</v>
@@ -2907,67 +2907,67 @@
         <v>9.6</v>
       </c>
       <c r="BG9">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="BH9">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ9">
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM9">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ9">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT9">
         <v>8</v>
       </c>
-      <c r="BT9">
-        <v>8.4</v>
-      </c>
       <c r="BU9">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BV9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW9">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX9">
         <v>46</v>
       </c>
       <c r="BY9">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2990,22 +2990,22 @@
         <v>131</v>
       </c>
       <c r="F10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H10">
         <v>6.6</v>
       </c>
       <c r="I10">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
         <v>4.7</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3014,13 +3014,13 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q10">
         <v>1.65</v>
@@ -3029,25 +3029,25 @@
         <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
         <v>1.78</v>
       </c>
       <c r="U10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X10">
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z10">
         <v>60</v>
@@ -3062,10 +3062,10 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>10.5</v>
@@ -3074,7 +3074,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI10">
         <v>75</v>
@@ -3083,16 +3083,16 @@
         <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL10">
         <v>29</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO10">
         <v>80</v>
@@ -3149,67 +3149,67 @@
         <v>6</v>
       </c>
       <c r="BG10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH10">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="BJ10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BL10">
         <v>110</v>
       </c>
       <c r="BM10">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BN10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="BP10">
+        <v>9.4</v>
+      </c>
+      <c r="BQ10">
+        <v>7.2</v>
+      </c>
+      <c r="BR10">
+        <v>23</v>
+      </c>
+      <c r="BS10">
+        <v>10</v>
+      </c>
+      <c r="BT10">
         <v>9.800000000000001</v>
       </c>
-      <c r="BQ10">
-        <v>4.9</v>
-      </c>
-      <c r="BR10">
-        <v>22</v>
-      </c>
-      <c r="BS10">
-        <v>6.8</v>
-      </c>
-      <c r="BT10">
-        <v>10.5</v>
-      </c>
       <c r="BU10">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW10">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BX10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY10">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10">
         <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="s">
         <v>148</v>
@@ -3232,13 +3232,13 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G11">
         <v>1.54</v>
       </c>
       <c r="H11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>7.8</v>
@@ -3247,34 +3247,34 @@
         <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>1.3</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
         <v>5.3</v>
       </c>
       <c r="O11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q11">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
         <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T11">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U11">
         <v>2.06</v>
@@ -3283,10 +3283,10 @@
         <v>1.16</v>
       </c>
       <c r="W11">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X11">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y11">
         <v>38</v>
@@ -3295,7 +3295,7 @@
         <v>80</v>
       </c>
       <c r="AA11">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AB11">
         <v>11</v>
@@ -3307,7 +3307,7 @@
         <v>30</v>
       </c>
       <c r="AE11">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AF11">
         <v>10.5</v>
@@ -3331,25 +3331,25 @@
         <v>38</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AN11">
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP11">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AQ11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR11">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AS11">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
@@ -3373,7 +3373,7 @@
         <v>18.5</v>
       </c>
       <c r="BA11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
@@ -3385,73 +3385,73 @@
         <v>23</v>
       </c>
       <c r="BE11">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG11">
         <v>50</v>
       </c>
       <c r="BH11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO11">
         <v>3.4</v>
       </c>
       <c r="BP11">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ11">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR11">
         <v>22</v>
       </c>
       <c r="BS11">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BT11">
         <v>11</v>
       </c>
       <c r="BU11">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA11">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,22 +3474,22 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J12">
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3510,43 +3510,43 @@
         <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S12">
         <v>2.24</v>
       </c>
       <c r="T12">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U12">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W12">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X12">
         <v>29</v>
       </c>
       <c r="Y12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12">
         <v>65</v>
       </c>
       <c r="AB12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE12">
         <v>34</v>
@@ -3555,7 +3555,7 @@
         <v>17.5</v>
       </c>
       <c r="AG12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12">
         <v>14</v>
@@ -3564,7 +3564,7 @@
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK12">
         <v>18</v>
@@ -3576,10 +3576,10 @@
         <v>46</v>
       </c>
       <c r="AN12">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP12">
         <v>27</v>
@@ -3588,25 +3588,25 @@
         <v>20</v>
       </c>
       <c r="AR12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT12">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU12">
         <v>9.6</v>
       </c>
       <c r="AV12">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3618,82 +3618,82 @@
         <v>30</v>
       </c>
       <c r="BB12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD12">
         <v>22</v>
       </c>
       <c r="BE12">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BF12">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG12">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH12">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BI12">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BJ12">
         <v>8.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BL12">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BP12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BR12">
         <v>21</v>
       </c>
       <c r="BS12">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT12">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV12">
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX12">
         <v>28</v>
       </c>
       <c r="BY12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA12">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3722,7 +3722,7 @@
         <v>3.25</v>
       </c>
       <c r="H13">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I13">
         <v>2.4</v>
@@ -3731,7 +3731,7 @@
         <v>3.7</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.35</v>
@@ -3758,13 +3758,13 @@
         <v>2.94</v>
       </c>
       <c r="T13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U13">
         <v>2.46</v>
       </c>
       <c r="V13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W13">
         <v>1.44</v>
@@ -3776,7 +3776,7 @@
         <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA13">
         <v>32</v>
@@ -3794,10 +3794,10 @@
         <v>24</v>
       </c>
       <c r="AF13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>15.5</v>
@@ -3806,34 +3806,34 @@
         <v>34</v>
       </c>
       <c r="AJ13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL13">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM13">
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13">
         <v>15</v>
       </c>
       <c r="AP13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR13">
         <v>15</v>
       </c>
       <c r="AS13">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT13">
         <v>14</v>
@@ -3860,7 +3860,7 @@
         <v>29</v>
       </c>
       <c r="BB13">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC13">
         <v>29</v>
@@ -3893,25 +3893,25 @@
         <v>90</v>
       </c>
       <c r="BM13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN13">
         <v>6.6</v>
       </c>
       <c r="BO13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP13">
         <v>23</v>
       </c>
       <c r="BQ13">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT13">
         <v>5.5</v>
@@ -3920,7 +3920,7 @@
         <v>4.2</v>
       </c>
       <c r="BV13">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BW13">
         <v>8</v>
@@ -3929,13 +3929,13 @@
         <v>26</v>
       </c>
       <c r="BY13">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BZ13">
         <v>20</v>
       </c>
       <c r="CA13">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,19 +3958,19 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G14">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H14">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I14">
         <v>3.6</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14">
         <v>4.1</v>
@@ -3982,34 +3982,34 @@
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O14">
         <v>1.2</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R14">
         <v>1.62</v>
       </c>
       <c r="S14">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
         <v>1.38</v>
       </c>
       <c r="W14">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="X14">
         <v>24</v>
@@ -4036,7 +4036,7 @@
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4141,7 +4141,7 @@
         <v>5.5</v>
       </c>
       <c r="BO14">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP14">
         <v>14.5</v>
@@ -4159,7 +4159,7 @@
         <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV14">
         <v>25</v>
@@ -4200,16 +4200,16 @@
         <v>136</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G15">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H15">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J15">
         <v>3.95</v>
@@ -4224,34 +4224,34 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Q15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R15">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="S15">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="T15">
         <v>1.48</v>
       </c>
       <c r="U15">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V15">
         <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X15">
         <v>29</v>
@@ -4263,7 +4263,7 @@
         <v>25</v>
       </c>
       <c r="AA15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB15">
         <v>18</v>
@@ -4299,16 +4299,16 @@
         <v>26</v>
       </c>
       <c r="AM15">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO15">
         <v>15.5</v>
       </c>
       <c r="AP15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ15">
         <v>18</v>
@@ -4323,7 +4323,7 @@
         <v>16</v>
       </c>
       <c r="AU15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV15">
         <v>12.5</v>
@@ -4353,31 +4353,31 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF15">
         <v>10</v>
       </c>
       <c r="BG15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BH15">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BI15">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BJ15">
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL15">
         <v>65</v>
       </c>
       <c r="BM15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN15">
         <v>6.2</v>
@@ -4389,13 +4389,13 @@
         <v>16</v>
       </c>
       <c r="BQ15">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR15">
         <v>23</v>
       </c>
       <c r="BS15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT15">
         <v>6.8</v>
@@ -4407,19 +4407,19 @@
         <v>19</v>
       </c>
       <c r="BW15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX15">
         <v>25</v>
       </c>
       <c r="BY15">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
         <v>14</v>
       </c>
       <c r="CA15">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4442,166 +4442,166 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="H16">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I16">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J16">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="K16">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O16">
         <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
         <v>1.37</v>
       </c>
       <c r="R16">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T16">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U16">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V16">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W16">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="X16">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA16">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB16">
         <v>18</v>
       </c>
       <c r="AC16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD16">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE16">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF16">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG16">
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AK16">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL16">
         <v>21</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AN16">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AO16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP16">
         <v>36</v>
       </c>
       <c r="AQ16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR16">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AS16">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="AT16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW16">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY16">
         <v>10</v>
       </c>
       <c r="AZ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA16">
         <v>34</v>
       </c>
       <c r="BB16">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG16">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BH16">
         <v>5.7</v>
@@ -4610,58 +4610,58 @@
         <v>4.4</v>
       </c>
       <c r="BJ16">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL16">
         <v>60</v>
       </c>
       <c r="BM16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN16">
         <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BP16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BQ16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR16">
         <v>17</v>
       </c>
       <c r="BS16">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT16">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU16">
         <v>5.5</v>
       </c>
       <c r="BV16">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BW16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BY16">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ16">
         <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4684,22 +4684,22 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G17">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="H17">
+        <v>4.5</v>
+      </c>
+      <c r="I17">
         <v>4.7</v>
       </c>
-      <c r="I17">
-        <v>4.9</v>
-      </c>
       <c r="J17">
+        <v>4.3</v>
+      </c>
+      <c r="K17">
         <v>4.4</v>
-      </c>
-      <c r="K17">
-        <v>4.6</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -4708,7 +4708,7 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O17">
         <v>1.19</v>
@@ -4717,7 +4717,7 @@
         <v>2.64</v>
       </c>
       <c r="Q17">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R17">
         <v>1.65</v>
@@ -4726,43 +4726,43 @@
         <v>2.46</v>
       </c>
       <c r="T17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U17">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="X17">
         <v>25</v>
       </c>
       <c r="Y17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB17">
         <v>13</v>
       </c>
       <c r="AC17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE17">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AF17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -4771,52 +4771,52 @@
         <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="AJ17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK17">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AL17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM17">
         <v>65</v>
       </c>
       <c r="AN17">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP17">
         <v>22</v>
       </c>
       <c r="AQ17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS17">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AT17">
         <v>12</v>
       </c>
       <c r="AU17">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV17">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW17">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY17">
         <v>9.4</v>
@@ -4825,13 +4825,13 @@
         <v>15</v>
       </c>
       <c r="BA17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC17">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD17">
         <v>23</v>
@@ -4840,70 +4840,70 @@
         <v>55</v>
       </c>
       <c r="BF17">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG17">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH17">
         <v>4.7</v>
       </c>
       <c r="BI17">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ17">
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL17">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM17">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO17">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ17">
         <v>5.4</v>
       </c>
       <c r="BR17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS17">
         <v>6.8</v>
       </c>
       <c r="BT17">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV17">
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY17">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ17">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CA17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,7 +4926,7 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="G18">
         <v>6.8</v>
@@ -4956,10 +4956,10 @@
         <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q18">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
         <v>1.67</v>
@@ -5037,7 +5037,7 @@
         <v>21</v>
       </c>
       <c r="AQ18">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18">
         <v>9.6</v>
@@ -5049,7 +5049,7 @@
         <v>20</v>
       </c>
       <c r="AU18">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AV18">
         <v>7.8</v>
@@ -5168,7 +5168,7 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G19">
         <v>2.8</v>
@@ -5177,16 +5177,16 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J19">
         <v>3.1</v>
       </c>
       <c r="K19">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M19">
         <v>1.1</v>
@@ -5216,7 +5216,7 @@
         <v>1.97</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
         <v>1.55</v>
@@ -5410,13 +5410,13 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G20">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H20">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I20">
         <v>6.6</v>
@@ -5425,7 +5425,7 @@
         <v>3.3</v>
       </c>
       <c r="K20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
         <v>1.5</v>
@@ -5461,7 +5461,7 @@
         <v>1.18</v>
       </c>
       <c r="W20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -5652,7 +5652,7 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G21">
         <v>2.18</v>
@@ -5667,13 +5667,13 @@
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L21">
         <v>1.45</v>
       </c>
       <c r="M21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N21">
         <v>2.86</v>
@@ -5691,7 +5691,7 @@
         <v>1.22</v>
       </c>
       <c r="S21">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T21">
         <v>2</v>
@@ -5796,13 +5796,13 @@
         <v>8.6</v>
       </c>
       <c r="BB21">
-        <v>7.2</v>
+        <v>22</v>
       </c>
       <c r="BC21">
         <v>7.2</v>
       </c>
       <c r="BD21">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BE21">
         <v>9.199999999999999</v>
@@ -5897,10 +5897,10 @@
         <v>4.9</v>
       </c>
       <c r="G22">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I22">
         <v>2.12</v>
@@ -5909,7 +5909,7 @@
         <v>3</v>
       </c>
       <c r="K22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L22">
         <v>1.64</v>
@@ -5918,16 +5918,16 @@
         <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O22">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="P22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R22">
         <v>1.13</v>
@@ -5936,19 +5936,19 @@
         <v>7.2</v>
       </c>
       <c r="T22">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="U22">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W22">
         <v>1.23</v>
       </c>
       <c r="X22">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Y22">
         <v>5.7</v>
@@ -5969,7 +5969,7 @@
         <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>36</v>
@@ -5984,76 +5984,76 @@
         <v>100</v>
       </c>
       <c r="AJ22">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
         <v>390</v>
       </c>
       <c r="AN22">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP22">
         <v>6</v>
       </c>
       <c r="AQ22">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR22">
         <v>9</v>
       </c>
       <c r="AS22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU22">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW22">
+        <v>26</v>
+      </c>
+      <c r="AX22">
         <v>25</v>
-      </c>
-      <c r="AX22">
-        <v>24</v>
       </c>
       <c r="AY22">
         <v>20</v>
       </c>
       <c r="AZ22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA22">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BB22">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BC22">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BD22">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BE22">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="BF22">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="BG22">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6139,7 +6139,7 @@
         <v>2.78</v>
       </c>
       <c r="G23">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H23">
         <v>3.2</v>
@@ -6151,7 +6151,7 @@
         <v>2.86</v>
       </c>
       <c r="K23">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L23">
         <v>1.64</v>
@@ -6166,7 +6166,7 @@
         <v>1.71</v>
       </c>
       <c r="P23">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -6178,7 +6178,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
         <v>1.65</v>
@@ -6190,7 +6190,7 @@
         <v>1.53</v>
       </c>
       <c r="X23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y23">
         <v>8.4</v>
@@ -6211,10 +6211,10 @@
         <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="AF23">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG23">
         <v>15</v>
@@ -6229,7 +6229,7 @@
         <v>140</v>
       </c>
       <c r="AK23">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AL23">
         <v>1000</v>
@@ -6238,7 +6238,7 @@
         <v>310</v>
       </c>
       <c r="AN23">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="AO23">
         <v>1000</v>
@@ -6253,7 +6253,7 @@
         <v>14</v>
       </c>
       <c r="AS23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT23">
         <v>6.6</v>
@@ -6265,7 +6265,7 @@
         <v>14</v>
       </c>
       <c r="AW23">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX23">
         <v>14</v>
@@ -6301,22 +6301,22 @@
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BJ23">
         <v>17.5</v>
       </c>
       <c r="BK23">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BN23">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BO23">
         <v>3.8</v>
@@ -6325,13 +6325,13 @@
         <v>40</v>
       </c>
       <c r="BQ23">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BT23">
         <v>8.199999999999999</v>
@@ -6349,13 +6349,13 @@
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CB23" t="s">
         <v>148</v>
@@ -6378,7 +6378,7 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G24">
         <v>1.57</v>
@@ -6387,13 +6387,13 @@
         <v>7.8</v>
       </c>
       <c r="I24">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>4.2</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L24">
         <v>1.41</v>
@@ -6429,7 +6429,7 @@
         <v>1.14</v>
       </c>
       <c r="W24">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X24">
         <v>13.5</v>
@@ -6441,7 +6441,7 @@
         <v>65</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AB24">
         <v>7.4</v>
@@ -6453,7 +6453,7 @@
         <v>29</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF24">
         <v>8.4</v>
@@ -6462,7 +6462,7 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24">
         <v>1000</v>
@@ -6474,7 +6474,7 @@
         <v>17.5</v>
       </c>
       <c r="AL24">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AM24">
         <v>180</v>
@@ -6498,7 +6498,7 @@
         <v>95</v>
       </c>
       <c r="AT24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU24">
         <v>8.800000000000001</v>
@@ -6620,22 +6620,22 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G25">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H25">
         <v>5.1</v>
       </c>
       <c r="I25">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J25">
         <v>3.8</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
         <v>1.37</v>
@@ -6647,7 +6647,7 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P25">
         <v>2.06</v>
@@ -6659,7 +6659,7 @@
         <v>1.42</v>
       </c>
       <c r="S25">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T25">
         <v>1.8</v>
@@ -6671,16 +6671,16 @@
         <v>1.22</v>
       </c>
       <c r="W25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X25">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y25">
         <v>26</v>
       </c>
       <c r="Z25">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AA25">
         <v>1000</v>
@@ -6710,7 +6710,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK25">
         <v>18.5</v>
@@ -6746,7 +6746,7 @@
         <v>7.6</v>
       </c>
       <c r="AV25">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW25">
         <v>42</v>
@@ -6773,7 +6773,7 @@
         <v>22</v>
       </c>
       <c r="BE25">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF25">
         <v>9.800000000000001</v>
@@ -6865,10 +6865,10 @@
         <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I26">
         <v>4.8</v>
@@ -6946,7 +6946,7 @@
         <v>12</v>
       </c>
       <c r="AH26">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI26">
         <v>120</v>
@@ -6976,10 +6976,10 @@
         <v>10</v>
       </c>
       <c r="AR26">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT26">
         <v>5.9</v>
@@ -6991,7 +6991,7 @@
         <v>16.5</v>
       </c>
       <c r="AW26">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX26">
         <v>9.800000000000001</v>
@@ -7003,13 +7003,13 @@
         <v>20</v>
       </c>
       <c r="BA26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB26">
+        <v>5.6</v>
+      </c>
+      <c r="BC26">
         <v>5.7</v>
-      </c>
-      <c r="BC26">
-        <v>5.8</v>
       </c>
       <c r="BD26">
         <v>6.4</v>
@@ -7018,10 +7018,10 @@
         <v>6.8</v>
       </c>
       <c r="BF26">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG26">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH26">
         <v>2.82</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 14:55:41</t>
+    <t>2026-07-22 17:04:10</t>
   </si>
 </sst>
 </file>
@@ -1057,46 +1057,46 @@
         <v>4.9</v>
       </c>
       <c r="G2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H2">
         <v>1.93</v>
       </c>
       <c r="I2">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
         <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
         <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
         <v>1.72</v>
@@ -1105,7 +1105,7 @@
         <v>2.02</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -1129,7 +1129,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF2">
         <v>40</v>
@@ -1141,7 +1141,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
         <v>170</v>
@@ -1153,28 +1153,28 @@
         <v>150</v>
       </c>
       <c r="AM2">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AO2">
         <v>21</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ2">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR2">
         <v>9.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -1183,7 +1183,7 @@
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
         <v>30</v>
@@ -1192,7 +1192,7 @@
         <v>18</v>
       </c>
       <c r="AZ2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA2">
         <v>38</v>
@@ -1201,16 +1201,16 @@
         <v>90</v>
       </c>
       <c r="BC2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE2">
         <v>10</v>
       </c>
       <c r="BF2">
-        <v>48</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
         <v>18</v>
@@ -1299,16 +1299,16 @@
         <v>2.12</v>
       </c>
       <c r="G3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
         <v>3.75</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
         <v>3.8</v>
@@ -1326,10 +1326,10 @@
         <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q3">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R3">
         <v>1.5</v>
@@ -1341,13 +1341,13 @@
         <v>1.66</v>
       </c>
       <c r="U3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
         <v>18.5</v>
@@ -1359,7 +1359,7 @@
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
         <v>12</v>
@@ -1371,7 +1371,7 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF3">
         <v>14.5</v>
@@ -1389,7 +1389,7 @@
         <v>26</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL3">
         <v>32</v>
@@ -1407,7 +1407,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR3">
         <v>25</v>
@@ -1446,13 +1446,13 @@
         <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
         <v>29</v>
@@ -1485,13 +1485,13 @@
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BR3">
         <v>26</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
         <v>7</v>
@@ -1515,7 +1515,7 @@
         <v>20</v>
       </c>
       <c r="CA3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,16 +1538,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
+        <v>4.3</v>
+      </c>
+      <c r="I4">
         <v>4.4</v>
-      </c>
-      <c r="I4">
-        <v>4.6</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1568,34 +1568,34 @@
         <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
         <v>2.38</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T4">
         <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z4">
         <v>32</v>
@@ -1604,7 +1604,7 @@
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
@@ -1613,19 +1613,19 @@
         <v>18</v>
       </c>
       <c r="AE4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF4">
         <v>11</v>
       </c>
       <c r="AG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ4">
         <v>25</v>
@@ -1634,7 +1634,7 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1655,10 +1655,10 @@
         <v>28</v>
       </c>
       <c r="AS4">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AT4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
@@ -1679,7 +1679,7 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB4">
         <v>23</v>
@@ -1709,13 +1709,13 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL4">
         <v>170</v>
       </c>
       <c r="BM4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BN4">
         <v>4.5</v>
@@ -1727,37 +1727,37 @@
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>36</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
         <v>5.6</v>
       </c>
       <c r="BV4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BX4">
         <v>60</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ4">
         <v>36</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
         <v>148</v>
@@ -1780,7 +1780,7 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G5">
         <v>2.48</v>
@@ -1798,34 +1798,34 @@
         <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q5">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="R5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="T5">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
         <v>1.42</v>
@@ -1834,7 +1834,7 @@
         <v>1.67</v>
       </c>
       <c r="X5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
         <v>12</v>
@@ -1846,13 +1846,13 @@
         <v>60</v>
       </c>
       <c r="AB5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE5">
         <v>42</v>
@@ -1864,7 +1864,7 @@
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5">
         <v>55</v>
@@ -1873,7 +1873,7 @@
         <v>34</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL5">
         <v>42</v>
@@ -1885,10 +1885,10 @@
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5">
         <v>11</v>
@@ -1900,7 +1900,7 @@
         <v>50</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
@@ -1909,7 +1909,7 @@
         <v>13</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX5">
         <v>14</v>
@@ -1918,10 +1918,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>29</v>
@@ -1930,16 +1930,16 @@
         <v>24</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE5">
         <v>38</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH5">
         <v>3.2</v>
@@ -1954,10 +1954,10 @@
         <v>6.6</v>
       </c>
       <c r="BL5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN5">
         <v>5.1</v>
@@ -1966,16 +1966,16 @@
         <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
@@ -1987,19 +1987,19 @@
         <v>28</v>
       </c>
       <c r="BW5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,16 +2022,16 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H6">
+        <v>1.46</v>
+      </c>
+      <c r="I6">
         <v>1.47</v>
-      </c>
-      <c r="I6">
-        <v>1.48</v>
       </c>
       <c r="J6">
         <v>4.7</v>
@@ -2040,7 +2040,7 @@
         <v>4.8</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -2049,7 +2049,7 @@
         <v>4.2</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
         <v>2.08</v>
@@ -2058,19 +2058,19 @@
         <v>1.9</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6">
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W6">
         <v>1.12</v>
@@ -2091,7 +2091,7 @@
         <v>27</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD6">
         <v>9.800000000000001</v>
@@ -2112,7 +2112,7 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="AK6">
         <v>150</v>
@@ -2121,16 +2121,16 @@
         <v>130</v>
       </c>
       <c r="AM6">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN6">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AO6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP6">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6">
         <v>7.6</v>
@@ -2145,7 +2145,7 @@
         <v>24</v>
       </c>
       <c r="AU6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
@@ -2154,7 +2154,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AY6">
         <v>29</v>
@@ -2166,22 +2166,22 @@
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BC6">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="BD6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF6">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="BG6">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>3.55</v>
@@ -2193,55 +2193,55 @@
         <v>11.5</v>
       </c>
       <c r="BK6">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BL6">
         <v>160</v>
       </c>
       <c r="BM6">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BP6">
         <v>80</v>
       </c>
       <c r="BQ6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BR6">
         <v>80</v>
       </c>
       <c r="BS6">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BT6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BU6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ6">
         <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2264,22 +2264,22 @@
         <v>128</v>
       </c>
       <c r="F7">
+        <v>1.89</v>
+      </c>
+      <c r="G7">
         <v>1.91</v>
-      </c>
-      <c r="G7">
-        <v>1.92</v>
       </c>
       <c r="H7">
         <v>4.7</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2294,7 +2294,7 @@
         <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
         <v>2.1</v>
@@ -2306,13 +2306,13 @@
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="U7">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W7">
         <v>2.08</v>
@@ -2327,19 +2327,19 @@
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AB7">
         <v>8</v>
       </c>
       <c r="AC7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD7">
         <v>19.5</v>
       </c>
       <c r="AE7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF7">
         <v>11</v>
@@ -2351,10 +2351,10 @@
         <v>22</v>
       </c>
       <c r="AI7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK7">
         <v>22</v>
@@ -2366,10 +2366,10 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
@@ -2381,7 +2381,7 @@
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT7">
         <v>7.4</v>
@@ -2390,7 +2390,7 @@
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
         <v>55</v>
@@ -2402,10 +2402,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BB7">
         <v>18.5</v>
@@ -2417,13 +2417,13 @@
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="BF7">
         <v>12.5</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
@@ -2435,13 +2435,13 @@
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
@@ -2453,13 +2453,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
         <v>30</v>
       </c>
       <c r="BS7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT7">
         <v>8.6</v>
@@ -2471,7 +2471,7 @@
         <v>46</v>
       </c>
       <c r="BW7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
         <v>60</v>
@@ -2480,10 +2480,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB7" t="s">
         <v>148</v>
@@ -2512,16 +2512,16 @@
         <v>3.6</v>
       </c>
       <c r="H8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>1.31</v>
@@ -2530,13 +2530,13 @@
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
         <v>1.63</v>
@@ -2548,13 +2548,13 @@
         <v>2.56</v>
       </c>
       <c r="T8">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U8">
         <v>2.64</v>
       </c>
       <c r="V8">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="W8">
         <v>1.38</v>
@@ -2566,7 +2566,7 @@
         <v>14</v>
       </c>
       <c r="Z8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA8">
         <v>26</v>
@@ -2581,7 +2581,7 @@
         <v>11</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF8">
         <v>29</v>
@@ -2590,7 +2590,7 @@
         <v>15</v>
       </c>
       <c r="AH8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
         <v>27</v>
@@ -2599,7 +2599,7 @@
         <v>65</v>
       </c>
       <c r="AK8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL8">
         <v>38</v>
@@ -2662,7 +2662,7 @@
         <v>50</v>
       </c>
       <c r="BF8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG8">
         <v>9.800000000000001</v>
@@ -2677,7 +2677,7 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL8">
         <v>80</v>
@@ -2725,7 +2725,7 @@
         <v>16.5</v>
       </c>
       <c r="CA8">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2748,16 +2748,16 @@
         <v>130</v>
       </c>
       <c r="F9">
+        <v>1.82</v>
+      </c>
+      <c r="G9">
         <v>1.83</v>
       </c>
-      <c r="G9">
-        <v>1.85</v>
-      </c>
       <c r="H9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2772,16 +2772,16 @@
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
         <v>1.27</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
         <v>1.46</v>
@@ -2793,13 +2793,13 @@
         <v>1.76</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X9">
         <v>17.5</v>
@@ -2814,7 +2814,7 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
@@ -2826,7 +2826,7 @@
         <v>60</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG9">
         <v>9.6</v>
@@ -2847,7 +2847,7 @@
         <v>32</v>
       </c>
       <c r="AM9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
         <v>10.5</v>
@@ -2865,7 +2865,7 @@
         <v>32</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AT9">
         <v>9.4</v>
@@ -2874,10 +2874,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV9">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AX9">
         <v>11</v>
@@ -2886,10 +2886,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="BB9">
         <v>18</v>
@@ -2904,10 +2904,10 @@
         <v>36</v>
       </c>
       <c r="BF9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BH9">
         <v>3.7</v>
@@ -2919,13 +2919,13 @@
         <v>10</v>
       </c>
       <c r="BK9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL9">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2943,7 +2943,7 @@
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>8</v>
@@ -2952,22 +2952,22 @@
         <v>7</v>
       </c>
       <c r="BV9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BY9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -3014,13 +3014,13 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O10">
         <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q10">
         <v>1.65</v>
@@ -3032,13 +3032,13 @@
         <v>2.66</v>
       </c>
       <c r="T10">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W10">
         <v>2.74</v>
@@ -3047,7 +3047,7 @@
         <v>23</v>
       </c>
       <c r="Y10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z10">
         <v>60</v>
@@ -3062,7 +3062,7 @@
         <v>11</v>
       </c>
       <c r="AD10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10">
         <v>85</v>
@@ -3083,16 +3083,16 @@
         <v>14.5</v>
       </c>
       <c r="AK10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL10">
         <v>29</v>
       </c>
       <c r="AM10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO10">
         <v>80</v>
@@ -3113,22 +3113,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10">
         <v>22</v>
       </c>
       <c r="AW10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AX10">
         <v>9.6</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA10">
         <v>60</v>
@@ -3143,7 +3143,7 @@
         <v>25</v>
       </c>
       <c r="BE10">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BF10">
         <v>6</v>
@@ -3155,7 +3155,7 @@
         <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
@@ -3232,85 +3232,85 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G11">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M11">
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="R11">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T11">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V11">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="X11">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Y11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA11">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AB11">
         <v>11</v>
       </c>
       <c r="AC11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD11">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AE11">
         <v>180</v>
       </c>
       <c r="AF11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG11">
         <v>10.5</v>
@@ -3319,13 +3319,13 @@
         <v>24</v>
       </c>
       <c r="AI11">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AJ11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK11">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL11">
         <v>38</v>
@@ -3337,19 +3337,19 @@
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP11">
         <v>18.5</v>
       </c>
       <c r="AQ11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR11">
         <v>50</v>
       </c>
       <c r="AS11">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
@@ -3361,7 +3361,7 @@
         <v>22</v>
       </c>
       <c r="AW11">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AX11">
         <v>8.800000000000001</v>
@@ -3385,52 +3385,52 @@
         <v>23</v>
       </c>
       <c r="BE11">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF11">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN11">
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP11">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BQ11">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BR11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS11">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BT11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
         <v>6.4</v>
@@ -3442,16 +3442,16 @@
         <v>12</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY11">
         <v>12</v>
       </c>
       <c r="BZ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB11" t="s">
         <v>148</v>
@@ -3474,7 +3474,7 @@
         <v>133</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G12">
         <v>2.06</v>
@@ -3486,7 +3486,7 @@
         <v>3.7</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3504,22 +3504,22 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="S12">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T12">
         <v>1.5</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
         <v>1.37</v>
@@ -3552,7 +3552,7 @@
         <v>34</v>
       </c>
       <c r="AF12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG12">
         <v>11</v>
@@ -3567,7 +3567,7 @@
         <v>26</v>
       </c>
       <c r="AK12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12">
         <v>24</v>
@@ -3585,7 +3585,7 @@
         <v>27</v>
       </c>
       <c r="AQ12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR12">
         <v>30</v>
@@ -3606,7 +3606,7 @@
         <v>30</v>
       </c>
       <c r="AX12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY12">
         <v>10</v>
@@ -3621,19 +3621,19 @@
         <v>24</v>
       </c>
       <c r="BC12">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD12">
         <v>22</v>
       </c>
       <c r="BE12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF12">
         <v>7.6</v>
       </c>
       <c r="BG12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH12">
         <v>4.7</v>
@@ -3642,16 +3642,16 @@
         <v>4.4</v>
       </c>
       <c r="BJ12">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL12">
         <v>70</v>
       </c>
       <c r="BM12">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
@@ -3663,37 +3663,37 @@
         <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR12">
         <v>21</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT12">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BU12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BV12">
         <v>24</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX12">
         <v>28</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ12">
         <v>14</v>
       </c>
       <c r="CA12">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3719,7 +3719,7 @@
         <v>3.15</v>
       </c>
       <c r="G13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H13">
         <v>2.36</v>
@@ -3728,64 +3728,64 @@
         <v>2.4</v>
       </c>
       <c r="J13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
         <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M13">
         <v>1.05</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P13">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q13">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S13">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T13">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U13">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y13">
         <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA13">
         <v>32</v>
       </c>
       <c r="AB13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13">
         <v>11.5</v>
@@ -3797,7 +3797,7 @@
         <v>23</v>
       </c>
       <c r="AG13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH13">
         <v>15.5</v>
@@ -3809,19 +3809,19 @@
         <v>50</v>
       </c>
       <c r="AK13">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL13">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM13">
         <v>70</v>
       </c>
       <c r="AN13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP13">
         <v>16.5</v>
@@ -3836,7 +3836,7 @@
         <v>29</v>
       </c>
       <c r="AT13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU13">
         <v>8</v>
@@ -3848,7 +3848,7 @@
         <v>21</v>
       </c>
       <c r="AX13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY13">
         <v>12.5</v>
@@ -3860,7 +3860,7 @@
         <v>29</v>
       </c>
       <c r="BB13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC13">
         <v>29</v>
@@ -3878,64 +3878,64 @@
         <v>13.5</v>
       </c>
       <c r="BH13">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BI13">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="BJ13">
         <v>9</v>
       </c>
       <c r="BK13">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BL13">
         <v>90</v>
       </c>
       <c r="BM13">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP13">
         <v>23</v>
       </c>
       <c r="BQ13">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BT13">
         <v>5.5</v>
       </c>
       <c r="BU13">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BV13">
         <v>16.5</v>
       </c>
       <c r="BW13">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BX13">
         <v>26</v>
       </c>
       <c r="BY13">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA13">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,7 +3958,7 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G14">
         <v>2.16</v>
@@ -3967,7 +3967,7 @@
         <v>3.5</v>
       </c>
       <c r="I14">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J14">
         <v>3.95</v>
@@ -3976,7 +3976,7 @@
         <v>4.1</v>
       </c>
       <c r="L14">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M14">
         <v>1.04</v>
@@ -3985,7 +3985,7 @@
         <v>5.6</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P14">
         <v>2.54</v>
@@ -3994,10 +3994,10 @@
         <v>1.62</v>
       </c>
       <c r="R14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T14">
         <v>1.58</v>
@@ -4006,7 +4006,7 @@
         <v>2.62</v>
       </c>
       <c r="V14">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
         <v>1.86</v>
@@ -4015,7 +4015,7 @@
         <v>24</v>
       </c>
       <c r="Y14">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z14">
         <v>29</v>
@@ -4024,7 +4024,7 @@
         <v>60</v>
       </c>
       <c r="AB14">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC14">
         <v>9.4</v>
@@ -4036,7 +4036,7 @@
         <v>36</v>
       </c>
       <c r="AF14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="AK14">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4069,19 +4069,19 @@
         <v>21</v>
       </c>
       <c r="AQ14">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
         <v>26</v>
       </c>
       <c r="AS14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT14">
         <v>13</v>
       </c>
       <c r="AU14">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14">
         <v>13.5</v>
@@ -4096,64 +4096,64 @@
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB14">
         <v>23</v>
       </c>
       <c r="BC14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD14">
         <v>24</v>
       </c>
       <c r="BE14">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI14">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="BJ14">
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BL14">
         <v>80</v>
       </c>
       <c r="BM14">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN14">
         <v>5.5</v>
       </c>
       <c r="BO14">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP14">
         <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BR14">
         <v>23</v>
       </c>
       <c r="BS14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT14">
         <v>7.4</v>
@@ -4165,19 +4165,19 @@
         <v>25</v>
       </c>
       <c r="BW14">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX14">
         <v>32</v>
       </c>
       <c r="BY14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14">
         <v>16.5</v>
       </c>
       <c r="CA14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4206,10 +4206,10 @@
         <v>2.44</v>
       </c>
       <c r="H15">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I15">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J15">
         <v>3.95</v>
@@ -4218,55 +4218,55 @@
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R15">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="S15">
         <v>2.22</v>
       </c>
       <c r="T15">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U15">
         <v>3</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15">
         <v>1.69</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA15">
         <v>46</v>
       </c>
       <c r="AB15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
@@ -4275,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="AE15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF15">
         <v>21</v>
@@ -4287,28 +4287,28 @@
         <v>13.5</v>
       </c>
       <c r="AI15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ15">
         <v>34</v>
       </c>
       <c r="AK15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM15">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN15">
         <v>11</v>
       </c>
       <c r="AO15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ15">
         <v>18</v>
@@ -4320,7 +4320,7 @@
         <v>42</v>
       </c>
       <c r="AT15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU15">
         <v>9.4</v>
@@ -4341,7 +4341,7 @@
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB15">
         <v>29</v>
@@ -4353,46 +4353,46 @@
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG15">
         <v>13</v>
       </c>
       <c r="BH15">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI15">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BJ15">
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BL15">
         <v>65</v>
       </c>
       <c r="BM15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>6.2</v>
       </c>
       <c r="BO15">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BP15">
         <v>16</v>
       </c>
       <c r="BQ15">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BR15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS15">
         <v>7.8</v>
@@ -4401,7 +4401,7 @@
         <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV15">
         <v>19</v>
@@ -4410,13 +4410,13 @@
         <v>7.4</v>
       </c>
       <c r="BX15">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BY15">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA15">
         <v>6.4</v>
@@ -4448,10 +4448,10 @@
         <v>1.73</v>
       </c>
       <c r="H16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I16">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J16">
         <v>4.7</v>
@@ -4547,16 +4547,16 @@
         <v>5.3</v>
       </c>
       <c r="AO16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP16">
         <v>36</v>
       </c>
       <c r="AQ16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AS16">
         <v>85</v>
@@ -4583,7 +4583,7 @@
         <v>14</v>
       </c>
       <c r="BA16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB16">
         <v>19</v>
@@ -4598,7 +4598,7 @@
         <v>40</v>
       </c>
       <c r="BF16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BG16">
         <v>22</v>
@@ -4607,13 +4607,13 @@
         <v>5.7</v>
       </c>
       <c r="BI16">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BJ16">
         <v>8.800000000000001</v>
       </c>
       <c r="BK16">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL16">
         <v>60</v>
@@ -4625,7 +4625,7 @@
         <v>5.2</v>
       </c>
       <c r="BO16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP16">
         <v>11</v>
@@ -4661,7 +4661,7 @@
         <v>9.6</v>
       </c>
       <c r="CA16">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4708,28 +4708,28 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q17">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S17">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T17">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U17">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V17">
         <v>1.27</v>
@@ -4738,7 +4738,7 @@
         <v>2.2</v>
       </c>
       <c r="X17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y17">
         <v>24</v>
@@ -4747,7 +4747,7 @@
         <v>40</v>
       </c>
       <c r="AA17">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>13</v>
@@ -4768,16 +4768,16 @@
         <v>10</v>
       </c>
       <c r="AH17">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI17">
         <v>46</v>
       </c>
       <c r="AJ17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL17">
         <v>25</v>
@@ -4798,7 +4798,7 @@
         <v>22</v>
       </c>
       <c r="AR17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS17">
         <v>75</v>
@@ -4813,7 +4813,7 @@
         <v>16.5</v>
       </c>
       <c r="AW17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX17">
         <v>12.5</v>
@@ -4822,7 +4822,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ17">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA17">
         <v>40</v>
@@ -4846,64 +4846,64 @@
         <v>30</v>
       </c>
       <c r="BH17">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BI17">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="BJ17">
         <v>9.4</v>
       </c>
       <c r="BK17">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL17">
         <v>80</v>
       </c>
       <c r="BM17">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN17">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BO17">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BP17">
         <v>12</v>
       </c>
       <c r="BQ17">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS17">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BT17">
         <v>8.6</v>
       </c>
       <c r="BU17">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV17">
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX17">
         <v>36</v>
       </c>
       <c r="BY17">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ17">
         <v>14.5</v>
       </c>
       <c r="CA17">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4926,22 +4926,22 @@
         <v>139</v>
       </c>
       <c r="F18">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G18">
         <v>6.8</v>
       </c>
       <c r="H18">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="I18">
         <v>1.69</v>
       </c>
       <c r="J18">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K18">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L18">
         <v>1.25</v>
@@ -4953,22 +4953,22 @@
         <v>6</v>
       </c>
       <c r="O18">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P18">
         <v>2.66</v>
       </c>
       <c r="Q18">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R18">
         <v>1.67</v>
       </c>
       <c r="S18">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="T18">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U18">
         <v>2.36</v>
@@ -4989,13 +4989,13 @@
         <v>16</v>
       </c>
       <c r="AA18">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AB18">
         <v>34</v>
       </c>
       <c r="AC18">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD18">
         <v>13</v>
@@ -5043,13 +5043,13 @@
         <v>9.6</v>
       </c>
       <c r="AS18">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT18">
         <v>20</v>
       </c>
       <c r="AU18">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AV18">
         <v>7.8</v>
@@ -5070,19 +5070,19 @@
         <v>21</v>
       </c>
       <c r="BB18">
+        <v>4.3</v>
+      </c>
+      <c r="BC18">
+        <v>4.2</v>
+      </c>
+      <c r="BD18">
+        <v>4.2</v>
+      </c>
+      <c r="BE18">
+        <v>4.2</v>
+      </c>
+      <c r="BF18">
         <v>4.1</v>
-      </c>
-      <c r="BC18">
-        <v>4</v>
-      </c>
-      <c r="BD18">
-        <v>4</v>
-      </c>
-      <c r="BE18">
-        <v>4</v>
-      </c>
-      <c r="BF18">
-        <v>3.95</v>
       </c>
       <c r="BG18">
         <v>5.2</v>
@@ -5171,13 +5171,13 @@
         <v>2.62</v>
       </c>
       <c r="G19">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H19">
         <v>3</v>
       </c>
       <c r="I19">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J19">
         <v>3.1</v>
@@ -5186,7 +5186,7 @@
         <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M19">
         <v>1.1</v>
@@ -5198,7 +5198,7 @@
         <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
@@ -5216,10 +5216,10 @@
         <v>1.97</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X19">
         <v>13</v>
@@ -5258,10 +5258,10 @@
         <v>60</v>
       </c>
       <c r="AJ19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK19">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL19">
         <v>55</v>
@@ -5333,55 +5333,55 @@
         <v>3.05</v>
       </c>
       <c r="BI19">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ19">
         <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN19">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT19">
         <v>5.9</v>
       </c>
       <c r="BU19">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
@@ -5410,10 +5410,10 @@
         <v>141</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G20">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H20">
         <v>5.5</v>
@@ -5425,7 +5425,7 @@
         <v>3.3</v>
       </c>
       <c r="K20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
         <v>1.5</v>
@@ -5434,22 +5434,22 @@
         <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O20">
         <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q20">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R20">
         <v>1.19</v>
       </c>
       <c r="S20">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T20">
         <v>2.24</v>
@@ -5461,7 +5461,7 @@
         <v>1.18</v>
       </c>
       <c r="W20">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -5473,7 +5473,7 @@
         <v>48</v>
       </c>
       <c r="AA20">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB20">
         <v>6.2</v>
@@ -5485,13 +5485,13 @@
         <v>26</v>
       </c>
       <c r="AE20">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF20">
         <v>10</v>
       </c>
       <c r="AG20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20">
         <v>30</v>
@@ -5500,7 +5500,7 @@
         <v>140</v>
       </c>
       <c r="AJ20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK20">
         <v>26</v>
@@ -5512,10 +5512,10 @@
         <v>260</v>
       </c>
       <c r="AN20">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO20">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP20">
         <v>8</v>
@@ -5524,22 +5524,22 @@
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT20">
         <v>5.2</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>19.5</v>
       </c>
       <c r="AW20">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX20">
         <v>8</v>
@@ -5548,28 +5548,28 @@
         <v>9</v>
       </c>
       <c r="AZ20">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BA20">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC20">
         <v>21</v>
       </c>
       <c r="BD20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF20">
         <v>16</v>
       </c>
       <c r="BG20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5900,10 +5900,10 @@
         <v>5.2</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I22">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -5915,37 +5915,37 @@
         <v>1.64</v>
       </c>
       <c r="M22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N22">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O22">
         <v>1.74</v>
       </c>
       <c r="P22">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q22">
         <v>3.25</v>
       </c>
       <c r="R22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S22">
         <v>7.2</v>
       </c>
       <c r="T22">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U22">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V22">
         <v>1.9</v>
       </c>
       <c r="W22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X22">
         <v>7.2</v>
@@ -5978,10 +5978,10 @@
         <v>24</v>
       </c>
       <c r="AH22">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AI22">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
         <v>1000</v>
@@ -5993,7 +5993,7 @@
         <v>1000</v>
       </c>
       <c r="AM22">
-        <v>390</v>
+        <v>430</v>
       </c>
       <c r="AN22">
         <v>1000</v>
@@ -6002,22 +6002,22 @@
         <v>42</v>
       </c>
       <c r="AP22">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ22">
         <v>5.2</v>
       </c>
       <c r="AR22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS22">
         <v>20</v>
       </c>
       <c r="AT22">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU22">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
         <v>11.5</v>
@@ -6136,10 +6136,10 @@
         <v>144</v>
       </c>
       <c r="F23">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G23">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H23">
         <v>3.2</v>
@@ -6151,7 +6151,7 @@
         <v>2.86</v>
       </c>
       <c r="K23">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L23">
         <v>1.64</v>
@@ -6163,40 +6163,40 @@
         <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P23">
         <v>1.42</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R23">
         <v>1.14</v>
       </c>
       <c r="S23">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="U23">
         <v>1.65</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X23">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y23">
         <v>8.4</v>
       </c>
       <c r="Z23">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA23">
         <v>1000</v>
@@ -6211,25 +6211,25 @@
         <v>17.5</v>
       </c>
       <c r="AE23">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="AF23">
         <v>19</v>
       </c>
       <c r="AG23">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH23">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AI23">
         <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AK23">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AL23">
         <v>1000</v>
@@ -6238,7 +6238,7 @@
         <v>310</v>
       </c>
       <c r="AN23">
-        <v>600</v>
+        <v>960</v>
       </c>
       <c r="AO23">
         <v>1000</v>
@@ -6274,7 +6274,7 @@
         <v>13</v>
       </c>
       <c r="AZ23">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA23">
         <v>40</v>
@@ -6292,7 +6292,7 @@
         <v>50</v>
       </c>
       <c r="BF23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG23">
         <v>36</v>
@@ -6378,13 +6378,13 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H24">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
@@ -6423,13 +6423,13 @@
         <v>2.14</v>
       </c>
       <c r="U24">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V24">
         <v>1.14</v>
       </c>
       <c r="W24">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="X24">
         <v>13.5</v>
@@ -6483,7 +6483,7 @@
         <v>9.6</v>
       </c>
       <c r="AO24">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP24">
         <v>12</v>
@@ -6507,7 +6507,7 @@
         <v>26</v>
       </c>
       <c r="AW24">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AX24">
         <v>7.6</v>
@@ -6623,19 +6623,19 @@
         <v>1.78</v>
       </c>
       <c r="G25">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H25">
         <v>5.1</v>
       </c>
       <c r="I25">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J25">
         <v>3.8</v>
       </c>
       <c r="K25">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>1.37</v>
@@ -6659,19 +6659,19 @@
         <v>1.42</v>
       </c>
       <c r="S25">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T25">
         <v>1.8</v>
       </c>
       <c r="U25">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V25">
         <v>1.22</v>
       </c>
       <c r="W25">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X25">
         <v>21</v>
@@ -6877,7 +6877,7 @@
         <v>3.05</v>
       </c>
       <c r="K26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L26">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -460,7 +460,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 17:04:10</t>
+    <t>2026-07-22 19:12:56</t>
   </si>
 </sst>
 </file>
@@ -1054,64 +1054,64 @@
         <v>123</v>
       </c>
       <c r="F2">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H2">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="I2">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.54</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O2">
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R2">
         <v>1.22</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="W2">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z2">
         <v>11</v>
@@ -1123,7 +1123,7 @@
         <v>13.5</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1132,7 +1132,7 @@
         <v>26</v>
       </c>
       <c r="AF2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AG2">
         <v>22</v>
@@ -1141,31 +1141,31 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
-        <v>170</v>
+        <v>380</v>
       </c>
       <c r="AK2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AL2">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AM2">
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AO2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP2">
         <v>8.4</v>
       </c>
       <c r="AQ2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
         <v>9.199999999999999</v>
@@ -1177,16 +1177,16 @@
         <v>11.5</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AX2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY2">
         <v>18</v>
@@ -1195,10 +1195,10 @@
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>90</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2">
         <v>55</v>
@@ -1207,73 +1207,73 @@
         <v>60</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>18</v>
       </c>
       <c r="BH2">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BP2">
         <v>60</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BU2">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BV2">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BW2">
         <v>6.6</v>
       </c>
       <c r="BX2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
         <v>148</v>
@@ -1296,70 +1296,70 @@
         <v>124</v>
       </c>
       <c r="F3">
+        <v>2.1</v>
+      </c>
+      <c r="G3">
         <v>2.12</v>
-      </c>
-      <c r="G3">
-        <v>2.14</v>
       </c>
       <c r="H3">
         <v>3.75</v>
       </c>
       <c r="I3">
+        <v>3.8</v>
+      </c>
+      <c r="J3">
+        <v>3.8</v>
+      </c>
+      <c r="K3">
         <v>3.85</v>
       </c>
-      <c r="J3">
-        <v>3.75</v>
-      </c>
-      <c r="K3">
-        <v>3.8</v>
-      </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="T3">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U3">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
         <v>1.35</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3">
         <v>28</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>12</v>
@@ -1371,10 +1371,10 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3">
         <v>11</v>
@@ -1386,40 +1386,40 @@
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK3">
         <v>20</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
         <v>32</v>
       </c>
       <c r="AP3">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3">
         <v>16</v>
       </c>
       <c r="AR3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT3">
         <v>11</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
         <v>14</v>
@@ -1431,7 +1431,7 @@
         <v>13.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
@@ -1443,7 +1443,7 @@
         <v>23</v>
       </c>
       <c r="BC3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD3">
         <v>27</v>
@@ -1452,28 +1452,28 @@
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG3">
         <v>29</v>
       </c>
       <c r="BH3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI3">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3">
         <v>8</v>
       </c>
       <c r="BL3">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
         <v>5.1</v>
@@ -1485,10 +1485,10 @@
         <v>15</v>
       </c>
       <c r="BQ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS3">
         <v>10.5</v>
@@ -1503,19 +1503,19 @@
         <v>27</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="CB3" t="s">
         <v>148</v>
@@ -1538,16 +1538,16 @@
         <v>125</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H4">
         <v>4.3</v>
       </c>
       <c r="I4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J4">
         <v>3.35</v>
@@ -1559,7 +1559,7 @@
         <v>1.5</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
         <v>3.1</v>
@@ -1577,25 +1577,25 @@
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
         <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
         <v>32</v>
@@ -1604,19 +1604,19 @@
         <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
         <v>65</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>11</v>
@@ -1634,13 +1634,13 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO4">
         <v>90</v>
@@ -1661,10 +1661,10 @@
         <v>7.2</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
         <v>55</v>
@@ -1679,7 +1679,7 @@
         <v>20</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB4">
         <v>23</v>
@@ -1691,7 +1691,7 @@
         <v>42</v>
       </c>
       <c r="BE4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF4">
         <v>20</v>
@@ -1709,7 +1709,7 @@
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL4">
         <v>170</v>
@@ -1718,7 +1718,7 @@
         <v>19</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO4">
         <v>4.2</v>
@@ -1727,7 +1727,7 @@
         <v>16</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BR4">
         <v>36</v>
@@ -1736,10 +1736,10 @@
         <v>13.5</v>
       </c>
       <c r="BT4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV4">
         <v>40</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="BX4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY4">
         <v>15.5</v>
@@ -1780,13 +1780,13 @@
         <v>126</v>
       </c>
       <c r="F5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
         <v>2.48</v>
       </c>
       <c r="H5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
         <v>3.35</v>
@@ -1804,28 +1804,28 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
         <v>1.42</v>
@@ -1837,13 +1837,13 @@
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z5">
         <v>22</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>9.800000000000001</v>
@@ -1852,22 +1852,22 @@
         <v>7.6</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF5">
         <v>15</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
         <v>17</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5">
         <v>34</v>
@@ -1876,22 +1876,22 @@
         <v>26</v>
       </c>
       <c r="AL5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN5">
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP5">
         <v>12</v>
       </c>
       <c r="AQ5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
         <v>20</v>
@@ -1906,7 +1906,7 @@
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
         <v>34</v>
@@ -1915,7 +1915,7 @@
         <v>14</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
         <v>16</v>
@@ -1924,7 +1924,7 @@
         <v>46</v>
       </c>
       <c r="BB5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC5">
         <v>24</v>
@@ -1933,73 +1933,73 @@
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="BF5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG5">
         <v>34</v>
       </c>
       <c r="BH5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL5">
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
         <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU5">
         <v>5.8</v>
       </c>
       <c r="BV5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <v>40</v>
       </c>
       <c r="BY5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
         <v>32</v>
       </c>
       <c r="CA5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>148</v>
@@ -2022,61 +2022,61 @@
         <v>127</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="G6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="I6">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R6">
         <v>1.42</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T6">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="W6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -2085,25 +2085,25 @@
         <v>7.8</v>
       </c>
       <c r="AA6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AB6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AC6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD6">
         <v>9.800000000000001</v>
       </c>
       <c r="AE6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH6">
         <v>27</v>
@@ -2112,40 +2112,40 @@
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>330</v>
+        <v>470</v>
       </c>
       <c r="AK6">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AL6">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN6">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AO6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
         <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV6">
         <v>9.4</v>
@@ -2154,34 +2154,34 @@
         <v>14.5</v>
       </c>
       <c r="AX6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AY6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA6">
         <v>36</v>
       </c>
       <c r="BB6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BC6">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="BD6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BF6">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH6">
         <v>3.55</v>
@@ -2190,58 +2190,58 @@
         <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BL6">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="BM6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BN6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BO6">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BP6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BQ6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BR6">
         <v>80</v>
       </c>
       <c r="BS6">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BT6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BU6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
         <v>8.800000000000001</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>148</v>
@@ -2270,16 +2270,16 @@
         <v>1.91</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>3.75</v>
       </c>
       <c r="K7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7">
         <v>1.44</v>
@@ -2300,22 +2300,22 @@
         <v>2.1</v>
       </c>
       <c r="R7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="U7">
         <v>1.98</v>
       </c>
       <c r="V7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X7">
         <v>13</v>
@@ -2327,10 +2327,10 @@
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
         <v>8.4</v>
@@ -2354,10 +2354,10 @@
         <v>75</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL7">
         <v>42</v>
@@ -2390,7 +2390,7 @@
         <v>7.6</v>
       </c>
       <c r="AV7">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW7">
         <v>55</v>
@@ -2402,40 +2402,40 @@
         <v>9.4</v>
       </c>
       <c r="AZ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA7">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BB7">
         <v>18.5</v>
       </c>
       <c r="BC7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="BF7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI7">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="BJ7">
         <v>11</v>
       </c>
       <c r="BK7">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2447,40 +2447,40 @@
         <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="BP7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV7">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW7">
         <v>8.6</v>
       </c>
       <c r="BX7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA7">
         <v>7.6</v>
@@ -2506,7 +2506,7 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G8">
         <v>3.6</v>
@@ -2536,10 +2536,10 @@
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R8">
         <v>1.62</v>
@@ -2548,13 +2548,13 @@
         <v>2.56</v>
       </c>
       <c r="T8">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U8">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="V8">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W8">
         <v>1.38</v>
@@ -2563,7 +2563,7 @@
         <v>23</v>
       </c>
       <c r="Y8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z8">
         <v>16</v>
@@ -2587,7 +2587,7 @@
         <v>29</v>
       </c>
       <c r="AG8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
         <v>15</v>
@@ -2626,10 +2626,10 @@
         <v>24</v>
       </c>
       <c r="AT8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>10</v>
@@ -2647,13 +2647,13 @@
         <v>13.5</v>
       </c>
       <c r="BA8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB8">
         <v>55</v>
       </c>
       <c r="BC8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD8">
         <v>34</v>
@@ -2674,7 +2674,7 @@
         <v>4</v>
       </c>
       <c r="BJ8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK8">
         <v>7.8</v>
@@ -2683,25 +2683,25 @@
         <v>80</v>
       </c>
       <c r="BM8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN8">
         <v>7.2</v>
       </c>
       <c r="BO8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BP8">
         <v>26</v>
       </c>
       <c r="BQ8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR8">
         <v>32</v>
       </c>
       <c r="BS8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT8">
         <v>5.2</v>
@@ -2713,19 +2713,19 @@
         <v>14.5</v>
       </c>
       <c r="BW8">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BX8">
         <v>23</v>
       </c>
       <c r="BY8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>16.5</v>
       </c>
       <c r="CA8">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="s">
         <v>148</v>
@@ -2784,10 +2784,10 @@
         <v>1.79</v>
       </c>
       <c r="R9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T9">
         <v>1.76</v>
@@ -2802,28 +2802,28 @@
         <v>2.2</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9">
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF9">
         <v>12</v>
@@ -2832,13 +2832,13 @@
         <v>9.6</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK9">
         <v>18</v>
@@ -2847,13 +2847,13 @@
         <v>32</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN9">
         <v>10.5</v>
       </c>
       <c r="AO9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP9">
         <v>16</v>
@@ -2865,19 +2865,19 @@
         <v>32</v>
       </c>
       <c r="AS9">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AT9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV9">
         <v>16.5</v>
       </c>
       <c r="AW9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX9">
         <v>11</v>
@@ -2886,13 +2886,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
@@ -2901,31 +2901,31 @@
         <v>28</v>
       </c>
       <c r="BE9">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH9">
         <v>3.7</v>
       </c>
       <c r="BI9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL9">
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2937,13 +2937,13 @@
         <v>13</v>
       </c>
       <c r="BQ9">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
         <v>26</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT9">
         <v>8</v>
@@ -2955,19 +2955,19 @@
         <v>38</v>
       </c>
       <c r="BW9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <v>44</v>
       </c>
       <c r="BY9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9">
         <v>20</v>
       </c>
       <c r="CA9">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB9" t="s">
         <v>148</v>
@@ -2999,13 +2999,13 @@
         <v>6.6</v>
       </c>
       <c r="I10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J10">
+        <v>4.6</v>
+      </c>
+      <c r="K10">
         <v>4.7</v>
-      </c>
-      <c r="K10">
-        <v>4.8</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3029,7 +3029,7 @@
         <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T10">
         <v>1.77</v>
@@ -3041,7 +3041,7 @@
         <v>1.16</v>
       </c>
       <c r="W10">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X10">
         <v>23</v>
@@ -3053,13 +3053,13 @@
         <v>60</v>
       </c>
       <c r="AA10">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB10">
+        <v>11</v>
+      </c>
+      <c r="AC10">
         <v>10.5</v>
-      </c>
-      <c r="AC10">
-        <v>11</v>
       </c>
       <c r="AD10">
         <v>25</v>
@@ -3101,7 +3101,7 @@
         <v>20</v>
       </c>
       <c r="AQ10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR10">
         <v>50</v>
@@ -3110,7 +3110,7 @@
         <v>46</v>
       </c>
       <c r="AT10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU10">
         <v>9.800000000000001</v>
@@ -3122,28 +3122,28 @@
         <v>70</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA10">
         <v>60</v>
       </c>
       <c r="BB10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC10">
         <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE10">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF10">
         <v>6</v>
@@ -3155,19 +3155,19 @@
         <v>4.2</v>
       </c>
       <c r="BI10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL10">
         <v>110</v>
       </c>
       <c r="BM10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN10">
         <v>4.3</v>
@@ -3179,31 +3179,31 @@
         <v>9.4</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BT10">
         <v>9.800000000000001</v>
       </c>
       <c r="BU10">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BV10">
         <v>50</v>
       </c>
       <c r="BW10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX10">
         <v>50</v>
       </c>
       <c r="BY10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ10">
         <v>14.5</v>
@@ -3232,7 +3232,7 @@
         <v>132</v>
       </c>
       <c r="F11">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G11">
         <v>1.48</v>
@@ -3253,7 +3253,7 @@
         <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11">
         <v>5.5</v>
@@ -3262,7 +3262,7 @@
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q11">
         <v>1.61</v>
@@ -3298,7 +3298,7 @@
         <v>260</v>
       </c>
       <c r="AB11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC11">
         <v>12</v>
@@ -3316,7 +3316,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI11">
         <v>150</v>
@@ -3337,7 +3337,7 @@
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP11">
         <v>18.5</v>
@@ -3349,7 +3349,7 @@
         <v>50</v>
       </c>
       <c r="AS11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
@@ -3358,16 +3358,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX11">
         <v>8.800000000000001</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
         <v>18.5</v>
@@ -3385,10 +3385,10 @@
         <v>23</v>
       </c>
       <c r="BE11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG11">
         <v>55</v>
@@ -3474,19 +3474,19 @@
         <v>133</v>
       </c>
       <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12">
         <v>2.04</v>
       </c>
-      <c r="G12">
-        <v>2.06</v>
-      </c>
       <c r="H12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
         <v>4.3</v>
@@ -3504,16 +3504,16 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="R12">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="S12">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T12">
         <v>1.5</v>
@@ -3522,10 +3522,10 @@
         <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="X12">
         <v>29</v>
@@ -3534,10 +3534,10 @@
         <v>24</v>
       </c>
       <c r="Z12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB12">
         <v>16.5</v>
@@ -3546,10 +3546,10 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF12">
         <v>17</v>
@@ -3564,10 +3564,10 @@
         <v>34</v>
       </c>
       <c r="AJ12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK12">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL12">
         <v>24</v>
@@ -3576,10 +3576,10 @@
         <v>46</v>
       </c>
       <c r="AN12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP12">
         <v>27</v>
@@ -3591,7 +3591,7 @@
         <v>30</v>
       </c>
       <c r="AS12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT12">
         <v>15</v>
@@ -3603,7 +3603,7 @@
         <v>14.5</v>
       </c>
       <c r="AW12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX12">
         <v>15.5</v>
@@ -3615,13 +3615,13 @@
         <v>13</v>
       </c>
       <c r="BA12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC12">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BD12">
         <v>22</v>
@@ -3645,22 +3645,22 @@
         <v>8.4</v>
       </c>
       <c r="BK12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL12">
         <v>70</v>
       </c>
       <c r="BM12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN12">
         <v>5.4</v>
       </c>
       <c r="BO12">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ12">
         <v>7.4</v>
@@ -3669,31 +3669,31 @@
         <v>21</v>
       </c>
       <c r="BS12">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT12">
         <v>7.4</v>
       </c>
       <c r="BU12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW12">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX12">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ12">
         <v>14</v>
       </c>
       <c r="CA12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB12" t="s">
         <v>148</v>
@@ -3722,22 +3722,22 @@
         <v>3.2</v>
       </c>
       <c r="H13">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I13">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
         <v>4.6</v>
@@ -3764,19 +3764,19 @@
         <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W13">
         <v>1.45</v>
       </c>
       <c r="X13">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y13">
         <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA13">
         <v>32</v>
@@ -3791,13 +3791,13 @@
         <v>11.5</v>
       </c>
       <c r="AE13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF13">
         <v>23</v>
       </c>
       <c r="AG13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH13">
         <v>15.5</v>
@@ -3806,10 +3806,10 @@
         <v>34</v>
       </c>
       <c r="AJ13">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK13">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL13">
         <v>40</v>
@@ -3824,13 +3824,13 @@
         <v>16</v>
       </c>
       <c r="AP13">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ13">
         <v>11.5</v>
       </c>
       <c r="AR13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS13">
         <v>29</v>
@@ -3848,34 +3848,34 @@
         <v>21</v>
       </c>
       <c r="AX13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ13">
         <v>14</v>
       </c>
       <c r="BA13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB13">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC13">
         <v>29</v>
       </c>
       <c r="BD13">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE13">
         <v>60</v>
       </c>
       <c r="BF13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG13">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH13">
         <v>3.75</v>
@@ -3890,13 +3890,13 @@
         <v>8</v>
       </c>
       <c r="BL13">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BO13">
         <v>5.8</v>
@@ -3905,37 +3905,37 @@
         <v>23</v>
       </c>
       <c r="BQ13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR13">
         <v>32</v>
       </c>
       <c r="BS13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV13">
         <v>16.5</v>
       </c>
       <c r="BW13">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BX13">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY13">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BZ13">
         <v>21</v>
       </c>
       <c r="CA13">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="CB13" t="s">
         <v>148</v>
@@ -3958,46 +3958,46 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H14">
+        <v>3.45</v>
+      </c>
+      <c r="I14">
         <v>3.5</v>
       </c>
-      <c r="I14">
-        <v>3.55</v>
-      </c>
       <c r="J14">
+        <v>3.9</v>
+      </c>
+      <c r="K14">
         <v>3.95</v>
       </c>
-      <c r="K14">
-        <v>4.1</v>
-      </c>
       <c r="L14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="O14">
         <v>1.21</v>
       </c>
       <c r="P14">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
         <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T14">
         <v>1.58</v>
@@ -4006,37 +4006,37 @@
         <v>2.62</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y14">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA14">
         <v>60</v>
       </c>
       <c r="AB14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC14">
         <v>9.4</v>
       </c>
       <c r="AD14">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4060,7 +4060,7 @@
         <v>60</v>
       </c>
       <c r="AN14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO14">
         <v>25</v>
@@ -4072,55 +4072,55 @@
         <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT14">
+        <v>12.5</v>
+      </c>
+      <c r="AU14">
+        <v>8.4</v>
+      </c>
+      <c r="AV14">
         <v>13</v>
-      </c>
-      <c r="AU14">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV14">
-        <v>13.5</v>
       </c>
       <c r="AW14">
         <v>30</v>
       </c>
       <c r="AX14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY14">
         <v>10</v>
       </c>
       <c r="AZ14">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA14">
         <v>34</v>
       </c>
       <c r="BB14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC14">
         <v>18</v>
       </c>
       <c r="BD14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE14">
         <v>48</v>
       </c>
       <c r="BF14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG14">
         <v>22</v>
       </c>
       <c r="BH14">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BI14">
         <v>3.85</v>
@@ -4129,55 +4129,55 @@
         <v>9</v>
       </c>
       <c r="BK14">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM14">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BN14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BO14">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BP14">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ14">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BS14">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT14">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU14">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV14">
         <v>25</v>
       </c>
       <c r="BW14">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BX14">
         <v>32</v>
       </c>
       <c r="BY14">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ14">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA14">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB14" t="s">
         <v>148</v>
@@ -4200,25 +4200,25 @@
         <v>136</v>
       </c>
       <c r="F15">
+        <v>2.38</v>
+      </c>
+      <c r="G15">
         <v>2.4</v>
       </c>
-      <c r="G15">
-        <v>2.44</v>
-      </c>
       <c r="H15">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I15">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J15">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.03</v>
@@ -4227,19 +4227,19 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="Q15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R15">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S15">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T15">
         <v>1.46</v>
@@ -4248,34 +4248,34 @@
         <v>3</v>
       </c>
       <c r="V15">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X15">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y15">
         <v>21</v>
       </c>
       <c r="Z15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC15">
         <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF15">
         <v>21</v>
@@ -4287,7 +4287,7 @@
         <v>13.5</v>
       </c>
       <c r="AI15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ15">
         <v>34</v>
@@ -4299,10 +4299,10 @@
         <v>25</v>
       </c>
       <c r="AM15">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO15">
         <v>14.5</v>
@@ -4311,16 +4311,16 @@
         <v>27</v>
       </c>
       <c r="AQ15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS15">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT15">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU15">
         <v>9.4</v>
@@ -4332,7 +4332,7 @@
         <v>23</v>
       </c>
       <c r="AX15">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY15">
         <v>11</v>
@@ -4341,46 +4341,46 @@
         <v>12.5</v>
       </c>
       <c r="BA15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB15">
         <v>29</v>
       </c>
       <c r="BC15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD15">
         <v>23</v>
       </c>
       <c r="BE15">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF15">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH15">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI15">
         <v>4.5</v>
       </c>
       <c r="BJ15">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK15">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL15">
         <v>65</v>
       </c>
       <c r="BM15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO15">
         <v>5.5</v>
@@ -4389,37 +4389,37 @@
         <v>16</v>
       </c>
       <c r="BQ15">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR15">
         <v>22</v>
       </c>
       <c r="BS15">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="BT15">
         <v>6.8</v>
       </c>
       <c r="BU15">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV15">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW15">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BX15">
         <v>24</v>
       </c>
       <c r="BY15">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="BZ15">
         <v>13.5</v>
       </c>
       <c r="CA15">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB15" t="s">
         <v>148</v>
@@ -4442,10 +4442,10 @@
         <v>137</v>
       </c>
       <c r="F16">
+        <v>1.7</v>
+      </c>
+      <c r="G16">
         <v>1.71</v>
-      </c>
-      <c r="G16">
-        <v>1.73</v>
       </c>
       <c r="H16">
         <v>4.7</v>
@@ -4454,37 +4454,37 @@
         <v>4.9</v>
       </c>
       <c r="J16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K16">
         <v>4.9</v>
       </c>
       <c r="L16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R16">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="S16">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="T16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U16">
         <v>3.05</v>
@@ -4493,22 +4493,22 @@
         <v>1.26</v>
       </c>
       <c r="W16">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X16">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y16">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z16">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA16">
         <v>110</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
         <v>13.5</v>
@@ -4520,7 +4520,7 @@
         <v>44</v>
       </c>
       <c r="AF16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4532,7 +4532,7 @@
         <v>38</v>
       </c>
       <c r="AJ16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK16">
         <v>15.5</v>
@@ -4544,37 +4544,37 @@
         <v>46</v>
       </c>
       <c r="AN16">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AO16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ16">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR16">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT16">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV16">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW16">
         <v>38</v>
       </c>
       <c r="AX16">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY16">
         <v>10</v>
@@ -4589,16 +4589,16 @@
         <v>19</v>
       </c>
       <c r="BC16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE16">
         <v>40</v>
       </c>
       <c r="BF16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG16">
         <v>22</v>
@@ -4607,61 +4607,61 @@
         <v>5.7</v>
       </c>
       <c r="BI16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BJ16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL16">
         <v>60</v>
       </c>
       <c r="BM16">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BN16">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO16">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP16">
         <v>11</v>
       </c>
       <c r="BQ16">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BS16">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT16">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU16">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BV16">
         <v>30</v>
       </c>
       <c r="BW16">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX16">
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CA16">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB16" t="s">
         <v>148</v>
@@ -4696,7 +4696,7 @@
         <v>4.7</v>
       </c>
       <c r="J17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4708,22 +4708,22 @@
         <v>1.03</v>
       </c>
       <c r="N17">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O17">
         <v>1.19</v>
       </c>
       <c r="P17">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S17">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T17">
         <v>1.6</v>
@@ -4753,7 +4753,7 @@
         <v>13</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17">
         <v>18</v>
@@ -4765,7 +4765,7 @@
         <v>14</v>
       </c>
       <c r="AG17">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH17">
         <v>16</v>
@@ -4777,10 +4777,10 @@
         <v>19.5</v>
       </c>
       <c r="AK17">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AL17">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM17">
         <v>65</v>
@@ -4795,10 +4795,10 @@
         <v>22</v>
       </c>
       <c r="AQ17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR17">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS17">
         <v>75</v>
@@ -4819,10 +4819,10 @@
         <v>12.5</v>
       </c>
       <c r="AY17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA17">
         <v>40</v>
@@ -4852,16 +4852,16 @@
         <v>4.1</v>
       </c>
       <c r="BJ17">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK17">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL17">
         <v>80</v>
       </c>
       <c r="BM17">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -4870,40 +4870,40 @@
         <v>4.4</v>
       </c>
       <c r="BP17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BQ17">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR17">
         <v>21</v>
       </c>
       <c r="BS17">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BT17">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV17">
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BX17">
         <v>36</v>
       </c>
       <c r="BY17">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BZ17">
         <v>14.5</v>
       </c>
       <c r="CA17">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB17" t="s">
         <v>148</v>
@@ -4929,73 +4929,73 @@
         <v>4.9</v>
       </c>
       <c r="G18">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="H18">
         <v>1.59</v>
       </c>
       <c r="I18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J18">
         <v>4.5</v>
       </c>
       <c r="K18">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L18">
         <v>1.25</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
         <v>6</v>
       </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
         <v>1.67</v>
       </c>
       <c r="S18">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T18">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U18">
         <v>2.36</v>
       </c>
       <c r="V18">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X18">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y18">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z18">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA18">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AB18">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AC18">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AD18">
         <v>13</v>
@@ -5007,7 +5007,7 @@
         <v>60</v>
       </c>
       <c r="AG18">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH18">
         <v>22</v>
@@ -5016,88 +5016,88 @@
         <v>32</v>
       </c>
       <c r="AJ18">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AK18">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AL18">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AM18">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN18">
         <v>55</v>
       </c>
       <c r="AO18">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP18">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AQ18">
+        <v>11</v>
+      </c>
+      <c r="AR18">
+        <v>10.5</v>
+      </c>
+      <c r="AS18">
+        <v>14.5</v>
+      </c>
+      <c r="AT18">
+        <v>13</v>
+      </c>
+      <c r="AU18">
         <v>9.800000000000001</v>
       </c>
-      <c r="AR18">
-        <v>9.6</v>
-      </c>
-      <c r="AS18">
-        <v>12.5</v>
-      </c>
-      <c r="AT18">
-        <v>20</v>
-      </c>
-      <c r="AU18">
-        <v>8.6</v>
-      </c>
       <c r="AV18">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AW18">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX18">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="AY18">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AZ18">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA18">
         <v>21</v>
       </c>
       <c r="BB18">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC18">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD18">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE18">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF18">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="BG18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH18">
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ18">
         <v>13</v>
       </c>
       <c r="BK18">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5109,25 +5109,25 @@
         <v>13.5</v>
       </c>
       <c r="BO18">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BP18">
         <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BT18">
         <v>6.6</v>
       </c>
       <c r="BU18">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BV18">
         <v>14.5</v>
@@ -5136,7 +5136,7 @@
         <v>1.76</v>
       </c>
       <c r="BX18">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY18">
         <v>1.87</v>
@@ -5145,7 +5145,7 @@
         <v>17.5</v>
       </c>
       <c r="CA18">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CB18" t="s">
         <v>148</v>
@@ -5168,25 +5168,25 @@
         <v>140</v>
       </c>
       <c r="F19">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="G19">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I19">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="J19">
         <v>3.1</v>
       </c>
       <c r="K19">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M19">
         <v>1.1</v>
@@ -5198,7 +5198,7 @@
         <v>1.42</v>
       </c>
       <c r="P19">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
         <v>2.24</v>
@@ -5210,85 +5210,85 @@
         <v>4.3</v>
       </c>
       <c r="T19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U19">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="X19">
         <v>13</v>
       </c>
       <c r="Y19">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA19">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AB19">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC19">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
         <v>17</v>
       </c>
       <c r="AE19">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AF19">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AG19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AI19">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="AJ19">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AK19">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AL19">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM19">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN19">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO19">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AP19">
         <v>9.4</v>
       </c>
       <c r="AQ19">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR19">
         <v>16.5</v>
       </c>
       <c r="AS19">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT19">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU19">
         <v>6.4</v>
@@ -5300,7 +5300,7 @@
         <v>32</v>
       </c>
       <c r="AX19">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY19">
         <v>10.5</v>
@@ -5309,22 +5309,22 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
+        <v>23</v>
+      </c>
+      <c r="BB19">
+        <v>6.2</v>
+      </c>
+      <c r="BC19">
+        <v>14.5</v>
+      </c>
+      <c r="BD19">
+        <v>23</v>
+      </c>
+      <c r="BE19">
+        <v>7</v>
+      </c>
+      <c r="BF19">
         <v>6</v>
-      </c>
-      <c r="BB19">
-        <v>5.9</v>
-      </c>
-      <c r="BC19">
-        <v>5.7</v>
-      </c>
-      <c r="BD19">
-        <v>6</v>
-      </c>
-      <c r="BE19">
-        <v>6.4</v>
-      </c>
-      <c r="BF19">
-        <v>5.7</v>
       </c>
       <c r="BG19">
         <v>29</v>
@@ -5348,34 +5348,34 @@
         <v>13.5</v>
       </c>
       <c r="BN19">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO19">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT19">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU19">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX19">
         <v>1000</v>
@@ -5413,7 +5413,7 @@
         <v>1.79</v>
       </c>
       <c r="G20">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H20">
         <v>5.5</v>
@@ -5422,34 +5422,34 @@
         <v>6.6</v>
       </c>
       <c r="J20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K20">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M20">
         <v>1.11</v>
       </c>
       <c r="N20">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
         <v>1.52</v>
       </c>
       <c r="P20">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="Q20">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
         <v>1.19</v>
       </c>
       <c r="S20">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T20">
         <v>2.24</v>
@@ -5461,10 +5461,10 @@
         <v>1.18</v>
       </c>
       <c r="W20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y20">
         <v>15</v>
@@ -5473,7 +5473,7 @@
         <v>48</v>
       </c>
       <c r="AA20">
-        <v>220</v>
+        <v>900</v>
       </c>
       <c r="AB20">
         <v>6.2</v>
@@ -5485,10 +5485,10 @@
         <v>26</v>
       </c>
       <c r="AE20">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AF20">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG20">
         <v>11</v>
@@ -5497,7 +5497,7 @@
         <v>30</v>
       </c>
       <c r="AI20">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="AJ20">
         <v>21</v>
@@ -5509,25 +5509,25 @@
         <v>60</v>
       </c>
       <c r="AM20">
-        <v>260</v>
+        <v>580</v>
       </c>
       <c r="AN20">
         <v>21</v>
       </c>
       <c r="AO20">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AP20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20">
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AS20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT20">
         <v>5.2</v>
@@ -5539,7 +5539,7 @@
         <v>19.5</v>
       </c>
       <c r="AW20">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX20">
         <v>8</v>
@@ -5551,7 +5551,7 @@
         <v>22</v>
       </c>
       <c r="BA20">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB20">
         <v>17</v>
@@ -5560,16 +5560,16 @@
         <v>21</v>
       </c>
       <c r="BD20">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF20">
         <v>16</v>
       </c>
       <c r="BG20">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
         <v>142</v>
       </c>
       <c r="F21">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G21">
         <v>2.18</v>
@@ -5667,7 +5667,7 @@
         <v>3.2</v>
       </c>
       <c r="K21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L21">
         <v>1.45</v>
@@ -5685,7 +5685,7 @@
         <v>1.63</v>
       </c>
       <c r="Q21">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
         <v>1.22</v>
@@ -5715,7 +5715,7 @@
         <v>32</v>
       </c>
       <c r="AA21">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB21">
         <v>7.8</v>
@@ -5727,7 +5727,7 @@
         <v>19</v>
       </c>
       <c r="AE21">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF21">
         <v>12.5</v>
@@ -5739,7 +5739,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
         <v>29</v>
@@ -5751,22 +5751,22 @@
         <v>55</v>
       </c>
       <c r="AM21">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN21">
         <v>25</v>
       </c>
       <c r="AO21">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="AP21">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ21">
         <v>10.5</v>
       </c>
       <c r="AR21">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS21">
         <v>9</v>
@@ -5781,7 +5781,7 @@
         <v>15.5</v>
       </c>
       <c r="AW21">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX21">
         <v>10</v>
@@ -5793,13 +5793,13 @@
         <v>19</v>
       </c>
       <c r="BA21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB21">
         <v>22</v>
       </c>
       <c r="BC21">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BD21">
         <v>42</v>
@@ -5811,7 +5811,7 @@
         <v>18</v>
       </c>
       <c r="BG21">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH21">
         <v>2.98</v>
@@ -5900,7 +5900,7 @@
         <v>5.2</v>
       </c>
       <c r="H22">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I22">
         <v>2.1</v>
@@ -5918,16 +5918,16 @@
         <v>1.17</v>
       </c>
       <c r="N22">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O22">
         <v>1.74</v>
       </c>
       <c r="P22">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
         <v>1.14</v>
@@ -5945,19 +5945,19 @@
         <v>1.9</v>
       </c>
       <c r="W22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z22">
         <v>10.5</v>
       </c>
       <c r="AA22">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB22">
         <v>11</v>
@@ -5969,7 +5969,7 @@
         <v>13.5</v>
       </c>
       <c r="AE22">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF22">
         <v>36</v>
@@ -5978,34 +5978,34 @@
         <v>24</v>
       </c>
       <c r="AH22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AM22">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AO22">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP22">
         <v>6.2</v>
       </c>
       <c r="AQ22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR22">
         <v>9.199999999999999</v>
@@ -6023,7 +6023,7 @@
         <v>11.5</v>
       </c>
       <c r="AW22">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX22">
         <v>25</v>
@@ -6032,7 +6032,7 @@
         <v>20</v>
       </c>
       <c r="AZ22">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA22">
         <v>36</v>
@@ -6044,76 +6044,76 @@
         <v>38</v>
       </c>
       <c r="BD22">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE22">
         <v>95</v>
       </c>
       <c r="BF22">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="BG22">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BJ22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BK22">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BN22">
         <v>11.5</v>
       </c>
       <c r="BO22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BT22">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU22">
-        <v>3.3</v>
+        <v>1.27</v>
       </c>
       <c r="BV22">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BW22">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CB22" t="s">
         <v>148</v>
@@ -6148,10 +6148,10 @@
         <v>3.35</v>
       </c>
       <c r="J23">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K23">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L23">
         <v>1.64</v>
@@ -6163,7 +6163,7 @@
         <v>2.28</v>
       </c>
       <c r="O23">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="P23">
         <v>1.42</v>
@@ -6190,16 +6190,16 @@
         <v>1.52</v>
       </c>
       <c r="X23">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>24</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB23">
         <v>7.4</v>
@@ -6208,43 +6208,43 @@
         <v>7.2</v>
       </c>
       <c r="AD23">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AE23">
-        <v>620</v>
+        <v>430</v>
       </c>
       <c r="AF23">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG23">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH23">
         <v>50</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ23">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AK23">
         <v>230</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AM23">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AN23">
-        <v>960</v>
+        <v>200</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP23">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23">
         <v>7.2</v>
@@ -6289,7 +6289,7 @@
         <v>38</v>
       </c>
       <c r="BE23">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF23">
         <v>30</v>
@@ -6319,7 +6319,7 @@
         <v>7.6</v>
       </c>
       <c r="BO23">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP23">
         <v>40</v>
@@ -6337,7 +6337,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU23">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV23">
         <v>48</v>
@@ -6378,13 +6378,13 @@
         <v>145</v>
       </c>
       <c r="F24">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G24">
         <v>1.58</v>
       </c>
       <c r="H24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -6408,7 +6408,7 @@
         <v>1.35</v>
       </c>
       <c r="P24">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q24">
         <v>2.04</v>
@@ -6441,7 +6441,7 @@
         <v>65</v>
       </c>
       <c r="AA24">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
         <v>7.4</v>
@@ -6462,22 +6462,22 @@
         <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AJ24">
         <v>14</v>
       </c>
       <c r="AK24">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL24">
         <v>44</v>
       </c>
       <c r="AM24">
-        <v>180</v>
+        <v>690</v>
       </c>
       <c r="AN24">
         <v>9.6</v>
@@ -6495,7 +6495,7 @@
         <v>55</v>
       </c>
       <c r="AS24">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AT24">
         <v>7</v>
@@ -6507,7 +6507,7 @@
         <v>26</v>
       </c>
       <c r="AW24">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX24">
         <v>7.6</v>
@@ -6531,13 +6531,13 @@
         <v>38</v>
       </c>
       <c r="BE24">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF24">
         <v>8.800000000000001</v>
       </c>
       <c r="BG24">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="BH24">
         <v>3.4</v>
@@ -6620,10 +6620,10 @@
         <v>146</v>
       </c>
       <c r="F25">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G25">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H25">
         <v>5.1</v>
@@ -6647,7 +6647,7 @@
         <v>4.2</v>
       </c>
       <c r="O25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P25">
         <v>2.06</v>
@@ -6671,10 +6671,10 @@
         <v>1.22</v>
       </c>
       <c r="W25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y25">
         <v>26</v>
@@ -6683,7 +6683,7 @@
         <v>100</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB25">
         <v>9.4</v>
@@ -6695,7 +6695,7 @@
         <v>21</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AF25">
         <v>11.5</v>
@@ -6707,34 +6707,34 @@
         <v>24</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ25">
         <v>24</v>
       </c>
       <c r="AK25">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AL25">
         <v>65</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN25">
         <v>11</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP25">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ25">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR25">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AS25">
         <v>40</v>
@@ -6743,13 +6743,13 @@
         <v>8.6</v>
       </c>
       <c r="AU25">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV25">
         <v>15.5</v>
       </c>
       <c r="AW25">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AX25">
         <v>10</v>
@@ -6761,7 +6761,7 @@
         <v>15</v>
       </c>
       <c r="BA25">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BB25">
         <v>17</v>
@@ -6770,10 +6770,10 @@
         <v>14.5</v>
       </c>
       <c r="BD25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE25">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF25">
         <v>9.800000000000001</v>
@@ -6865,7 +6865,7 @@
         <v>2.16</v>
       </c>
       <c r="G26">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H26">
         <v>4.3</v>
@@ -6889,13 +6889,13 @@
         <v>2.62</v>
       </c>
       <c r="O26">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P26">
         <v>1.54</v>
       </c>
       <c r="Q26">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R26">
         <v>1.19</v>
@@ -6913,7 +6913,7 @@
         <v>1.26</v>
       </c>
       <c r="W26">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X26">
         <v>10.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="153">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Icelandic 3 Deild</t>
+  </si>
+  <si>
     <t>Argentinian Primera Division</t>
   </si>
   <si>
@@ -283,12 +286,15 @@
     <t>00:00:00</t>
   </si>
   <si>
-    <t>00:15:00</t>
+    <t>00:25:00</t>
   </si>
   <si>
     <t>00:30:00</t>
   </si>
   <si>
+    <t>00:40:00</t>
+  </si>
+  <si>
     <t>01:00:00</t>
   </si>
   <si>
@@ -361,6 +367,9 @@
     <t>Leiknir R</t>
   </si>
   <si>
+    <t>KA Asvellir</t>
+  </si>
+  <si>
     <t>Orense Sporting Club</t>
   </si>
   <si>
@@ -436,6 +445,9 @@
     <t>Throttur</t>
   </si>
   <si>
+    <t>Augnablik</t>
+  </si>
+  <si>
     <t>Aucas</t>
   </si>
   <si>
@@ -460,7 +472,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-22 19:12:56</t>
+    <t>2026-07-22 21:21:53</t>
   </si>
 </sst>
 </file>
@@ -792,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB26"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1042,241 +1054,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F2">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
+        <v>2.48</v>
+      </c>
+      <c r="H2">
+        <v>3.6</v>
+      </c>
+      <c r="I2">
+        <v>3.9</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.15</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1.18</v>
+      </c>
+      <c r="N2">
+        <v>2.2</v>
+      </c>
+      <c r="O2">
+        <v>1.78</v>
+      </c>
+      <c r="P2">
+        <v>1.36</v>
+      </c>
+      <c r="Q2">
+        <v>3.05</v>
+      </c>
+      <c r="R2">
+        <v>1.12</v>
+      </c>
+      <c r="S2">
+        <v>8.4</v>
+      </c>
+      <c r="T2">
+        <v>1.07</v>
+      </c>
+      <c r="U2">
+        <v>1.02</v>
+      </c>
+      <c r="V2">
+        <v>1.37</v>
+      </c>
+      <c r="W2">
+        <v>1.65</v>
+      </c>
+      <c r="X2">
+        <v>7.6</v>
+      </c>
+      <c r="Y2">
+        <v>12.5</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>10</v>
+      </c>
+      <c r="AD2">
+        <v>160</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>36</v>
+      </c>
+      <c r="AG2">
+        <v>990</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.8</v>
+      </c>
+      <c r="AQ2">
+        <v>7.2</v>
+      </c>
+      <c r="AR2">
+        <v>2.18</v>
+      </c>
+      <c r="AS2">
+        <v>2.18</v>
+      </c>
+      <c r="AT2">
+        <v>5.4</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>2.18</v>
+      </c>
+      <c r="AX2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>2.18</v>
+      </c>
+      <c r="BA2">
+        <v>2.18</v>
+      </c>
+      <c r="BB2">
+        <v>2.18</v>
+      </c>
+      <c r="BC2">
+        <v>2.18</v>
+      </c>
+      <c r="BD2">
+        <v>2.18</v>
+      </c>
+      <c r="BE2">
+        <v>2.18</v>
+      </c>
+      <c r="BF2">
+        <v>2.16</v>
+      </c>
+      <c r="BG2">
+        <v>18.5</v>
+      </c>
+      <c r="BH2">
+        <v>2.12</v>
+      </c>
+      <c r="BI2">
+        <v>1.95</v>
+      </c>
+      <c r="BJ2">
+        <v>21</v>
+      </c>
+      <c r="BK2">
+        <v>14.5</v>
+      </c>
+      <c r="BL2">
+        <v>820</v>
+      </c>
+      <c r="BM2">
+        <v>10</v>
+      </c>
+      <c r="BN2">
         <v>5.5</v>
       </c>
-      <c r="H2">
-        <v>1.88</v>
-      </c>
-      <c r="I2">
-        <v>1.94</v>
-      </c>
-      <c r="J2">
-        <v>3.35</v>
-      </c>
-      <c r="K2">
-        <v>3.5</v>
-      </c>
-      <c r="L2">
-        <v>1.54</v>
-      </c>
-      <c r="M2">
-        <v>1.12</v>
-      </c>
-      <c r="N2">
-        <v>2.88</v>
-      </c>
-      <c r="O2">
-        <v>1.5</v>
-      </c>
-      <c r="P2">
-        <v>1.61</v>
-      </c>
-      <c r="Q2">
-        <v>2.52</v>
-      </c>
-      <c r="R2">
-        <v>1.22</v>
-      </c>
-      <c r="S2">
-        <v>5</v>
-      </c>
-      <c r="T2">
-        <v>2.18</v>
-      </c>
-      <c r="U2">
-        <v>1.74</v>
-      </c>
-      <c r="V2">
-        <v>2.06</v>
-      </c>
-      <c r="W2">
-        <v>1.22</v>
-      </c>
-      <c r="X2">
+      <c r="BO2">
+        <v>4.8</v>
+      </c>
+      <c r="BP2">
+        <v>40</v>
+      </c>
+      <c r="BQ2">
+        <v>24</v>
+      </c>
+      <c r="BR2">
+        <v>120</v>
+      </c>
+      <c r="BS2">
         <v>10</v>
       </c>
-      <c r="Y2">
+      <c r="BT2">
         <v>7</v>
       </c>
-      <c r="Z2">
-        <v>11</v>
-      </c>
-      <c r="AA2">
-        <v>24</v>
-      </c>
-      <c r="AB2">
-        <v>13.5</v>
-      </c>
-      <c r="AC2">
-        <v>8</v>
-      </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
-      <c r="AE2">
-        <v>26</v>
-      </c>
-      <c r="AF2">
-        <v>46</v>
-      </c>
-      <c r="AG2">
-        <v>22</v>
-      </c>
-      <c r="AH2">
-        <v>26</v>
-      </c>
-      <c r="AI2">
-        <v>60</v>
-      </c>
-      <c r="AJ2">
-        <v>380</v>
-      </c>
-      <c r="AK2">
-        <v>180</v>
-      </c>
-      <c r="AL2">
-        <v>250</v>
-      </c>
-      <c r="AM2">
-        <v>220</v>
-      </c>
-      <c r="AN2">
-        <v>250</v>
-      </c>
-      <c r="AO2">
-        <v>22</v>
-      </c>
-      <c r="AP2">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2">
-        <v>5.8</v>
-      </c>
-      <c r="AR2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS2">
-        <v>19.5</v>
-      </c>
-      <c r="AT2">
-        <v>11.5</v>
-      </c>
-      <c r="AU2">
-        <v>6.8</v>
-      </c>
-      <c r="AV2">
-        <v>9.4</v>
-      </c>
-      <c r="AW2">
-        <v>21</v>
-      </c>
-      <c r="AX2">
-        <v>32</v>
-      </c>
-      <c r="AY2">
-        <v>18</v>
-      </c>
-      <c r="AZ2">
-        <v>21</v>
-      </c>
-      <c r="BA2">
-        <v>40</v>
-      </c>
-      <c r="BB2">
+      <c r="BU2">
+        <v>5.9</v>
+      </c>
+      <c r="BV2">
+        <v>65</v>
+      </c>
+      <c r="BW2">
+        <v>36</v>
+      </c>
+      <c r="BX2">
+        <v>150</v>
+      </c>
+      <c r="BY2">
+        <v>10.5</v>
+      </c>
+      <c r="BZ2">
+        <v>160</v>
+      </c>
+      <c r="CA2">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC2">
-        <v>55</v>
-      </c>
-      <c r="BD2">
-        <v>60</v>
-      </c>
-      <c r="BE2">
-        <v>9.6</v>
-      </c>
-      <c r="BF2">
-        <v>9.6</v>
-      </c>
-      <c r="BG2">
-        <v>18</v>
-      </c>
-      <c r="BH2">
-        <v>3.05</v>
-      </c>
-      <c r="BI2">
-        <v>2.68</v>
-      </c>
-      <c r="BJ2">
-        <v>13</v>
-      </c>
-      <c r="BK2">
-        <v>7.2</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>12</v>
-      </c>
-      <c r="BN2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO2">
-        <v>7.4</v>
-      </c>
-      <c r="BP2">
-        <v>60</v>
-      </c>
-      <c r="BQ2">
-        <v>10.5</v>
-      </c>
-      <c r="BR2">
-        <v>80</v>
-      </c>
-      <c r="BS2">
-        <v>11</v>
-      </c>
-      <c r="BT2">
-        <v>4</v>
-      </c>
-      <c r="BU2">
-        <v>3.5</v>
-      </c>
-      <c r="BV2">
-        <v>14</v>
-      </c>
-      <c r="BW2">
-        <v>6.6</v>
-      </c>
-      <c r="BX2">
-        <v>36</v>
-      </c>
-      <c r="BY2">
-        <v>9.6</v>
-      </c>
-      <c r="BZ2">
-        <v>36</v>
-      </c>
-      <c r="CA2">
-        <v>9.6</v>
-      </c>
       <c r="CB2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1284,241 +1296,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F3">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
         <v>1.35</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q3">
+        <v>1.76</v>
+      </c>
+      <c r="R3">
+        <v>1.47</v>
+      </c>
+      <c r="S3">
+        <v>2.92</v>
+      </c>
+      <c r="T3">
+        <v>1.65</v>
+      </c>
+      <c r="U3">
+        <v>2.46</v>
+      </c>
+      <c r="V3">
+        <v>1.41</v>
+      </c>
+      <c r="W3">
         <v>1.74</v>
       </c>
-      <c r="R3">
-        <v>1.52</v>
-      </c>
-      <c r="S3">
-        <v>2.84</v>
-      </c>
-      <c r="T3">
-        <v>1.63</v>
-      </c>
-      <c r="U3">
-        <v>2.5</v>
-      </c>
-      <c r="V3">
-        <v>1.35</v>
-      </c>
-      <c r="W3">
-        <v>1.89</v>
-      </c>
       <c r="X3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
         <v>38</v>
       </c>
       <c r="AF3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AG3">
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3">
         <v>46</v>
       </c>
       <c r="AJ3">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
         <v>32</v>
       </c>
       <c r="AP3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
         <v>14.5</v>
       </c>
       <c r="BA3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
+        <v>13</v>
+      </c>
+      <c r="BG3">
+        <v>25</v>
+      </c>
+      <c r="BH3">
+        <v>4.4</v>
+      </c>
+      <c r="BI3">
+        <v>3.2</v>
+      </c>
+      <c r="BJ3">
+        <v>8.4</v>
+      </c>
+      <c r="BK3">
+        <v>6.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>65</v>
+      </c>
+      <c r="BN3">
+        <v>6.4</v>
+      </c>
+      <c r="BO3">
+        <v>4.9</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
         <v>11</v>
       </c>
-      <c r="BG3">
-        <v>29</v>
-      </c>
-      <c r="BH3">
-        <v>3.95</v>
-      </c>
-      <c r="BI3">
-        <v>3.7</v>
-      </c>
-      <c r="BJ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK3">
-        <v>8</v>
-      </c>
-      <c r="BL3">
-        <v>90</v>
-      </c>
-      <c r="BM3">
-        <v>14.5</v>
-      </c>
-      <c r="BN3">
-        <v>5.1</v>
-      </c>
-      <c r="BO3">
-        <v>4.7</v>
-      </c>
-      <c r="BP3">
-        <v>15</v>
-      </c>
-      <c r="BQ3">
-        <v>12.5</v>
-      </c>
       <c r="BR3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>2.6</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>16.5</v>
+        <v>2.7</v>
       </c>
       <c r="CB3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1526,241 +1538,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H4">
+        <v>4.2</v>
+      </c>
+      <c r="I4">
         <v>4.3</v>
       </c>
-      <c r="I4">
-        <v>4.5</v>
-      </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M4">
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="O4">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="V4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>17.5</v>
       </c>
       <c r="AE4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
         <v>11</v>
       </c>
       <c r="AH4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4">
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AS4">
         <v>90</v>
       </c>
       <c r="AT4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX4">
         <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB4">
+        <v>26</v>
+      </c>
+      <c r="BC4">
+        <v>26</v>
+      </c>
+      <c r="BD4">
+        <v>48</v>
+      </c>
+      <c r="BE4">
+        <v>110</v>
+      </c>
+      <c r="BF4">
         <v>23</v>
       </c>
-      <c r="BC4">
-        <v>23</v>
-      </c>
-      <c r="BD4">
-        <v>42</v>
-      </c>
-      <c r="BE4">
-        <v>42</v>
-      </c>
-      <c r="BF4">
-        <v>20</v>
-      </c>
       <c r="BG4">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="BI4">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BL4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BM4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4">
         <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BR4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BS4">
-        <v>13.5</v>
+        <v>32</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
         <v>40</v>
       </c>
       <c r="BW4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY4">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="BZ4">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="CB4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1768,49 +1780,49 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F5">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G5">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="H5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5">
         <v>1.35</v>
       </c>
       <c r="P5">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q5">
         <v>2.04</v>
@@ -1825,73 +1837,73 @@
         <v>1.8</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA5">
         <v>55</v>
       </c>
       <c r="AB5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>11</v>
       </c>
       <c r="AH5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR5">
         <v>20</v>
@@ -1900,55 +1912,55 @@
         <v>50</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
         <v>7.2</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW5">
         <v>34</v>
       </c>
       <c r="AX5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD5">
         <v>36</v>
       </c>
       <c r="BE5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BI5">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
         <v>8.4</v>
@@ -1957,52 +1969,52 @@
         <v>130</v>
       </c>
       <c r="BM5">
-        <v>15.5</v>
+        <v>100</v>
       </c>
       <c r="BN5">
         <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>34</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY5">
+        <v>13</v>
+      </c>
+      <c r="BZ5">
+        <v>30</v>
+      </c>
+      <c r="CA5">
         <v>12</v>
       </c>
-      <c r="BZ5">
-        <v>32</v>
-      </c>
-      <c r="CA5">
-        <v>11</v>
-      </c>
       <c r="CB5" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2010,139 +2022,139 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="I6">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="J6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
         <v>1.83</v>
       </c>
       <c r="V6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Z6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AA6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC6">
         <v>11</v>
       </c>
       <c r="AD6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AF6">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AG6">
         <v>34</v>
       </c>
       <c r="AH6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI6">
         <v>40</v>
       </c>
       <c r="AJ6">
-        <v>470</v>
+        <v>510</v>
       </c>
       <c r="AK6">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AL6">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AM6">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AO6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AP6">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR6">
         <v>7.4</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AU6">
         <v>10.5</v>
@@ -2151,100 +2163,100 @@
         <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX6">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AY6">
         <v>32</v>
       </c>
       <c r="AZ6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB6">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BC6">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="BD6">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="BE6">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="BF6">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="BG6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH6">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL6">
         <v>170</v>
       </c>
       <c r="BM6">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="BN6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BO6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BP6">
+        <v>90</v>
+      </c>
+      <c r="BQ6">
+        <v>20</v>
+      </c>
+      <c r="BR6">
         <v>85</v>
       </c>
-      <c r="BQ6">
-        <v>19</v>
-      </c>
-      <c r="BR6">
-        <v>80</v>
-      </c>
       <c r="BS6">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BT6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BU6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV6">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BW6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX6">
         <v>26</v>
       </c>
       <c r="BY6">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="CB6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2252,52 +2264,52 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F7">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="G7">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K7">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
         <v>1.08</v>
       </c>
       <c r="N7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R7">
         <v>1.32</v>
@@ -2306,19 +2318,19 @@
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y7">
         <v>15.5</v>
@@ -2327,13 +2339,13 @@
         <v>36</v>
       </c>
       <c r="AA7">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB7">
         <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
         <v>19.5</v>
@@ -2345,148 +2357,148 @@
         <v>11</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH7">
+        <v>21</v>
+      </c>
+      <c r="AI7">
+        <v>70</v>
+      </c>
+      <c r="AJ7">
         <v>22</v>
       </c>
-      <c r="AI7">
+      <c r="AK7">
+        <v>23</v>
+      </c>
+      <c r="AL7">
+        <v>38</v>
+      </c>
+      <c r="AM7">
+        <v>120</v>
+      </c>
+      <c r="AN7">
+        <v>15.5</v>
+      </c>
+      <c r="AO7">
         <v>75</v>
-      </c>
-      <c r="AJ7">
-        <v>21</v>
-      </c>
-      <c r="AK7">
-        <v>21</v>
-      </c>
-      <c r="AL7">
-        <v>42</v>
-      </c>
-      <c r="AM7">
-        <v>130</v>
-      </c>
-      <c r="AN7">
-        <v>15</v>
-      </c>
-      <c r="AO7">
-        <v>80</v>
       </c>
       <c r="AP7">
         <v>11.5</v>
       </c>
       <c r="AQ7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR7">
         <v>30</v>
       </c>
       <c r="AS7">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="AT7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW7">
         <v>55</v>
       </c>
       <c r="AX7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB7">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD7">
         <v>34</v>
       </c>
       <c r="BE7">
-        <v>15.5</v>
+        <v>90</v>
       </c>
       <c r="BF7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BH7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI7">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BM7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN7">
         <v>4.6</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
         <v>32</v>
       </c>
       <c r="BS7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU7">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BV7">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7">
         <v>55</v>
       </c>
       <c r="BY7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA7">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2494,43 +2506,43 @@
         <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F8">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H8">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O8">
         <v>1.2</v>
@@ -2539,109 +2551,109 @@
         <v>2.54</v>
       </c>
       <c r="Q8">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R8">
         <v>1.62</v>
       </c>
       <c r="S8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T8">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V8">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="W8">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="X8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z8">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AA8">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AB8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8">
         <v>11</v>
       </c>
       <c r="AE8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AF8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI8">
         <v>27</v>
       </c>
       <c r="AJ8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK8">
+        <v>30</v>
+      </c>
+      <c r="AL8">
         <v>34</v>
       </c>
-      <c r="AL8">
-        <v>38</v>
-      </c>
       <c r="AM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN8">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP8">
         <v>21</v>
       </c>
       <c r="AQ8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR8">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS8">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AT8">
         <v>17</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AX8">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AY8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>13.5</v>
@@ -2650,85 +2662,85 @@
         <v>25</v>
       </c>
       <c r="BB8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC8">
+        <v>27</v>
+      </c>
+      <c r="BD8">
         <v>30</v>
       </c>
-      <c r="BD8">
-        <v>34</v>
-      </c>
       <c r="BE8">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BF8">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BG8">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BJ8">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BN8">
-        <v>7.2</v>
+        <v>950</v>
       </c>
       <c r="BO8">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="BP8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.6</v>
+        <v>4.1</v>
       </c>
       <c r="BR8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>10</v>
+        <v>2.38</v>
       </c>
       <c r="BT8">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="BU8">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12</v>
+        <v>2.42</v>
       </c>
       <c r="BX8">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>9.199999999999999</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>14</v>
+        <v>2.42</v>
       </c>
       <c r="CB8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2736,22 +2748,22 @@
         <v>81</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F9">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2763,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
         <v>1.37</v>
@@ -2781,7 +2793,7 @@
         <v>2.22</v>
       </c>
       <c r="Q9">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>1.47</v>
@@ -2790,16 +2802,16 @@
         <v>3</v>
       </c>
       <c r="T9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
         <v>1.26</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X9">
         <v>18</v>
@@ -2814,25 +2826,25 @@
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>9</v>
       </c>
       <c r="AD9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
         <v>55</v>
       </c>
       <c r="AF9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>9.6</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI9">
         <v>55</v>
@@ -2844,10 +2856,10 @@
         <v>18</v>
       </c>
       <c r="AL9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM9">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN9">
         <v>10.5</v>
@@ -2856,61 +2868,61 @@
         <v>55</v>
       </c>
       <c r="AP9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ9">
+        <v>18</v>
+      </c>
+      <c r="AR9">
+        <v>34</v>
+      </c>
+      <c r="AS9">
+        <v>85</v>
+      </c>
+      <c r="AT9">
+        <v>9.6</v>
+      </c>
+      <c r="AU9">
+        <v>8.6</v>
+      </c>
+      <c r="AV9">
         <v>17</v>
       </c>
-      <c r="AR9">
-        <v>32</v>
-      </c>
-      <c r="AS9">
-        <v>38</v>
-      </c>
-      <c r="AT9">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU9">
-        <v>8.4</v>
-      </c>
-      <c r="AV9">
-        <v>16.5</v>
-      </c>
       <c r="AW9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX9">
         <v>11</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9">
         <v>50</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
       </c>
       <c r="BD9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF9">
         <v>9.4</v>
       </c>
       <c r="BG9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BH9">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI9">
         <v>3.5</v>
@@ -2925,25 +2937,25 @@
         <v>110</v>
       </c>
       <c r="BM9">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP9">
         <v>13</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>8</v>
@@ -2952,7 +2964,7 @@
         <v>7</v>
       </c>
       <c r="BV9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BW9">
         <v>11.5</v>
@@ -2961,16 +2973,16 @@
         <v>44</v>
       </c>
       <c r="BY9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2978,34 +2990,34 @@
         <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="G10">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H10">
+        <v>6.4</v>
+      </c>
+      <c r="I10">
         <v>6.6</v>
       </c>
-      <c r="I10">
-        <v>7</v>
-      </c>
       <c r="J10">
+        <v>4.5</v>
+      </c>
+      <c r="K10">
         <v>4.6</v>
-      </c>
-      <c r="K10">
-        <v>4.7</v>
       </c>
       <c r="L10">
         <v>1.31</v>
@@ -3014,55 +3026,55 @@
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q10">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
         <v>1.58</v>
       </c>
       <c r="S10">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="T10">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V10">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X10">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA10">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
         <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE10">
         <v>85</v>
@@ -3071,61 +3083,61 @@
         <v>10.5</v>
       </c>
       <c r="AG10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK10">
         <v>15</v>
       </c>
       <c r="AL10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM10">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO10">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP10">
         <v>20</v>
       </c>
       <c r="AQ10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR10">
         <v>50</v>
       </c>
       <c r="AS10">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AT10">
         <v>10</v>
       </c>
       <c r="AU10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV10">
         <v>22</v>
       </c>
       <c r="AW10">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
         <v>18</v>
@@ -3134,19 +3146,19 @@
         <v>60</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD10">
         <v>26</v>
       </c>
       <c r="BE10">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG10">
         <v>60</v>
@@ -3158,16 +3170,16 @@
         <v>3.95</v>
       </c>
       <c r="BJ10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK10">
         <v>8.6</v>
       </c>
       <c r="BL10">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BM10">
-        <v>15.5</v>
+        <v>85</v>
       </c>
       <c r="BN10">
         <v>4.3</v>
@@ -3179,40 +3191,40 @@
         <v>9.4</v>
       </c>
       <c r="BQ10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR10">
         <v>22</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BT10">
         <v>9.800000000000001</v>
       </c>
       <c r="BU10">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BV10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BW10">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BX10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA10">
         <v>8.800000000000001</v>
       </c>
       <c r="CB10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3220,19 +3232,19 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G11">
         <v>1.48</v>
@@ -3241,25 +3253,25 @@
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.29</v>
       </c>
       <c r="M11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O11">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P11">
         <v>2.54</v>
@@ -3277,25 +3289,25 @@
         <v>1.84</v>
       </c>
       <c r="U11">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
         <v>3.05</v>
       </c>
       <c r="X11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Z11">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA11">
-        <v>260</v>
+        <v>850</v>
       </c>
       <c r="AB11">
         <v>10.5</v>
@@ -3307,7 +3319,7 @@
         <v>36</v>
       </c>
       <c r="AE11">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF11">
         <v>10</v>
@@ -3331,37 +3343,37 @@
         <v>38</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO11">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP11">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AQ11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR11">
         <v>50</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AT11">
         <v>9.199999999999999</v>
       </c>
       <c r="AU11">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
         <v>23</v>
       </c>
       <c r="AW11">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="AX11">
         <v>8.800000000000001</v>
@@ -3382,13 +3394,13 @@
         <v>13</v>
       </c>
       <c r="BD11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BE11">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="BF11">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG11">
         <v>55</v>
@@ -3397,13 +3409,13 @@
         <v>4.4</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BJ11">
         <v>10.5</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3415,13 +3427,13 @@
         <v>4.2</v>
       </c>
       <c r="BO11">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="BP11">
         <v>8.6</v>
       </c>
       <c r="BQ11">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR11">
         <v>21</v>
@@ -3433,7 +3445,7 @@
         <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -3454,7 +3466,7 @@
         <v>6.8</v>
       </c>
       <c r="CB11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3462,19 +3474,19 @@
         <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
         <v>2.04</v>
@@ -3483,16 +3495,16 @@
         <v>3.7</v>
       </c>
       <c r="I12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J12">
         <v>4.1</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M12">
         <v>1.03</v>
@@ -3504,7 +3516,7 @@
         <v>1.16</v>
       </c>
       <c r="P12">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q12">
         <v>1.5</v>
@@ -3519,13 +3531,13 @@
         <v>1.5</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X12">
         <v>29</v>
@@ -3534,7 +3546,7 @@
         <v>24</v>
       </c>
       <c r="Z12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA12">
         <v>70</v>
@@ -3543,13 +3555,13 @@
         <v>16.5</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD12">
         <v>16</v>
       </c>
       <c r="AE12">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>17</v>
@@ -3567,10 +3579,10 @@
         <v>25</v>
       </c>
       <c r="AK12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM12">
         <v>46</v>
@@ -3594,7 +3606,7 @@
         <v>60</v>
       </c>
       <c r="AT12">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU12">
         <v>9.6</v>
@@ -3609,7 +3621,7 @@
         <v>15.5</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
         <v>13</v>
@@ -3624,7 +3636,7 @@
         <v>15.5</v>
       </c>
       <c r="BD12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE12">
         <v>40</v>
@@ -3645,16 +3657,16 @@
         <v>8.4</v>
       </c>
       <c r="BK12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL12">
         <v>70</v>
       </c>
       <c r="BM12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN12">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO12">
         <v>4.9</v>
@@ -3663,13 +3675,13 @@
         <v>12.5</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BR12">
         <v>21</v>
       </c>
       <c r="BS12">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT12">
         <v>7.4</v>
@@ -3681,7 +3693,7 @@
         <v>25</v>
       </c>
       <c r="BW12">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX12">
         <v>29</v>
@@ -3696,7 +3708,7 @@
         <v>7.8</v>
       </c>
       <c r="CB12" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3704,34 +3716,34 @@
         <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F13">
         <v>3.15</v>
       </c>
       <c r="G13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I13">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J13">
         <v>3.6</v>
       </c>
       <c r="K13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L13">
         <v>1.37</v>
@@ -3746,7 +3758,7 @@
         <v>1.26</v>
       </c>
       <c r="P13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q13">
         <v>1.8</v>
@@ -3764,10 +3776,10 @@
         <v>2.42</v>
       </c>
       <c r="V13">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W13">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
         <v>17.5</v>
@@ -3776,7 +3788,7 @@
         <v>12.5</v>
       </c>
       <c r="Z13">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA13">
         <v>32</v>
@@ -3797,10 +3809,10 @@
         <v>23</v>
       </c>
       <c r="AG13">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI13">
         <v>34</v>
@@ -3842,7 +3854,7 @@
         <v>8</v>
       </c>
       <c r="AV13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW13">
         <v>21</v>
@@ -3851,10 +3863,10 @@
         <v>21</v>
       </c>
       <c r="AY13">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ13">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA13">
         <v>30</v>
@@ -3869,7 +3881,7 @@
         <v>36</v>
       </c>
       <c r="BE13">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF13">
         <v>23</v>
@@ -3878,7 +3890,7 @@
         <v>14.5</v>
       </c>
       <c r="BH13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI13">
         <v>3.45</v>
@@ -3890,13 +3902,13 @@
         <v>8</v>
       </c>
       <c r="BL13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM13">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN13">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
         <v>5.8</v>
@@ -3905,7 +3917,7 @@
         <v>23</v>
       </c>
       <c r="BQ13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR13">
         <v>32</v>
@@ -3938,7 +3950,7 @@
         <v>13</v>
       </c>
       <c r="CB13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3946,43 +3958,43 @@
         <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F14">
         <v>2.18</v>
       </c>
       <c r="G14">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H14">
+        <v>3.35</v>
+      </c>
+      <c r="I14">
         <v>3.45</v>
-      </c>
-      <c r="I14">
-        <v>3.5</v>
       </c>
       <c r="J14">
         <v>3.9</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L14">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M14">
         <v>1.04</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O14">
         <v>1.21</v>
@@ -3991,10 +4003,10 @@
         <v>2.5</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S14">
         <v>2.6</v>
@@ -4009,7 +4021,7 @@
         <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X14">
         <v>22</v>
@@ -4027,7 +4039,7 @@
         <v>14</v>
       </c>
       <c r="AC14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14">
         <v>14</v>
@@ -4042,16 +4054,16 @@
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ14">
         <v>27</v>
       </c>
       <c r="AK14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL14">
         <v>28</v>
@@ -4066,7 +4078,7 @@
         <v>25</v>
       </c>
       <c r="AP14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ14">
         <v>16.5</v>
@@ -4099,7 +4111,7 @@
         <v>13.5</v>
       </c>
       <c r="BA14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB14">
         <v>25</v>
@@ -4126,16 +4138,16 @@
         <v>3.85</v>
       </c>
       <c r="BJ14">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK14">
         <v>7.8</v>
       </c>
       <c r="BL14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BM14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN14">
         <v>5.3</v>
@@ -4147,13 +4159,13 @@
         <v>15</v>
       </c>
       <c r="BQ14">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BR14">
         <v>24</v>
       </c>
       <c r="BS14">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT14">
         <v>7</v>
@@ -4165,22 +4177,22 @@
         <v>25</v>
       </c>
       <c r="BW14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX14">
         <v>32</v>
       </c>
       <c r="BY14">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ14">
         <v>17.5</v>
       </c>
       <c r="CA14">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="CB14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4188,28 +4200,28 @@
         <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G15">
         <v>2.4</v>
       </c>
       <c r="H15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4230,7 +4242,7 @@
         <v>1.15</v>
       </c>
       <c r="P15">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="Q15">
         <v>1.49</v>
@@ -4245,34 +4257,34 @@
         <v>1.46</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
         <v>1.71</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA15">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB15">
         <v>18.5</v>
       </c>
       <c r="AC15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE15">
         <v>27</v>
@@ -4287,13 +4299,13 @@
         <v>13.5</v>
       </c>
       <c r="AI15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ15">
         <v>34</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL15">
         <v>25</v>
@@ -4302,7 +4314,7 @@
         <v>44</v>
       </c>
       <c r="AN15">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO15">
         <v>14.5</v>
@@ -4320,7 +4332,7 @@
         <v>44</v>
       </c>
       <c r="AT15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU15">
         <v>9.4</v>
@@ -4332,7 +4344,7 @@
         <v>23</v>
       </c>
       <c r="AX15">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY15">
         <v>11</v>
@@ -4344,7 +4356,7 @@
         <v>26</v>
       </c>
       <c r="BB15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC15">
         <v>18.5</v>
@@ -4356,7 +4368,7 @@
         <v>36</v>
       </c>
       <c r="BF15">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG15">
         <v>13.5</v>
@@ -4374,10 +4386,10 @@
         <v>7.4</v>
       </c>
       <c r="BL15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN15">
         <v>6</v>
@@ -4386,10 +4398,10 @@
         <v>5.5</v>
       </c>
       <c r="BP15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BR15">
         <v>22</v>
@@ -4407,7 +4419,7 @@
         <v>19.5</v>
       </c>
       <c r="BW15">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BX15">
         <v>24</v>
@@ -4416,13 +4428,13 @@
         <v>15.5</v>
       </c>
       <c r="BZ15">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4430,31 +4442,31 @@
         <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F16">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G16">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H16">
         <v>4.7</v>
       </c>
       <c r="I16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J16">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K16">
         <v>4.9</v>
@@ -4472,7 +4484,7 @@
         <v>1.12</v>
       </c>
       <c r="P16">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q16">
         <v>1.36</v>
@@ -4481,19 +4493,19 @@
         <v>2.08</v>
       </c>
       <c r="S16">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T16">
         <v>1.44</v>
       </c>
       <c r="U16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="V16">
         <v>1.26</v>
       </c>
       <c r="W16">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X16">
         <v>42</v>
@@ -4511,16 +4523,16 @@
         <v>18.5</v>
       </c>
       <c r="AC16">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD16">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF16">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG16">
         <v>11</v>
@@ -4538,7 +4550,7 @@
         <v>15.5</v>
       </c>
       <c r="AL16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM16">
         <v>46</v>
@@ -4559,7 +4571,7 @@
         <v>46</v>
       </c>
       <c r="AS16">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AT16">
         <v>17.5</v>
@@ -4583,7 +4595,7 @@
         <v>14</v>
       </c>
       <c r="BA16">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB16">
         <v>19</v>
@@ -4610,16 +4622,16 @@
         <v>5.1</v>
       </c>
       <c r="BJ16">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL16">
         <v>60</v>
       </c>
       <c r="BM16">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BN16">
         <v>5.3</v>
@@ -4628,19 +4640,19 @@
         <v>4.8</v>
       </c>
       <c r="BP16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ16">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR16">
         <v>17.5</v>
       </c>
       <c r="BS16">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BT16">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BU16">
         <v>8</v>
@@ -4649,22 +4661,22 @@
         <v>30</v>
       </c>
       <c r="BW16">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX16">
         <v>29</v>
       </c>
       <c r="BY16">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ16">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA16">
         <v>8.4</v>
       </c>
       <c r="CB16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4672,31 +4684,31 @@
         <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F17">
         <v>1.8</v>
       </c>
       <c r="G17">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K17">
         <v>4.4</v>
@@ -4705,7 +4717,7 @@
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
         <v>5.8</v>
@@ -4720,10 +4732,10 @@
         <v>1.59</v>
       </c>
       <c r="R17">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="S17">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
         <v>1.6</v>
@@ -4735,13 +4747,13 @@
         <v>1.27</v>
       </c>
       <c r="W17">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z17">
         <v>40</v>
@@ -4756,7 +4768,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE17">
         <v>46</v>
@@ -4777,7 +4789,7 @@
         <v>19.5</v>
       </c>
       <c r="AK17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL17">
         <v>26</v>
@@ -4798,10 +4810,10 @@
         <v>23</v>
       </c>
       <c r="AR17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS17">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AT17">
         <v>12</v>
@@ -4843,10 +4855,10 @@
         <v>7.2</v>
       </c>
       <c r="BG17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BI17">
         <v>4.1</v>
@@ -4861,7 +4873,7 @@
         <v>80</v>
       </c>
       <c r="BM17">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -4873,40 +4885,40 @@
         <v>11</v>
       </c>
       <c r="BQ17">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BR17">
         <v>21</v>
       </c>
       <c r="BS17">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT17">
         <v>8.199999999999999</v>
       </c>
       <c r="BU17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV17">
         <v>34</v>
       </c>
       <c r="BW17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX17">
         <v>36</v>
       </c>
       <c r="BY17">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ17">
         <v>14.5</v>
       </c>
       <c r="CA17">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB17" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4914,19 +4926,19 @@
         <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F18">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>5.8</v>
@@ -4965,7 +4977,7 @@
         <v>1.67</v>
       </c>
       <c r="S18">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T18">
         <v>1.6</v>
@@ -5091,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>3.55</v>
+        <v>2</v>
       </c>
       <c r="BJ18">
         <v>13</v>
@@ -5148,249 +5160,249 @@
         <v>1.79</v>
       </c>
       <c r="CB18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F19">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="G19">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="H19">
-        <v>3.25</v>
+        <v>1.68</v>
       </c>
       <c r="I19">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="O19">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
       <c r="R19">
-        <v>1.26</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="W19">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="X19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5398,760 +5410,760 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F20">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="G20">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="H20">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="I20">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K20">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L20">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="M20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="P20">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q20">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="S20">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="T20">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="U20">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="V20">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="X20">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Y20">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Z20">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AA20">
+        <v>80</v>
+      </c>
+      <c r="AB20">
+        <v>10.5</v>
+      </c>
+      <c r="AC20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20">
+        <v>17</v>
+      </c>
+      <c r="AE20">
+        <v>500</v>
+      </c>
+      <c r="AF20">
+        <v>38</v>
+      </c>
+      <c r="AG20">
+        <v>12</v>
+      </c>
+      <c r="AH20">
+        <v>32</v>
+      </c>
+      <c r="AI20">
+        <v>290</v>
+      </c>
+      <c r="AJ20">
         <v>900</v>
       </c>
-      <c r="AB20">
-        <v>6.2</v>
-      </c>
-      <c r="AC20">
-        <v>8.6</v>
-      </c>
-      <c r="AD20">
-        <v>26</v>
-      </c>
-      <c r="AE20">
-        <v>480</v>
-      </c>
-      <c r="AF20">
-        <v>9.6</v>
-      </c>
-      <c r="AG20">
-        <v>11</v>
-      </c>
-      <c r="AH20">
-        <v>30</v>
-      </c>
-      <c r="AI20">
-        <v>450</v>
-      </c>
-      <c r="AJ20">
-        <v>21</v>
-      </c>
       <c r="AK20">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AL20">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AM20">
         <v>580</v>
       </c>
       <c r="AN20">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AO20">
-        <v>700</v>
+        <v>80</v>
       </c>
       <c r="AP20">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ20">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AR20">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AS20">
+        <v>6.8</v>
+      </c>
+      <c r="AT20">
+        <v>7.8</v>
+      </c>
+      <c r="AU20">
+        <v>6.4</v>
+      </c>
+      <c r="AV20">
+        <v>11.5</v>
+      </c>
+      <c r="AW20">
+        <v>32</v>
+      </c>
+      <c r="AX20">
+        <v>13.5</v>
+      </c>
+      <c r="AY20">
         <v>10.5</v>
       </c>
-      <c r="AT20">
-        <v>5.2</v>
-      </c>
-      <c r="AU20">
-        <v>7.2</v>
-      </c>
-      <c r="AV20">
-        <v>19.5</v>
-      </c>
-      <c r="AW20">
-        <v>10</v>
-      </c>
-      <c r="AX20">
-        <v>8</v>
-      </c>
-      <c r="AY20">
-        <v>9</v>
-      </c>
       <c r="AZ20">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BA20">
+        <v>23</v>
+      </c>
+      <c r="BB20">
+        <v>6.2</v>
+      </c>
+      <c r="BC20">
+        <v>14.5</v>
+      </c>
+      <c r="BD20">
+        <v>23</v>
+      </c>
+      <c r="BE20">
+        <v>7</v>
+      </c>
+      <c r="BF20">
+        <v>6</v>
+      </c>
+      <c r="BG20">
+        <v>29</v>
+      </c>
+      <c r="BH20">
+        <v>3.05</v>
+      </c>
+      <c r="BI20">
+        <v>2.54</v>
+      </c>
+      <c r="BJ20">
         <v>10.5</v>
       </c>
-      <c r="BB20">
-        <v>17</v>
-      </c>
-      <c r="BC20">
-        <v>21</v>
-      </c>
-      <c r="BD20">
-        <v>28</v>
-      </c>
-      <c r="BE20">
+      <c r="BK20">
+        <v>6.2</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>13.5</v>
+      </c>
+      <c r="BN20">
+        <v>5.4</v>
+      </c>
+      <c r="BO20">
+        <v>4.1</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
         <v>10.5</v>
       </c>
-      <c r="BF20">
-        <v>16</v>
-      </c>
-      <c r="BG20">
+      <c r="BT20">
+        <v>6.2</v>
+      </c>
+      <c r="BU20">
+        <v>4.7</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>11</v>
+      </c>
+      <c r="BZ20">
+        <v>1000</v>
+      </c>
+      <c r="CA20">
         <v>10.5</v>
       </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.04</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.04</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.04</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.04</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.04</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.04</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.04</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.04</v>
-      </c>
       <c r="CB20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F21">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="G21">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="H21">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="I21">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="J21">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L21">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="M21">
         <v>1.11</v>
       </c>
       <c r="N21">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="P21">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q21">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S21">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="W21">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="X21">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z21">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AA21">
         <v>900</v>
       </c>
       <c r="AB21">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC21">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AD21">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE21">
-        <v>75</v>
+        <v>480</v>
       </c>
       <c r="AF21">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AI21">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="AJ21">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AK21">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL21">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM21">
         <v>580</v>
       </c>
       <c r="AN21">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO21">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AP21">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21">
+        <v>12</v>
+      </c>
+      <c r="AR21">
+        <v>34</v>
+      </c>
+      <c r="AS21">
         <v>10.5</v>
       </c>
-      <c r="AR21">
-        <v>14.5</v>
-      </c>
-      <c r="AS21">
+      <c r="AT21">
+        <v>5.2</v>
+      </c>
+      <c r="AU21">
+        <v>7.2</v>
+      </c>
+      <c r="AV21">
+        <v>19.5</v>
+      </c>
+      <c r="AW21">
+        <v>10</v>
+      </c>
+      <c r="AX21">
+        <v>8</v>
+      </c>
+      <c r="AY21">
         <v>9</v>
       </c>
-      <c r="AT21">
-        <v>6.2</v>
-      </c>
-      <c r="AU21">
-        <v>6.4</v>
-      </c>
-      <c r="AV21">
-        <v>15.5</v>
-      </c>
-      <c r="AW21">
-        <v>8.6</v>
-      </c>
-      <c r="AX21">
-        <v>10</v>
-      </c>
-      <c r="AY21">
-        <v>9.4</v>
-      </c>
       <c r="AZ21">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA21">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB21">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BC21">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BD21">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BE21">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF21">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BG21">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH21">
-        <v>2.98</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F22">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="H22">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="I22">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K22">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L22">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="M22">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="N22">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="O22">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="P22">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="S22">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="T22">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
       <c r="U22">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="V22">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="X22">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="Y22">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="Z22">
+        <v>32</v>
+      </c>
+      <c r="AA22">
+        <v>900</v>
+      </c>
+      <c r="AB22">
+        <v>7.8</v>
+      </c>
+      <c r="AC22">
+        <v>7.8</v>
+      </c>
+      <c r="AD22">
+        <v>19</v>
+      </c>
+      <c r="AE22">
+        <v>75</v>
+      </c>
+      <c r="AF22">
+        <v>12.5</v>
+      </c>
+      <c r="AG22">
+        <v>11.5</v>
+      </c>
+      <c r="AH22">
+        <v>23</v>
+      </c>
+      <c r="AI22">
+        <v>90</v>
+      </c>
+      <c r="AJ22">
+        <v>29</v>
+      </c>
+      <c r="AK22">
+        <v>28</v>
+      </c>
+      <c r="AL22">
+        <v>55</v>
+      </c>
+      <c r="AM22">
+        <v>580</v>
+      </c>
+      <c r="AN22">
+        <v>25</v>
+      </c>
+      <c r="AO22">
+        <v>300</v>
+      </c>
+      <c r="AP22">
+        <v>5.1</v>
+      </c>
+      <c r="AQ22">
         <v>10.5</v>
       </c>
-      <c r="AA22">
-        <v>29</v>
-      </c>
-      <c r="AB22">
-        <v>11</v>
-      </c>
-      <c r="AC22">
-        <v>8</v>
-      </c>
-      <c r="AD22">
-        <v>13.5</v>
-      </c>
-      <c r="AE22">
-        <v>40</v>
-      </c>
-      <c r="AF22">
-        <v>36</v>
-      </c>
-      <c r="AG22">
-        <v>24</v>
-      </c>
-      <c r="AH22">
-        <v>38</v>
-      </c>
-      <c r="AI22">
-        <v>190</v>
-      </c>
-      <c r="AJ22">
-        <v>690</v>
-      </c>
-      <c r="AK22">
-        <v>250</v>
-      </c>
-      <c r="AL22">
-        <v>690</v>
-      </c>
-      <c r="AM22">
-        <v>500</v>
-      </c>
-      <c r="AN22">
-        <v>690</v>
-      </c>
-      <c r="AO22">
-        <v>38</v>
-      </c>
-      <c r="AP22">
+      <c r="AR22">
+        <v>19.5</v>
+      </c>
+      <c r="AS22">
+        <v>9</v>
+      </c>
+      <c r="AT22">
         <v>6.2</v>
       </c>
-      <c r="AQ22">
-        <v>5.3</v>
-      </c>
-      <c r="AR22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS22">
-        <v>20</v>
-      </c>
-      <c r="AT22">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AU22">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV22">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW22">
         <v>28</v>
       </c>
       <c r="AX22">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AY22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ22">
+        <v>19.5</v>
+      </c>
+      <c r="BA22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB22">
         <v>20</v>
       </c>
-      <c r="AZ22">
-        <v>24</v>
-      </c>
-      <c r="BA22">
-        <v>36</v>
-      </c>
-      <c r="BB22">
-        <v>42</v>
-      </c>
       <c r="BC22">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="BD22">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BE22">
-        <v>95</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="BG22">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI22">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="BJ22">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BK22">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.62</v>
+        <v>10</v>
       </c>
       <c r="BN22">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BO22">
-        <v>1.42</v>
+        <v>4</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ22">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS22">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="BT22">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BU22">
-        <v>1.27</v>
+        <v>5.8</v>
       </c>
       <c r="BV22">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BW22">
-        <v>1.53</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY22">
-        <v>1.59</v>
+        <v>9.4</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA22">
-        <v>1.59</v>
+        <v>8.6</v>
       </c>
       <c r="CB22" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F23">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G23">
-        <v>2.92</v>
+        <v>5.3</v>
       </c>
       <c r="H23">
+        <v>2.04</v>
+      </c>
+      <c r="I23">
+        <v>2.1</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
         <v>3.2</v>
-      </c>
-      <c r="I23">
-        <v>3.35</v>
-      </c>
-      <c r="J23">
-        <v>2.84</v>
-      </c>
-      <c r="K23">
-        <v>2.98</v>
       </c>
       <c r="L23">
         <v>1.64</v>
@@ -6160,16 +6172,16 @@
         <v>1.17</v>
       </c>
       <c r="N23">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q23">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
         <v>1.14</v>
@@ -6178,133 +6190,133 @@
         <v>7.2</v>
       </c>
       <c r="T23">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="U23">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="W23">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y23">
+        <v>5.7</v>
+      </c>
+      <c r="Z23">
+        <v>10.5</v>
+      </c>
+      <c r="AA23">
+        <v>29</v>
+      </c>
+      <c r="AB23">
+        <v>11</v>
+      </c>
+      <c r="AC23">
         <v>8</v>
       </c>
-      <c r="Z23">
+      <c r="AD23">
+        <v>13.5</v>
+      </c>
+      <c r="AE23">
+        <v>40</v>
+      </c>
+      <c r="AF23">
+        <v>36</v>
+      </c>
+      <c r="AG23">
         <v>24</v>
       </c>
-      <c r="AA23">
-        <v>490</v>
-      </c>
-      <c r="AB23">
-        <v>7.4</v>
-      </c>
-      <c r="AC23">
-        <v>7.2</v>
-      </c>
-      <c r="AD23">
-        <v>21</v>
-      </c>
-      <c r="AE23">
-        <v>430</v>
-      </c>
-      <c r="AF23">
-        <v>16.5</v>
-      </c>
-      <c r="AG23">
-        <v>19.5</v>
-      </c>
       <c r="AH23">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AI23">
-        <v>490</v>
+        <v>190</v>
       </c>
       <c r="AJ23">
-        <v>120</v>
+        <v>690</v>
       </c>
       <c r="AK23">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AL23">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AM23">
         <v>500</v>
       </c>
       <c r="AN23">
-        <v>200</v>
+        <v>690</v>
       </c>
       <c r="AO23">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="AP23">
         <v>6.2</v>
       </c>
       <c r="AQ23">
+        <v>5.2</v>
+      </c>
+      <c r="AR23">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS23">
+        <v>20</v>
+      </c>
+      <c r="AT23">
+        <v>9.6</v>
+      </c>
+      <c r="AU23">
         <v>7.2</v>
       </c>
-      <c r="AR23">
-        <v>14</v>
-      </c>
-      <c r="AS23">
-        <v>30</v>
-      </c>
-      <c r="AT23">
-        <v>6.6</v>
-      </c>
-      <c r="AU23">
-        <v>6.4</v>
-      </c>
       <c r="AV23">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW23">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX23">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AY23">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ23">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA23">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BB23">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BC23">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BD23">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BE23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF23">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="BG23">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BH23">
         <v>1000</v>
       </c>
       <c r="BI23">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BJ23">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BK23">
         <v>1.5</v>
@@ -6313,294 +6325,294 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="BN23">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BO23">
-        <v>3.9</v>
+        <v>1.42</v>
       </c>
       <c r="BP23">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BR23">
         <v>1000</v>
       </c>
       <c r="BS23">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BT23">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BU23">
-        <v>4.1</v>
+        <v>1.27</v>
       </c>
       <c r="BV23">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="BW23">
+        <v>1.53</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
         <v>1.59</v>
       </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.61</v>
-      </c>
       <c r="BZ23">
         <v>1000</v>
       </c>
       <c r="CA23">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CB23" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F24">
-        <v>1.56</v>
+        <v>2.8</v>
       </c>
       <c r="G24">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
       <c r="H24">
-        <v>7.6</v>
+        <v>3.2</v>
       </c>
       <c r="I24">
+        <v>3.35</v>
+      </c>
+      <c r="J24">
+        <v>2.84</v>
+      </c>
+      <c r="K24">
+        <v>2.98</v>
+      </c>
+      <c r="L24">
+        <v>1.64</v>
+      </c>
+      <c r="M24">
+        <v>1.17</v>
+      </c>
+      <c r="N24">
+        <v>2.28</v>
+      </c>
+      <c r="O24">
+        <v>1.72</v>
+      </c>
+      <c r="P24">
+        <v>1.42</v>
+      </c>
+      <c r="Q24">
+        <v>3.15</v>
+      </c>
+      <c r="R24">
+        <v>1.14</v>
+      </c>
+      <c r="S24">
+        <v>7.2</v>
+      </c>
+      <c r="T24">
+        <v>2.38</v>
+      </c>
+      <c r="U24">
+        <v>1.65</v>
+      </c>
+      <c r="V24">
+        <v>1.43</v>
+      </c>
+      <c r="W24">
+        <v>1.52</v>
+      </c>
+      <c r="X24">
+        <v>7</v>
+      </c>
+      <c r="Y24">
         <v>8</v>
       </c>
-      <c r="J24">
-        <v>4.2</v>
-      </c>
-      <c r="K24">
-        <v>4.4</v>
-      </c>
-      <c r="L24">
-        <v>1.41</v>
-      </c>
-      <c r="M24">
-        <v>1.08</v>
-      </c>
-      <c r="N24">
-        <v>3.65</v>
-      </c>
-      <c r="O24">
-        <v>1.35</v>
-      </c>
-      <c r="P24">
-        <v>1.9</v>
-      </c>
-      <c r="Q24">
-        <v>2.04</v>
-      </c>
-      <c r="R24">
-        <v>1.34</v>
-      </c>
-      <c r="S24">
-        <v>3.7</v>
-      </c>
-      <c r="T24">
-        <v>2.14</v>
-      </c>
-      <c r="U24">
-        <v>1.82</v>
-      </c>
-      <c r="V24">
-        <v>1.14</v>
-      </c>
-      <c r="W24">
-        <v>2.72</v>
-      </c>
-      <c r="X24">
-        <v>13.5</v>
-      </c>
-      <c r="Y24">
-        <v>23</v>
-      </c>
       <c r="Z24">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB24">
         <v>7.4</v>
       </c>
       <c r="AC24">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD24">
+        <v>21</v>
+      </c>
+      <c r="AE24">
+        <v>120</v>
+      </c>
+      <c r="AF24">
+        <v>16.5</v>
+      </c>
+      <c r="AG24">
+        <v>19.5</v>
+      </c>
+      <c r="AH24">
+        <v>46</v>
+      </c>
+      <c r="AI24">
+        <v>220</v>
+      </c>
+      <c r="AJ24">
+        <v>110</v>
+      </c>
+      <c r="AK24">
+        <v>100</v>
+      </c>
+      <c r="AL24">
+        <v>190</v>
+      </c>
+      <c r="AM24">
+        <v>500</v>
+      </c>
+      <c r="AN24">
+        <v>490</v>
+      </c>
+      <c r="AO24">
+        <v>350</v>
+      </c>
+      <c r="AP24">
+        <v>6.2</v>
+      </c>
+      <c r="AQ24">
+        <v>7.2</v>
+      </c>
+      <c r="AR24">
+        <v>14</v>
+      </c>
+      <c r="AS24">
+        <v>30</v>
+      </c>
+      <c r="AT24">
+        <v>6.6</v>
+      </c>
+      <c r="AU24">
+        <v>6.4</v>
+      </c>
+      <c r="AV24">
+        <v>14</v>
+      </c>
+      <c r="AW24">
         <v>29</v>
       </c>
-      <c r="AE24">
-        <v>130</v>
-      </c>
-      <c r="AF24">
-        <v>8.4</v>
-      </c>
-      <c r="AG24">
-        <v>10.5</v>
-      </c>
-      <c r="AH24">
-        <v>25</v>
-      </c>
-      <c r="AI24">
-        <v>260</v>
-      </c>
-      <c r="AJ24">
+      <c r="AX24">
         <v>14</v>
       </c>
-      <c r="AK24">
-        <v>18</v>
-      </c>
-      <c r="AL24">
-        <v>44</v>
-      </c>
-      <c r="AM24">
-        <v>690</v>
-      </c>
-      <c r="AN24">
-        <v>9.6</v>
-      </c>
-      <c r="AO24">
-        <v>190</v>
-      </c>
-      <c r="AP24">
-        <v>12</v>
-      </c>
-      <c r="AQ24">
-        <v>20</v>
-      </c>
-      <c r="AR24">
-        <v>55</v>
-      </c>
-      <c r="AS24">
-        <v>48</v>
-      </c>
-      <c r="AT24">
-        <v>7</v>
-      </c>
-      <c r="AU24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV24">
+      <c r="AY24">
+        <v>13</v>
+      </c>
+      <c r="AZ24">
+        <v>19.5</v>
+      </c>
+      <c r="BA24">
+        <v>40</v>
+      </c>
+      <c r="BB24">
         <v>26</v>
       </c>
-      <c r="AW24">
-        <v>42</v>
-      </c>
-      <c r="AX24">
-        <v>7.6</v>
-      </c>
-      <c r="AY24">
-        <v>9.4</v>
-      </c>
-      <c r="AZ24">
-        <v>24</v>
-      </c>
-      <c r="BA24">
-        <v>42</v>
-      </c>
-      <c r="BB24">
-        <v>12.5</v>
-      </c>
       <c r="BC24">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BD24">
         <v>38</v>
       </c>
       <c r="BE24">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF24">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG24">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BH24">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.82</v>
+        <v>1.64</v>
       </c>
       <c r="BJ24">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BK24">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>15.5</v>
+        <v>1.64</v>
       </c>
       <c r="BN24">
-        <v>3.85</v>
+        <v>7.6</v>
       </c>
       <c r="BO24">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="BP24">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BQ24">
-        <v>6.2</v>
+        <v>1.58</v>
       </c>
       <c r="BR24">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>10.5</v>
+        <v>1.61</v>
       </c>
       <c r="BT24">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU24">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW24">
-        <v>13.5</v>
+        <v>1.59</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>14</v>
+        <v>1.61</v>
       </c>
       <c r="BZ24">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>9.4</v>
+        <v>1.62</v>
       </c>
       <c r="CB24" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6608,447 +6620,447 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F25">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="G25">
+        <v>1.58</v>
+      </c>
+      <c r="H25">
+        <v>7.8</v>
+      </c>
+      <c r="I25">
+        <v>8</v>
+      </c>
+      <c r="J25">
+        <v>4.2</v>
+      </c>
+      <c r="K25">
+        <v>4.4</v>
+      </c>
+      <c r="L25">
+        <v>1.41</v>
+      </c>
+      <c r="M25">
+        <v>1.08</v>
+      </c>
+      <c r="N25">
+        <v>3.65</v>
+      </c>
+      <c r="O25">
+        <v>1.35</v>
+      </c>
+      <c r="P25">
+        <v>1.92</v>
+      </c>
+      <c r="Q25">
+        <v>2.06</v>
+      </c>
+      <c r="R25">
+        <v>1.34</v>
+      </c>
+      <c r="S25">
+        <v>3.75</v>
+      </c>
+      <c r="T25">
+        <v>2.14</v>
+      </c>
+      <c r="U25">
         <v>1.82</v>
       </c>
-      <c r="H25">
-        <v>5.1</v>
-      </c>
-      <c r="I25">
-        <v>5.5</v>
-      </c>
-      <c r="J25">
-        <v>3.8</v>
-      </c>
-      <c r="K25">
-        <v>4</v>
-      </c>
-      <c r="L25">
-        <v>1.37</v>
-      </c>
-      <c r="M25">
-        <v>1.06</v>
-      </c>
-      <c r="N25">
-        <v>4.2</v>
-      </c>
-      <c r="O25">
-        <v>1.3</v>
-      </c>
-      <c r="P25">
-        <v>2.06</v>
-      </c>
-      <c r="Q25">
-        <v>1.88</v>
-      </c>
-      <c r="R25">
-        <v>1.42</v>
-      </c>
-      <c r="S25">
-        <v>3.2</v>
-      </c>
-      <c r="T25">
-        <v>1.8</v>
-      </c>
-      <c r="U25">
-        <v>2.16</v>
-      </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W25">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="X25">
+        <v>13.5</v>
+      </c>
+      <c r="Y25">
+        <v>23</v>
+      </c>
+      <c r="Z25">
+        <v>65</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>7.4</v>
+      </c>
+      <c r="AC25">
+        <v>9.4</v>
+      </c>
+      <c r="AD25">
+        <v>50</v>
+      </c>
+      <c r="AE25">
+        <v>130</v>
+      </c>
+      <c r="AF25">
+        <v>8.4</v>
+      </c>
+      <c r="AG25">
+        <v>10.5</v>
+      </c>
+      <c r="AH25">
+        <v>25</v>
+      </c>
+      <c r="AI25">
+        <v>260</v>
+      </c>
+      <c r="AJ25">
+        <v>14</v>
+      </c>
+      <c r="AK25">
+        <v>18</v>
+      </c>
+      <c r="AL25">
+        <v>90</v>
+      </c>
+      <c r="AM25">
+        <v>570</v>
+      </c>
+      <c r="AN25">
+        <v>9.6</v>
+      </c>
+      <c r="AO25">
+        <v>190</v>
+      </c>
+      <c r="AP25">
+        <v>12</v>
+      </c>
+      <c r="AQ25">
         <v>20</v>
       </c>
-      <c r="Y25">
+      <c r="AR25">
+        <v>55</v>
+      </c>
+      <c r="AS25">
+        <v>48</v>
+      </c>
+      <c r="AT25">
+        <v>7</v>
+      </c>
+      <c r="AU25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV25">
         <v>26</v>
       </c>
-      <c r="Z25">
-        <v>100</v>
-      </c>
-      <c r="AA25">
-        <v>690</v>
-      </c>
-      <c r="AB25">
+      <c r="AW25">
+        <v>42</v>
+      </c>
+      <c r="AX25">
+        <v>7.6</v>
+      </c>
+      <c r="AY25">
         <v>9.4</v>
       </c>
-      <c r="AC25">
-        <v>8.6</v>
-      </c>
-      <c r="AD25">
-        <v>21</v>
-      </c>
-      <c r="AE25">
-        <v>390</v>
-      </c>
-      <c r="AF25">
-        <v>11.5</v>
-      </c>
-      <c r="AG25">
+      <c r="AZ25">
+        <v>24</v>
+      </c>
+      <c r="BA25">
+        <v>42</v>
+      </c>
+      <c r="BB25">
+        <v>12.5</v>
+      </c>
+      <c r="BC25">
+        <v>16</v>
+      </c>
+      <c r="BD25">
+        <v>38</v>
+      </c>
+      <c r="BE25">
+        <v>70</v>
+      </c>
+      <c r="BF25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG25">
+        <v>46</v>
+      </c>
+      <c r="BH25">
+        <v>3.4</v>
+      </c>
+      <c r="BI25">
+        <v>2.82</v>
+      </c>
+      <c r="BJ25">
+        <v>12</v>
+      </c>
+      <c r="BK25">
+        <v>7</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>15.5</v>
+      </c>
+      <c r="BN25">
+        <v>3.85</v>
+      </c>
+      <c r="BO25">
+        <v>3.1</v>
+      </c>
+      <c r="BP25">
         <v>10</v>
       </c>
-      <c r="AH25">
-        <v>24</v>
-      </c>
-      <c r="AI25">
-        <v>310</v>
-      </c>
-      <c r="AJ25">
-        <v>24</v>
-      </c>
-      <c r="AK25">
-        <v>23</v>
-      </c>
-      <c r="AL25">
-        <v>65</v>
-      </c>
-      <c r="AM25">
-        <v>190</v>
-      </c>
-      <c r="AN25">
+      <c r="BQ25">
+        <v>6.2</v>
+      </c>
+      <c r="BR25">
+        <v>29</v>
+      </c>
+      <c r="BS25">
+        <v>10.5</v>
+      </c>
+      <c r="BT25">
         <v>11</v>
       </c>
-      <c r="AO25">
-        <v>140</v>
-      </c>
-      <c r="AP25">
+      <c r="BU25">
+        <v>6.6</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
         <v>13.5</v>
       </c>
-      <c r="AQ25">
-        <v>14.5</v>
-      </c>
-      <c r="AR25">
-        <v>24</v>
-      </c>
-      <c r="AS25">
-        <v>40</v>
-      </c>
-      <c r="AT25">
-        <v>8.6</v>
-      </c>
-      <c r="AU25">
-        <v>7.8</v>
-      </c>
-      <c r="AV25">
-        <v>15.5</v>
-      </c>
-      <c r="AW25">
-        <v>32</v>
-      </c>
-      <c r="AX25">
-        <v>10</v>
-      </c>
-      <c r="AY25">
-        <v>9</v>
-      </c>
-      <c r="AZ25">
-        <v>15</v>
-      </c>
-      <c r="BA25">
-        <v>32</v>
-      </c>
-      <c r="BB25">
-        <v>17</v>
-      </c>
-      <c r="BC25">
-        <v>14.5</v>
-      </c>
-      <c r="BD25">
-        <v>21</v>
-      </c>
-      <c r="BE25">
-        <v>38</v>
-      </c>
-      <c r="BF25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG25">
-        <v>32</v>
-      </c>
-      <c r="BH25">
-        <v>3.65</v>
-      </c>
-      <c r="BI25">
-        <v>3.3</v>
-      </c>
-      <c r="BJ25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK25">
-        <v>6</v>
-      </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
         <v>14</v>
-      </c>
-      <c r="BN25">
-        <v>4.5</v>
-      </c>
-      <c r="BO25">
-        <v>4</v>
-      </c>
-      <c r="BP25">
-        <v>12.5</v>
-      </c>
-      <c r="BQ25">
-        <v>7</v>
-      </c>
-      <c r="BR25">
-        <v>1000</v>
-      </c>
-      <c r="BS25">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT25">
-        <v>8.4</v>
-      </c>
-      <c r="BU25">
-        <v>5.5</v>
-      </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
-        <v>11</v>
-      </c>
-      <c r="BX25">
-        <v>1000</v>
-      </c>
-      <c r="BY25">
-        <v>12</v>
       </c>
       <c r="BZ25">
         <v>21</v>
       </c>
       <c r="CA25">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB25" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F26">
+        <v>1.79</v>
+      </c>
+      <c r="G26">
+        <v>1.82</v>
+      </c>
+      <c r="H26">
+        <v>5.2</v>
+      </c>
+      <c r="I26">
+        <v>5.5</v>
+      </c>
+      <c r="J26">
+        <v>3.8</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
+        <v>1.37</v>
+      </c>
+      <c r="M26">
+        <v>1.06</v>
+      </c>
+      <c r="N26">
+        <v>4.2</v>
+      </c>
+      <c r="O26">
+        <v>1.29</v>
+      </c>
+      <c r="P26">
+        <v>2.08</v>
+      </c>
+      <c r="Q26">
+        <v>1.88</v>
+      </c>
+      <c r="R26">
+        <v>1.42</v>
+      </c>
+      <c r="S26">
+        <v>3.2</v>
+      </c>
+      <c r="T26">
+        <v>1.82</v>
+      </c>
+      <c r="U26">
         <v>2.16</v>
       </c>
-      <c r="G26">
-        <v>2.22</v>
-      </c>
-      <c r="H26">
-        <v>4.3</v>
-      </c>
-      <c r="I26">
-        <v>4.8</v>
-      </c>
-      <c r="J26">
-        <v>3.05</v>
-      </c>
-      <c r="K26">
-        <v>3.25</v>
-      </c>
-      <c r="L26">
-        <v>1.01</v>
-      </c>
-      <c r="M26">
-        <v>1.12</v>
-      </c>
-      <c r="N26">
-        <v>2.62</v>
-      </c>
-      <c r="O26">
-        <v>1.53</v>
-      </c>
-      <c r="P26">
-        <v>1.54</v>
-      </c>
-      <c r="Q26">
-        <v>2.56</v>
-      </c>
-      <c r="R26">
-        <v>1.19</v>
-      </c>
-      <c r="S26">
-        <v>5.2</v>
-      </c>
-      <c r="T26">
-        <v>2.14</v>
-      </c>
-      <c r="U26">
-        <v>1.73</v>
-      </c>
       <c r="V26">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="W26">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="X26">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="Y26">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AA26">
+        <v>690</v>
+      </c>
+      <c r="AB26">
+        <v>9.4</v>
+      </c>
+      <c r="AC26">
+        <v>8.4</v>
+      </c>
+      <c r="AD26">
+        <v>21</v>
+      </c>
+      <c r="AE26">
+        <v>150</v>
+      </c>
+      <c r="AF26">
+        <v>11.5</v>
+      </c>
+      <c r="AG26">
+        <v>10</v>
+      </c>
+      <c r="AH26">
+        <v>24</v>
+      </c>
+      <c r="AI26">
+        <v>150</v>
+      </c>
+      <c r="AJ26">
+        <v>25</v>
+      </c>
+      <c r="AK26">
+        <v>24</v>
+      </c>
+      <c r="AL26">
+        <v>65</v>
+      </c>
+      <c r="AM26">
+        <v>190</v>
+      </c>
+      <c r="AN26">
+        <v>11</v>
+      </c>
+      <c r="AO26">
         <v>140</v>
       </c>
-      <c r="AB26">
-        <v>7.2</v>
-      </c>
-      <c r="AC26">
-        <v>8.6</v>
-      </c>
-      <c r="AD26">
-        <v>23</v>
-      </c>
-      <c r="AE26">
-        <v>85</v>
-      </c>
-      <c r="AF26">
-        <v>12.5</v>
-      </c>
-      <c r="AG26">
+      <c r="AP26">
+        <v>14</v>
+      </c>
+      <c r="AQ26">
+        <v>17</v>
+      </c>
+      <c r="AR26">
+        <v>24</v>
+      </c>
+      <c r="AS26">
+        <v>40</v>
+      </c>
+      <c r="AT26">
+        <v>8.4</v>
+      </c>
+      <c r="AU26">
+        <v>7.6</v>
+      </c>
+      <c r="AV26">
+        <v>18</v>
+      </c>
+      <c r="AW26">
+        <v>32</v>
+      </c>
+      <c r="AX26">
+        <v>10</v>
+      </c>
+      <c r="AY26">
+        <v>9</v>
+      </c>
+      <c r="AZ26">
+        <v>15</v>
+      </c>
+      <c r="BA26">
+        <v>32</v>
+      </c>
+      <c r="BB26">
+        <v>17</v>
+      </c>
+      <c r="BC26">
+        <v>16</v>
+      </c>
+      <c r="BD26">
+        <v>22</v>
+      </c>
+      <c r="BE26">
+        <v>38</v>
+      </c>
+      <c r="BF26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG26">
+        <v>32</v>
+      </c>
+      <c r="BH26">
+        <v>3.65</v>
+      </c>
+      <c r="BI26">
+        <v>3.3</v>
+      </c>
+      <c r="BJ26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK26">
+        <v>6.2</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>14.5</v>
+      </c>
+      <c r="BN26">
+        <v>4.5</v>
+      </c>
+      <c r="BO26">
+        <v>4</v>
+      </c>
+      <c r="BP26">
         <v>12</v>
-      </c>
-      <c r="AH26">
-        <v>28</v>
-      </c>
-      <c r="AI26">
-        <v>120</v>
-      </c>
-      <c r="AJ26">
-        <v>29</v>
-      </c>
-      <c r="AK26">
-        <v>30</v>
-      </c>
-      <c r="AL26">
-        <v>70</v>
-      </c>
-      <c r="AM26">
-        <v>220</v>
-      </c>
-      <c r="AN26">
-        <v>28</v>
-      </c>
-      <c r="AO26">
-        <v>150</v>
-      </c>
-      <c r="AP26">
-        <v>7.8</v>
-      </c>
-      <c r="AQ26">
-        <v>10</v>
-      </c>
-      <c r="AR26">
-        <v>5.8</v>
-      </c>
-      <c r="AS26">
-        <v>6.6</v>
-      </c>
-      <c r="AT26">
-        <v>5.9</v>
-      </c>
-      <c r="AU26">
-        <v>6.4</v>
-      </c>
-      <c r="AV26">
-        <v>16.5</v>
-      </c>
-      <c r="AW26">
-        <v>6.4</v>
-      </c>
-      <c r="AX26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY26">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26">
-        <v>20</v>
-      </c>
-      <c r="BA26">
-        <v>6.6</v>
-      </c>
-      <c r="BB26">
-        <v>5.6</v>
-      </c>
-      <c r="BC26">
-        <v>5.7</v>
-      </c>
-      <c r="BD26">
-        <v>6.4</v>
-      </c>
-      <c r="BE26">
-        <v>6.8</v>
-      </c>
-      <c r="BF26">
-        <v>5.6</v>
-      </c>
-      <c r="BG26">
-        <v>6.6</v>
-      </c>
-      <c r="BH26">
-        <v>2.82</v>
-      </c>
-      <c r="BI26">
-        <v>2.32</v>
-      </c>
-      <c r="BJ26">
-        <v>12</v>
-      </c>
-      <c r="BK26">
-        <v>5.9</v>
-      </c>
-      <c r="BL26">
-        <v>1000</v>
-      </c>
-      <c r="BM26">
-        <v>11</v>
-      </c>
-      <c r="BN26">
-        <v>4.7</v>
-      </c>
-      <c r="BO26">
-        <v>3.65</v>
-      </c>
-      <c r="BP26">
-        <v>18</v>
       </c>
       <c r="BQ26">
         <v>7</v>
@@ -7057,34 +7069,276 @@
         <v>1000</v>
       </c>
       <c r="BS26">
+        <v>10</v>
+      </c>
+      <c r="BT26">
+        <v>8.4</v>
+      </c>
+      <c r="BU26">
+        <v>5.6</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>11.5</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>12.5</v>
+      </c>
+      <c r="BZ26">
+        <v>21</v>
+      </c>
+      <c r="CA26">
         <v>9.199999999999999</v>
       </c>
-      <c r="BT26">
+      <c r="CB26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27">
+        <v>2.16</v>
+      </c>
+      <c r="G27">
+        <v>2.2</v>
+      </c>
+      <c r="H27">
+        <v>4.3</v>
+      </c>
+      <c r="I27">
+        <v>4.6</v>
+      </c>
+      <c r="J27">
+        <v>3.15</v>
+      </c>
+      <c r="K27">
+        <v>3.25</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.12</v>
+      </c>
+      <c r="N27">
+        <v>2.62</v>
+      </c>
+      <c r="O27">
+        <v>1.53</v>
+      </c>
+      <c r="P27">
+        <v>1.54</v>
+      </c>
+      <c r="Q27">
+        <v>2.58</v>
+      </c>
+      <c r="R27">
+        <v>1.19</v>
+      </c>
+      <c r="S27">
+        <v>5.2</v>
+      </c>
+      <c r="T27">
+        <v>2.14</v>
+      </c>
+      <c r="U27">
+        <v>1.73</v>
+      </c>
+      <c r="V27">
+        <v>1.28</v>
+      </c>
+      <c r="W27">
+        <v>1.83</v>
+      </c>
+      <c r="X27">
+        <v>10.5</v>
+      </c>
+      <c r="Y27">
+        <v>12.5</v>
+      </c>
+      <c r="Z27">
+        <v>34</v>
+      </c>
+      <c r="AA27">
+        <v>140</v>
+      </c>
+      <c r="AB27">
+        <v>7.2</v>
+      </c>
+      <c r="AC27">
+        <v>7.8</v>
+      </c>
+      <c r="AD27">
+        <v>23</v>
+      </c>
+      <c r="AE27">
+        <v>85</v>
+      </c>
+      <c r="AF27">
+        <v>12.5</v>
+      </c>
+      <c r="AG27">
+        <v>12</v>
+      </c>
+      <c r="AH27">
+        <v>28</v>
+      </c>
+      <c r="AI27">
+        <v>120</v>
+      </c>
+      <c r="AJ27">
+        <v>29</v>
+      </c>
+      <c r="AK27">
+        <v>30</v>
+      </c>
+      <c r="AL27">
+        <v>70</v>
+      </c>
+      <c r="AM27">
+        <v>220</v>
+      </c>
+      <c r="AN27">
+        <v>28</v>
+      </c>
+      <c r="AO27">
+        <v>150</v>
+      </c>
+      <c r="AP27">
+        <v>7.8</v>
+      </c>
+      <c r="AQ27">
+        <v>10</v>
+      </c>
+      <c r="AR27">
+        <v>6.2</v>
+      </c>
+      <c r="AS27">
+        <v>7.2</v>
+      </c>
+      <c r="AT27">
+        <v>5.9</v>
+      </c>
+      <c r="AU27">
+        <v>6.4</v>
+      </c>
+      <c r="AV27">
+        <v>16.5</v>
+      </c>
+      <c r="AW27">
+        <v>7</v>
+      </c>
+      <c r="AX27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY27">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27">
+        <v>20</v>
+      </c>
+      <c r="BA27">
+        <v>7.2</v>
+      </c>
+      <c r="BB27">
+        <v>6</v>
+      </c>
+      <c r="BC27">
+        <v>6</v>
+      </c>
+      <c r="BD27">
+        <v>6.8</v>
+      </c>
+      <c r="BE27">
+        <v>7.4</v>
+      </c>
+      <c r="BF27">
+        <v>6</v>
+      </c>
+      <c r="BG27">
+        <v>7.2</v>
+      </c>
+      <c r="BH27">
+        <v>2.82</v>
+      </c>
+      <c r="BI27">
+        <v>2.32</v>
+      </c>
+      <c r="BJ27">
+        <v>12</v>
+      </c>
+      <c r="BK27">
+        <v>5.8</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>10.5</v>
+      </c>
+      <c r="BN27">
+        <v>4.8</v>
+      </c>
+      <c r="BO27">
+        <v>3.7</v>
+      </c>
+      <c r="BP27">
+        <v>18</v>
+      </c>
+      <c r="BQ27">
+        <v>6.8</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT27">
         <v>8</v>
       </c>
-      <c r="BU26">
-        <v>6</v>
-      </c>
-      <c r="BV26">
-        <v>1000</v>
-      </c>
-      <c r="BW26">
-        <v>9.4</v>
-      </c>
-      <c r="BX26">
-        <v>1000</v>
-      </c>
-      <c r="BY26">
-        <v>10</v>
-      </c>
-      <c r="BZ26">
-        <v>1000</v>
-      </c>
-      <c r="CA26">
-        <v>9.4</v>
-      </c>
-      <c r="CB26" t="s">
-        <v>148</v>
+      <c r="BU27">
+        <v>4.6</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>9</v>
+      </c>
+      <c r="BX27">
+        <v>1000</v>
+      </c>
+      <c r="BY27">
+        <v>9.6</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>9</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -349,7 +349,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 03:47:31</t>
+    <t>2026-07-23 05:56:42</t>
   </si>
 </sst>
 </file>
@@ -946,13 +946,13 @@
         <v>4.9</v>
       </c>
       <c r="G2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="I2">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J2">
         <v>4.5</v>
@@ -973,31 +973,31 @@
         <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T2">
         <v>1.59</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W2">
         <v>1.22</v>
       </c>
       <c r="X2">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="Y2">
         <v>14</v>
@@ -1030,13 +1030,13 @@
         <v>18</v>
       </c>
       <c r="AI2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
         <v>700</v>
       </c>
       <c r="AK2">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AL2">
         <v>150</v>
@@ -1093,13 +1093,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BD2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG2">
         <v>3.9</v>
@@ -1108,10 +1108,10 @@
         <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK2">
         <v>5.6</v>
@@ -1120,28 +1120,28 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BO2">
         <v>5.8</v>
       </c>
       <c r="BP2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU2">
         <v>4.1</v>
@@ -1153,10 +1153,10 @@
         <v>6.2</v>
       </c>
       <c r="BX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ2">
         <v>13</v>
@@ -1188,22 +1188,22 @@
         <v>2.86</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="I3">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K3">
         <v>5.4</v>
       </c>
       <c r="L3">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M3">
         <v>1.01</v>
@@ -1215,16 +1215,16 @@
         <v>1.07</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q3">
         <v>1.24</v>
       </c>
       <c r="R3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="T3">
         <v>1.29</v>
@@ -1236,115 +1236,115 @@
         <v>1.8</v>
       </c>
       <c r="W3">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
         <v>85</v>
       </c>
       <c r="Y3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Z3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA3">
+        <v>36</v>
+      </c>
+      <c r="AB3">
+        <v>40</v>
+      </c>
+      <c r="AC3">
+        <v>17</v>
+      </c>
+      <c r="AD3">
+        <v>15</v>
+      </c>
+      <c r="AE3">
+        <v>20</v>
+      </c>
+      <c r="AF3">
         <v>42</v>
-      </c>
-      <c r="AB3">
-        <v>46</v>
-      </c>
-      <c r="AC3">
-        <v>19.5</v>
-      </c>
-      <c r="AD3">
-        <v>17.5</v>
-      </c>
-      <c r="AE3">
-        <v>24</v>
-      </c>
-      <c r="AF3">
-        <v>48</v>
       </c>
       <c r="AG3">
         <v>22</v>
       </c>
       <c r="AH3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AI3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL3">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AM3">
         <v>38</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO3">
+        <v>5.9</v>
+      </c>
+      <c r="AP3">
+        <v>7.6</v>
+      </c>
+      <c r="AQ3">
+        <v>6.6</v>
+      </c>
+      <c r="AR3">
+        <v>6.6</v>
+      </c>
+      <c r="AS3">
         <v>6.8</v>
       </c>
-      <c r="AP3">
-        <v>4.1</v>
-      </c>
-      <c r="AQ3">
-        <v>3.9</v>
-      </c>
-      <c r="AR3">
-        <v>3.85</v>
-      </c>
-      <c r="AS3">
-        <v>3.9</v>
-      </c>
       <c r="AT3">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
+        <v>5.4</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>7</v>
+      </c>
+      <c r="AY3">
+        <v>6</v>
+      </c>
+      <c r="AZ3">
+        <v>5.4</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>7.4</v>
+      </c>
+      <c r="BC3">
+        <v>6.6</v>
+      </c>
+      <c r="BD3">
+        <v>6.2</v>
+      </c>
+      <c r="BE3">
+        <v>6.8</v>
+      </c>
+      <c r="BF3">
+        <v>4.6</v>
+      </c>
+      <c r="BG3">
         <v>3.45</v>
-      </c>
-      <c r="AW3">
-        <v>3.65</v>
-      </c>
-      <c r="AX3">
-        <v>3.95</v>
-      </c>
-      <c r="AY3">
-        <v>3.6</v>
-      </c>
-      <c r="AZ3">
-        <v>3.45</v>
-      </c>
-      <c r="BA3">
-        <v>3.65</v>
-      </c>
-      <c r="BB3">
-        <v>4</v>
-      </c>
-      <c r="BC3">
-        <v>3.85</v>
-      </c>
-      <c r="BD3">
-        <v>3.75</v>
-      </c>
-      <c r="BE3">
-        <v>3.9</v>
-      </c>
-      <c r="BF3">
-        <v>3.15</v>
-      </c>
-      <c r="BG3">
-        <v>2.64</v>
       </c>
       <c r="BH3">
         <v>7.4</v>
@@ -1433,10 +1433,10 @@
         <v>2.64</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1475,10 +1475,10 @@
         <v>1.99</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1544,7 +1544,7 @@
         <v>9</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -1556,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX4">
         <v>13.5</v>
@@ -1565,7 +1565,7 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA4">
         <v>12</v>
@@ -1574,7 +1574,7 @@
         <v>32</v>
       </c>
       <c r="BC4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD4">
         <v>11.5</v>
@@ -1583,7 +1583,7 @@
         <v>13</v>
       </c>
       <c r="BF4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
         <v>11</v>
@@ -1672,13 +1672,13 @@
         <v>1.85</v>
       </c>
       <c r="G5">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
         <v>3.35</v>
@@ -1687,43 +1687,43 @@
         <v>3.45</v>
       </c>
       <c r="L5">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M5">
         <v>1.12</v>
       </c>
       <c r="N5">
+        <v>2.64</v>
+      </c>
+      <c r="O5">
+        <v>1.55</v>
+      </c>
+      <c r="P5">
+        <v>1.53</v>
+      </c>
+      <c r="Q5">
         <v>2.68</v>
       </c>
-      <c r="O5">
-        <v>1.54</v>
-      </c>
-      <c r="P5">
-        <v>1.54</v>
-      </c>
-      <c r="Q5">
-        <v>2.66</v>
-      </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y5">
         <v>14</v>
@@ -1732,7 +1732,7 @@
         <v>42</v>
       </c>
       <c r="AA5">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB5">
         <v>6.4</v>
@@ -1741,10 +1741,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="AF5">
         <v>10</v>
@@ -1756,28 +1756,28 @@
         <v>29</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>700</v>
       </c>
       <c r="AJ5">
         <v>21</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO5">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AP5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5">
         <v>12</v>
@@ -1798,7 +1798,7 @@
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="AX5">
         <v>8.6</v>
@@ -1822,7 +1822,7 @@
         <v>50</v>
       </c>
       <c r="BE5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF5">
         <v>18.5</v>
@@ -1831,10 +1831,10 @@
         <v>13</v>
       </c>
       <c r="BH5">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BI5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5">
         <v>13</v>
@@ -1855,40 +1855,40 @@
         <v>3.6</v>
       </c>
       <c r="BP5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT5">
         <v>9.4</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>70</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
         <v>10</v>
       </c>
       <c r="BZ5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1920,13 +1920,13 @@
         <v>2.1</v>
       </c>
       <c r="I6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L6">
         <v>1.72</v>
@@ -1935,16 +1935,16 @@
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O6">
         <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
         <v>1.13</v>
@@ -1953,40 +1953,40 @@
         <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W6">
         <v>1.24</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Z6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB6">
         <v>11</v>
       </c>
       <c r="AC6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF6">
         <v>34</v>
@@ -2019,22 +2019,22 @@
         <v>40</v>
       </c>
       <c r="AP6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR6">
         <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AT6">
         <v>9.6</v>
       </c>
       <c r="AU6">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2064,7 +2064,7 @@
         <v>46</v>
       </c>
       <c r="BE6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF6">
         <v>95</v>
@@ -2073,7 +2073,7 @@
         <v>27</v>
       </c>
       <c r="BH6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BI6">
         <v>2.26</v>
@@ -2082,13 +2082,13 @@
         <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>17.5</v>
+        <v>2.14</v>
       </c>
       <c r="BN6">
         <v>8.199999999999999</v>
@@ -2100,13 +2100,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>14</v>
+        <v>2.08</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BT6">
         <v>4.5</v>
@@ -2115,16 +2115,16 @@
         <v>4</v>
       </c>
       <c r="BV6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX6">
         <v>55</v>
       </c>
       <c r="BY6">
-        <v>14</v>
+        <v>2.06</v>
       </c>
       <c r="BZ6">
         <v>65</v>
@@ -2156,7 +2156,7 @@
         <v>2.9</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H7">
         <v>3.2</v>
@@ -2165,49 +2165,49 @@
         <v>3.3</v>
       </c>
       <c r="J7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K7">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="L7">
         <v>1.71</v>
       </c>
       <c r="M7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="P7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q7">
         <v>3.25</v>
       </c>
       <c r="R7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="T7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U7">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V7">
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -2219,13 +2219,13 @@
         <v>65</v>
       </c>
       <c r="AB7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE7">
         <v>120</v>
@@ -2240,13 +2240,13 @@
         <v>46</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="AJ7">
         <v>55</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AL7">
         <v>190</v>
@@ -2255,7 +2255,7 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>70</v>
+        <v>490</v>
       </c>
       <c r="AO7">
         <v>95</v>
@@ -2273,7 +2273,7 @@
         <v>55</v>
       </c>
       <c r="AT7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU7">
         <v>6.4</v>
@@ -2282,7 +2282,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX7">
         <v>14</v>
@@ -2294,7 +2294,7 @@
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB7">
         <v>26</v>
@@ -2312,67 +2312,67 @@
         <v>55</v>
       </c>
       <c r="BG7">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BH7">
         <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="BJ7">
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU7">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,22 +2395,22 @@
         <v>107</v>
       </c>
       <c r="F8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G8">
         <v>1.57</v>
       </c>
       <c r="H8">
+        <v>7.4</v>
+      </c>
+      <c r="I8">
         <v>7.8</v>
       </c>
-      <c r="I8">
-        <v>8.199999999999999</v>
-      </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.43</v>
@@ -2422,10 +2422,10 @@
         <v>3.75</v>
       </c>
       <c r="O8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P8">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
         <v>2.04</v>
@@ -2434,16 +2434,16 @@
         <v>1.34</v>
       </c>
       <c r="S8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T8">
         <v>2.14</v>
       </c>
       <c r="U8">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W8">
         <v>2.74</v>
@@ -2452,7 +2452,7 @@
         <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2464,25 +2464,25 @@
         <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AE8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI8">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="AJ8">
         <v>13.5</v>
@@ -2491,25 +2491,25 @@
         <v>17.5</v>
       </c>
       <c r="AL8">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AM8">
+        <v>570</v>
+      </c>
+      <c r="AN8">
+        <v>9.6</v>
+      </c>
+      <c r="AO8">
         <v>180</v>
-      </c>
-      <c r="AN8">
-        <v>9.4</v>
-      </c>
-      <c r="AO8">
-        <v>190</v>
       </c>
       <c r="AP8">
         <v>12</v>
       </c>
       <c r="AQ8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AS8">
         <v>95</v>
@@ -2521,13 +2521,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW8">
         <v>40</v>
       </c>
       <c r="AX8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY8">
         <v>9.4</v>
@@ -2554,7 +2554,7 @@
         <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BN8">
         <v>3.85</v>
@@ -2599,7 +2599,7 @@
         <v>7.2</v>
       </c>
       <c r="BV8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
         <v>15.5</v>
@@ -2646,7 +2646,7 @@
         <v>5.2</v>
       </c>
       <c r="I9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
         <v>3.8</v>
@@ -2655,7 +2655,7 @@
         <v>3.9</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
         <v>1.07</v>
@@ -2664,25 +2664,25 @@
         <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S9">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T9">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V9">
         <v>1.22</v>
@@ -2694,7 +2694,7 @@
         <v>15</v>
       </c>
       <c r="Y9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z9">
         <v>40</v>
@@ -2709,7 +2709,7 @@
         <v>8.4</v>
       </c>
       <c r="AD9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE9">
         <v>70</v>
@@ -2724,16 +2724,16 @@
         <v>19</v>
       </c>
       <c r="AI9">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AM9">
         <v>110</v>
@@ -2757,7 +2757,7 @@
         <v>42</v>
       </c>
       <c r="AT9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -2775,13 +2775,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA9">
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
@@ -2799,7 +2799,7 @@
         <v>60</v>
       </c>
       <c r="BH9">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI9">
         <v>3.2</v>
@@ -2814,7 +2814,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN9">
         <v>4.5</v>
@@ -2826,25 +2826,25 @@
         <v>12.5</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
         <v>8.4</v>
       </c>
       <c r="BU9">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2856,7 +2856,7 @@
         <v>22</v>
       </c>
       <c r="CA9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2891,7 +2891,7 @@
         <v>4.5</v>
       </c>
       <c r="J10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K10">
         <v>3.35</v>
@@ -2912,7 +2912,7 @@
         <v>1.63</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R10">
         <v>1.23</v>
@@ -3130,13 +3130,13 @@
         <v>4.3</v>
       </c>
       <c r="I11">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L11">
         <v>1.58</v>
@@ -3169,10 +3169,10 @@
         <v>1.74</v>
       </c>
       <c r="V11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X11">
         <v>10</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -349,7 +349,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 05:56:42</t>
+    <t>2026-07-23 08:06:18</t>
   </si>
 </sst>
 </file>
@@ -943,22 +943,22 @@
         <v>101</v>
       </c>
       <c r="F2">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="G2">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="H2">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="I2">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="J2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.27</v>
@@ -967,7 +967,7 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O2">
         <v>1.17</v>
@@ -979,58 +979,58 @@
         <v>1.53</v>
       </c>
       <c r="R2">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U2">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="V2">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="Y2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AB2">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="AC2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF2">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AG2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AJ2">
         <v>700</v>
@@ -1039,22 +1039,22 @@
         <v>160</v>
       </c>
       <c r="AL2">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AO2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AP2">
         <v>13</v>
       </c>
       <c r="AQ2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AR2">
         <v>11</v>
@@ -1063,7 +1063,7 @@
         <v>15</v>
       </c>
       <c r="AT2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AU2">
         <v>9.6</v>
@@ -1075,25 +1075,25 @@
         <v>13</v>
       </c>
       <c r="AX2">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="AY2">
         <v>15</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA2">
         <v>21</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD2">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>8.6</v>
@@ -1102,67 +1102,67 @@
         <v>7.8</v>
       </c>
       <c r="BG2">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="BH2">
         <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="BV2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BW2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BX2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="CB2" t="s">
         <v>111</v>
@@ -1191,13 +1191,13 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I3">
         <v>2.24</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>5.4</v>
@@ -1209,13 +1209,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.1</v>
+        <v>11</v>
       </c>
       <c r="O3">
         <v>1.07</v>
       </c>
       <c r="P3">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
         <v>1.24</v>
@@ -1236,7 +1236,7 @@
         <v>1.8</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
         <v>85</v>
@@ -1254,7 +1254,7 @@
         <v>40</v>
       </c>
       <c r="AC3">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AD3">
         <v>15</v>
@@ -1284,7 +1284,7 @@
         <v>25</v>
       </c>
       <c r="AM3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AN3">
         <v>10</v>
@@ -1299,22 +1299,22 @@
         <v>6.6</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AS3">
         <v>6.8</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AV3">
         <v>5.4</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX3">
         <v>7</v>
@@ -1332,16 +1332,16 @@
         <v>7.4</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD3">
         <v>6.2</v>
       </c>
       <c r="BE3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG3">
         <v>3.45</v>
@@ -1350,7 +1350,7 @@
         <v>7.4</v>
       </c>
       <c r="BI3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ3">
         <v>8.199999999999999</v>
@@ -1362,13 +1362,13 @@
         <v>40</v>
       </c>
       <c r="BM3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BN3">
         <v>8.4</v>
       </c>
       <c r="BO3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
         <v>19.5</v>
@@ -1389,7 +1389,7 @@
         <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BW3">
         <v>5.8</v>
@@ -1427,22 +1427,22 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="G4">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J4">
         <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4">
         <v>1.48</v>
@@ -1451,16 +1451,16 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>1.42</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
         <v>1.28</v>
@@ -1475,10 +1475,10 @@
         <v>1.99</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X4">
         <v>11</v>
@@ -1487,10 +1487,10 @@
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AA4">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB4">
         <v>9.199999999999999</v>
@@ -1499,37 +1499,37 @@
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ4">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="AK4">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM4">
         <v>580</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AO4">
         <v>500</v>
@@ -1538,13 +1538,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AS4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT4">
         <v>7.8</v>
@@ -1553,10 +1553,10 @@
         <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AX4">
         <v>13.5</v>
@@ -1565,28 +1565,28 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BB4">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BC4">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BD4">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BE4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="BH4">
         <v>3.1</v>
@@ -1669,73 +1669,73 @@
         <v>104</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M5">
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="P5">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
         <v>1.2</v>
       </c>
       <c r="W5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X5">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC5">
         <v>8.199999999999999</v>
@@ -1744,28 +1744,28 @@
         <v>25</v>
       </c>
       <c r="AE5">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="AF5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ5">
         <v>21</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL5">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM5">
         <v>500</v>
@@ -1774,121 +1774,121 @@
         <v>23</v>
       </c>
       <c r="AO5">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AP5">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
         <v>36</v>
       </c>
       <c r="AS5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AX5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA5">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BE5">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BF5">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BH5">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>111</v>
@@ -1929,34 +1929,34 @@
         <v>3.1</v>
       </c>
       <c r="L6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O6">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="P6">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T6">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
         <v>1.87</v>
@@ -1974,7 +1974,7 @@
         <v>11</v>
       </c>
       <c r="AA6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB6">
         <v>11</v>
@@ -1986,10 +1986,10 @@
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG6">
         <v>24</v>
@@ -1998,13 +1998,13 @@
         <v>34</v>
       </c>
       <c r="AI6">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AJ6">
         <v>690</v>
       </c>
       <c r="AK6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL6">
         <v>690</v>
@@ -2013,25 +2013,25 @@
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>690</v>
+        <v>590</v>
       </c>
       <c r="AO6">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AP6">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR6">
         <v>9.4</v>
       </c>
       <c r="AS6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU6">
         <v>6.8</v>
@@ -2043,13 +2043,13 @@
         <v>28</v>
       </c>
       <c r="AX6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY6">
         <v>21</v>
       </c>
       <c r="AZ6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA6">
         <v>36</v>
@@ -2061,7 +2061,7 @@
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE6">
         <v>90</v>
@@ -2073,64 +2073,64 @@
         <v>27</v>
       </c>
       <c r="BH6">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>2.06</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>111</v>
@@ -2153,64 +2153,64 @@
         <v>106</v>
       </c>
       <c r="F7">
+        <v>2.84</v>
+      </c>
+      <c r="G7">
+        <v>2.92</v>
+      </c>
+      <c r="H7">
+        <v>3.25</v>
+      </c>
+      <c r="I7">
+        <v>3.35</v>
+      </c>
+      <c r="J7">
+        <v>2.86</v>
+      </c>
+      <c r="K7">
         <v>2.9</v>
       </c>
-      <c r="G7">
-        <v>2.96</v>
-      </c>
-      <c r="H7">
-        <v>3.2</v>
-      </c>
-      <c r="I7">
-        <v>3.3</v>
-      </c>
-      <c r="J7">
-        <v>2.84</v>
-      </c>
-      <c r="K7">
-        <v>2.88</v>
-      </c>
       <c r="L7">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M7">
         <v>1.17</v>
       </c>
       <c r="N7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O7">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P7">
         <v>1.43</v>
       </c>
       <c r="Q7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T7">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
         <v>1.67</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z7">
         <v>19</v>
@@ -2219,13 +2219,13 @@
         <v>65</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC7">
         <v>7</v>
       </c>
       <c r="AD7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE7">
         <v>120</v>
@@ -2234,10 +2234,10 @@
         <v>16.5</v>
       </c>
       <c r="AG7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AI7">
         <v>220</v>
@@ -2255,10 +2255,10 @@
         <v>500</v>
       </c>
       <c r="AN7">
-        <v>490</v>
+        <v>65</v>
       </c>
       <c r="AO7">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP7">
         <v>6.2</v>
@@ -2282,19 +2282,19 @@
         <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX7">
         <v>14</v>
       </c>
       <c r="AY7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
         <v>25</v>
       </c>
       <c r="BA7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB7">
         <v>26</v>
@@ -2312,25 +2312,25 @@
         <v>55</v>
       </c>
       <c r="BG7">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BH7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI7">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
@@ -2342,13 +2342,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT7">
         <v>6</v>
@@ -2360,19 +2360,19 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB7" t="s">
         <v>111</v>
@@ -2395,25 +2395,25 @@
         <v>107</v>
       </c>
       <c r="F8">
+        <v>1.54</v>
+      </c>
+      <c r="G8">
         <v>1.56</v>
       </c>
-      <c r="G8">
-        <v>1.57</v>
-      </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I8">
         <v>7.8</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M8">
         <v>1.08</v>
@@ -2422,37 +2422,37 @@
         <v>3.75</v>
       </c>
       <c r="O8">
+        <v>1.34</v>
+      </c>
+      <c r="P8">
+        <v>1.94</v>
+      </c>
+      <c r="Q8">
+        <v>2.02</v>
+      </c>
+      <c r="R8">
         <v>1.35</v>
-      </c>
-      <c r="P8">
-        <v>1.92</v>
-      </c>
-      <c r="Q8">
-        <v>2.04</v>
-      </c>
-      <c r="R8">
-        <v>1.34</v>
       </c>
       <c r="S8">
         <v>3.7</v>
       </c>
       <c r="T8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W8">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2464,16 +2464,16 @@
         <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE8">
         <v>130</v>
       </c>
       <c r="AF8">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -2482,13 +2482,13 @@
         <v>27</v>
       </c>
       <c r="AI8">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL8">
         <v>44</v>
@@ -2497,28 +2497,28 @@
         <v>570</v>
       </c>
       <c r="AN8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO8">
         <v>180</v>
       </c>
       <c r="AP8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
         <v>19.5</v>
       </c>
       <c r="AR8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS8">
         <v>95</v>
       </c>
       <c r="AT8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>25</v>
@@ -2527,7 +2527,7 @@
         <v>40</v>
       </c>
       <c r="AX8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY8">
         <v>9.4</v>
@@ -2551,16 +2551,16 @@
         <v>70</v>
       </c>
       <c r="BF8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH8">
         <v>3.35</v>
       </c>
       <c r="BI8">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
         <v>11.5</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BN8">
         <v>3.85</v>
@@ -2581,16 +2581,16 @@
         <v>3.5</v>
       </c>
       <c r="BP8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT8">
         <v>11</v>
@@ -2602,19 +2602,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BX8">
         <v>100</v>
       </c>
       <c r="BY8">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BZ8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="s">
         <v>111</v>
@@ -2637,16 +2637,16 @@
         <v>108</v>
       </c>
       <c r="F9">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="H9">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I9">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J9">
         <v>3.8</v>
@@ -2661,49 +2661,49 @@
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
         <v>2.14</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W9">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X9">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>690</v>
       </c>
       <c r="AB9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8.4</v>
@@ -2715,7 +2715,7 @@
         <v>70</v>
       </c>
       <c r="AF9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG9">
         <v>10</v>
@@ -2727,10 +2727,10 @@
         <v>75</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL9">
         <v>36</v>
@@ -2739,31 +2739,31 @@
         <v>110</v>
       </c>
       <c r="AN9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO9">
         <v>80</v>
       </c>
       <c r="AP9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AR9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS9">
         <v>42</v>
       </c>
       <c r="AT9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
       </c>
       <c r="AV9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW9">
         <v>55</v>
@@ -2772,7 +2772,7 @@
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>17.5</v>
@@ -2781,7 +2781,7 @@
         <v>55</v>
       </c>
       <c r="BB9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC9">
         <v>16.5</v>
@@ -2793,7 +2793,7 @@
         <v>38</v>
       </c>
       <c r="BF9">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG9">
         <v>60</v>
@@ -2805,58 +2805,58 @@
         <v>3.2</v>
       </c>
       <c r="BJ9">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>15.5</v>
+        <v>5.3</v>
       </c>
       <c r="BN9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>2.46</v>
       </c>
       <c r="BP9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>10.5</v>
+        <v>4.6</v>
       </c>
       <c r="BT9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA9">
-        <v>9.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="CB9" t="s">
         <v>111</v>
@@ -2879,22 +2879,22 @@
         <v>109</v>
       </c>
       <c r="F10">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J10">
         <v>3.25</v>
       </c>
       <c r="K10">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L10">
         <v>1.54</v>
@@ -2903,40 +2903,40 @@
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q10">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U10">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X10">
         <v>9.800000000000001</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z10">
         <v>32</v>
@@ -2951,7 +2951,7 @@
         <v>7.8</v>
       </c>
       <c r="AD10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE10">
         <v>75</v>
@@ -2972,7 +2972,7 @@
         <v>29</v>
       </c>
       <c r="AK10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL10">
         <v>55</v>
@@ -2981,10 +2981,10 @@
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP10">
         <v>8.6</v>
@@ -2993,43 +2993,43 @@
         <v>10.5</v>
       </c>
       <c r="AR10">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AS10">
         <v>10</v>
       </c>
       <c r="AT10">
+        <v>6.4</v>
+      </c>
+      <c r="AU10">
         <v>6.6</v>
       </c>
-      <c r="AU10">
-        <v>6.4</v>
-      </c>
       <c r="AV10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW10">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AX10">
         <v>10</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BB10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC10">
         <v>21</v>
       </c>
       <c r="BD10">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE10">
         <v>10.5</v>
@@ -3038,67 +3038,67 @@
         <v>21</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BH10">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>111</v>
@@ -3136,7 +3136,7 @@
         <v>3.25</v>
       </c>
       <c r="K11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
         <v>1.58</v>
@@ -3154,19 +3154,19 @@
         <v>1.54</v>
       </c>
       <c r="Q11">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T11">
         <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V11">
         <v>1.28</v>
@@ -3223,7 +3223,7 @@
         <v>230</v>
       </c>
       <c r="AN11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO11">
         <v>140</v>
@@ -3235,10 +3235,10 @@
         <v>10</v>
       </c>
       <c r="AR11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT11">
         <v>5.9</v>
@@ -3250,7 +3250,7 @@
         <v>16</v>
       </c>
       <c r="AW11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX11">
         <v>10</v>
@@ -3262,16 +3262,16 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BC11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BD11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE11">
         <v>6</v>
@@ -3280,7 +3280,7 @@
         <v>21</v>
       </c>
       <c r="BG11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH11">
         <v>2.8</v>
@@ -3325,7 +3325,7 @@
         <v>6</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW11">
         <v>9.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="116">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Icelandic 3 Deild</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -295,6 +301,9 @@
     <t>KA Asvellir</t>
   </si>
   <si>
+    <t>Independiente Juniors</t>
+  </si>
+  <si>
     <t>Orense Sporting Club</t>
   </si>
   <si>
@@ -325,6 +334,9 @@
     <t>Augnablik</t>
   </si>
   <si>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
     <t>Aucas</t>
   </si>
   <si>
@@ -349,7 +361,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 08:06:18</t>
+    <t>2026-07-23 10:16:15</t>
   </si>
 </sst>
 </file>
@@ -681,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -931,37 +943,37 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G2">
         <v>4.6</v>
       </c>
       <c r="H2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I2">
         <v>1.82</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
         <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2">
         <v>1.03</v>
@@ -973,34 +985,34 @@
         <v>1.17</v>
       </c>
       <c r="P2">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="Q2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R2">
         <v>1.73</v>
       </c>
       <c r="S2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W2">
         <v>1.27</v>
       </c>
       <c r="X2">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
         <v>15</v>
@@ -1018,7 +1030,7 @@
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF2">
         <v>130</v>
@@ -1036,7 +1048,7 @@
         <v>700</v>
       </c>
       <c r="AK2">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AL2">
         <v>55</v>
@@ -1045,22 +1057,22 @@
         <v>200</v>
       </c>
       <c r="AN2">
-        <v>260</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP2">
         <v>13</v>
       </c>
       <c r="AQ2">
+        <v>11.5</v>
+      </c>
+      <c r="AR2">
         <v>6</v>
       </c>
-      <c r="AR2">
-        <v>11</v>
-      </c>
       <c r="AS2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT2">
         <v>20</v>
@@ -1072,7 +1084,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX2">
         <v>19.5</v>
@@ -1087,70 +1099,70 @@
         <v>21</v>
       </c>
       <c r="BB2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD2">
+        <v>22</v>
+      </c>
+      <c r="BE2">
         <v>8.4</v>
       </c>
-      <c r="BD2">
-        <v>34</v>
-      </c>
-      <c r="BE2">
-        <v>8.6</v>
-      </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH2">
         <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BJ2">
         <v>9.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2">
         <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BV2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BW2">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>21</v>
@@ -1162,10 +1174,10 @@
         <v>13.5</v>
       </c>
       <c r="CA2">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1173,34 +1185,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H3">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="I3">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L3">
         <v>1.16</v>
@@ -1212,64 +1224,64 @@
         <v>11</v>
       </c>
       <c r="O3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="S3">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="T3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="U3">
         <v>3.7</v>
       </c>
       <c r="V3">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB3">
+        <v>38</v>
+      </c>
+      <c r="AC3">
+        <v>16</v>
+      </c>
+      <c r="AD3">
+        <v>14.5</v>
+      </c>
+      <c r="AE3">
+        <v>19.5</v>
+      </c>
+      <c r="AF3">
         <v>40</v>
-      </c>
-      <c r="AC3">
-        <v>19.5</v>
-      </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
-      <c r="AE3">
-        <v>20</v>
-      </c>
-      <c r="AF3">
-        <v>42</v>
       </c>
       <c r="AG3">
         <v>22</v>
       </c>
       <c r="AH3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
         <v>21</v>
@@ -1278,7 +1290,7 @@
         <v>60</v>
       </c>
       <c r="AK3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL3">
         <v>25</v>
@@ -1287,127 +1299,127 @@
         <v>32</v>
       </c>
       <c r="AN3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
         <v>5.9</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AU3">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AV3">
-        <v>5.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>5.9</v>
+        <v>16.5</v>
       </c>
       <c r="AX3">
+        <v>18.5</v>
+      </c>
+      <c r="AY3">
+        <v>15</v>
+      </c>
+      <c r="AZ3">
+        <v>12</v>
+      </c>
+      <c r="BA3">
+        <v>17</v>
+      </c>
+      <c r="BB3">
+        <v>22</v>
+      </c>
+      <c r="BC3">
+        <v>13</v>
+      </c>
+      <c r="BD3">
+        <v>21</v>
+      </c>
+      <c r="BE3">
+        <v>14</v>
+      </c>
+      <c r="BF3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG3">
+        <v>5.2</v>
+      </c>
+      <c r="BH3">
         <v>7</v>
       </c>
-      <c r="AY3">
-        <v>6</v>
-      </c>
-      <c r="AZ3">
-        <v>5.4</v>
-      </c>
-      <c r="BA3">
-        <v>6</v>
-      </c>
-      <c r="BB3">
-        <v>7.4</v>
-      </c>
-      <c r="BC3">
-        <v>6.4</v>
-      </c>
-      <c r="BD3">
-        <v>6.2</v>
-      </c>
-      <c r="BE3">
-        <v>6.6</v>
-      </c>
-      <c r="BF3">
-        <v>4.5</v>
-      </c>
-      <c r="BG3">
-        <v>3.45</v>
-      </c>
-      <c r="BH3">
-        <v>7.4</v>
-      </c>
       <c r="BI3">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BJ3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>40</v>
       </c>
       <c r="BM3">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ3">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>19.5</v>
       </c>
       <c r="BS3">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BT3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BV3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BX3">
         <v>16.5</v>
       </c>
       <c r="BY3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3">
         <v>8.199999999999999</v>
       </c>
       <c r="CA3">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1415,196 +1427,196 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="G4">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
+        <v>3.85</v>
+      </c>
+      <c r="J4">
+        <v>2.96</v>
+      </c>
+      <c r="K4">
         <v>3.3</v>
       </c>
-      <c r="J4">
-        <v>3.15</v>
-      </c>
-      <c r="K4">
-        <v>3.35</v>
-      </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="O4">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X4">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE4">
         <v>100</v>
       </c>
       <c r="AF4">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH4">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI4">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AJ4">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AL4">
         <v>110</v>
       </c>
       <c r="AM4">
-        <v>580</v>
+        <v>230</v>
       </c>
       <c r="AN4">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AV4">
+        <v>13.5</v>
+      </c>
+      <c r="AW4">
+        <v>7.2</v>
+      </c>
+      <c r="AX4">
+        <v>12</v>
+      </c>
+      <c r="AY4">
         <v>10.5</v>
       </c>
-      <c r="AW4">
-        <v>29</v>
-      </c>
-      <c r="AX4">
-        <v>13.5</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
       <c r="AZ4">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA4">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="BC4">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BD4">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="BG4">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="BH4">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
         <v>5.4</v>
@@ -1613,285 +1625,285 @@
         <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU4">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="G5">
-        <v>1.87</v>
+        <v>2.72</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="X5">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="AA5">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB5">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD5">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF5">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="AG5">
+        <v>13</v>
+      </c>
+      <c r="AH5">
+        <v>24</v>
+      </c>
+      <c r="AI5">
+        <v>290</v>
+      </c>
+      <c r="AJ5">
+        <v>44</v>
+      </c>
+      <c r="AK5">
+        <v>38</v>
+      </c>
+      <c r="AL5">
+        <v>75</v>
+      </c>
+      <c r="AM5">
+        <v>580</v>
+      </c>
+      <c r="AN5">
+        <v>42</v>
+      </c>
+      <c r="AO5">
+        <v>500</v>
+      </c>
+      <c r="AP5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR5">
+        <v>18</v>
+      </c>
+      <c r="AS5">
+        <v>40</v>
+      </c>
+      <c r="AT5">
+        <v>8</v>
+      </c>
+      <c r="AU5">
+        <v>6.4</v>
+      </c>
+      <c r="AV5">
+        <v>12.5</v>
+      </c>
+      <c r="AW5">
+        <v>27</v>
+      </c>
+      <c r="AX5">
+        <v>13</v>
+      </c>
+      <c r="AY5">
         <v>11</v>
       </c>
-      <c r="AH5">
+      <c r="AZ5">
+        <v>17</v>
+      </c>
+      <c r="BA5">
+        <v>40</v>
+      </c>
+      <c r="BB5">
         <v>27</v>
       </c>
-      <c r="AI5">
-        <v>140</v>
-      </c>
-      <c r="AJ5">
-        <v>21</v>
-      </c>
-      <c r="AK5">
-        <v>32</v>
-      </c>
-      <c r="AL5">
-        <v>60</v>
-      </c>
-      <c r="AM5">
-        <v>500</v>
-      </c>
-      <c r="AN5">
-        <v>23</v>
-      </c>
-      <c r="AO5">
-        <v>200</v>
-      </c>
-      <c r="AP5">
-        <v>8.4</v>
-      </c>
-      <c r="AQ5">
-        <v>11.5</v>
-      </c>
-      <c r="AR5">
-        <v>36</v>
-      </c>
-      <c r="AS5">
-        <v>11.5</v>
-      </c>
-      <c r="AT5">
-        <v>5.7</v>
-      </c>
-      <c r="AU5">
-        <v>7.4</v>
-      </c>
-      <c r="AV5">
-        <v>21</v>
-      </c>
-      <c r="AW5">
-        <v>55</v>
-      </c>
-      <c r="AX5">
-        <v>8.4</v>
-      </c>
-      <c r="AY5">
-        <v>10</v>
-      </c>
-      <c r="AZ5">
+      <c r="BC5">
+        <v>24</v>
+      </c>
+      <c r="BD5">
+        <v>40</v>
+      </c>
+      <c r="BE5">
+        <v>29</v>
+      </c>
+      <c r="BF5">
         <v>26</v>
       </c>
-      <c r="BA5">
+      <c r="BG5">
         <v>29</v>
       </c>
-      <c r="BB5">
-        <v>17.5</v>
-      </c>
-      <c r="BC5">
-        <v>21</v>
-      </c>
-      <c r="BD5">
-        <v>46</v>
-      </c>
-      <c r="BE5">
-        <v>28</v>
-      </c>
-      <c r="BF5">
-        <v>17</v>
-      </c>
-      <c r="BG5">
-        <v>11.5</v>
-      </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>15</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1899,276 +1911,276 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F6">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="G6">
-        <v>5.1</v>
+        <v>1.87</v>
       </c>
       <c r="H6">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="I6">
+        <v>5.9</v>
+      </c>
+      <c r="J6">
+        <v>3.45</v>
+      </c>
+      <c r="K6">
+        <v>3.55</v>
+      </c>
+      <c r="L6">
+        <v>1.56</v>
+      </c>
+      <c r="M6">
+        <v>1.11</v>
+      </c>
+      <c r="N6">
+        <v>2.92</v>
+      </c>
+      <c r="O6">
+        <v>1.5</v>
+      </c>
+      <c r="P6">
+        <v>1.64</v>
+      </c>
+      <c r="Q6">
+        <v>2.46</v>
+      </c>
+      <c r="R6">
+        <v>1.22</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <v>2.2</v>
+      </c>
+      <c r="U6">
+        <v>1.71</v>
+      </c>
+      <c r="V6">
+        <v>1.21</v>
+      </c>
+      <c r="W6">
         <v>2.14</v>
       </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3.1</v>
-      </c>
-      <c r="L6">
-        <v>1.7</v>
-      </c>
-      <c r="M6">
-        <v>1.17</v>
-      </c>
-      <c r="N6">
-        <v>2.36</v>
-      </c>
-      <c r="O6">
-        <v>1.71</v>
-      </c>
-      <c r="P6">
-        <v>1.43</v>
-      </c>
-      <c r="Q6">
-        <v>3.25</v>
-      </c>
-      <c r="R6">
-        <v>1.14</v>
-      </c>
-      <c r="S6">
-        <v>7.4</v>
-      </c>
-      <c r="T6">
-        <v>2.56</v>
-      </c>
-      <c r="U6">
-        <v>1.6</v>
-      </c>
-      <c r="V6">
-        <v>1.87</v>
-      </c>
-      <c r="W6">
-        <v>1.24</v>
-      </c>
       <c r="X6">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="Z6">
+        <v>44</v>
+      </c>
+      <c r="AA6">
+        <v>170</v>
+      </c>
+      <c r="AB6">
+        <v>6.6</v>
+      </c>
+      <c r="AC6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD6">
+        <v>23</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
+        <v>9.4</v>
+      </c>
+      <c r="AG6">
         <v>11</v>
       </c>
-      <c r="AA6">
-        <v>29</v>
-      </c>
-      <c r="AB6">
-        <v>11</v>
-      </c>
-      <c r="AC6">
-        <v>7.6</v>
-      </c>
-      <c r="AD6">
-        <v>13</v>
-      </c>
-      <c r="AE6">
-        <v>36</v>
-      </c>
-      <c r="AF6">
-        <v>36</v>
-      </c>
-      <c r="AG6">
-        <v>24</v>
-      </c>
       <c r="AH6">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AJ6">
-        <v>690</v>
+        <v>21</v>
       </c>
       <c r="AK6">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="AL6">
-        <v>690</v>
+        <v>60</v>
       </c>
       <c r="AM6">
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>590</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="AP6">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="AS6">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="AT6">
+        <v>6.2</v>
+      </c>
+      <c r="AU6">
+        <v>7.4</v>
+      </c>
+      <c r="AV6">
+        <v>20</v>
+      </c>
+      <c r="AW6">
+        <v>60</v>
+      </c>
+      <c r="AX6">
+        <v>8.6</v>
+      </c>
+      <c r="AY6">
         <v>10</v>
       </c>
-      <c r="AU6">
-        <v>6.8</v>
-      </c>
-      <c r="AV6">
-        <v>11.5</v>
-      </c>
-      <c r="AW6">
-        <v>28</v>
-      </c>
-      <c r="AX6">
-        <v>26</v>
-      </c>
-      <c r="AY6">
+      <c r="AZ6">
+        <v>24</v>
+      </c>
+      <c r="BA6">
+        <v>60</v>
+      </c>
+      <c r="BB6">
+        <v>18.5</v>
+      </c>
+      <c r="BC6">
         <v>21</v>
       </c>
-      <c r="AZ6">
-        <v>26</v>
-      </c>
-      <c r="BA6">
-        <v>36</v>
-      </c>
-      <c r="BB6">
-        <v>42</v>
-      </c>
-      <c r="BC6">
+      <c r="BD6">
+        <v>46</v>
+      </c>
+      <c r="BE6">
         <v>38</v>
       </c>
-      <c r="BD6">
-        <v>44</v>
-      </c>
-      <c r="BE6">
-        <v>90</v>
-      </c>
       <c r="BF6">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="BG6">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="G7">
-        <v>2.92</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="I7">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="J7">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K7">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>1.69</v>
@@ -2189,193 +2201,193 @@
         <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
         <v>7.4</v>
       </c>
       <c r="T7">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="U7">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="V7">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="W7">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="X7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AA7">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="AB7">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AD7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AF7">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AH7">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI7">
-        <v>220</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AK7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL7">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AM7">
         <v>500</v>
       </c>
       <c r="AN7">
+        <v>210</v>
+      </c>
+      <c r="AO7">
+        <v>36</v>
+      </c>
+      <c r="AP7">
+        <v>6.4</v>
+      </c>
+      <c r="AQ7">
+        <v>5.5</v>
+      </c>
+      <c r="AR7">
+        <v>9.6</v>
+      </c>
+      <c r="AS7">
+        <v>24</v>
+      </c>
+      <c r="AT7">
+        <v>10</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>11.5</v>
+      </c>
+      <c r="AW7">
+        <v>26</v>
+      </c>
+      <c r="AX7">
+        <v>29</v>
+      </c>
+      <c r="AY7">
+        <v>20</v>
+      </c>
+      <c r="AZ7">
+        <v>28</v>
+      </c>
+      <c r="BA7">
         <v>65</v>
       </c>
-      <c r="AO7">
-        <v>90</v>
-      </c>
-      <c r="AP7">
-        <v>6.2</v>
-      </c>
-      <c r="AQ7">
-        <v>7.4</v>
-      </c>
-      <c r="AR7">
-        <v>16.5</v>
-      </c>
-      <c r="AS7">
-        <v>55</v>
-      </c>
-      <c r="AT7">
-        <v>7</v>
-      </c>
-      <c r="AU7">
-        <v>6.4</v>
-      </c>
-      <c r="AV7">
-        <v>14.5</v>
-      </c>
-      <c r="AW7">
-        <v>50</v>
-      </c>
-      <c r="AX7">
-        <v>14</v>
-      </c>
-      <c r="AY7">
-        <v>13</v>
-      </c>
-      <c r="AZ7">
-        <v>25</v>
-      </c>
-      <c r="BA7">
-        <v>40</v>
-      </c>
       <c r="BB7">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BC7">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE7">
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BG7">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BH7">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BJ7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO7">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ7">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BS7">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BT7">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BU7">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA7">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2383,483 +2395,483 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>1.54</v>
+        <v>2.82</v>
       </c>
       <c r="G8">
-        <v>1.56</v>
+        <v>2.88</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="I8">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="L8">
+        <v>1.69</v>
+      </c>
+      <c r="M8">
+        <v>1.17</v>
+      </c>
+      <c r="N8">
+        <v>2.34</v>
+      </c>
+      <c r="O8">
+        <v>1.71</v>
+      </c>
+      <c r="P8">
+        <v>1.43</v>
+      </c>
+      <c r="Q8">
+        <v>3.25</v>
+      </c>
+      <c r="R8">
+        <v>1.14</v>
+      </c>
+      <c r="S8">
+        <v>7.4</v>
+      </c>
+      <c r="T8">
+        <v>2.42</v>
+      </c>
+      <c r="U8">
+        <v>1.67</v>
+      </c>
+      <c r="V8">
         <v>1.42</v>
       </c>
-      <c r="M8">
-        <v>1.08</v>
-      </c>
-      <c r="N8">
-        <v>3.75</v>
-      </c>
-      <c r="O8">
-        <v>1.34</v>
-      </c>
-      <c r="P8">
-        <v>1.94</v>
-      </c>
-      <c r="Q8">
-        <v>2.02</v>
-      </c>
-      <c r="R8">
-        <v>1.35</v>
-      </c>
-      <c r="S8">
-        <v>3.7</v>
-      </c>
-      <c r="T8">
-        <v>2.16</v>
-      </c>
-      <c r="U8">
-        <v>1.82</v>
-      </c>
-      <c r="V8">
-        <v>1.14</v>
-      </c>
       <c r="W8">
-        <v>2.78</v>
+        <v>1.53</v>
       </c>
       <c r="X8">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="Y8">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AA8">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="AB8">
         <v>7.4</v>
       </c>
       <c r="AC8">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AD8">
-        <v>29</v>
+        <v>16.5</v>
       </c>
       <c r="AE8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AG8">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AJ8">
+        <v>55</v>
+      </c>
+      <c r="AK8">
+        <v>100</v>
+      </c>
+      <c r="AL8">
+        <v>190</v>
+      </c>
+      <c r="AM8">
+        <v>500</v>
+      </c>
+      <c r="AN8">
+        <v>65</v>
+      </c>
+      <c r="AO8">
+        <v>90</v>
+      </c>
+      <c r="AP8">
+        <v>6.2</v>
+      </c>
+      <c r="AQ8">
+        <v>7.6</v>
+      </c>
+      <c r="AR8">
+        <v>17.5</v>
+      </c>
+      <c r="AS8">
+        <v>55</v>
+      </c>
+      <c r="AT8">
+        <v>6.8</v>
+      </c>
+      <c r="AU8">
+        <v>6.6</v>
+      </c>
+      <c r="AV8">
+        <v>14.5</v>
+      </c>
+      <c r="AW8">
+        <v>50</v>
+      </c>
+      <c r="AX8">
+        <v>14</v>
+      </c>
+      <c r="AY8">
         <v>13</v>
       </c>
-      <c r="AK8">
-        <v>17</v>
-      </c>
-      <c r="AL8">
-        <v>44</v>
-      </c>
-      <c r="AM8">
-        <v>570</v>
-      </c>
-      <c r="AN8">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO8">
-        <v>180</v>
-      </c>
-      <c r="AP8">
-        <v>13</v>
-      </c>
-      <c r="AQ8">
-        <v>19.5</v>
-      </c>
-      <c r="AR8">
+      <c r="AZ8">
+        <v>25</v>
+      </c>
+      <c r="BA8">
+        <v>46</v>
+      </c>
+      <c r="BB8">
+        <v>42</v>
+      </c>
+      <c r="BC8">
+        <v>42</v>
+      </c>
+      <c r="BD8">
+        <v>70</v>
+      </c>
+      <c r="BE8">
+        <v>110</v>
+      </c>
+      <c r="BF8">
         <v>55</v>
       </c>
-      <c r="AS8">
-        <v>95</v>
-      </c>
-      <c r="AT8">
-        <v>7.2</v>
-      </c>
-      <c r="AU8">
-        <v>9</v>
-      </c>
-      <c r="AV8">
-        <v>25</v>
-      </c>
-      <c r="AW8">
-        <v>40</v>
-      </c>
-      <c r="AX8">
-        <v>7.6</v>
-      </c>
-      <c r="AY8">
-        <v>9.4</v>
-      </c>
-      <c r="AZ8">
-        <v>24</v>
-      </c>
-      <c r="BA8">
-        <v>42</v>
-      </c>
-      <c r="BB8">
-        <v>12.5</v>
-      </c>
-      <c r="BC8">
-        <v>16</v>
-      </c>
-      <c r="BD8">
-        <v>38</v>
-      </c>
-      <c r="BE8">
-        <v>70</v>
-      </c>
-      <c r="BF8">
-        <v>8.4</v>
-      </c>
       <c r="BG8">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH8">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="BI8">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="BJ8">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>19.5</v>
+        <v>2.16</v>
       </c>
       <c r="BN8">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="BO8">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="BP8">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>2.1</v>
       </c>
       <c r="BT8">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BU8">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>17</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F9">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="H9">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M9">
         <v>1.07</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="P9">
+        <v>1.92</v>
+      </c>
+      <c r="Q9">
         <v>2.06</v>
       </c>
-      <c r="Q9">
-        <v>1.91</v>
-      </c>
       <c r="R9">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
+        <v>3.8</v>
+      </c>
+      <c r="T9">
+        <v>2.16</v>
+      </c>
+      <c r="U9">
+        <v>1.82</v>
+      </c>
+      <c r="V9">
+        <v>1.14</v>
+      </c>
+      <c r="W9">
+        <v>2.78</v>
+      </c>
+      <c r="X9">
+        <v>13.5</v>
+      </c>
+      <c r="Y9">
+        <v>22</v>
+      </c>
+      <c r="Z9">
+        <v>65</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>7.2</v>
+      </c>
+      <c r="AC9">
+        <v>9.6</v>
+      </c>
+      <c r="AD9">
+        <v>28</v>
+      </c>
+      <c r="AE9">
+        <v>140</v>
+      </c>
+      <c r="AF9">
+        <v>8.4</v>
+      </c>
+      <c r="AG9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH9">
+        <v>27</v>
+      </c>
+      <c r="AI9">
+        <v>130</v>
+      </c>
+      <c r="AJ9">
+        <v>13.5</v>
+      </c>
+      <c r="AK9">
+        <v>17.5</v>
+      </c>
+      <c r="AL9">
+        <v>44</v>
+      </c>
+      <c r="AM9">
+        <v>180</v>
+      </c>
+      <c r="AN9">
+        <v>9.6</v>
+      </c>
+      <c r="AO9">
+        <v>220</v>
+      </c>
+      <c r="AP9">
+        <v>12.5</v>
+      </c>
+      <c r="AQ9">
+        <v>19.5</v>
+      </c>
+      <c r="AR9">
+        <v>55</v>
+      </c>
+      <c r="AS9">
+        <v>95</v>
+      </c>
+      <c r="AT9">
+        <v>6.6</v>
+      </c>
+      <c r="AU9">
+        <v>9</v>
+      </c>
+      <c r="AV9">
+        <v>26</v>
+      </c>
+      <c r="AW9">
+        <v>40</v>
+      </c>
+      <c r="AX9">
+        <v>8</v>
+      </c>
+      <c r="AY9">
+        <v>9.4</v>
+      </c>
+      <c r="AZ9">
+        <v>24</v>
+      </c>
+      <c r="BA9">
+        <v>95</v>
+      </c>
+      <c r="BB9">
+        <v>13</v>
+      </c>
+      <c r="BC9">
+        <v>16</v>
+      </c>
+      <c r="BD9">
+        <v>38</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG9">
+        <v>46</v>
+      </c>
+      <c r="BH9">
         <v>3.3</v>
       </c>
-      <c r="T9">
-        <v>1.85</v>
-      </c>
-      <c r="U9">
-        <v>2.14</v>
-      </c>
-      <c r="V9">
-        <v>1.21</v>
-      </c>
-      <c r="W9">
-        <v>2.26</v>
-      </c>
-      <c r="X9">
-        <v>15.5</v>
-      </c>
-      <c r="Y9">
-        <v>19</v>
-      </c>
-      <c r="Z9">
-        <v>42</v>
-      </c>
-      <c r="AA9">
-        <v>690</v>
-      </c>
-      <c r="AB9">
-        <v>9</v>
-      </c>
-      <c r="AC9">
-        <v>8.4</v>
-      </c>
-      <c r="AD9">
-        <v>21</v>
-      </c>
-      <c r="AE9">
-        <v>70</v>
-      </c>
-      <c r="AF9">
-        <v>10.5</v>
-      </c>
-      <c r="AG9">
+      <c r="BI9">
+        <v>3.05</v>
+      </c>
+      <c r="BJ9">
+        <v>11.5</v>
+      </c>
+      <c r="BK9">
         <v>10</v>
-      </c>
-      <c r="AH9">
-        <v>19</v>
-      </c>
-      <c r="AI9">
-        <v>75</v>
-      </c>
-      <c r="AJ9">
-        <v>18.5</v>
-      </c>
-      <c r="AK9">
-        <v>18</v>
-      </c>
-      <c r="AL9">
-        <v>36</v>
-      </c>
-      <c r="AM9">
-        <v>110</v>
-      </c>
-      <c r="AN9">
-        <v>11</v>
-      </c>
-      <c r="AO9">
-        <v>80</v>
-      </c>
-      <c r="AP9">
-        <v>14.5</v>
-      </c>
-      <c r="AQ9">
-        <v>18</v>
-      </c>
-      <c r="AR9">
-        <v>38</v>
-      </c>
-      <c r="AS9">
-        <v>42</v>
-      </c>
-      <c r="AT9">
-        <v>8.6</v>
-      </c>
-      <c r="AU9">
-        <v>7.8</v>
-      </c>
-      <c r="AV9">
-        <v>19</v>
-      </c>
-      <c r="AW9">
-        <v>55</v>
-      </c>
-      <c r="AX9">
-        <v>10</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
-        <v>17.5</v>
-      </c>
-      <c r="BA9">
-        <v>55</v>
-      </c>
-      <c r="BB9">
-        <v>17</v>
-      </c>
-      <c r="BC9">
-        <v>16.5</v>
-      </c>
-      <c r="BD9">
-        <v>32</v>
-      </c>
-      <c r="BE9">
-        <v>38</v>
-      </c>
-      <c r="BF9">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG9">
-        <v>60</v>
-      </c>
-      <c r="BH9">
-        <v>3.5</v>
-      </c>
-      <c r="BI9">
-        <v>3.2</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
-      <c r="BK9">
-        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BN9">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BO9">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS9">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BT9">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BU9">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BW9">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY9">
-        <v>5.1</v>
+        <v>19</v>
       </c>
       <c r="BZ9">
         <v>21</v>
       </c>
       <c r="CA9">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2867,429 +2879,429 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F10">
+        <v>1.82</v>
+      </c>
+      <c r="G10">
+        <v>1.83</v>
+      </c>
+      <c r="H10">
+        <v>5.2</v>
+      </c>
+      <c r="I10">
+        <v>5.3</v>
+      </c>
+      <c r="J10">
+        <v>3.8</v>
+      </c>
+      <c r="K10">
+        <v>3.9</v>
+      </c>
+      <c r="L10">
+        <v>1.39</v>
+      </c>
+      <c r="M10">
+        <v>1.07</v>
+      </c>
+      <c r="N10">
+        <v>4.2</v>
+      </c>
+      <c r="O10">
+        <v>1.3</v>
+      </c>
+      <c r="P10">
+        <v>2.08</v>
+      </c>
+      <c r="Q10">
+        <v>1.9</v>
+      </c>
+      <c r="R10">
+        <v>1.42</v>
+      </c>
+      <c r="S10">
+        <v>3.3</v>
+      </c>
+      <c r="T10">
+        <v>1.85</v>
+      </c>
+      <c r="U10">
         <v>2.14</v>
       </c>
-      <c r="G10">
+      <c r="V10">
+        <v>1.23</v>
+      </c>
+      <c r="W10">
         <v>2.2</v>
       </c>
-      <c r="H10">
-        <v>4.1</v>
-      </c>
-      <c r="I10">
-        <v>4.3</v>
-      </c>
-      <c r="J10">
-        <v>3.25</v>
-      </c>
-      <c r="K10">
+      <c r="X10">
+        <v>15</v>
+      </c>
+      <c r="Y10">
+        <v>19</v>
+      </c>
+      <c r="Z10">
+        <v>40</v>
+      </c>
+      <c r="AA10">
+        <v>120</v>
+      </c>
+      <c r="AB10">
+        <v>9.4</v>
+      </c>
+      <c r="AC10">
+        <v>8.4</v>
+      </c>
+      <c r="AD10">
+        <v>19.5</v>
+      </c>
+      <c r="AE10">
+        <v>65</v>
+      </c>
+      <c r="AF10">
+        <v>11.5</v>
+      </c>
+      <c r="AG10">
+        <v>9.6</v>
+      </c>
+      <c r="AH10">
+        <v>18.5</v>
+      </c>
+      <c r="AI10">
+        <v>65</v>
+      </c>
+      <c r="AJ10">
+        <v>19.5</v>
+      </c>
+      <c r="AK10">
+        <v>18.5</v>
+      </c>
+      <c r="AL10">
+        <v>34</v>
+      </c>
+      <c r="AM10">
+        <v>95</v>
+      </c>
+      <c r="AN10">
+        <v>11</v>
+      </c>
+      <c r="AO10">
+        <v>70</v>
+      </c>
+      <c r="AP10">
+        <v>14</v>
+      </c>
+      <c r="AQ10">
+        <v>17.5</v>
+      </c>
+      <c r="AR10">
+        <v>34</v>
+      </c>
+      <c r="AS10">
+        <v>100</v>
+      </c>
+      <c r="AT10">
+        <v>8.6</v>
+      </c>
+      <c r="AU10">
+        <v>8</v>
+      </c>
+      <c r="AV10">
+        <v>18</v>
+      </c>
+      <c r="AW10">
+        <v>55</v>
+      </c>
+      <c r="AX10">
+        <v>10.5</v>
+      </c>
+      <c r="AY10">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10">
+        <v>16.5</v>
+      </c>
+      <c r="BA10">
+        <v>60</v>
+      </c>
+      <c r="BB10">
+        <v>17</v>
+      </c>
+      <c r="BC10">
+        <v>17</v>
+      </c>
+      <c r="BD10">
+        <v>30</v>
+      </c>
+      <c r="BE10">
+        <v>80</v>
+      </c>
+      <c r="BF10">
+        <v>10</v>
+      </c>
+      <c r="BG10">
+        <v>60</v>
+      </c>
+      <c r="BH10">
+        <v>3.65</v>
+      </c>
+      <c r="BI10">
         <v>3.3</v>
       </c>
-      <c r="L10">
-        <v>1.54</v>
-      </c>
-      <c r="M10">
-        <v>1.11</v>
-      </c>
-      <c r="N10">
-        <v>2.88</v>
-      </c>
-      <c r="O10">
-        <v>1.49</v>
-      </c>
-      <c r="P10">
-        <v>1.61</v>
-      </c>
-      <c r="Q10">
-        <v>2.52</v>
-      </c>
-      <c r="R10">
-        <v>1.22</v>
-      </c>
-      <c r="S10">
-        <v>5.1</v>
-      </c>
-      <c r="T10">
-        <v>2.06</v>
-      </c>
-      <c r="U10">
-        <v>1.83</v>
-      </c>
-      <c r="V10">
-        <v>1.3</v>
-      </c>
-      <c r="W10">
-        <v>1.83</v>
-      </c>
-      <c r="X10">
+      <c r="BJ10">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y10">
+      <c r="BK10">
+        <v>8.6</v>
+      </c>
+      <c r="BL10">
+        <v>120</v>
+      </c>
+      <c r="BM10">
+        <v>13</v>
+      </c>
+      <c r="BN10">
+        <v>4.6</v>
+      </c>
+      <c r="BO10">
+        <v>4</v>
+      </c>
+      <c r="BP10">
         <v>12.5</v>
       </c>
-      <c r="Z10">
-        <v>32</v>
-      </c>
-      <c r="AA10">
-        <v>900</v>
-      </c>
-      <c r="AB10">
-        <v>7.6</v>
-      </c>
-      <c r="AC10">
-        <v>7.8</v>
-      </c>
-      <c r="AD10">
-        <v>18.5</v>
-      </c>
-      <c r="AE10">
-        <v>75</v>
-      </c>
-      <c r="AF10">
-        <v>12.5</v>
-      </c>
-      <c r="AG10">
-        <v>11.5</v>
-      </c>
-      <c r="AH10">
-        <v>23</v>
-      </c>
-      <c r="AI10">
-        <v>90</v>
-      </c>
-      <c r="AJ10">
-        <v>29</v>
-      </c>
-      <c r="AK10">
+      <c r="BQ10">
+        <v>10.5</v>
+      </c>
+      <c r="BR10">
+        <v>26</v>
+      </c>
+      <c r="BS10">
+        <v>17</v>
+      </c>
+      <c r="BT10">
+        <v>8.4</v>
+      </c>
+      <c r="BU10">
+        <v>7.2</v>
+      </c>
+      <c r="BV10">
+        <v>40</v>
+      </c>
+      <c r="BW10">
+        <v>25</v>
+      </c>
+      <c r="BX10">
+        <v>46</v>
+      </c>
+      <c r="BY10">
         <v>30</v>
       </c>
-      <c r="AL10">
-        <v>55</v>
-      </c>
-      <c r="AM10">
-        <v>580</v>
-      </c>
-      <c r="AN10">
-        <v>27</v>
-      </c>
-      <c r="AO10">
-        <v>600</v>
-      </c>
-      <c r="AP10">
-        <v>8.6</v>
-      </c>
-      <c r="AQ10">
-        <v>10.5</v>
-      </c>
-      <c r="AR10">
-        <v>23</v>
-      </c>
-      <c r="AS10">
-        <v>10</v>
-      </c>
-      <c r="AT10">
-        <v>6.4</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
-      <c r="AV10">
-        <v>16</v>
-      </c>
-      <c r="AW10">
-        <v>44</v>
-      </c>
-      <c r="AX10">
-        <v>10</v>
-      </c>
-      <c r="AY10">
-        <v>10</v>
-      </c>
-      <c r="AZ10">
-        <v>19.5</v>
-      </c>
-      <c r="BA10">
-        <v>38</v>
-      </c>
-      <c r="BB10">
+      <c r="BZ10">
         <v>21</v>
       </c>
-      <c r="BC10">
-        <v>21</v>
-      </c>
-      <c r="BD10">
-        <v>36</v>
-      </c>
-      <c r="BE10">
-        <v>10.5</v>
-      </c>
-      <c r="BF10">
-        <v>21</v>
-      </c>
-      <c r="BG10">
-        <v>14</v>
-      </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
-        <v>1.04</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
-        <v>1.04</v>
-      </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
-        <v>1.04</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
-        <v>1.04</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>1.04</v>
-      </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
-        <v>1.04</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>1.04</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>1.04</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>15.5</v>
       </c>
       <c r="CB10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>2.16</v>
+      </c>
+      <c r="G11">
+        <v>2.22</v>
+      </c>
+      <c r="H11">
+        <v>4.1</v>
+      </c>
+      <c r="I11">
+        <v>4.3</v>
+      </c>
+      <c r="J11">
+        <v>3.2</v>
+      </c>
+      <c r="K11">
+        <v>3.35</v>
+      </c>
+      <c r="L11">
+        <v>1.55</v>
+      </c>
+      <c r="M11">
+        <v>1.12</v>
+      </c>
+      <c r="N11">
+        <v>2.88</v>
+      </c>
+      <c r="O11">
+        <v>1.51</v>
+      </c>
+      <c r="P11">
+        <v>1.6</v>
+      </c>
+      <c r="Q11">
+        <v>2.56</v>
+      </c>
+      <c r="R11">
+        <v>1.22</v>
+      </c>
+      <c r="S11">
+        <v>5.2</v>
+      </c>
+      <c r="T11">
+        <v>2.1</v>
+      </c>
+      <c r="U11">
+        <v>1.83</v>
+      </c>
+      <c r="V11">
+        <v>1.3</v>
+      </c>
+      <c r="W11">
+        <v>1.81</v>
+      </c>
+      <c r="X11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y11">
+        <v>12.5</v>
+      </c>
+      <c r="Z11">
+        <v>32</v>
+      </c>
+      <c r="AA11">
+        <v>900</v>
+      </c>
+      <c r="AB11">
+        <v>7.6</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>18.5</v>
+      </c>
+      <c r="AE11">
+        <v>75</v>
+      </c>
+      <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
+        <v>11.5</v>
+      </c>
+      <c r="AH11">
+        <v>23</v>
+      </c>
+      <c r="AI11">
         <v>90</v>
       </c>
-      <c r="D11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F11">
-        <v>2.12</v>
-      </c>
-      <c r="G11">
-        <v>2.18</v>
-      </c>
-      <c r="H11">
-        <v>4.3</v>
-      </c>
-      <c r="I11">
-        <v>4.6</v>
-      </c>
-      <c r="J11">
-        <v>3.25</v>
-      </c>
-      <c r="K11">
-        <v>3.3</v>
-      </c>
-      <c r="L11">
-        <v>1.58</v>
-      </c>
-      <c r="M11">
-        <v>1.13</v>
-      </c>
-      <c r="N11">
-        <v>2.72</v>
-      </c>
-      <c r="O11">
-        <v>1.54</v>
-      </c>
-      <c r="P11">
-        <v>1.54</v>
-      </c>
-      <c r="Q11">
-        <v>2.72</v>
-      </c>
-      <c r="R11">
-        <v>1.19</v>
-      </c>
-      <c r="S11">
-        <v>5.6</v>
-      </c>
-      <c r="T11">
-        <v>2.14</v>
-      </c>
-      <c r="U11">
-        <v>1.78</v>
-      </c>
-      <c r="V11">
-        <v>1.28</v>
-      </c>
-      <c r="W11">
-        <v>1.85</v>
-      </c>
-      <c r="X11">
+      <c r="AJ11">
+        <v>29</v>
+      </c>
+      <c r="AK11">
+        <v>30</v>
+      </c>
+      <c r="AL11">
+        <v>55</v>
+      </c>
+      <c r="AM11">
+        <v>580</v>
+      </c>
+      <c r="AN11">
+        <v>27</v>
+      </c>
+      <c r="AO11">
+        <v>600</v>
+      </c>
+      <c r="AP11">
+        <v>8.4</v>
+      </c>
+      <c r="AQ11">
+        <v>10.5</v>
+      </c>
+      <c r="AR11">
+        <v>22</v>
+      </c>
+      <c r="AS11">
         <v>10</v>
       </c>
-      <c r="Y11">
-        <v>13.5</v>
-      </c>
-      <c r="Z11">
-        <v>38</v>
-      </c>
-      <c r="AA11">
-        <v>140</v>
-      </c>
-      <c r="AB11">
-        <v>7</v>
-      </c>
-      <c r="AC11">
-        <v>8.4</v>
-      </c>
-      <c r="AD11">
-        <v>23</v>
-      </c>
-      <c r="AE11">
-        <v>85</v>
-      </c>
-      <c r="AF11">
-        <v>13.5</v>
-      </c>
-      <c r="AG11">
-        <v>13</v>
-      </c>
-      <c r="AH11">
-        <v>26</v>
-      </c>
-      <c r="AI11">
-        <v>120</v>
-      </c>
-      <c r="AJ11">
-        <v>34</v>
-      </c>
-      <c r="AK11">
-        <v>34</v>
-      </c>
-      <c r="AL11">
-        <v>70</v>
-      </c>
-      <c r="AM11">
-        <v>230</v>
-      </c>
-      <c r="AN11">
-        <v>29</v>
-      </c>
-      <c r="AO11">
-        <v>140</v>
-      </c>
-      <c r="AP11">
-        <v>6.8</v>
-      </c>
-      <c r="AQ11">
-        <v>10</v>
-      </c>
-      <c r="AR11">
-        <v>5.4</v>
-      </c>
-      <c r="AS11">
-        <v>6</v>
-      </c>
       <c r="AT11">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
         <v>16</v>
       </c>
       <c r="AW11">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="AX11">
         <v>10</v>
       </c>
       <c r="AY11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA11">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BB11">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="BC11">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="BD11">
-        <v>5.7</v>
+        <v>38</v>
       </c>
       <c r="BE11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BF11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG11">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BH11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BI11">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
         <v>6</v>
@@ -3304,46 +3316,288 @@
         <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP11">
         <v>18</v>
       </c>
       <c r="BQ11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV11">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA11">
         <v>9.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12">
+        <v>2.1</v>
+      </c>
+      <c r="G12">
+        <v>2.16</v>
+      </c>
+      <c r="H12">
+        <v>4.4</v>
+      </c>
+      <c r="I12">
+        <v>4.7</v>
+      </c>
+      <c r="J12">
+        <v>3.15</v>
+      </c>
+      <c r="K12">
+        <v>3.2</v>
+      </c>
+      <c r="L12">
+        <v>1.58</v>
+      </c>
+      <c r="M12">
+        <v>1.13</v>
+      </c>
+      <c r="N12">
+        <v>2.68</v>
+      </c>
+      <c r="O12">
+        <v>1.55</v>
+      </c>
+      <c r="P12">
+        <v>1.54</v>
+      </c>
+      <c r="Q12">
+        <v>2.74</v>
+      </c>
+      <c r="R12">
+        <v>1.2</v>
+      </c>
+      <c r="S12">
+        <v>5.8</v>
+      </c>
+      <c r="T12">
+        <v>2.16</v>
+      </c>
+      <c r="U12">
+        <v>1.78</v>
+      </c>
+      <c r="V12">
+        <v>1.27</v>
+      </c>
+      <c r="W12">
+        <v>1.86</v>
+      </c>
+      <c r="X12">
+        <v>9</v>
+      </c>
+      <c r="Y12">
+        <v>13.5</v>
+      </c>
+      <c r="Z12">
+        <v>38</v>
+      </c>
+      <c r="AA12">
+        <v>140</v>
+      </c>
+      <c r="AB12">
+        <v>7</v>
+      </c>
+      <c r="AC12">
+        <v>7.6</v>
+      </c>
+      <c r="AD12">
+        <v>23</v>
+      </c>
+      <c r="AE12">
+        <v>95</v>
+      </c>
+      <c r="AF12">
+        <v>12.5</v>
+      </c>
+      <c r="AG12">
+        <v>13.5</v>
+      </c>
+      <c r="AH12">
+        <v>26</v>
+      </c>
+      <c r="AI12">
+        <v>120</v>
+      </c>
+      <c r="AJ12">
+        <v>34</v>
+      </c>
+      <c r="AK12">
+        <v>34</v>
+      </c>
+      <c r="AL12">
+        <v>65</v>
+      </c>
+      <c r="AM12">
+        <v>230</v>
+      </c>
+      <c r="AN12">
+        <v>34</v>
+      </c>
+      <c r="AO12">
+        <v>190</v>
+      </c>
+      <c r="AP12">
+        <v>7.6</v>
+      </c>
+      <c r="AQ12">
+        <v>10</v>
+      </c>
+      <c r="AR12">
+        <v>23</v>
+      </c>
+      <c r="AS12">
+        <v>7</v>
+      </c>
+      <c r="AT12">
+        <v>5.9</v>
+      </c>
+      <c r="AU12">
+        <v>6.4</v>
+      </c>
+      <c r="AV12">
+        <v>17</v>
+      </c>
+      <c r="AW12">
+        <v>6.6</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>10</v>
+      </c>
+      <c r="AZ12">
+        <v>21</v>
+      </c>
+      <c r="BA12">
+        <v>7.2</v>
+      </c>
+      <c r="BB12">
+        <v>21</v>
+      </c>
+      <c r="BC12">
+        <v>22</v>
+      </c>
+      <c r="BD12">
+        <v>6.8</v>
+      </c>
+      <c r="BE12">
+        <v>7</v>
+      </c>
+      <c r="BF12">
+        <v>23</v>
+      </c>
+      <c r="BG12">
+        <v>7</v>
+      </c>
+      <c r="BH12">
+        <v>2.76</v>
+      </c>
+      <c r="BI12">
+        <v>2.32</v>
+      </c>
+      <c r="BJ12">
+        <v>12</v>
+      </c>
+      <c r="BK12">
+        <v>6.2</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>12</v>
+      </c>
+      <c r="BN12">
+        <v>4.8</v>
+      </c>
+      <c r="BO12">
+        <v>3.75</v>
+      </c>
+      <c r="BP12">
+        <v>18</v>
+      </c>
+      <c r="BQ12">
+        <v>7.4</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT12">
+        <v>7.8</v>
+      </c>
+      <c r="BU12">
+        <v>6</v>
+      </c>
+      <c r="BV12">
+        <v>48</v>
+      </c>
+      <c r="BW12">
+        <v>10</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>10.5</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
+        <v>10</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -361,7 +361,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 10:16:15</t>
+    <t>2026-07-23 12:27:09</t>
   </si>
 </sst>
 </file>
@@ -955,19 +955,19 @@
         <v>104</v>
       </c>
       <c r="F2">
+        <v>4.2</v>
+      </c>
+      <c r="G2">
         <v>4.5</v>
       </c>
-      <c r="G2">
-        <v>4.6</v>
-      </c>
       <c r="H2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2">
         <v>4.7</v>
@@ -979,46 +979,46 @@
         <v>1.03</v>
       </c>
       <c r="N2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P2">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="Q2">
         <v>1.5</v>
       </c>
       <c r="R2">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="T2">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="U2">
         <v>2.62</v>
       </c>
       <c r="V2">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="W2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X2">
         <v>32</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AB2">
         <v>26</v>
@@ -1036,16 +1036,16 @@
         <v>130</v>
       </c>
       <c r="AG2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI2">
         <v>26</v>
       </c>
       <c r="AJ2">
-        <v>700</v>
+        <v>170</v>
       </c>
       <c r="AK2">
         <v>55</v>
@@ -1054,10 +1054,10 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO2">
         <v>7.4</v>
@@ -1069,7 +1069,7 @@
         <v>11.5</v>
       </c>
       <c r="AR2">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AS2">
         <v>17</v>
@@ -1090,28 +1090,28 @@
         <v>19.5</v>
       </c>
       <c r="AY2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BC2">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BD2">
         <v>22</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG2">
         <v>6.2</v>
@@ -1120,43 +1120,43 @@
         <v>4.9</v>
       </c>
       <c r="BI2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BJ2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM2">
+        <v>10</v>
+      </c>
+      <c r="BN2">
+        <v>8.4</v>
+      </c>
+      <c r="BO2">
+        <v>4.9</v>
+      </c>
+      <c r="BP2">
+        <v>29</v>
+      </c>
+      <c r="BQ2">
+        <v>8.4</v>
+      </c>
+      <c r="BR2">
+        <v>32</v>
+      </c>
+      <c r="BS2">
         <v>8.6</v>
       </c>
-      <c r="BN2">
-        <v>8.6</v>
-      </c>
-      <c r="BO2">
+      <c r="BT2">
+        <v>5.2</v>
+      </c>
+      <c r="BU2">
         <v>4.5</v>
-      </c>
-      <c r="BP2">
-        <v>30</v>
-      </c>
-      <c r="BQ2">
-        <v>7.4</v>
-      </c>
-      <c r="BR2">
-        <v>34</v>
-      </c>
-      <c r="BS2">
-        <v>7.6</v>
-      </c>
-      <c r="BT2">
-        <v>5.3</v>
-      </c>
-      <c r="BU2">
-        <v>4.4</v>
       </c>
       <c r="BV2">
         <v>12</v>
@@ -1165,13 +1165,13 @@
         <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="CA2">
         <v>8.4</v>
@@ -1197,19 +1197,19 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G3">
         <v>3.25</v>
       </c>
       <c r="H3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
         <v>5.1</v>
@@ -1227,22 +1227,22 @@
         <v>1.08</v>
       </c>
       <c r="P3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="R3">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="T3">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
         <v>1.83</v>
@@ -1251,10 +1251,10 @@
         <v>1.45</v>
       </c>
       <c r="X3">
-        <v>170</v>
+        <v>950</v>
       </c>
       <c r="Y3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z3">
         <v>28</v>
@@ -1266,7 +1266,7 @@
         <v>38</v>
       </c>
       <c r="AC3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AD3">
         <v>14.5</v>
@@ -1278,7 +1278,7 @@
         <v>40</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3">
         <v>14.5</v>
@@ -1299,70 +1299,70 @@
         <v>32</v>
       </c>
       <c r="AN3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO3">
         <v>5.9</v>
       </c>
       <c r="AP3">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="AT3">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AU3">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>6</v>
       </c>
       <c r="AX3">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="AY3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="BA3">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="BB3">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>6.6</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>8.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BG3">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="BH3">
         <v>7</v>
       </c>
       <c r="BI3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BJ3">
         <v>8</v>
@@ -1374,7 +1374,7 @@
         <v>40</v>
       </c>
       <c r="BM3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
         <v>8.199999999999999</v>
@@ -1392,7 +1392,7 @@
         <v>19.5</v>
       </c>
       <c r="BS3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT3">
         <v>6.8</v>
@@ -1404,10 +1404,10 @@
         <v>13.5</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BY3">
         <v>7.2</v>
@@ -1439,100 +1439,100 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H4">
         <v>3.4</v>
       </c>
       <c r="I4">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J4">
         <v>2.96</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="R4">
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
         <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG4">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>160</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL4">
         <v>110</v>
@@ -1541,25 +1541,25 @@
         <v>230</v>
       </c>
       <c r="AN4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
         <v>8.199999999999999</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>13.5</v>
       </c>
       <c r="AW4">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AX4">
         <v>12</v>
@@ -1577,46 +1577,46 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>7.4</v>
+        <v>50</v>
       </c>
       <c r="BB4">
-        <v>12.5</v>
+        <v>27</v>
       </c>
       <c r="BC4">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BH4">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BI4">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4">
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>5.4</v>
@@ -1625,19 +1625,19 @@
         <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU4">
         <v>5.1</v>
@@ -1646,13 +1646,13 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,10 +1681,10 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G5">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H5">
         <v>3.1</v>
@@ -1693,31 +1693,31 @@
         <v>3.25</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>1.44</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
         <v>4.3</v>
@@ -1726,7 +1726,7 @@
         <v>1.92</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1744,34 +1744,34 @@
         <v>24</v>
       </c>
       <c r="AA5">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="AB5">
         <v>9</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>15</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>18</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AJ5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK5">
         <v>38</v>
@@ -1783,7 +1783,7 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO5">
         <v>500</v>
@@ -1792,7 +1792,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR5">
         <v>18</v>
@@ -1813,7 +1813,7 @@
         <v>27</v>
       </c>
       <c r="AX5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY5">
         <v>11</v>
@@ -1828,7 +1828,7 @@
         <v>27</v>
       </c>
       <c r="BC5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD5">
         <v>40</v>
@@ -1837,10 +1837,10 @@
         <v>29</v>
       </c>
       <c r="BF5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BG5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BH5">
         <v>3.1</v>
@@ -1923,70 +1923,70 @@
         <v>108</v>
       </c>
       <c r="F6">
+        <v>1.81</v>
+      </c>
+      <c r="G6">
         <v>1.83</v>
       </c>
-      <c r="G6">
-        <v>1.87</v>
-      </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q6">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
+        <v>2.18</v>
+      </c>
+      <c r="U6">
+        <v>1.73</v>
+      </c>
+      <c r="V6">
+        <v>1.2</v>
+      </c>
+      <c r="W6">
         <v>2.2</v>
       </c>
-      <c r="U6">
-        <v>1.71</v>
-      </c>
-      <c r="V6">
-        <v>1.21</v>
-      </c>
-      <c r="W6">
-        <v>2.14</v>
-      </c>
       <c r="X6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA6">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB6">
         <v>6.6</v>
@@ -1995,13 +1995,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE6">
         <v>110</v>
       </c>
       <c r="AF6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6">
         <v>11</v>
@@ -2010,28 +2010,28 @@
         <v>28</v>
       </c>
       <c r="AI6">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
         <v>21</v>
       </c>
       <c r="AK6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6">
         <v>500</v>
       </c>
       <c r="AN6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO6">
         <v>180</v>
       </c>
       <c r="AP6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6">
         <v>12.5</v>
@@ -2043,7 +2043,7 @@
         <v>110</v>
       </c>
       <c r="AT6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU6">
         <v>7.4</v>
@@ -2055,40 +2055,40 @@
         <v>60</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA6">
         <v>60</v>
       </c>
       <c r="BB6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC6">
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="BF6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BG6">
         <v>17</v>
       </c>
       <c r="BH6">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2103,46 +2103,46 @@
         <v>12</v>
       </c>
       <c r="BN6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BQ6">
         <v>6.8</v>
       </c>
       <c r="BR6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS6">
         <v>9.6</v>
       </c>
       <c r="BT6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU6">
         <v>5.5</v>
       </c>
       <c r="BV6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY6">
         <v>11</v>
       </c>
       <c r="BZ6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2165,16 +2165,16 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G7">
         <v>5</v>
       </c>
       <c r="H7">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -2183,7 +2183,7 @@
         <v>3.1</v>
       </c>
       <c r="L7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M7">
         <v>1.17</v>
@@ -2207,37 +2207,37 @@
         <v>7.4</v>
       </c>
       <c r="T7">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
         <v>1.61</v>
       </c>
       <c r="V7">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z7">
         <v>11</v>
       </c>
       <c r="AA7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB7">
         <v>11</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
         <v>36</v>
@@ -2252,7 +2252,7 @@
         <v>34</v>
       </c>
       <c r="AI7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ7">
         <v>150</v>
@@ -2288,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
         <v>11.5</v>
@@ -2306,7 +2306,7 @@
         <v>28</v>
       </c>
       <c r="BA7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB7">
         <v>42</v>
@@ -2315,7 +2315,7 @@
         <v>75</v>
       </c>
       <c r="BD7">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="BE7">
         <v>110</v>
@@ -2327,25 +2327,25 @@
         <v>30</v>
       </c>
       <c r="BH7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7">
         <v>13</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BO7">
         <v>5.7</v>
@@ -2354,13 +2354,13 @@
         <v>60</v>
       </c>
       <c r="BQ7">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BR7">
         <v>90</v>
       </c>
       <c r="BS7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
@@ -2369,22 +2369,22 @@
         <v>4</v>
       </c>
       <c r="BV7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BW7">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX7">
         <v>50</v>
       </c>
       <c r="BY7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
         <v>60</v>
       </c>
       <c r="CA7">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2407,142 +2407,142 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="G8">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="H8">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I8">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K8">
         <v>2.9</v>
       </c>
       <c r="L8">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M8">
         <v>1.17</v>
       </c>
       <c r="N8">
+        <v>2.42</v>
+      </c>
+      <c r="O8">
+        <v>1.69</v>
+      </c>
+      <c r="P8">
+        <v>1.45</v>
+      </c>
+      <c r="Q8">
+        <v>3.15</v>
+      </c>
+      <c r="R8">
+        <v>1.15</v>
+      </c>
+      <c r="S8">
+        <v>6.8</v>
+      </c>
+      <c r="T8">
         <v>2.34</v>
       </c>
-      <c r="O8">
+      <c r="U8">
         <v>1.71</v>
       </c>
-      <c r="P8">
-        <v>1.43</v>
-      </c>
-      <c r="Q8">
-        <v>3.25</v>
-      </c>
-      <c r="R8">
-        <v>1.14</v>
-      </c>
-      <c r="S8">
-        <v>7.4</v>
-      </c>
-      <c r="T8">
-        <v>2.42</v>
-      </c>
-      <c r="U8">
-        <v>1.67</v>
-      </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
+        <v>7</v>
+      </c>
+      <c r="Y8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z8">
+        <v>23</v>
+      </c>
+      <c r="AA8">
+        <v>100</v>
+      </c>
+      <c r="AB8">
+        <v>7</v>
+      </c>
+      <c r="AC8">
         <v>6.8</v>
-      </c>
-      <c r="Y8">
-        <v>8.4</v>
-      </c>
-      <c r="Z8">
-        <v>20</v>
-      </c>
-      <c r="AA8">
-        <v>150</v>
-      </c>
-      <c r="AB8">
-        <v>7.4</v>
-      </c>
-      <c r="AC8">
-        <v>7</v>
       </c>
       <c r="AD8">
         <v>16.5</v>
       </c>
       <c r="AE8">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AF8">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AI8">
-        <v>220</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AK8">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AL8">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="AM8">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AN8">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AO8">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS8">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AT8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW8">
         <v>50</v>
       </c>
       <c r="AX8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8">
         <v>25</v>
@@ -2551,19 +2551,19 @@
         <v>46</v>
       </c>
       <c r="BB8">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BC8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BD8">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="BE8">
         <v>110</v>
       </c>
       <c r="BF8">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="BG8">
         <v>55</v>
@@ -2572,49 +2572,49 @@
         <v>2.46</v>
       </c>
       <c r="BI8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BJ8">
         <v>12</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BN8">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BP8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BQ8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BT8">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
         <v>5.3</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
@@ -2649,13 +2649,13 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G9">
         <v>1.56</v>
       </c>
       <c r="H9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>8.199999999999999</v>
@@ -2679,58 +2679,58 @@
         <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q9">
         <v>2.06</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U9">
         <v>1.82</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y9">
         <v>22</v>
       </c>
       <c r="Z9">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA9">
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE9">
         <v>140</v>
       </c>
       <c r="AF9">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH9">
         <v>27</v>
@@ -2751,16 +2751,16 @@
         <v>180</v>
       </c>
       <c r="AN9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO9">
         <v>220</v>
       </c>
       <c r="AP9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR9">
         <v>55</v>
@@ -2778,22 +2778,22 @@
         <v>26</v>
       </c>
       <c r="AW9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AX9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY9">
         <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA9">
         <v>95</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC9">
         <v>16</v>
@@ -2802,70 +2802,70 @@
         <v>38</v>
       </c>
       <c r="BE9">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BF9">
         <v>8.800000000000001</v>
       </c>
       <c r="BG9">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="BH9">
         <v>3.3</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9">
         <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BN9">
         <v>3.8</v>
       </c>
       <c r="BO9">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BP9">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
         <v>28</v>
       </c>
       <c r="BS9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT9">
         <v>11</v>
       </c>
       <c r="BU9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BV9">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BW9">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BX9">
         <v>80</v>
       </c>
       <c r="BY9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BZ9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA9">
         <v>11.5</v>
@@ -2894,7 +2894,7 @@
         <v>1.82</v>
       </c>
       <c r="G10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H10">
         <v>5.2</v>
@@ -2903,10 +2903,10 @@
         <v>5.3</v>
       </c>
       <c r="J10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10">
         <v>1.39</v>
@@ -2933,22 +2933,22 @@
         <v>3.3</v>
       </c>
       <c r="T10">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V10">
         <v>1.23</v>
       </c>
       <c r="W10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X10">
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10">
         <v>40</v>
@@ -2957,7 +2957,7 @@
         <v>120</v>
       </c>
       <c r="AB10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>8.4</v>
@@ -2972,19 +2972,19 @@
         <v>11.5</v>
       </c>
       <c r="AG10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI10">
         <v>65</v>
       </c>
       <c r="AJ10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10">
         <v>34</v>
@@ -2996,7 +2996,7 @@
         <v>11</v>
       </c>
       <c r="AO10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP10">
         <v>14</v>
@@ -3005,19 +3005,19 @@
         <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS10">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AT10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
         <v>8</v>
       </c>
       <c r="AV10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW10">
         <v>55</v>
@@ -3032,10 +3032,10 @@
         <v>16.5</v>
       </c>
       <c r="BA10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC10">
         <v>17</v>
@@ -3044,19 +3044,19 @@
         <v>30</v>
       </c>
       <c r="BE10">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="BF10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH10">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
@@ -3068,13 +3068,13 @@
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BN10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP10">
         <v>12.5</v>
@@ -3095,22 +3095,22 @@
         <v>7.2</v>
       </c>
       <c r="BV10">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW10">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="BX10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BY10">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10">
         <v>21</v>
       </c>
       <c r="CA10">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3133,10 +3133,10 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
         <v>4.1</v>
@@ -3148,61 +3148,61 @@
         <v>3.2</v>
       </c>
       <c r="K11">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M11">
         <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V11">
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA11">
         <v>900</v>
       </c>
       <c r="AB11">
+        <v>7.4</v>
+      </c>
+      <c r="AC11">
         <v>7.6</v>
-      </c>
-      <c r="AC11">
-        <v>7.8</v>
       </c>
       <c r="AD11">
         <v>18.5</v>
@@ -3229,16 +3229,16 @@
         <v>30</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM11">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO11">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AP11">
         <v>8.4</v>
@@ -3247,10 +3247,10 @@
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT11">
         <v>6.4</v>
@@ -3262,10 +3262,10 @@
         <v>16</v>
       </c>
       <c r="AW11">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY11">
         <v>10</v>
@@ -3277,16 +3277,16 @@
         <v>38</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC11">
         <v>22</v>
       </c>
       <c r="BD11">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF11">
         <v>24</v>
@@ -3295,7 +3295,7 @@
         <v>30</v>
       </c>
       <c r="BH11">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI11">
         <v>2.4</v>
@@ -3310,7 +3310,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
@@ -3322,13 +3322,13 @@
         <v>18</v>
       </c>
       <c r="BQ11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
@@ -3340,7 +3340,7 @@
         <v>44</v>
       </c>
       <c r="BW11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>65</v>
@@ -3352,7 +3352,7 @@
         <v>42</v>
       </c>
       <c r="CA11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>
@@ -3375,16 +3375,16 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G12">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J12">
         <v>3.15</v>
@@ -3402,16 +3402,16 @@
         <v>2.68</v>
       </c>
       <c r="O12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P12">
         <v>1.54</v>
       </c>
       <c r="Q12">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R12">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S12">
         <v>5.8</v>
@@ -3423,52 +3423,52 @@
         <v>1.78</v>
       </c>
       <c r="V12">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Y12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB12">
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD12">
         <v>23</v>
       </c>
       <c r="AE12">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AF12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ12">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL12">
         <v>65</v>
@@ -3477,64 +3477,64 @@
         <v>230</v>
       </c>
       <c r="AN12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO12">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="AP12">
         <v>7.6</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR12">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS12">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AT12">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV12">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW12">
-        <v>6.6</v>
+        <v>65</v>
       </c>
       <c r="AX12">
         <v>10</v>
       </c>
       <c r="AY12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA12">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BC12">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BD12">
-        <v>6.8</v>
+        <v>50</v>
       </c>
       <c r="BE12">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BF12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG12">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BH12">
         <v>2.76</v>
@@ -3546,7 +3546,7 @@
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3561,7 +3561,7 @@
         <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ12">
         <v>7.4</v>
@@ -3570,7 +3570,7 @@
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT12">
         <v>7.8</v>
@@ -3579,7 +3579,7 @@
         <v>6</v>
       </c>
       <c r="BV12">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
         <v>10</v>
@@ -3591,10 +3591,10 @@
         <v>10.5</v>
       </c>
       <c r="BZ12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB12" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -361,7 +361,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 12:27:09</t>
+    <t>2026-07-23 14:38:54</t>
   </si>
 </sst>
 </file>
@@ -955,19 +955,19 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="I2">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="J2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K2">
         <v>4.7</v>
@@ -976,97 +976,97 @@
         <v>1.26</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P2">
         <v>2.94</v>
       </c>
       <c r="Q2">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T2">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V2">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="W2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AC2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF2">
         <v>130</v>
       </c>
       <c r="AG2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AH2">
         <v>16.5</v>
       </c>
       <c r="AI2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ2">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AK2">
         <v>55</v>
       </c>
       <c r="AL2">
+        <v>65</v>
+      </c>
+      <c r="AM2">
         <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>65</v>
       </c>
       <c r="AN2">
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
         <v>12.5</v>
@@ -1087,10 +1087,10 @@
         <v>14</v>
       </c>
       <c r="AX2">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
@@ -1099,58 +1099,58 @@
         <v>20</v>
       </c>
       <c r="BB2">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BC2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD2">
+        <v>23</v>
+      </c>
+      <c r="BE2">
+        <v>12.5</v>
+      </c>
+      <c r="BF2">
         <v>22</v>
       </c>
-      <c r="BE2">
-        <v>8</v>
-      </c>
-      <c r="BF2">
-        <v>7.4</v>
-      </c>
       <c r="BG2">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH2">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BJ2">
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="BL2">
         <v>75</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="BN2">
         <v>8.4</v>
       </c>
       <c r="BO2">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="BP2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="BT2">
         <v>5.2</v>
@@ -1159,19 +1159,19 @@
         <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BW2">
         <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BY2">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="BZ2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CA2">
         <v>8.4</v>
@@ -1209,10 +1209,10 @@
         <v>2.2</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L3">
         <v>1.16</v>
@@ -1221,7 +1221,7 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O3">
         <v>1.08</v>
@@ -1230,19 +1230,19 @@
         <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R3">
         <v>2.44</v>
       </c>
       <c r="S3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>3.7</v>
       </c>
       <c r="V3">
         <v>1.83</v>
@@ -1266,7 +1266,7 @@
         <v>38</v>
       </c>
       <c r="AC3">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AD3">
         <v>14.5</v>
@@ -1305,58 +1305,58 @@
         <v>5.9</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AT3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="AV3">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AX3">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AY3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AZ3">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BA3">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB3">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC3">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BD3">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BE3">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BF3">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>7</v>
@@ -1439,85 +1439,85 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="G4">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I4">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
         <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="X4">
         <v>8.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA4">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
@@ -1526,52 +1526,52 @@
         <v>24</v>
       </c>
       <c r="AI4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM4">
         <v>230</v>
       </c>
       <c r="AN4">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP4">
         <v>7.2</v>
       </c>
       <c r="AQ4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
         <v>6</v>
       </c>
       <c r="AV4">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1583,22 +1583,22 @@
         <v>50</v>
       </c>
       <c r="BB4">
+        <v>32</v>
+      </c>
+      <c r="BC4">
         <v>27</v>
       </c>
-      <c r="BC4">
-        <v>25</v>
-      </c>
       <c r="BD4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BG4">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH4">
         <v>2.76</v>
@@ -1610,25 +1610,25 @@
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BP4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1637,7 +1637,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BT4">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
         <v>5.1</v>
@@ -1646,13 +1646,13 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,88 +1681,88 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H5">
+        <v>2.96</v>
+      </c>
+      <c r="I5">
         <v>3.1</v>
-      </c>
-      <c r="I5">
-        <v>3.25</v>
       </c>
       <c r="J5">
         <v>3.15</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M5">
         <v>1.1</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O5">
         <v>1.44</v>
       </c>
       <c r="P5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U5">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="X5">
         <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA5">
         <v>75</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>23</v>
@@ -1771,10 +1771,10 @@
         <v>130</v>
       </c>
       <c r="AJ5">
+        <v>50</v>
+      </c>
+      <c r="AK5">
         <v>46</v>
-      </c>
-      <c r="AK5">
-        <v>38</v>
       </c>
       <c r="AL5">
         <v>75</v>
@@ -1783,22 +1783,22 @@
         <v>580</v>
       </c>
       <c r="AN5">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AP5">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AT5">
         <v>8</v>
@@ -1810,7 +1810,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AX5">
         <v>14</v>
@@ -1825,10 +1825,10 @@
         <v>40</v>
       </c>
       <c r="BB5">
+        <v>30</v>
+      </c>
+      <c r="BC5">
         <v>27</v>
-      </c>
-      <c r="BC5">
-        <v>23</v>
       </c>
       <c r="BD5">
         <v>40</v>
@@ -1837,13 +1837,13 @@
         <v>29</v>
       </c>
       <c r="BF5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BG5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI5">
         <v>2.6</v>
@@ -1858,28 +1858,28 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BU5">
         <v>4.6</v>
@@ -1894,13 +1894,13 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="s">
         <v>115</v>
@@ -1923,52 +1923,52 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G6">
         <v>1.83</v>
       </c>
       <c r="H6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M6">
         <v>1.1</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="P6">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
         <v>4.7</v>
       </c>
       <c r="T6">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U6">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="V6">
         <v>1.2</v>
@@ -1977,10 +1977,10 @@
         <v>2.2</v>
       </c>
       <c r="X6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z6">
         <v>42</v>
@@ -1989,10 +1989,10 @@
         <v>180</v>
       </c>
       <c r="AB6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
         <v>24</v>
@@ -2001,49 +2001,49 @@
         <v>110</v>
       </c>
       <c r="AF6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI6">
         <v>130</v>
       </c>
       <c r="AJ6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL6">
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN6">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO6">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS6">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AT6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
         <v>7.4</v>
@@ -2058,7 +2058,7 @@
         <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
         <v>23</v>
@@ -2067,10 +2067,10 @@
         <v>60</v>
       </c>
       <c r="BB6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD6">
         <v>44</v>
@@ -2079,7 +2079,7 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG6">
         <v>17</v>
@@ -2088,61 +2088,61 @@
         <v>3</v>
       </c>
       <c r="BI6">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR6">
         <v>36</v>
       </c>
       <c r="BS6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BV6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX6">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>115</v>
@@ -2165,13 +2165,13 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
         <v>2.16</v>
@@ -2180,7 +2180,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L7">
         <v>1.7</v>
@@ -2201,34 +2201,34 @@
         <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S7">
         <v>7.4</v>
       </c>
       <c r="T7">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="U7">
         <v>1.61</v>
       </c>
       <c r="V7">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="W7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>11</v>
       </c>
       <c r="AA7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AB7">
         <v>11</v>
@@ -2237,7 +2237,7 @@
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE7">
         <v>36</v>
@@ -2246,16 +2246,16 @@
         <v>34</v>
       </c>
       <c r="AG7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI7">
         <v>90</v>
       </c>
       <c r="AJ7">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK7">
         <v>110</v>
@@ -2264,22 +2264,22 @@
         <v>160</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AN7">
         <v>210</v>
       </c>
       <c r="AO7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP7">
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR7">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7">
         <v>24</v>
@@ -2294,10 +2294,10 @@
         <v>11.5</v>
       </c>
       <c r="AW7">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AY7">
         <v>20</v>
@@ -2327,7 +2327,7 @@
         <v>30</v>
       </c>
       <c r="BH7">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BI7">
         <v>2.3</v>
@@ -2342,25 +2342,25 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>2.16</v>
       </c>
       <c r="BN7">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BO7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP7">
         <v>60</v>
       </c>
       <c r="BQ7">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BR7">
         <v>90</v>
       </c>
       <c r="BS7">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
@@ -2369,22 +2369,22 @@
         <v>4</v>
       </c>
       <c r="BV7">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BW7">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BX7">
         <v>50</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="BZ7">
         <v>60</v>
       </c>
       <c r="CA7">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2407,37 +2407,37 @@
         <v>110</v>
       </c>
       <c r="F8">
+        <v>2.58</v>
+      </c>
+      <c r="G8">
         <v>2.62</v>
       </c>
-      <c r="G8">
-        <v>2.66</v>
-      </c>
       <c r="H8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J8">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M8">
         <v>1.17</v>
       </c>
       <c r="N8">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O8">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
         <v>3.15</v>
@@ -2446,31 +2446,31 @@
         <v>1.15</v>
       </c>
       <c r="S8">
+        <v>7.2</v>
+      </c>
+      <c r="T8">
+        <v>2.38</v>
+      </c>
+      <c r="U8">
+        <v>1.68</v>
+      </c>
+      <c r="V8">
+        <v>1.36</v>
+      </c>
+      <c r="W8">
+        <v>1.61</v>
+      </c>
+      <c r="X8">
         <v>6.8</v>
       </c>
-      <c r="T8">
-        <v>2.34</v>
-      </c>
-      <c r="U8">
-        <v>1.71</v>
-      </c>
-      <c r="V8">
-        <v>1.37</v>
-      </c>
-      <c r="W8">
-        <v>1.6</v>
-      </c>
-      <c r="X8">
-        <v>7</v>
-      </c>
       <c r="Y8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z8">
         <v>23</v>
       </c>
       <c r="AA8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB8">
         <v>7</v>
@@ -2479,10 +2479,10 @@
         <v>6.8</v>
       </c>
       <c r="AD8">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF8">
         <v>14.5</v>
@@ -2491,10 +2491,10 @@
         <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ8">
         <v>40</v>
@@ -2527,7 +2527,7 @@
         <v>70</v>
       </c>
       <c r="AT8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
@@ -2539,7 +2539,7 @@
         <v>50</v>
       </c>
       <c r="AX8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2548,16 +2548,16 @@
         <v>25</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="BB8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC8">
         <v>38</v>
       </c>
       <c r="BD8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE8">
         <v>110</v>
@@ -2566,19 +2566,19 @@
         <v>27</v>
       </c>
       <c r="BG8">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BH8">
         <v>2.46</v>
       </c>
       <c r="BI8">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BJ8">
         <v>12</v>
       </c>
       <c r="BK8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2590,7 +2590,7 @@
         <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
         <v>25</v>
@@ -2602,7 +2602,7 @@
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
@@ -2614,10 +2614,10 @@
         <v>38</v>
       </c>
       <c r="BW8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY8">
         <v>2.12</v>
@@ -2658,7 +2658,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
         <v>4.3</v>
@@ -2667,10 +2667,10 @@
         <v>4.4</v>
       </c>
       <c r="L9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9">
         <v>3.7</v>
@@ -2679,7 +2679,7 @@
         <v>1.36</v>
       </c>
       <c r="P9">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q9">
         <v>2.06</v>
@@ -2700,7 +2700,7 @@
         <v>1.13</v>
       </c>
       <c r="W9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X9">
         <v>14</v>
@@ -2715,7 +2715,7 @@
         <v>1000</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC9">
         <v>9.4</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="AG9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH9">
         <v>27</v>
@@ -2754,7 +2754,7 @@
         <v>9.4</v>
       </c>
       <c r="AO9">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AP9">
         <v>13</v>
@@ -2769,7 +2769,7 @@
         <v>95</v>
       </c>
       <c r="AT9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU9">
         <v>9</v>
@@ -2784,7 +2784,7 @@
         <v>7.8</v>
       </c>
       <c r="AY9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
         <v>25</v>
@@ -2793,13 +2793,13 @@
         <v>95</v>
       </c>
       <c r="BB9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC9">
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE9">
         <v>70</v>
@@ -2808,7 +2808,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG9">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="BH9">
         <v>3.3</v>
@@ -2832,7 +2832,7 @@
         <v>3.8</v>
       </c>
       <c r="BO9">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
         <v>9.800000000000001</v>
@@ -2891,55 +2891,55 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G10">
         <v>1.84</v>
       </c>
       <c r="H10">
+        <v>5.1</v>
+      </c>
+      <c r="I10">
         <v>5.2</v>
       </c>
-      <c r="I10">
-        <v>5.3</v>
-      </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M10">
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O10">
         <v>1.3</v>
       </c>
       <c r="P10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R10">
         <v>1.42</v>
       </c>
       <c r="S10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U10">
         <v>2.16</v>
       </c>
       <c r="V10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
         <v>2.18</v>
@@ -2948,7 +2948,7 @@
         <v>15</v>
       </c>
       <c r="Y10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Z10">
         <v>40</v>
@@ -2957,7 +2957,7 @@
         <v>120</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10">
         <v>8.4</v>
@@ -2993,7 +2993,7 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO10">
         <v>75</v>
@@ -3008,16 +3008,16 @@
         <v>36</v>
       </c>
       <c r="AS10">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AT10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU10">
         <v>8</v>
       </c>
       <c r="AV10">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AW10">
         <v>55</v>
@@ -3044,16 +3044,16 @@
         <v>30</v>
       </c>
       <c r="BE10">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BF10">
         <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BH10">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI10">
         <v>3.2</v>
@@ -3077,13 +3077,13 @@
         <v>3.95</v>
       </c>
       <c r="BP10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ10">
         <v>10.5</v>
       </c>
       <c r="BR10">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS10">
         <v>17</v>
@@ -3095,13 +3095,13 @@
         <v>7.2</v>
       </c>
       <c r="BV10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW10">
         <v>13</v>
       </c>
       <c r="BX10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BY10">
         <v>13.5</v>
@@ -3133,10 +3133,10 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
         <v>4.1</v>
@@ -3145,7 +3145,7 @@
         <v>4.3</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K11">
         <v>3.25</v>
@@ -3163,7 +3163,7 @@
         <v>1.52</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q11">
         <v>2.62</v>
@@ -3184,7 +3184,7 @@
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X11">
         <v>9.6</v>
@@ -3217,13 +3217,13 @@
         <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI11">
         <v>90</v>
       </c>
       <c r="AJ11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK11">
         <v>30</v>
@@ -3247,10 +3247,10 @@
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT11">
         <v>6.4</v>
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="AZ11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA11">
         <v>38</v>
@@ -3280,13 +3280,13 @@
         <v>22</v>
       </c>
       <c r="BC11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD11">
         <v>42</v>
       </c>
       <c r="BE11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF11">
         <v>24</v>
@@ -3375,16 +3375,16 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
         <v>4.3</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J12">
         <v>3.15</v>
@@ -3393,46 +3393,46 @@
         <v>3.2</v>
       </c>
       <c r="L12">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N12">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="P12">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="R12">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S12">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="T12">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U12">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X12">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z12">
         <v>32</v>
@@ -3441,16 +3441,16 @@
         <v>120</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC12">
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE12">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF12">
         <v>12</v>
@@ -3459,40 +3459,40 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AI12">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK12">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM12">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AN12">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO12">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP12">
         <v>7.6</v>
       </c>
       <c r="AQ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR12">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AS12">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT12">
         <v>6.2</v>
@@ -3504,7 +3504,7 @@
         <v>17.5</v>
       </c>
       <c r="AW12">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AX12">
         <v>10</v>
@@ -3513,10 +3513,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB12">
         <v>25</v>
@@ -3528,16 +3528,16 @@
         <v>50</v>
       </c>
       <c r="BE12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG12">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH12">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="BI12">
         <v>2.32</v>
@@ -3546,7 +3546,7 @@
         <v>12</v>
       </c>
       <c r="BK12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3561,22 +3561,22 @@
         <v>3.75</v>
       </c>
       <c r="BP12">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BQ12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR12">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT12">
         <v>7.8</v>
       </c>
       <c r="BU12">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV12">
         <v>1000</v>
@@ -3585,16 +3585,16 @@
         <v>10</v>
       </c>
       <c r="BX12">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY12">
+        <v>11</v>
+      </c>
+      <c r="BZ12">
+        <v>55</v>
+      </c>
+      <c r="CA12">
         <v>10.5</v>
-      </c>
-      <c r="BZ12">
-        <v>46</v>
-      </c>
-      <c r="CA12">
-        <v>9.800000000000001</v>
       </c>
       <c r="CB12" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-23.xlsx
@@ -361,7 +361,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-07-23 14:38:54</t>
+    <t>2026-07-23 16:51:23</t>
   </si>
 </sst>
 </file>
@@ -955,226 +955,226 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="H2">
+        <v>1.25</v>
+      </c>
+      <c r="I2">
+        <v>1.26</v>
+      </c>
+      <c r="J2">
+        <v>6.8</v>
+      </c>
+      <c r="K2">
+        <v>7.4</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.5</v>
+      </c>
+      <c r="O2">
+        <v>1.08</v>
+      </c>
+      <c r="P2">
+        <v>3.4</v>
+      </c>
+      <c r="Q2">
+        <v>1.39</v>
+      </c>
+      <c r="R2">
+        <v>1.81</v>
+      </c>
+      <c r="S2">
+        <v>2.16</v>
+      </c>
+      <c r="T2">
+        <v>1.69</v>
+      </c>
+      <c r="U2">
+        <v>2.28</v>
+      </c>
+      <c r="V2">
+        <v>4.5</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>13.5</v>
+      </c>
+      <c r="Z2">
+        <v>8.4</v>
+      </c>
+      <c r="AA2">
+        <v>10</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>14.5</v>
+      </c>
+      <c r="AD2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>11.5</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>38</v>
+      </c>
+      <c r="AH2">
+        <v>20</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>150</v>
+      </c>
+      <c r="AL2">
+        <v>95</v>
+      </c>
+      <c r="AM2">
+        <v>120</v>
+      </c>
+      <c r="AN2">
+        <v>140</v>
+      </c>
+      <c r="AO2">
+        <v>4.9</v>
+      </c>
+      <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
+        <v>11.5</v>
+      </c>
+      <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>8.6</v>
+      </c>
+      <c r="AT2">
+        <v>7.6</v>
+      </c>
+      <c r="AU2">
+        <v>12</v>
+      </c>
+      <c r="AV2">
+        <v>8</v>
+      </c>
+      <c r="AW2">
+        <v>10</v>
+      </c>
+      <c r="AX2">
+        <v>7.6</v>
+      </c>
+      <c r="AY2">
+        <v>29</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
+        <v>22</v>
+      </c>
+      <c r="BB2">
+        <v>7.6</v>
+      </c>
+      <c r="BC2">
+        <v>90</v>
+      </c>
+      <c r="BD2">
+        <v>60</v>
+      </c>
+      <c r="BE2">
+        <v>70</v>
+      </c>
+      <c r="BF2">
+        <v>75</v>
+      </c>
+      <c r="BG2">
+        <v>4.5</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>7.2</v>
+      </c>
+      <c r="BJ2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK2">
+        <v>7.4</v>
+      </c>
+      <c r="BL2">
+        <v>950</v>
+      </c>
+      <c r="BM2">
+        <v>11</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>7.2</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>7.2</v>
+      </c>
+      <c r="BR2">
+        <v>130</v>
+      </c>
+      <c r="BS2">
+        <v>13</v>
+      </c>
+      <c r="BT2">
+        <v>1.86</v>
+      </c>
+      <c r="BU2">
         <v>1.78</v>
       </c>
-      <c r="I2">
-        <v>1.82</v>
-      </c>
-      <c r="J2">
-        <v>4.4</v>
-      </c>
-      <c r="K2">
-        <v>4.7</v>
-      </c>
-      <c r="L2">
-        <v>1.26</v>
-      </c>
-      <c r="M2">
-        <v>1.02</v>
-      </c>
-      <c r="N2">
-        <v>6.8</v>
-      </c>
-      <c r="O2">
-        <v>1.15</v>
-      </c>
-      <c r="P2">
-        <v>2.94</v>
-      </c>
-      <c r="Q2">
-        <v>1.48</v>
-      </c>
-      <c r="R2">
-        <v>1.8</v>
-      </c>
-      <c r="S2">
-        <v>2.22</v>
-      </c>
-      <c r="T2">
-        <v>1.51</v>
-      </c>
-      <c r="U2">
-        <v>2.66</v>
-      </c>
-      <c r="V2">
-        <v>2.2</v>
-      </c>
-      <c r="W2">
-        <v>1.27</v>
-      </c>
-      <c r="X2">
-        <v>36</v>
-      </c>
-      <c r="Y2">
-        <v>15.5</v>
-      </c>
-      <c r="Z2">
-        <v>16</v>
-      </c>
-      <c r="AA2">
-        <v>20</v>
-      </c>
-      <c r="AB2">
-        <v>28</v>
-      </c>
-      <c r="AC2">
+      <c r="BV2">
+        <v>4.9</v>
+      </c>
+      <c r="BW2">
+        <v>4.2</v>
+      </c>
+      <c r="BX2">
+        <v>32</v>
+      </c>
+      <c r="BY2">
         <v>12</v>
       </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
-      <c r="AE2">
+      <c r="BZ2">
+        <v>860</v>
+      </c>
+      <c r="CA2">
         <v>16.5</v>
-      </c>
-      <c r="AF2">
-        <v>130</v>
-      </c>
-      <c r="AG2">
-        <v>20</v>
-      </c>
-      <c r="AH2">
-        <v>16.5</v>
-      </c>
-      <c r="AI2">
-        <v>24</v>
-      </c>
-      <c r="AJ2">
-        <v>700</v>
-      </c>
-      <c r="AK2">
-        <v>55</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>55</v>
-      </c>
-      <c r="AN2">
-        <v>34</v>
-      </c>
-      <c r="AO2">
-        <v>6.6</v>
-      </c>
-      <c r="AP2">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>12.5</v>
-      </c>
-      <c r="AS2">
-        <v>17</v>
-      </c>
-      <c r="AT2">
-        <v>20</v>
-      </c>
-      <c r="AU2">
-        <v>9.6</v>
-      </c>
-      <c r="AV2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW2">
-        <v>14</v>
-      </c>
-      <c r="AX2">
-        <v>34</v>
-      </c>
-      <c r="AY2">
-        <v>17</v>
-      </c>
-      <c r="AZ2">
-        <v>13.5</v>
-      </c>
-      <c r="BA2">
-        <v>20</v>
-      </c>
-      <c r="BB2">
-        <v>13.5</v>
-      </c>
-      <c r="BC2">
-        <v>36</v>
-      </c>
-      <c r="BD2">
-        <v>23</v>
-      </c>
-      <c r="BE2">
-        <v>12.5</v>
-      </c>
-      <c r="BF2">
-        <v>22</v>
-      </c>
-      <c r="BG2">
-        <v>5.8</v>
-      </c>
-      <c r="BH2">
-        <v>1000</v>
-      </c>
-      <c r="BI2">
-        <v>3.85</v>
-      </c>
-      <c r="BJ2">
-        <v>9</v>
-      </c>
-      <c r="BK2">
-        <v>2.56</v>
-      </c>
-      <c r="BL2">
-        <v>75</v>
-      </c>
-      <c r="BM2">
-        <v>3.4</v>
-      </c>
-      <c r="BN2">
-        <v>8.4</v>
-      </c>
-      <c r="BO2">
-        <v>2.5</v>
-      </c>
-      <c r="BP2">
-        <v>32</v>
-      </c>
-      <c r="BQ2">
-        <v>3.2</v>
-      </c>
-      <c r="BR2">
-        <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>3.2</v>
-      </c>
-      <c r="BT2">
-        <v>5.2</v>
-      </c>
-      <c r="BU2">
-        <v>4.5</v>
-      </c>
-      <c r="BV2">
-        <v>11.5</v>
-      </c>
-      <c r="BW2">
-        <v>8.4</v>
-      </c>
-      <c r="BX2">
-        <v>19.5</v>
-      </c>
-      <c r="BY2">
-        <v>3</v>
-      </c>
-      <c r="BZ2">
-        <v>12</v>
-      </c>
-      <c r="CA2">
-        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>115</v>
@@ -1197,226 +1197,226 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="G3">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="I3">
-        <v>2.2</v>
+        <v>870</v>
       </c>
       <c r="J3">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="K3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L3">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>11.5</v>
+        <v>1.02</v>
       </c>
       <c r="O3">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="P3">
-        <v>4.4</v>
+        <v>1.06</v>
       </c>
       <c r="Q3">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="R3">
-        <v>2.44</v>
+        <v>1.06</v>
       </c>
       <c r="S3">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="T3">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>115</v>
@@ -1439,70 +1439,70 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J4">
         <v>2.94</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V4">
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB4">
         <v>8.199999999999999</v>
@@ -1511,64 +1511,64 @@
         <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG4">
         <v>13.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AJ4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AL4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AM4">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN4">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AO4">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4">
         <v>18</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU4">
         <v>6</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4">
         <v>13</v>
@@ -1577,82 +1577,82 @@
         <v>10.5</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB4">
         <v>32</v>
       </c>
       <c r="BC4">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BE4">
+        <v>10</v>
+      </c>
+      <c r="BF4">
+        <v>25</v>
+      </c>
+      <c r="BG4">
         <v>9</v>
       </c>
-      <c r="BF4">
-        <v>34</v>
-      </c>
-      <c r="BG4">
-        <v>46</v>
-      </c>
       <c r="BH4">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BI4">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>2.7</v>
       </c>
       <c r="G5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H5">
         <v>2.96</v>
@@ -1693,13 +1693,13 @@
         <v>3.1</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M5">
         <v>1.1</v>
@@ -1714,19 +1714,19 @@
         <v>1.71</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R5">
         <v>1.26</v>
       </c>
       <c r="S5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T5">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V5">
         <v>1.48</v>
@@ -1741,22 +1741,22 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA5">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>17.5</v>
@@ -1765,94 +1765,94 @@
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI5">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK5">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN5">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AP5">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
         <v>12.5</v>
       </c>
       <c r="AW5">
+        <v>34</v>
+      </c>
+      <c r="AX5">
+        <v>15</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>17.5</v>
+      </c>
+      <c r="BA5">
+        <v>44</v>
+      </c>
+      <c r="BB5">
+        <v>38</v>
+      </c>
+      <c r="BC5">
         <v>30</v>
       </c>
-      <c r="AX5">
-        <v>14</v>
-      </c>
-      <c r="AY5">
-        <v>11</v>
-      </c>
-      <c r="AZ5">
-        <v>17</v>
-      </c>
-      <c r="BA5">
-        <v>40</v>
-      </c>
-      <c r="BB5">
+      <c r="BD5">
+        <v>44</v>
+      </c>
+      <c r="BE5">
+        <v>90</v>
+      </c>
+      <c r="BF5">
         <v>30</v>
       </c>
-      <c r="BC5">
-        <v>27</v>
-      </c>
-      <c r="BD5">
-        <v>40</v>
-      </c>
-      <c r="BE5">
-        <v>29</v>
-      </c>
-      <c r="BF5">
-        <v>27</v>
-      </c>
       <c r="BG5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BH5">
         <v>3.05</v>
       </c>
       <c r="BI5">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1882,7 +1882,7 @@
         <v>5.8</v>
       </c>
       <c r="BU5">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
@@ -1923,31 +1923,31 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H6">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J6">
         <v>3.6</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
         <v>1.45</v>
@@ -1959,7 +1959,7 @@
         <v>2.36</v>
       </c>
       <c r="R6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S6">
         <v>4.7</v>
@@ -1971,16 +1971,16 @@
         <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X6">
         <v>11</v>
       </c>
       <c r="Y6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>42</v>
@@ -2010,19 +2010,19 @@
         <v>26</v>
       </c>
       <c r="AI6">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AJ6">
         <v>19.5</v>
       </c>
       <c r="AK6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL6">
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AN6">
         <v>16.5</v>
@@ -2031,7 +2031,7 @@
         <v>160</v>
       </c>
       <c r="AP6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6">
         <v>14</v>
@@ -2046,7 +2046,7 @@
         <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
         <v>20</v>
@@ -2058,7 +2058,7 @@
         <v>8.4</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
         <v>23</v>
@@ -2076,19 +2076,19 @@
         <v>44</v>
       </c>
       <c r="BE6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2103,10 +2103,10 @@
         <v>14</v>
       </c>
       <c r="BN6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO6">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BP6">
         <v>13.5</v>
@@ -2171,49 +2171,49 @@
         <v>4.9</v>
       </c>
       <c r="H7">
+        <v>2.12</v>
+      </c>
+      <c r="I7">
         <v>2.14</v>
       </c>
-      <c r="I7">
-        <v>2.16</v>
-      </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
+        <v>1.69</v>
+      </c>
+      <c r="M7">
+        <v>1.16</v>
+      </c>
+      <c r="N7">
+        <v>2.4</v>
+      </c>
+      <c r="O7">
         <v>1.7</v>
       </c>
-      <c r="M7">
-        <v>1.17</v>
-      </c>
-      <c r="N7">
-        <v>2.36</v>
-      </c>
-      <c r="O7">
-        <v>1.71</v>
-      </c>
       <c r="P7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
       </c>
       <c r="R7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="T7">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="U7">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W7">
         <v>1.25</v>
@@ -2222,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z7">
         <v>11</v>
@@ -2237,19 +2237,19 @@
         <v>7.4</v>
       </c>
       <c r="AD7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE7">
         <v>36</v>
       </c>
       <c r="AF7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG7">
         <v>22</v>
       </c>
       <c r="AH7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI7">
         <v>90</v>
@@ -2258,28 +2258,28 @@
         <v>140</v>
       </c>
       <c r="AK7">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM7">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AN7">
         <v>210</v>
       </c>
       <c r="AO7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP7">
         <v>6.4</v>
       </c>
       <c r="AQ7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS7">
         <v>24</v>
@@ -2288,7 +2288,7 @@
         <v>10</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
         <v>11.5</v>
@@ -2297,40 +2297,40 @@
         <v>30</v>
       </c>
       <c r="AX7">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY7">
         <v>20</v>
       </c>
       <c r="AZ7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA7">
         <v>60</v>
       </c>
       <c r="BB7">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BC7">
         <v>75</v>
       </c>
       <c r="BD7">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BE7">
         <v>110</v>
       </c>
       <c r="BF7">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BG7">
         <v>30</v>
       </c>
       <c r="BH7">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BI7">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
         <v>13</v>
@@ -2342,7 +2342,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.16</v>
+        <v>32</v>
       </c>
       <c r="BN7">
         <v>8</v>
@@ -2351,16 +2351,16 @@
         <v>5.8</v>
       </c>
       <c r="BP7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BQ7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BS7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BT7">
         <v>4.5</v>
@@ -2369,22 +2369,22 @@
         <v>4</v>
       </c>
       <c r="BV7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX7">
         <v>50</v>
       </c>
       <c r="BY7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ7">
         <v>60</v>
       </c>
       <c r="CA7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2407,22 +2407,22 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G8">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="K8">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="L8">
         <v>1.69</v>
@@ -2431,10 +2431,10 @@
         <v>1.17</v>
       </c>
       <c r="N8">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O8">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P8">
         <v>1.44</v>
@@ -2449,19 +2449,19 @@
         <v>7.2</v>
       </c>
       <c r="T8">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -2470,13 +2470,13 @@
         <v>23</v>
       </c>
       <c r="AA8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB8">
         <v>7</v>
       </c>
       <c r="AC8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2491,7 +2491,7 @@
         <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8">
         <v>110</v>
@@ -2509,7 +2509,7 @@
         <v>260</v>
       </c>
       <c r="AN8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO8">
         <v>110</v>
@@ -2521,7 +2521,7 @@
         <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS8">
         <v>70</v>
@@ -2539,7 +2539,7 @@
         <v>50</v>
       </c>
       <c r="AX8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY8">
         <v>12.5</v>
@@ -2548,31 +2548,31 @@
         <v>25</v>
       </c>
       <c r="BA8">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BB8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC8">
         <v>38</v>
       </c>
       <c r="BD8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE8">
         <v>110</v>
       </c>
       <c r="BF8">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BG8">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="BH8">
         <v>2.46</v>
       </c>
       <c r="BI8">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BJ8">
         <v>12</v>
@@ -2590,7 +2590,7 @@
         <v>5.2</v>
       </c>
       <c r="BO8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
         <v>25</v>
@@ -2608,7 +2608,7 @@
         <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
         <v>38</v>
@@ -2652,40 +2652,40 @@
         <v>1.54</v>
       </c>
       <c r="G9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H9">
+        <v>7.6</v>
+      </c>
+      <c r="I9">
         <v>8</v>
-      </c>
-      <c r="I9">
-        <v>8.4</v>
       </c>
       <c r="J9">
         <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>1.45</v>
       </c>
       <c r="M9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P9">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q9">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
         <v>3.75</v>
@@ -2697,16 +2697,16 @@
         <v>1.82</v>
       </c>
       <c r="V9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W9">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X9">
         <v>14</v>
       </c>
       <c r="Y9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z9">
         <v>70</v>
@@ -2721,7 +2721,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE9">
         <v>140</v>
@@ -2730,7 +2730,7 @@
         <v>8</v>
       </c>
       <c r="AG9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH9">
         <v>27</v>
@@ -2742,7 +2742,7 @@
         <v>13.5</v>
       </c>
       <c r="AK9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL9">
         <v>44</v>
@@ -2751,16 +2751,16 @@
         <v>180</v>
       </c>
       <c r="AN9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO9">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP9">
         <v>13</v>
       </c>
       <c r="AQ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR9">
         <v>55</v>
@@ -2769,7 +2769,7 @@
         <v>95</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU9">
         <v>9</v>
@@ -2778,7 +2778,7 @@
         <v>26</v>
       </c>
       <c r="AW9">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AX9">
         <v>7.8</v>
@@ -2790,10 +2790,10 @@
         <v>25</v>
       </c>
       <c r="BA9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC9">
         <v>16</v>
@@ -2802,16 +2802,16 @@
         <v>40</v>
       </c>
       <c r="BE9">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="BF9">
         <v>8.800000000000001</v>
       </c>
       <c r="BG9">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="BH9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI9">
         <v>3.15</v>
@@ -2820,13 +2820,13 @@
         <v>11.5</v>
       </c>
       <c r="BK9">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BN9">
         <v>3.8</v>
@@ -2838,37 +2838,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR9">
         <v>28</v>
       </c>
       <c r="BS9">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT9">
         <v>11</v>
       </c>
       <c r="BU9">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BV9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BW9">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BX9">
         <v>80</v>
       </c>
       <c r="BY9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BZ9">
         <v>20</v>
       </c>
       <c r="CA9">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,22 +2891,22 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
         <v>5.1</v>
       </c>
-      <c r="I10">
-        <v>5.2</v>
-      </c>
       <c r="J10">
+        <v>3.8</v>
+      </c>
+      <c r="K10">
         <v>3.85</v>
-      </c>
-      <c r="K10">
-        <v>3.9</v>
       </c>
       <c r="L10">
         <v>1.38</v>
@@ -2933,19 +2933,19 @@
         <v>3.25</v>
       </c>
       <c r="T10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
         <v>1.24</v>
       </c>
       <c r="W10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y10">
         <v>19</v>
@@ -2963,7 +2963,7 @@
         <v>8.4</v>
       </c>
       <c r="AD10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE10">
         <v>65</v>
@@ -2975,7 +2975,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10">
         <v>65</v>
@@ -2993,31 +2993,31 @@
         <v>95</v>
       </c>
       <c r="AN10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO10">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP10">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AS10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
         <v>8</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW10">
         <v>55</v>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
       <c r="BB10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC10">
         <v>17</v>
@@ -3044,10 +3044,10 @@
         <v>30</v>
       </c>
       <c r="BE10">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="BF10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG10">
         <v>60</v>
@@ -3056,7 +3056,7 @@
         <v>3.65</v>
       </c>
       <c r="BI10">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BJ10">
         <v>9.800000000000001</v>
@@ -3068,19 +3068,19 @@
         <v>120</v>
       </c>
       <c r="BM10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BN10">
         <v>4.4</v>
       </c>
       <c r="BO10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP10">
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR10">
         <v>25</v>
@@ -3092,7 +3092,7 @@
         <v>8.4</v>
       </c>
       <c r="BU10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV10">
         <v>40</v>
@@ -3104,10 +3104,10 @@
         <v>46</v>
       </c>
       <c r="BY10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA10">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>2.2</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H11">
         <v>4.1</v>
@@ -3145,10 +3145,10 @@
         <v>4.3</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L11">
         <v>1.56</v>
@@ -3157,19 +3157,19 @@
         <v>1.12</v>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O11">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P11">
         <v>1.58</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
         <v>5.4</v>
@@ -3184,7 +3184,7 @@
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X11">
         <v>9.6</v>
@@ -3247,10 +3247,10 @@
         <v>10.5</v>
       </c>
       <c r="AR11">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS11">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="AT11">
         <v>6.4</v>
@@ -3274,7 +3274,7 @@
         <v>20</v>
       </c>
       <c r="BA11">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BB11">
         <v>22</v>
@@ -3286,13 +3286,13 @@
         <v>42</v>
       </c>
       <c r="BE11">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BF11">
         <v>24</v>
       </c>
       <c r="BG11">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="BH11">
         <v>2.86</v>
@@ -3304,19 +3304,19 @@
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BN11">
         <v>4.8</v>
       </c>
       <c r="BO11">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP11">
         <v>18</v>
@@ -3375,13 +3375,13 @@
         <v>114</v>
       </c>
       <c r="F12">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H12">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12">
         <v>4.4</v>
@@ -3393,7 +3393,7 @@
         <v>3.2</v>
       </c>
       <c r="L12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M12">
         <v>1.14</v>
@@ -3402,34 +3402,34 @@
         <v>2.52</v>
       </c>
       <c r="O12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P12">
         <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
         <v>6.2</v>
       </c>
       <c r="T12">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V12">
         <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y12">
         <v>11</v>
@@ -3447,10 +3447,10 @@
         <v>7.4</v>
       </c>
       <c r="AD12">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE12">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF12">
         <v>12</v>
@@ -3459,7 +3459,7 @@
         <v>12</v>
       </c>
       <c r="AH12">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI12">
         <v>120</v>
@@ -3471,7 +3471,7 @@
         <v>34</v>
       </c>
       <c r="AL12">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="AM12">
         <v>260</v>
@@ -3480,22 +3480,22 @@
         <v>36</v>
       </c>
       <c r="AO12">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP12">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR12">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT12">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU12">
         <v>6.8</v>
@@ -3516,10 +3516,10 @@
         <v>24</v>
       </c>
       <c r="BA12">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BB12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC12">
         <v>26</v>
@@ -3528,13 +3528,13 @@
         <v>50</v>
       </c>
       <c r="BE12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF12">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BG12">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="BH12">
         <v>2.66</v>
@@ -3558,7 +3558,7 @@
         <v>4.8</v>
       </c>
       <c r="BO12">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BP12">
         <v>20</v>
